--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922878AC-AF15-4AED-B4B2-34578709AEE7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887E7133-46D1-7842-8B24-A1314F3B5C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12540" yWindow="780" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -99,22 +99,22 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -128,7 +128,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -136,7 +136,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -145,7 +145,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -159,7 +159,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -196,7 +196,7 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -212,26 +212,26 @@
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -509,25 +509,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M751"/>
-  <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M752"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="11" customWidth="1"/>
-    <col min="4" max="4" width="10.875" style="10" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="10" customWidth="1"/>
     <col min="5" max="5" width="13.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="20.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="7.625" style="6"/>
+    <col min="14" max="16384" width="7.6640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="2" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -568,7 +568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="A2" s="10">
         <v>40716</v>
       </c>
@@ -609,7 +609,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13">
       <c r="A3" s="10">
         <v>40723</v>
       </c>
@@ -650,7 +650,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13">
       <c r="A4" s="10">
         <v>40730</v>
       </c>
@@ -691,7 +691,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13">
       <c r="A5" s="10">
         <v>40737</v>
       </c>
@@ -732,7 +732,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="A6" s="10">
         <v>40744</v>
       </c>
@@ -773,7 +773,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13">
       <c r="A7" s="10">
         <v>40751</v>
       </c>
@@ -814,7 +814,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="A8" s="10">
         <v>40758</v>
       </c>
@@ -855,7 +855,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13">
       <c r="A9" s="10">
         <v>40765</v>
       </c>
@@ -896,7 +896,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13">
       <c r="A10" s="10">
         <v>40772</v>
       </c>
@@ -937,7 +937,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13">
       <c r="A11" s="10">
         <v>40779</v>
       </c>
@@ -978,7 +978,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13">
       <c r="A12" s="10">
         <v>40786</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13">
       <c r="A13" s="10">
         <v>40793</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13">
       <c r="A14" s="10">
         <v>40800</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13">
       <c r="A15" s="10">
         <v>40807</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13">
       <c r="A16" s="10">
         <v>40814</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="10">
         <v>40821</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="10">
         <v>40828</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="10">
         <v>40835</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="10">
         <v>40842</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="10">
         <v>40849</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="10">
         <v>40856</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="10">
         <v>40863</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="10">
         <v>40870</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="10">
         <v>40877</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="10">
         <v>40884</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="10">
         <v>40891</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="10">
         <v>40898</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="10">
         <v>40905</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="10">
         <v>40912</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="10">
         <v>40919</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13">
       <c r="A32" s="10">
         <v>40926</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13">
       <c r="A33" s="10">
         <v>40933</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13">
       <c r="A34" s="10">
         <v>40940</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13">
       <c r="A35" s="10">
         <v>40947</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13">
       <c r="A36" s="10">
         <v>40954</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13">
       <c r="A37" s="10">
         <v>40961</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13">
       <c r="A38" s="10">
         <v>40968</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13">
       <c r="A39" s="10">
         <v>40975</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13">
       <c r="A40" s="10">
         <v>40982</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13">
       <c r="A41" s="10">
         <v>40989</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13">
       <c r="A42" s="10">
         <v>40996</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13">
       <c r="A43" s="10">
         <v>41003</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13">
       <c r="A44" s="10">
         <v>41010</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13">
       <c r="A45" s="10">
         <v>41017</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13">
       <c r="A46" s="10">
         <v>41024</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13">
       <c r="A47" s="10">
         <v>41031</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13">
       <c r="A48" s="10">
         <v>41038</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13">
       <c r="A49" s="10">
         <v>41045</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13">
       <c r="A50" s="10">
         <v>41052</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13">
       <c r="A51" s="10">
         <v>41059</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13">
       <c r="A52" s="10">
         <v>41066</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13">
       <c r="A53" s="10">
         <v>41073</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13">
       <c r="A54" s="10">
         <v>41080</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13">
       <c r="A55" s="10">
         <v>41087</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13">
       <c r="A56" s="10">
         <v>41094</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13">
       <c r="A57" s="10">
         <v>41101</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13">
       <c r="A58" s="10">
         <v>41108</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13">
       <c r="A59" s="10">
         <v>41115</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13">
       <c r="A60" s="10">
         <v>41122</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13">
       <c r="A61" s="10">
         <v>41129</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13">
       <c r="A62" s="10">
         <v>41136</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13">
       <c r="A63" s="10">
         <v>41143</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13">
       <c r="A64" s="10">
         <v>41150</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13">
       <c r="A65" s="10">
         <v>41157</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13">
       <c r="A66" s="10">
         <v>41164</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13">
       <c r="A67" s="10">
         <v>41171</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13">
       <c r="A68" s="10">
         <v>41178</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13">
       <c r="A69" s="10">
         <v>41185</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13">
       <c r="A70" s="10">
         <v>41192</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13">
       <c r="A71" s="10">
         <v>41199</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13">
       <c r="A72" s="10">
         <v>41206</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13">
       <c r="A73" s="10">
         <v>41213</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13">
       <c r="A74" s="10">
         <v>41220</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13">
       <c r="A75" s="10">
         <v>41227</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13">
       <c r="A76" s="10">
         <v>41234</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13">
       <c r="A77" s="10">
         <v>41241</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13">
       <c r="A78" s="10">
         <v>41248</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13">
       <c r="A79" s="10">
         <v>41255</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13">
       <c r="A80" s="10">
         <v>41262</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13">
       <c r="A81" s="10">
         <v>41269</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13">
       <c r="A82" s="10">
         <v>41276</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13">
       <c r="A83" s="10">
         <v>41283</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13">
       <c r="A84" s="10">
         <v>41290</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13">
       <c r="A85" s="10">
         <v>41297</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13">
       <c r="A86" s="10">
         <v>41304</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13">
       <c r="A87" s="10">
         <v>41311</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13">
       <c r="A88" s="10">
         <v>41318</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13">
       <c r="A89" s="10">
         <v>41325</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13">
       <c r="A90" s="10">
         <v>41332</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13">
       <c r="A91" s="10">
         <v>41339</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13">
       <c r="A92" s="10">
         <v>41346</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13">
       <c r="A93" s="10">
         <v>41353</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13">
       <c r="A94" s="10">
         <v>41360</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13">
       <c r="A95" s="10">
         <v>41367</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13">
       <c r="A96" s="10">
         <v>41374</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13">
       <c r="A97" s="10">
         <v>41381</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13">
       <c r="A98" s="10">
         <v>41388</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13">
       <c r="A99" s="10">
         <v>41395</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13">
       <c r="A100" s="10">
         <v>41402</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13">
       <c r="A101" s="10">
         <v>41409</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13">
       <c r="A102" s="10">
         <v>41416</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13">
       <c r="A103" s="10">
         <v>41423</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13">
       <c r="A104" s="10">
         <v>41430</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13">
       <c r="A105" s="10">
         <v>41437</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13">
       <c r="A106" s="10">
         <v>41444</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13">
       <c r="A107" s="10">
         <v>41451</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13">
       <c r="A108" s="10">
         <v>41458</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13">
       <c r="A109" s="10">
         <v>41465</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13">
       <c r="A110" s="10">
         <v>41472</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13">
       <c r="A111" s="10">
         <v>41479</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13">
       <c r="A112" s="10">
         <v>41486</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13">
       <c r="A113" s="10">
         <v>41493</v>
       </c>
@@ -5160,7 +5160,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13">
       <c r="A114" s="10">
         <v>41500</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13">
       <c r="A115" s="10">
         <v>41507</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13">
       <c r="A116" s="10">
         <v>41514</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13">
       <c r="A117" s="10">
         <v>41521</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13">
       <c r="A118" s="10">
         <v>41528</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13">
       <c r="A119" s="10">
         <v>41535</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13">
       <c r="A120" s="10">
         <v>41542</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13">
       <c r="A121" s="10">
         <v>41549</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13">
       <c r="A122" s="10">
         <v>41556</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13">
       <c r="A123" s="10">
         <v>41563</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13">
       <c r="A124" s="10">
         <v>41570</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13">
       <c r="A125" s="10">
         <v>41577</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13">
       <c r="A126" s="10">
         <v>41584</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13">
       <c r="A127" s="10">
         <v>41591</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13">
       <c r="A128" s="10">
         <v>41598</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13">
       <c r="A129" s="10">
         <v>41605</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13">
       <c r="A130" s="10">
         <v>41612</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13">
       <c r="A131" s="10">
         <v>41619</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13">
       <c r="A132" s="10">
         <v>41626</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13">
       <c r="A133" s="10">
         <v>41640</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13">
       <c r="A134" s="10">
         <v>41647</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13">
       <c r="A135" s="10">
         <v>41654</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13">
       <c r="A136" s="10">
         <v>41661</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13">
       <c r="A137" s="10">
         <v>41668</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13">
       <c r="A138" s="10">
         <v>41675</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13">
       <c r="A139" s="10">
         <v>41682</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13">
       <c r="A140" s="10">
         <v>41689</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13">
       <c r="A141" s="10">
         <v>41696</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13">
       <c r="A142" s="10">
         <v>41703</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13">
       <c r="A143" s="10">
         <v>41710</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13">
       <c r="A144" s="10">
         <v>41717</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13">
       <c r="A145" s="10">
         <v>41724</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13">
       <c r="A146" s="10">
         <v>41731</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13">
       <c r="A147" s="10">
         <v>41738</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13">
       <c r="A148" s="10">
         <v>41745</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13">
       <c r="A149" s="10">
         <v>41752</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13">
       <c r="A150" s="10">
         <v>41759</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13">
       <c r="A151" s="10">
         <v>41766</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13">
       <c r="A152" s="10">
         <v>41773</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13">
       <c r="A153" s="10">
         <v>41780</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13">
       <c r="A154" s="10">
         <v>41787</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13">
       <c r="A155" s="10">
         <v>41794</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13">
       <c r="A156" s="10">
         <v>41801</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13">
       <c r="A157" s="10">
         <v>41808</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13">
       <c r="A158" s="10">
         <v>41815</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13">
       <c r="A159" s="10">
         <v>41822</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13">
       <c r="A160" s="10">
         <v>41829</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13">
       <c r="A161" s="10">
         <v>41836</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13">
       <c r="A162" s="10">
         <v>41843</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13">
       <c r="A163" s="10">
         <v>41850</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13">
       <c r="A164" s="10">
         <v>41857</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13">
       <c r="A165" s="10">
         <v>41864</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13">
       <c r="A166" s="10">
         <v>41871</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13">
       <c r="A167" s="10">
         <v>41878</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13">
       <c r="A168" s="10">
         <v>41885</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13">
       <c r="A169" s="10">
         <v>41892</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13">
       <c r="A170" s="10">
         <v>41899</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13">
       <c r="A171" s="10">
         <v>41906</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13">
       <c r="A172" s="10">
         <v>41913</v>
       </c>
@@ -7579,7 +7579,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13">
       <c r="A173" s="10">
         <v>41920</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13">
       <c r="A174" s="10">
         <v>41927</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13">
       <c r="A175" s="10">
         <v>41934</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13">
       <c r="A176" s="10">
         <v>41941</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13">
       <c r="A177" s="10">
         <v>41948</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13">
       <c r="A178" s="10">
         <v>41955</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13">
       <c r="A179" s="10">
         <v>41962</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13">
       <c r="A180" s="10">
         <v>41969</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13">
       <c r="A181" s="10">
         <v>41976</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13">
       <c r="A182" s="10">
         <v>41983</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13">
       <c r="A183" s="10">
         <v>41990</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13">
       <c r="A184" s="10">
         <v>42011</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13">
       <c r="A185" s="10">
         <v>42018</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13">
       <c r="A186" s="10">
         <v>42025</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13">
       <c r="A187" s="10">
         <v>42032</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13">
       <c r="A188" s="10">
         <v>42039</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13">
       <c r="A189" s="10">
         <v>42046</v>
       </c>
@@ -8276,7 +8276,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13">
       <c r="A190" s="10">
         <v>42053</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13">
       <c r="A191" s="10">
         <v>42060</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13">
       <c r="A192" s="10">
         <v>42067</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13">
       <c r="A193" s="10">
         <v>42074</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13">
       <c r="A194" s="10">
         <v>42081</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13">
       <c r="A195" s="10">
         <v>42088</v>
       </c>
@@ -8522,7 +8522,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13">
       <c r="A196" s="10">
         <v>42095</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13">
       <c r="A197" s="10">
         <v>42102</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13">
       <c r="A198" s="10">
         <v>42109</v>
       </c>
@@ -8645,7 +8645,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13">
       <c r="A199" s="10">
         <v>42116</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13">
       <c r="A200" s="10">
         <v>42123</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13">
       <c r="A201" s="10">
         <v>42130</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13">
       <c r="A202" s="10">
         <v>42137</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13">
       <c r="A203" s="10">
         <v>42144</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13">
       <c r="A204" s="10">
         <v>42151</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13">
       <c r="A205" s="10">
         <v>42158</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13">
       <c r="A206" s="10">
         <v>42165</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13">
       <c r="A207" s="10">
         <v>42172</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13">
       <c r="A208" s="10">
         <v>42179</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13">
       <c r="A209" s="10">
         <v>42186</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13">
       <c r="A210" s="10">
         <v>42193</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13">
       <c r="A211" s="10">
         <v>42200</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13">
       <c r="A212" s="10">
         <v>42207</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13">
       <c r="A213" s="10">
         <v>42214</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13">
       <c r="A214" s="10">
         <v>42221</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13">
       <c r="A215" s="10">
         <v>42228</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13">
       <c r="A216" s="10">
         <v>42235</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13">
       <c r="A217" s="10">
         <v>42242</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13">
       <c r="A218" s="10">
         <v>42249</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13">
       <c r="A219" s="10">
         <v>42256</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13">
       <c r="A220" s="10">
         <v>42263</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13">
       <c r="A221" s="10">
         <v>42270</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13">
       <c r="A222" s="10">
         <v>42277</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13">
       <c r="A223" s="10">
         <v>42284</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13">
       <c r="A224" s="10">
         <v>42291</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:13">
       <c r="A225" s="10">
         <v>42298</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:13">
       <c r="A226" s="10">
         <v>42305</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:13">
       <c r="A227" s="10">
         <v>42312</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:13">
       <c r="A228" s="10">
         <v>42319</v>
       </c>
@@ -9875,7 +9875,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:13">
       <c r="A229" s="10">
         <v>42326</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:13">
       <c r="A230" s="10">
         <v>42333</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:13">
       <c r="A231" s="10">
         <v>42340</v>
       </c>
@@ -9998,7 +9998,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:13">
       <c r="A232" s="10">
         <v>42347</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:13">
       <c r="A233" s="10">
         <v>42354</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:13">
       <c r="A234" s="10">
         <v>42361</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:13">
       <c r="A235" s="10">
         <v>42368</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:13">
       <c r="A236" s="10">
         <v>42375</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:13">
       <c r="A237" s="10">
         <v>42382</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:13">
       <c r="A238" s="10">
         <v>42389</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:13">
       <c r="A239" s="10">
         <v>42396</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:13">
       <c r="A240" s="10">
         <v>42403</v>
       </c>
@@ -10367,7 +10367,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:13">
       <c r="A241" s="10">
         <v>42410</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:13">
       <c r="A242" s="10">
         <v>42417</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:13">
       <c r="A243" s="10">
         <v>42424</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:13">
       <c r="A244" s="10">
         <v>42431</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:13">
       <c r="A245" s="10">
         <v>42438</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:13">
       <c r="A246" s="10">
         <v>42445</v>
       </c>
@@ -10613,7 +10613,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:13">
       <c r="A247" s="10">
         <v>42452</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:13">
       <c r="A248" s="10">
         <v>42459</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:13">
       <c r="A249" s="10">
         <v>42466</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:13">
       <c r="A250" s="10">
         <v>42473</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:13">
       <c r="A251" s="10">
         <v>42480</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:13">
       <c r="A252" s="10">
         <v>42487</v>
       </c>
@@ -10859,7 +10859,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:13">
       <c r="A253" s="10">
         <v>42494</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:13">
       <c r="A254" s="10">
         <v>42501</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:13">
       <c r="A255" s="10">
         <v>42508</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:13">
       <c r="A256" s="10">
         <v>42515</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:13">
       <c r="A257" s="10">
         <v>42522</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:13">
       <c r="A258" s="10">
         <v>42529</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:13">
       <c r="A259" s="10">
         <v>42536</v>
       </c>
@@ -11146,7 +11146,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13">
       <c r="A260" s="10">
         <v>42543</v>
       </c>
@@ -11187,7 +11187,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:13">
       <c r="A261" s="10">
         <v>42550</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13">
       <c r="A262" s="10">
         <v>42557</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:13">
       <c r="A263" s="10">
         <v>42564</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13">
       <c r="A264" s="10">
         <v>42571</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13">
       <c r="A265" s="10">
         <v>42578</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13">
       <c r="A266" s="10">
         <v>42585</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:13">
       <c r="A267" s="10">
         <v>42592</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:13">
       <c r="A268" s="10">
         <v>42599</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:13">
       <c r="A269" s="10">
         <v>42606</v>
       </c>
@@ -11556,7 +11556,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:13">
       <c r="A270" s="10">
         <v>42613</v>
       </c>
@@ -11597,7 +11597,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:13">
       <c r="A271" s="10">
         <v>42620</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:13">
       <c r="A272" s="10">
         <v>42627</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:13">
       <c r="A273" s="10">
         <v>42634</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:13">
       <c r="A274" s="10">
         <v>42641</v>
       </c>
@@ -11761,7 +11761,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:13">
       <c r="A275" s="10">
         <v>42648</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13">
       <c r="A276" s="10">
         <v>42655</v>
       </c>
@@ -11843,7 +11843,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:13">
       <c r="A277" s="10">
         <v>42662</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:13">
       <c r="A278" s="10">
         <v>42669</v>
       </c>
@@ -11925,7 +11925,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:13">
       <c r="A279" s="10">
         <v>42676</v>
       </c>
@@ -11966,7 +11966,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:13">
       <c r="A280" s="10">
         <v>42683</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:13">
       <c r="A281" s="10">
         <v>42690</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:13">
       <c r="A282" s="10">
         <v>42697</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:13">
       <c r="A283" s="10">
         <v>42704</v>
       </c>
@@ -12130,7 +12130,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:13">
       <c r="A284" s="10">
         <v>42711</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:13">
       <c r="A285" s="10">
         <v>42718</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:13">
       <c r="A286" s="10">
         <v>42725</v>
       </c>
@@ -12253,7 +12253,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:13">
       <c r="A287" s="10">
         <v>42732</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:13">
       <c r="A288" s="10">
         <v>42739</v>
       </c>
@@ -12335,7 +12335,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:13">
       <c r="A289" s="10">
         <v>42746</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:13">
       <c r="A290" s="10">
         <v>42753</v>
       </c>
@@ -12417,7 +12417,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:13">
       <c r="A291" s="10">
         <v>42760</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:13">
       <c r="A292" s="10">
         <v>42767</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:13">
       <c r="A293" s="10">
         <v>42774</v>
       </c>
@@ -12540,7 +12540,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:13">
       <c r="A294" s="10">
         <v>42781</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:13">
       <c r="A295" s="10">
         <v>42788</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:13">
       <c r="A296" s="10">
         <v>42795</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:13">
       <c r="A297" s="10">
         <v>42802</v>
       </c>
@@ -12704,7 +12704,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:13">
       <c r="A298" s="10">
         <v>42809</v>
       </c>
@@ -12745,7 +12745,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:13">
       <c r="A299" s="10">
         <v>42816</v>
       </c>
@@ -12786,7 +12786,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:13">
       <c r="A300" s="10">
         <v>42823</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:13">
       <c r="A301" s="10">
         <v>42830</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:13">
       <c r="A302" s="10">
         <v>42837</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:13">
       <c r="A303" s="10">
         <v>42844</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:13">
       <c r="A304" s="10">
         <v>42851</v>
       </c>
@@ -12991,7 +12991,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:13">
       <c r="A305" s="10">
         <v>42858</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:13">
       <c r="A306" s="10">
         <v>42865</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:13">
       <c r="A307" s="10">
         <v>42872</v>
       </c>
@@ -13114,7 +13114,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:13">
       <c r="A308" s="10">
         <v>42879</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:13">
       <c r="A309" s="10">
         <v>42886</v>
       </c>
@@ -13196,7 +13196,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:13">
       <c r="A310" s="10">
         <v>42893</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:13">
       <c r="A311" s="10">
         <v>42900</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:13">
       <c r="A312" s="10">
         <v>42907</v>
       </c>
@@ -13319,7 +13319,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:13">
       <c r="A313" s="10">
         <v>42914</v>
       </c>
@@ -13360,7 +13360,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:13">
       <c r="A314" s="10">
         <v>42921</v>
       </c>
@@ -13401,7 +13401,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:13">
       <c r="A315" s="10">
         <v>42928</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:13">
       <c r="A316" s="10">
         <v>42935</v>
       </c>
@@ -13483,7 +13483,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:13">
       <c r="A317" s="10">
         <v>42942</v>
       </c>
@@ -13524,7 +13524,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:13">
       <c r="A318" s="10">
         <v>42949</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:13">
       <c r="A319" s="10">
         <v>42956</v>
       </c>
@@ -13606,7 +13606,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:13">
       <c r="A320" s="10">
         <v>42963</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:13">
       <c r="A321" s="10">
         <v>42970</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:13">
       <c r="A322" s="10">
         <v>42977</v>
       </c>
@@ -13729,7 +13729,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:13">
       <c r="A323" s="10">
         <v>42984</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13">
       <c r="A324" s="10">
         <v>42991</v>
       </c>
@@ -13811,7 +13811,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:13">
       <c r="A325" s="10">
         <v>42998</v>
       </c>
@@ -13852,7 +13852,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:13">
       <c r="A326" s="10">
         <v>43005</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:13">
       <c r="A327" s="10">
         <v>43012</v>
       </c>
@@ -13934,7 +13934,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:13">
       <c r="A328" s="10">
         <v>43019</v>
       </c>
@@ -13975,7 +13975,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:13">
       <c r="A329" s="10">
         <v>43026</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:13">
       <c r="A330" s="10">
         <v>43033</v>
       </c>
@@ -14057,7 +14057,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:13">
       <c r="A331" s="10">
         <v>43040</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:13">
       <c r="A332" s="10">
         <v>43047</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:13">
       <c r="A333" s="10">
         <v>43054</v>
       </c>
@@ -14180,7 +14180,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:13">
       <c r="A334" s="10">
         <v>43061</v>
       </c>
@@ -14221,7 +14221,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:13">
       <c r="A335" s="10">
         <v>43068</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:13">
       <c r="A336" s="10">
         <v>43075</v>
       </c>
@@ -14303,7 +14303,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13">
       <c r="A337" s="10">
         <v>43082</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:13">
       <c r="A338" s="10">
         <v>43089</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13">
       <c r="A339" s="10">
         <v>43096</v>
       </c>
@@ -14426,7 +14426,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:13">
       <c r="A340" s="10">
         <v>43103</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:13">
       <c r="A341" s="10">
         <v>43110</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:13">
       <c r="A342" s="10">
         <v>43117</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:13">
       <c r="A343" s="10">
         <v>43124</v>
       </c>
@@ -14590,7 +14590,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:13">
       <c r="A344" s="10">
         <v>43131</v>
       </c>
@@ -14631,7 +14631,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:13">
       <c r="A345" s="10">
         <v>43138</v>
       </c>
@@ -14672,7 +14672,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:13">
       <c r="A346" s="10">
         <v>43145</v>
       </c>
@@ -14713,7 +14713,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:13">
       <c r="A347" s="10">
         <v>43152</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:13">
       <c r="A348" s="10">
         <v>43159</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:13">
       <c r="A349" s="10">
         <v>43166</v>
       </c>
@@ -14836,7 +14836,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:13">
       <c r="A350" s="10">
         <v>43173</v>
       </c>
@@ -14877,7 +14877,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:13">
       <c r="A351" s="10">
         <v>43180</v>
       </c>
@@ -14918,7 +14918,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:13">
       <c r="A352" s="10">
         <v>43187</v>
       </c>
@@ -14959,7 +14959,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:13">
       <c r="A353" s="10">
         <v>43194</v>
       </c>
@@ -15000,7 +15000,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:13">
       <c r="A354" s="10">
         <v>43201</v>
       </c>
@@ -15041,7 +15041,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:13">
       <c r="A355" s="10">
         <v>43208</v>
       </c>
@@ -15082,7 +15082,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:13">
       <c r="A356" s="10">
         <v>43215</v>
       </c>
@@ -15123,7 +15123,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:13">
       <c r="A357" s="10">
         <v>43222</v>
       </c>
@@ -15164,7 +15164,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:13">
       <c r="A358" s="10">
         <v>43229</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:13">
       <c r="A359" s="10">
         <v>43236</v>
       </c>
@@ -15246,7 +15246,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:13">
       <c r="A360" s="10">
         <v>43243</v>
       </c>
@@ -15287,7 +15287,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:13">
       <c r="A361" s="10">
         <v>43250</v>
       </c>
@@ -15328,7 +15328,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:13">
       <c r="A362" s="10">
         <v>43257</v>
       </c>
@@ -15369,7 +15369,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:13">
       <c r="A363" s="10">
         <v>43264</v>
       </c>
@@ -15410,7 +15410,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:13">
       <c r="A364" s="10">
         <v>43271</v>
       </c>
@@ -15451,7 +15451,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:13">
       <c r="A365" s="10">
         <v>43278</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:13">
       <c r="A366" s="10">
         <v>43285</v>
       </c>
@@ -15533,7 +15533,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:13">
       <c r="A367" s="10">
         <v>43292</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:13">
       <c r="A368" s="10">
         <v>43299</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:13">
       <c r="A369" s="10">
         <v>43306</v>
       </c>
@@ -15656,7 +15656,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:13">
       <c r="A370" s="10">
         <v>43313</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:13">
       <c r="A371" s="10">
         <v>43320</v>
       </c>
@@ -15738,7 +15738,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:13">
       <c r="A372" s="10">
         <v>43327</v>
       </c>
@@ -15779,7 +15779,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:13">
       <c r="A373" s="10">
         <v>43334</v>
       </c>
@@ -15820,7 +15820,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:13">
       <c r="A374" s="10">
         <v>43341</v>
       </c>
@@ -15861,7 +15861,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:13">
       <c r="A375" s="10">
         <v>43348</v>
       </c>
@@ -15902,7 +15902,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:13">
       <c r="A376" s="10">
         <v>43355</v>
       </c>
@@ -15943,7 +15943,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:13">
       <c r="A377" s="10">
         <v>43362</v>
       </c>
@@ -15984,7 +15984,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:13">
       <c r="A378" s="10">
         <v>43369</v>
       </c>
@@ -16025,7 +16025,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:13">
       <c r="A379" s="10">
         <v>43376</v>
       </c>
@@ -16066,7 +16066,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:13">
       <c r="A380" s="10">
         <v>43383</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:13">
       <c r="A381" s="10">
         <v>43390</v>
       </c>
@@ -16148,7 +16148,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:13">
       <c r="A382" s="10">
         <v>43397</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:13">
       <c r="A383" s="10">
         <v>43404</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:13">
       <c r="A384" s="10">
         <v>43411</v>
       </c>
@@ -16271,7 +16271,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:13">
       <c r="A385" s="10">
         <v>43418</v>
       </c>
@@ -16312,7 +16312,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:13">
       <c r="A386" s="10">
         <v>43425</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:13">
       <c r="A387" s="10">
         <v>43432</v>
       </c>
@@ -16394,7 +16394,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:13">
       <c r="A388" s="10">
         <v>43439</v>
       </c>
@@ -16435,7 +16435,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:13">
       <c r="A389" s="10">
         <v>43446</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:13">
       <c r="A390" s="10">
         <v>43453</v>
       </c>
@@ -16517,7 +16517,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:13">
       <c r="A391" s="10">
         <v>43460</v>
       </c>
@@ -16558,7 +16558,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:13">
       <c r="A392" s="10">
         <v>43467</v>
       </c>
@@ -16599,7 +16599,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:13">
       <c r="A393" s="10">
         <v>43474</v>
       </c>
@@ -16640,7 +16640,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:13">
       <c r="A394" s="10">
         <v>43481</v>
       </c>
@@ -16681,7 +16681,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:13">
       <c r="A395" s="10">
         <v>43488</v>
       </c>
@@ -16722,7 +16722,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:13">
       <c r="A396" s="10">
         <v>43495</v>
       </c>
@@ -16763,7 +16763,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:13">
       <c r="A397" s="10">
         <v>43502</v>
       </c>
@@ -16804,7 +16804,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:13">
       <c r="A398" s="10">
         <v>43509</v>
       </c>
@@ -16845,7 +16845,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:13">
       <c r="A399" s="10">
         <v>43516</v>
       </c>
@@ -16886,7 +16886,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:13">
       <c r="A400" s="10">
         <v>43523</v>
       </c>
@@ -16927,7 +16927,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:13">
       <c r="A401" s="10">
         <v>43530</v>
       </c>
@@ -16968,7 +16968,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:13">
       <c r="A402" s="10">
         <v>43537</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:13">
       <c r="A403" s="10">
         <v>43544</v>
       </c>
@@ -17050,7 +17050,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:13">
       <c r="A404" s="10">
         <v>43551</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:13">
       <c r="A405" s="10">
         <v>43558</v>
       </c>
@@ -17132,7 +17132,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:13">
       <c r="A406" s="10">
         <v>43565</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:13">
       <c r="A407" s="10">
         <v>43572</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:13">
       <c r="A408" s="10">
         <v>43579</v>
       </c>
@@ -17255,7 +17255,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:13">
       <c r="A409" s="10">
         <v>43586</v>
       </c>
@@ -17296,7 +17296,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:13">
       <c r="A410" s="10">
         <v>43593</v>
       </c>
@@ -17337,7 +17337,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:13">
       <c r="A411" s="10">
         <v>43600</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:13">
       <c r="A412" s="10">
         <v>43607</v>
       </c>
@@ -17419,7 +17419,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:13">
       <c r="A413" s="10">
         <v>43614</v>
       </c>
@@ -17460,7 +17460,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:13">
       <c r="A414" s="10">
         <v>43621</v>
       </c>
@@ -17501,7 +17501,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:13">
       <c r="A415" s="10">
         <v>43628</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:13">
       <c r="A416" s="10">
         <v>43635</v>
       </c>
@@ -17583,7 +17583,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:13">
       <c r="A417" s="10">
         <v>43642</v>
       </c>
@@ -17624,7 +17624,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:13">
       <c r="A418" s="10">
         <v>43649</v>
       </c>
@@ -17665,7 +17665,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:13">
       <c r="A419" s="10">
         <v>43656</v>
       </c>
@@ -17706,7 +17706,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:13">
       <c r="A420" s="10">
         <v>43663</v>
       </c>
@@ -17747,7 +17747,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:13">
       <c r="A421" s="10">
         <v>43670</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:13">
       <c r="A422" s="10">
         <v>43677</v>
       </c>
@@ -17829,7 +17829,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:13">
       <c r="A423" s="10">
         <v>43684</v>
       </c>
@@ -17870,7 +17870,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:13">
       <c r="A424" s="10">
         <v>43691</v>
       </c>
@@ -17911,7 +17911,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:13">
       <c r="A425" s="10">
         <v>43698</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:13">
       <c r="A426" s="10">
         <v>43705</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:13">
       <c r="A427" s="10">
         <v>43712</v>
       </c>
@@ -18034,7 +18034,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:13">
       <c r="A428" s="10">
         <v>43719</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:13">
       <c r="A429" s="10">
         <v>43726</v>
       </c>
@@ -18116,7 +18116,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:13">
       <c r="A430" s="10">
         <v>43733</v>
       </c>
@@ -18157,7 +18157,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:13">
       <c r="A431" s="10">
         <v>43740</v>
       </c>
@@ -18198,7 +18198,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:13">
       <c r="A432" s="10">
         <v>43747</v>
       </c>
@@ -18239,7 +18239,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:13">
       <c r="A433" s="10">
         <v>43754</v>
       </c>
@@ -18280,7 +18280,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:13">
       <c r="A434" s="10">
         <v>43761</v>
       </c>
@@ -18321,7 +18321,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:13">
       <c r="A435" s="10">
         <v>43768</v>
       </c>
@@ -18362,7 +18362,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:13">
       <c r="A436" s="10">
         <v>43775</v>
       </c>
@@ -18403,7 +18403,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:13">
       <c r="A437" s="10">
         <v>43782</v>
       </c>
@@ -18444,7 +18444,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:13">
       <c r="A438" s="10">
         <v>43789</v>
       </c>
@@ -18485,7 +18485,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:13">
       <c r="A439" s="10">
         <v>43796</v>
       </c>
@@ -18526,7 +18526,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:13">
       <c r="A440" s="10">
         <v>43803</v>
       </c>
@@ -18567,7 +18567,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:13">
       <c r="A441" s="10">
         <v>43810</v>
       </c>
@@ -18608,7 +18608,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:13">
       <c r="A442" s="10">
         <v>43817</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:13">
       <c r="A443" s="10">
         <v>43831</v>
       </c>
@@ -18690,7 +18690,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:13">
       <c r="A444" s="10">
         <v>43838</v>
       </c>
@@ -18731,7 +18731,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:13">
       <c r="A445" s="10">
         <v>43845</v>
       </c>
@@ -18772,7 +18772,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:13">
       <c r="A446" s="10">
         <v>43852</v>
       </c>
@@ -18813,7 +18813,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:13">
       <c r="A447" s="10">
         <v>43859</v>
       </c>
@@ -18854,7 +18854,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:13">
       <c r="A448" s="10">
         <v>43866</v>
       </c>
@@ -18895,7 +18895,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:13">
       <c r="A449" s="10">
         <v>43873</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:13">
       <c r="A450" s="10">
         <v>43880</v>
       </c>
@@ -18977,7 +18977,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:13">
       <c r="A451" s="10">
         <v>43887</v>
       </c>
@@ -19018,7 +19018,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:13">
       <c r="A452" s="10">
         <v>43894</v>
       </c>
@@ -19059,7 +19059,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:13">
       <c r="A453" s="10">
         <v>43901</v>
       </c>
@@ -19100,7 +19100,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:13">
       <c r="A454" s="10">
         <v>43908</v>
       </c>
@@ -19141,7 +19141,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:13">
       <c r="A455" s="10">
         <v>43915</v>
       </c>
@@ -19182,7 +19182,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:13">
       <c r="A456" s="10">
         <v>43922</v>
       </c>
@@ -19223,7 +19223,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:13">
       <c r="A457" s="10">
         <v>43929</v>
       </c>
@@ -19264,7 +19264,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:13">
       <c r="A458" s="10">
         <v>43936</v>
       </c>
@@ -19305,7 +19305,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:13">
       <c r="A459" s="10">
         <v>43943</v>
       </c>
@@ -19346,7 +19346,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:13">
       <c r="A460" s="10">
         <v>43950</v>
       </c>
@@ -19387,7 +19387,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:13">
       <c r="A461" s="10">
         <v>43957</v>
       </c>
@@ -19428,7 +19428,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:13">
       <c r="A462" s="10">
         <v>43964</v>
       </c>
@@ -19469,7 +19469,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:13">
       <c r="A463" s="10">
         <v>43971</v>
       </c>
@@ -19510,7 +19510,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:13">
       <c r="A464" s="10">
         <v>43978</v>
       </c>
@@ -19551,7 +19551,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:13">
       <c r="A465" s="10">
         <v>43985</v>
       </c>
@@ -19592,7 +19592,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:13">
       <c r="A466" s="10">
         <v>43992</v>
       </c>
@@ -19633,7 +19633,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:13">
       <c r="A467" s="10">
         <v>43999</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:13">
       <c r="A468" s="10">
         <v>44006</v>
       </c>
@@ -19715,7 +19715,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:13">
       <c r="A469" s="10">
         <v>44013</v>
       </c>
@@ -19756,7 +19756,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:13">
       <c r="A470" s="10">
         <v>44020</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:13">
       <c r="A471" s="10">
         <v>44027</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:13">
       <c r="A472" s="10">
         <v>44034</v>
       </c>
@@ -19879,7 +19879,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:13">
       <c r="A473" s="10">
         <v>44041</v>
       </c>
@@ -19920,7 +19920,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:13">
       <c r="A474" s="10">
         <v>44048</v>
       </c>
@@ -19961,7 +19961,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:13">
       <c r="A475" s="10">
         <v>44055</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:13">
       <c r="A476" s="10">
         <v>44062</v>
       </c>
@@ -20043,7 +20043,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:13">
       <c r="A477" s="10">
         <v>44069</v>
       </c>
@@ -20084,7 +20084,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:13">
       <c r="A478" s="10">
         <v>44076</v>
       </c>
@@ -20125,7 +20125,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:13">
       <c r="A479" s="10">
         <v>44083</v>
       </c>
@@ -20166,7 +20166,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:13">
       <c r="A480" s="10">
         <v>44090</v>
       </c>
@@ -20207,7 +20207,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:13">
       <c r="A481" s="10">
         <v>44097</v>
       </c>
@@ -20248,7 +20248,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:13">
       <c r="A482" s="10">
         <v>44104</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:13">
       <c r="A483" s="10">
         <v>44111</v>
       </c>
@@ -20330,7 +20330,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:13">
       <c r="A484" s="10">
         <v>44118</v>
       </c>
@@ -20371,7 +20371,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:13">
       <c r="A485" s="10">
         <v>44125</v>
       </c>
@@ -20412,7 +20412,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:13">
       <c r="A486" s="10">
         <v>44132</v>
       </c>
@@ -20453,7 +20453,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:13">
       <c r="A487" s="10">
         <v>44139</v>
       </c>
@@ -20494,7 +20494,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:13">
       <c r="A488" s="10">
         <v>44146</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:13">
       <c r="A489" s="10">
         <v>44153</v>
       </c>
@@ -20576,7 +20576,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:13">
       <c r="A490" s="10">
         <v>44160</v>
       </c>
@@ -20617,7 +20617,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:13">
       <c r="A491" s="10">
         <v>44167</v>
       </c>
@@ -20658,7 +20658,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:13">
       <c r="A492" s="10">
         <v>44174</v>
       </c>
@@ -20699,7 +20699,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:13">
       <c r="A493" s="10">
         <v>44181</v>
       </c>
@@ -20740,7 +20740,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:13">
       <c r="A494" s="10">
         <v>44188</v>
       </c>
@@ -20781,7 +20781,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:13">
       <c r="A495" s="10">
         <v>44195</v>
       </c>
@@ -20822,7 +20822,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:13">
       <c r="A496" s="10">
         <v>44202</v>
       </c>
@@ -20863,7 +20863,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:13">
       <c r="A497" s="10">
         <v>44209</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:13">
       <c r="A498" s="10">
         <v>44216</v>
       </c>
@@ -20945,7 +20945,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:13">
       <c r="A499" s="10">
         <v>44223</v>
       </c>
@@ -20986,7 +20986,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:13">
       <c r="A500" s="10">
         <v>44230</v>
       </c>
@@ -21027,7 +21027,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:13">
       <c r="A501" s="10">
         <v>44237</v>
       </c>
@@ -21068,7 +21068,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:13">
       <c r="A502" s="10">
         <v>44244</v>
       </c>
@@ -21109,7 +21109,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:13">
       <c r="A503" s="10">
         <v>44251</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:13">
       <c r="A504" s="10">
         <v>44258</v>
       </c>
@@ -21191,7 +21191,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:13">
       <c r="A505" s="10">
         <v>44265</v>
       </c>
@@ -21232,7 +21232,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:13">
       <c r="A506" s="10">
         <v>44272</v>
       </c>
@@ -21273,7 +21273,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:13">
       <c r="A507" s="10">
         <v>44279</v>
       </c>
@@ -21314,7 +21314,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:13">
       <c r="A508" s="10">
         <v>44286</v>
       </c>
@@ -21355,7 +21355,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:13">
       <c r="A509" s="10">
         <v>44293</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:13">
       <c r="A510" s="10">
         <v>44300</v>
       </c>
@@ -21437,7 +21437,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:13">
       <c r="A511" s="10">
         <v>44307</v>
       </c>
@@ -21478,7 +21478,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:13">
       <c r="A512" s="10">
         <v>44314</v>
       </c>
@@ -21519,7 +21519,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:13">
       <c r="A513" s="10">
         <v>44321</v>
       </c>
@@ -21560,7 +21560,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:13">
       <c r="A514" s="10">
         <v>44328</v>
       </c>
@@ -21601,7 +21601,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:13">
       <c r="A515" s="10">
         <v>44335</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:13">
       <c r="A516" s="10">
         <v>44342</v>
       </c>
@@ -21683,7 +21683,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:13">
       <c r="A517" s="10">
         <v>44349</v>
       </c>
@@ -21724,7 +21724,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:13">
       <c r="A518" s="10">
         <v>44356</v>
       </c>
@@ -21765,7 +21765,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:13">
       <c r="A519" s="10">
         <v>44363</v>
       </c>
@@ -21806,7 +21806,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:13">
       <c r="A520" s="10">
         <v>44370</v>
       </c>
@@ -21847,7 +21847,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:13">
       <c r="A521" s="10">
         <v>44377</v>
       </c>
@@ -21888,7 +21888,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:13">
       <c r="A522" s="10">
         <v>44384</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:13">
       <c r="A523" s="10">
         <v>44391</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:13">
       <c r="A524" s="10">
         <v>44398</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:13">
       <c r="A525" s="10">
         <v>44405</v>
       </c>
@@ -22052,7 +22052,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:13">
       <c r="A526" s="10">
         <v>44412</v>
       </c>
@@ -22093,7 +22093,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:13">
       <c r="A527" s="10">
         <v>44419</v>
       </c>
@@ -22134,7 +22134,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:13">
       <c r="A528" s="10">
         <v>44426</v>
       </c>
@@ -22175,7 +22175,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:13">
       <c r="A529" s="10">
         <v>44433</v>
       </c>
@@ -22216,7 +22216,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:13">
       <c r="A530" s="10">
         <v>44440</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:13">
       <c r="A531" s="10">
         <v>44447</v>
       </c>
@@ -22298,7 +22298,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:13">
       <c r="A532" s="10">
         <v>44454</v>
       </c>
@@ -22339,7 +22339,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:13">
       <c r="A533" s="10">
         <v>44461</v>
       </c>
@@ -22380,7 +22380,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:13">
       <c r="A534" s="10">
         <v>44468</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:13">
       <c r="A535" s="10">
         <v>44475</v>
       </c>
@@ -22462,7 +22462,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:13">
       <c r="A536" s="10">
         <v>44482</v>
       </c>
@@ -22503,7 +22503,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:13">
       <c r="A537" s="10">
         <v>44489</v>
       </c>
@@ -22544,7 +22544,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:13">
       <c r="A538" s="10">
         <v>44496</v>
       </c>
@@ -22585,7 +22585,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:13">
       <c r="A539" s="10">
         <v>44503</v>
       </c>
@@ -22626,7 +22626,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:13">
       <c r="A540" s="10">
         <v>44510</v>
       </c>
@@ -22667,7 +22667,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:13">
       <c r="A541" s="10">
         <v>44517</v>
       </c>
@@ -22708,7 +22708,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:13">
       <c r="A542" s="10">
         <v>44524</v>
       </c>
@@ -22749,7 +22749,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:13">
       <c r="A543" s="10">
         <v>44531</v>
       </c>
@@ -22790,7 +22790,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:13">
       <c r="A544" s="10">
         <v>44538</v>
       </c>
@@ -22831,7 +22831,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:13">
       <c r="A545" s="10">
         <v>44545</v>
       </c>
@@ -22872,7 +22872,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:13">
       <c r="A546" s="10">
         <v>44552</v>
       </c>
@@ -22913,7 +22913,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:13">
       <c r="A547" s="10">
         <v>44566</v>
       </c>
@@ -22954,7 +22954,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:13">
       <c r="A548" s="10">
         <v>44573</v>
       </c>
@@ -22995,7 +22995,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:13">
       <c r="A549" s="10">
         <v>44580</v>
       </c>
@@ -23036,7 +23036,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:13">
       <c r="A550" s="10">
         <v>44587</v>
       </c>
@@ -23077,7 +23077,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:13">
       <c r="A551" s="10">
         <v>44594</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:13">
       <c r="A552" s="10">
         <v>44601</v>
       </c>
@@ -23159,7 +23159,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:13">
       <c r="A553" s="10">
         <v>44608</v>
       </c>
@@ -23200,7 +23200,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:13">
       <c r="A554" s="10">
         <v>44615</v>
       </c>
@@ -23241,7 +23241,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:13">
       <c r="A555" s="10">
         <v>44622</v>
       </c>
@@ -23282,7 +23282,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:13">
       <c r="A556" s="10">
         <v>44629</v>
       </c>
@@ -23323,7 +23323,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:13">
       <c r="A557" s="10">
         <v>44636</v>
       </c>
@@ -23364,7 +23364,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:13">
       <c r="A558" s="10">
         <v>44643</v>
       </c>
@@ -23405,7 +23405,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:13">
       <c r="A559" s="10">
         <v>44650</v>
       </c>
@@ -23446,7 +23446,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:13">
       <c r="A560" s="10">
         <v>44657</v>
       </c>
@@ -23487,7 +23487,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:13">
       <c r="A561" s="10">
         <v>44664</v>
       </c>
@@ -23528,7 +23528,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:13">
       <c r="A562" s="10">
         <v>44671</v>
       </c>
@@ -23569,7 +23569,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:13">
       <c r="A563" s="10">
         <v>44678</v>
       </c>
@@ -23610,7 +23610,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:13">
       <c r="A564" s="10">
         <v>44685</v>
       </c>
@@ -23651,7 +23651,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:13">
       <c r="A565" s="10">
         <v>44692</v>
       </c>
@@ -23692,7 +23692,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:13">
       <c r="A566" s="10">
         <v>44699</v>
       </c>
@@ -23733,7 +23733,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:13">
       <c r="A567" s="10">
         <v>44706</v>
       </c>
@@ -23774,7 +23774,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:13">
       <c r="A568" s="10">
         <v>44713</v>
       </c>
@@ -23815,7 +23815,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:13">
       <c r="A569" s="10">
         <v>44720</v>
       </c>
@@ -23856,7 +23856,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:13">
       <c r="A570" s="10">
         <v>44727</v>
       </c>
@@ -23897,7 +23897,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:13">
       <c r="A571" s="10">
         <v>44734</v>
       </c>
@@ -23938,7 +23938,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:13">
       <c r="A572" s="10">
         <v>44741</v>
       </c>
@@ -23979,7 +23979,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:13">
       <c r="A573" s="10">
         <v>44748</v>
       </c>
@@ -24020,7 +24020,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:13">
       <c r="A574" s="10">
         <v>44755</v>
       </c>
@@ -24061,7 +24061,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:13">
       <c r="A575" s="10">
         <v>44762</v>
       </c>
@@ -24102,7 +24102,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:13">
       <c r="A576" s="10">
         <v>44769</v>
       </c>
@@ -24143,7 +24143,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:13">
       <c r="A577" s="10">
         <v>44776</v>
       </c>
@@ -24184,7 +24184,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:13">
       <c r="A578" s="10">
         <v>44783</v>
       </c>
@@ -24225,7 +24225,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:13">
       <c r="A579" s="10">
         <v>44790</v>
       </c>
@@ -24266,7 +24266,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:13">
       <c r="A580" s="10">
         <v>44797</v>
       </c>
@@ -24307,7 +24307,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:13">
       <c r="A581" s="10">
         <v>44804</v>
       </c>
@@ -24348,7 +24348,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:13">
       <c r="A582" s="10">
         <v>44811</v>
       </c>
@@ -24389,7 +24389,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:13">
       <c r="A583" s="10">
         <v>44818</v>
       </c>
@@ -24430,7 +24430,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:13">
       <c r="A584" s="10">
         <v>44825</v>
       </c>
@@ -24471,7 +24471,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:13">
       <c r="A585" s="10">
         <v>44832</v>
       </c>
@@ -24512,7 +24512,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:13">
       <c r="A586" s="10">
         <v>44839</v>
       </c>
@@ -24553,7 +24553,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:13">
       <c r="A587" s="10">
         <v>44846</v>
       </c>
@@ -24594,7 +24594,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:13">
       <c r="A588" s="10">
         <v>44853</v>
       </c>
@@ -24635,7 +24635,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:13">
       <c r="A589" s="10">
         <v>44860</v>
       </c>
@@ -24676,7 +24676,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:13">
       <c r="A590" s="10">
         <v>44867</v>
       </c>
@@ -24717,7 +24717,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:13">
       <c r="A591" s="10">
         <v>44874</v>
       </c>
@@ -24758,7 +24758,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:13">
       <c r="A592" s="10">
         <v>44881</v>
       </c>
@@ -24799,7 +24799,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:13">
       <c r="A593" s="10">
         <v>44888</v>
       </c>
@@ -24840,7 +24840,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:13">
       <c r="A594" s="10">
         <v>44895</v>
       </c>
@@ -24881,7 +24881,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:13">
       <c r="A595" s="10">
         <v>44902</v>
       </c>
@@ -24922,7 +24922,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:13">
       <c r="A596" s="10">
         <v>44909</v>
       </c>
@@ -24963,7 +24963,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:13">
       <c r="A597" s="10">
         <v>44916</v>
       </c>
@@ -25004,7 +25004,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:13">
       <c r="A598" s="10">
         <v>44930</v>
       </c>
@@ -25045,7 +25045,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:13">
       <c r="A599" s="10">
         <v>44937</v>
       </c>
@@ -25086,7 +25086,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:13">
       <c r="A600" s="10">
         <v>44944</v>
       </c>
@@ -25127,7 +25127,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:13">
       <c r="A601" s="10">
         <v>44951</v>
       </c>
@@ -25168,7 +25168,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:13">
       <c r="A602" s="10">
         <v>44958</v>
       </c>
@@ -25209,7 +25209,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:13">
       <c r="A603" s="10">
         <v>44965</v>
       </c>
@@ -25250,7 +25250,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:13">
       <c r="A604" s="10">
         <v>44972</v>
       </c>
@@ -25291,7 +25291,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:13">
       <c r="A605" s="10">
         <v>44979</v>
       </c>
@@ -25332,7 +25332,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:13">
       <c r="A606" s="10">
         <v>44986</v>
       </c>
@@ -25373,7 +25373,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:13">
       <c r="A607" s="10">
         <v>44993</v>
       </c>
@@ -25414,7 +25414,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:13">
       <c r="A608" s="10">
         <v>45000</v>
       </c>
@@ -25455,7 +25455,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:13">
       <c r="A609" s="10">
         <v>45007</v>
       </c>
@@ -25496,7 +25496,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:13">
       <c r="A610" s="10">
         <v>45014</v>
       </c>
@@ -25537,7 +25537,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:13">
       <c r="A611" s="10">
         <v>45021</v>
       </c>
@@ -25578,7 +25578,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:13">
       <c r="A612" s="10">
         <v>45028</v>
       </c>
@@ -25619,7 +25619,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:13">
       <c r="A613" s="10">
         <v>45035</v>
       </c>
@@ -25660,7 +25660,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:13">
       <c r="A614" s="10">
         <v>45042</v>
       </c>
@@ -25701,7 +25701,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:13">
       <c r="A615" s="10">
         <v>45049</v>
       </c>
@@ -25742,7 +25742,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:13">
       <c r="A616" s="10">
         <v>45056</v>
       </c>
@@ -25783,7 +25783,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:13">
       <c r="A617" s="10">
         <v>45063</v>
       </c>
@@ -25824,7 +25824,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:13">
       <c r="A618" s="10">
         <v>45070</v>
       </c>
@@ -25865,7 +25865,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:13">
       <c r="A619" s="10">
         <v>45077</v>
       </c>
@@ -25906,7 +25906,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:13">
       <c r="A620" s="10">
         <v>45084</v>
       </c>
@@ -25947,7 +25947,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:13">
       <c r="A621" s="10">
         <v>45091</v>
       </c>
@@ -25988,7 +25988,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:13">
       <c r="A622" s="10">
         <v>45098</v>
       </c>
@@ -26029,7 +26029,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:13">
       <c r="A623" s="10">
         <v>45105</v>
       </c>
@@ -26070,7 +26070,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:13">
       <c r="A624" s="10">
         <v>45112</v>
       </c>
@@ -26111,7 +26111,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:13">
       <c r="A625" s="10">
         <v>45119</v>
       </c>
@@ -26152,7 +26152,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:13">
       <c r="A626" s="10">
         <v>45126</v>
       </c>
@@ -26193,7 +26193,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:13">
       <c r="A627" s="10">
         <v>45133</v>
       </c>
@@ -26234,7 +26234,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:13">
       <c r="A628" s="10">
         <v>45140</v>
       </c>
@@ -26275,7 +26275,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:13">
       <c r="A629" s="10">
         <v>45147</v>
       </c>
@@ -26316,7 +26316,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:13">
       <c r="A630" s="10">
         <v>45154</v>
       </c>
@@ -26357,7 +26357,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:13">
       <c r="A631" s="10">
         <v>45161</v>
       </c>
@@ -26398,7 +26398,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:13">
       <c r="A632" s="10">
         <v>45168</v>
       </c>
@@ -26439,7 +26439,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:13">
       <c r="A633" s="10">
         <v>45175</v>
       </c>
@@ -26480,7 +26480,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:13">
       <c r="A634" s="10">
         <v>45182</v>
       </c>
@@ -26521,7 +26521,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:13">
       <c r="A635" s="10">
         <v>45189</v>
       </c>
@@ -26562,7 +26562,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:13">
       <c r="A636" s="10">
         <v>45196</v>
       </c>
@@ -26603,7 +26603,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:13">
       <c r="A637" s="10">
         <v>45203</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:13">
       <c r="A638" s="10">
         <v>45210</v>
       </c>
@@ -26685,7 +26685,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:13">
       <c r="A639" s="10">
         <v>45217</v>
       </c>
@@ -26726,7 +26726,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:13">
       <c r="A640" s="10">
         <v>45224</v>
       </c>
@@ -26767,7 +26767,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:13">
       <c r="A641" s="10">
         <v>45231</v>
       </c>
@@ -26808,7 +26808,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:13">
       <c r="A642" s="10">
         <v>45238</v>
       </c>
@@ -26849,7 +26849,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:13">
       <c r="A643" s="10">
         <v>45245</v>
       </c>
@@ -26890,7 +26890,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:13">
       <c r="A644" s="10">
         <v>45252</v>
       </c>
@@ -26931,7 +26931,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:13">
       <c r="A645" s="10">
         <v>45259</v>
       </c>
@@ -26972,7 +26972,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:13">
       <c r="A646" s="10">
         <v>45266</v>
       </c>
@@ -27013,7 +27013,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:13">
       <c r="A647" s="10">
         <v>45273</v>
       </c>
@@ -27054,7 +27054,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:13">
       <c r="A648" s="10">
         <v>45280</v>
       </c>
@@ -27095,7 +27095,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:13">
       <c r="A649" s="10">
         <v>45294</v>
       </c>
@@ -27136,7 +27136,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:13">
       <c r="A650" s="10">
         <v>45301</v>
       </c>
@@ -27177,7 +27177,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:13">
       <c r="A651" s="10">
         <v>45308</v>
       </c>
@@ -27218,7 +27218,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:13">
       <c r="A652" s="10">
         <v>45315</v>
       </c>
@@ -27259,7 +27259,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:13">
       <c r="A653" s="10">
         <v>45322</v>
       </c>
@@ -27300,7 +27300,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:13">
       <c r="A654" s="10">
         <v>45329</v>
       </c>
@@ -27341,7 +27341,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:13">
       <c r="A655" s="10">
         <v>45336</v>
       </c>
@@ -27382,7 +27382,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:13">
       <c r="A656" s="10">
         <v>45343</v>
       </c>
@@ -27423,7 +27423,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:13">
       <c r="A657" s="10">
         <v>45350</v>
       </c>
@@ -27464,7 +27464,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:13">
       <c r="A658" s="10">
         <v>45357</v>
       </c>
@@ -27505,7 +27505,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:13">
       <c r="A659" s="10">
         <v>45364</v>
       </c>
@@ -27546,7 +27546,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:13">
       <c r="A660" s="10">
         <v>45371</v>
       </c>
@@ -27587,7 +27587,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:13">
       <c r="A661" s="10">
         <v>45378</v>
       </c>
@@ -27628,7 +27628,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:13">
       <c r="A662" s="10">
         <v>45385</v>
       </c>
@@ -27669,7 +27669,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:13">
       <c r="A663" s="10">
         <v>45392</v>
       </c>
@@ -27710,7 +27710,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:13">
       <c r="A664" s="10">
         <v>45399</v>
       </c>
@@ -27751,7 +27751,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:13">
       <c r="A665" s="10">
         <v>45406</v>
       </c>
@@ -27792,7 +27792,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:13">
       <c r="A666" s="10">
         <v>45413</v>
       </c>
@@ -27833,7 +27833,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:13">
       <c r="A667" s="10">
         <v>45420</v>
       </c>
@@ -27874,7 +27874,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:13">
       <c r="A668" s="10">
         <v>45427</v>
       </c>
@@ -27915,7 +27915,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:13">
       <c r="A669" s="10">
         <v>45434</v>
       </c>
@@ -27956,7 +27956,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:13">
       <c r="A670" s="10">
         <v>45441</v>
       </c>
@@ -27997,7 +27997,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:13">
       <c r="A671" s="10">
         <v>45448</v>
       </c>
@@ -28038,7 +28038,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:13">
       <c r="A672" s="10">
         <v>45455</v>
       </c>
@@ -28079,7 +28079,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:13">
       <c r="A673" s="10">
         <v>45462</v>
       </c>
@@ -28120,7 +28120,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:13">
       <c r="A674" s="10">
         <v>45469</v>
       </c>
@@ -28161,7 +28161,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:13">
       <c r="A675" s="10">
         <v>45476</v>
       </c>
@@ -28202,7 +28202,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:13">
       <c r="A676" s="10">
         <v>45483</v>
       </c>
@@ -28243,7 +28243,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:13">
       <c r="A677" s="10">
         <v>45490</v>
       </c>
@@ -28284,7 +28284,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:13">
       <c r="A678" s="10">
         <v>45497</v>
       </c>
@@ -28325,7 +28325,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:13">
       <c r="A679" s="10">
         <v>45504</v>
       </c>
@@ -28366,7 +28366,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:13">
       <c r="A680" s="10">
         <v>45511</v>
       </c>
@@ -28407,7 +28407,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:13">
       <c r="A681" s="10">
         <v>45518</v>
       </c>
@@ -28448,7 +28448,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:13">
       <c r="A682" s="10">
         <v>45525</v>
       </c>
@@ -28489,7 +28489,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:13">
       <c r="A683" s="10">
         <v>45532</v>
       </c>
@@ -28530,7 +28530,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:13">
       <c r="A684" s="10">
         <v>45539</v>
       </c>
@@ -28571,7 +28571,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:13">
       <c r="A685" s="10">
         <v>45546</v>
       </c>
@@ -28612,7 +28612,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:13">
       <c r="A686" s="10">
         <v>45553</v>
       </c>
@@ -28653,7 +28653,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:13">
       <c r="A687" s="10">
         <v>45560</v>
       </c>
@@ -28694,7 +28694,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:13">
       <c r="A688" s="10">
         <v>45567</v>
       </c>
@@ -28735,7 +28735,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:13">
       <c r="A689" s="10">
         <v>45574</v>
       </c>
@@ -28776,7 +28776,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:13">
       <c r="A690" s="10">
         <v>45581</v>
       </c>
@@ -28817,7 +28817,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:13">
       <c r="A691" s="10">
         <v>45588</v>
       </c>
@@ -28858,7 +28858,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:13">
       <c r="A692" s="10">
         <v>45595</v>
       </c>
@@ -28899,7 +28899,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:13">
       <c r="A693" s="10">
         <v>45602</v>
       </c>
@@ -28940,7 +28940,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:13">
       <c r="A694" s="10">
         <v>45609</v>
       </c>
@@ -28981,7 +28981,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:13">
       <c r="A695" s="10">
         <v>45616</v>
       </c>
@@ -29022,7 +29022,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:13">
       <c r="A696" s="10">
         <v>45623</v>
       </c>
@@ -29063,7 +29063,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:13">
       <c r="A697" s="10">
         <v>45630</v>
       </c>
@@ -29104,7 +29104,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:13">
       <c r="A698" s="10">
         <v>45637</v>
       </c>
@@ -29145,7 +29145,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:13">
       <c r="A699" s="10">
         <v>45644</v>
       </c>
@@ -29186,7 +29186,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:13">
       <c r="A700" s="10">
         <v>45658</v>
       </c>
@@ -29227,7 +29227,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:13">
       <c r="A701" s="10">
         <v>45665</v>
       </c>
@@ -29268,7 +29268,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:13">
       <c r="A702" s="10">
         <v>45672</v>
       </c>
@@ -29309,7 +29309,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:13">
       <c r="A703" s="10">
         <v>45679</v>
       </c>
@@ -29350,7 +29350,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:13">
       <c r="A704" s="10">
         <v>45686</v>
       </c>
@@ -29391,7 +29391,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:13">
       <c r="A705" s="10">
         <v>45693</v>
       </c>
@@ -29432,7 +29432,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:13">
       <c r="A706" s="10">
         <v>45700</v>
       </c>
@@ -29473,7 +29473,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:13">
       <c r="A707" s="10">
         <v>45707</v>
       </c>
@@ -29514,7 +29514,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:13">
       <c r="A708" s="10">
         <v>45714</v>
       </c>
@@ -29555,7 +29555,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:13">
       <c r="A709" s="10">
         <v>45721</v>
       </c>
@@ -29596,7 +29596,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:13">
       <c r="A710" s="10">
         <v>45728</v>
       </c>
@@ -29637,7 +29637,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:13">
       <c r="A711" s="10">
         <v>45735</v>
       </c>
@@ -29678,7 +29678,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:13">
       <c r="A712" s="10">
         <v>45742</v>
       </c>
@@ -29719,7 +29719,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:13">
       <c r="A713" s="10">
         <v>45749</v>
       </c>
@@ -29760,7 +29760,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:13">
       <c r="A714" s="10">
         <v>45756</v>
       </c>
@@ -29801,7 +29801,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:13">
       <c r="A715" s="10">
         <v>45763</v>
       </c>
@@ -29842,7 +29842,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:13">
       <c r="A716" s="10">
         <v>45770</v>
       </c>
@@ -29883,7 +29883,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:13">
       <c r="A717" s="10">
         <v>45777</v>
       </c>
@@ -29924,7 +29924,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:13">
       <c r="A718" s="10">
         <v>45784</v>
       </c>
@@ -29965,7 +29965,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:13">
       <c r="A719" s="10">
         <v>45791</v>
       </c>
@@ -30006,7 +30006,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:13">
       <c r="A720" s="10">
         <v>45798</v>
       </c>
@@ -30047,7 +30047,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:13">
       <c r="A721" s="10">
         <v>45805</v>
       </c>
@@ -30088,7 +30088,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:13">
       <c r="A722" s="10">
         <v>45812</v>
       </c>
@@ -30129,7 +30129,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:13">
       <c r="A723" s="10">
         <v>45819</v>
       </c>
@@ -30170,7 +30170,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:13">
       <c r="A724" s="10">
         <v>45826</v>
       </c>
@@ -30211,7 +30211,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:13">
       <c r="A725" s="10">
         <v>45833</v>
       </c>
@@ -30252,7 +30252,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:13">
       <c r="A726" s="10">
         <v>45840</v>
       </c>
@@ -30293,7 +30293,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:13">
       <c r="A727" s="10">
         <v>45847</v>
       </c>
@@ -30334,7 +30334,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:13">
       <c r="A728" s="10">
         <v>45854</v>
       </c>
@@ -30375,7 +30375,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:13">
       <c r="A729" s="10">
         <v>45861</v>
       </c>
@@ -30416,7 +30416,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:13">
       <c r="A730" s="10">
         <v>45868</v>
       </c>
@@ -30457,7 +30457,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:13">
       <c r="A731" s="10">
         <v>45875</v>
       </c>
@@ -30498,7 +30498,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:13">
       <c r="A732" s="10">
         <v>45882</v>
       </c>
@@ -30539,7 +30539,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:13">
       <c r="A733" s="10">
         <v>45889</v>
       </c>
@@ -30580,7 +30580,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:13">
       <c r="A734" s="10">
         <v>45896</v>
       </c>
@@ -30621,7 +30621,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:13">
       <c r="A735" s="10">
         <v>45903</v>
       </c>
@@ -30662,7 +30662,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:13">
       <c r="A736" s="10">
         <v>45910</v>
       </c>
@@ -30703,7 +30703,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:13">
       <c r="A737" s="10">
         <v>45917</v>
       </c>
@@ -30744,7 +30744,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:13">
       <c r="A738" s="10">
         <v>45924</v>
       </c>
@@ -30785,7 +30785,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:13">
       <c r="A739" s="10">
         <v>45931</v>
       </c>
@@ -30826,7 +30826,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:13">
       <c r="A740" s="10">
         <v>45938</v>
       </c>
@@ -30867,7 +30867,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:13">
       <c r="A741" s="10">
         <v>45945</v>
       </c>
@@ -30908,7 +30908,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:13">
       <c r="A742" s="10">
         <v>45952</v>
       </c>
@@ -30949,7 +30949,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:13">
       <c r="A743" s="10">
         <v>45959</v>
       </c>
@@ -30990,7 +30990,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:13">
       <c r="A744" s="10">
         <v>45966</v>
       </c>
@@ -31031,7 +31031,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:13">
       <c r="A745" s="10">
         <v>45973</v>
       </c>
@@ -31072,7 +31072,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:13">
       <c r="A746" s="10">
         <v>45980</v>
       </c>
@@ -31113,7 +31113,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:13">
       <c r="A747" s="10">
         <v>45987</v>
       </c>
@@ -31154,7 +31154,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:13">
       <c r="A748" s="10">
         <v>45994</v>
       </c>
@@ -31195,7 +31195,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:13">
       <c r="A749" s="10">
         <v>46001</v>
       </c>
@@ -31236,7 +31236,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:13">
       <c r="A750" s="10">
         <v>46008</v>
       </c>
@@ -31277,7 +31277,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:13">
       <c r="A751" s="10">
         <v>46015</v>
       </c>
@@ -31316,6 +31316,20 @@
       </c>
       <c r="M751" s="6">
         <v>1652</v>
+      </c>
+    </row>
+    <row r="752" spans="1:13">
+      <c r="A752" s="10">
+        <v>46022</v>
+      </c>
+      <c r="B752" s="10">
+        <v>46023</v>
+      </c>
+      <c r="C752" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D752" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -31328,12 +31342,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14">
       <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
@@ -31352,7 +31366,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14">
       <c r="B3" s="5" t="s">
         <v>11</v>
       </c>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887E7133-46D1-7842-8B24-A1314F3B5C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7CA9AC-8939-B64C-82B7-71731D9D62BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12540" yWindow="780" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31331,6 +31331,33 @@
       <c r="D752" s="10" t="s">
         <v>16</v>
       </c>
+      <c r="E752" s="8">
+        <v>2212.79</v>
+      </c>
+      <c r="F752" s="6">
+        <v>2584</v>
+      </c>
+      <c r="G752" s="6">
+        <v>3427</v>
+      </c>
+      <c r="H752" s="6">
+        <v>2481</v>
+      </c>
+      <c r="I752" s="6">
+        <v>3302</v>
+      </c>
+      <c r="J752" s="6">
+        <v>487</v>
+      </c>
+      <c r="K752" s="6">
+        <v>712</v>
+      </c>
+      <c r="L752" s="6">
+        <v>962</v>
+      </c>
+      <c r="M752" s="6">
+        <v>1652</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7CA9AC-8939-B64C-82B7-71731D9D62BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022A661C-4BEA-4CA5-9070-E609FCFC4A61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="780" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12540" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -99,22 +99,22 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -128,7 +128,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -136,7 +136,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -145,7 +145,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -159,7 +159,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -196,7 +196,7 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -212,26 +212,26 @@
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -509,25 +509,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M752"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.6640625" defaultRowHeight="15"/>
+  <dimension ref="A1:M753"/>
+  <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="10.875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="10.875" style="10" customWidth="1"/>
     <col min="5" max="5" width="13.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.125" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.625" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="20.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="7.6640625" style="6"/>
+    <col min="14" max="16384" width="7.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -568,7 +568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
         <v>40716</v>
       </c>
@@ -609,7 +609,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>40723</v>
       </c>
@@ -650,7 +650,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>40730</v>
       </c>
@@ -691,7 +691,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>40737</v>
       </c>
@@ -732,7 +732,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>40744</v>
       </c>
@@ -773,7 +773,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>40751</v>
       </c>
@@ -814,7 +814,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>40758</v>
       </c>
@@ -855,7 +855,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>40765</v>
       </c>
@@ -896,7 +896,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>40772</v>
       </c>
@@ -937,7 +937,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>40779</v>
       </c>
@@ -978,7 +978,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>40786</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>40793</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>40800</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>40807</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>40814</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>40821</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>40828</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>40835</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>40842</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>40849</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>40856</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>40863</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>40870</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>40877</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>40884</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>40891</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>40898</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>40905</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>40912</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>40919</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>40926</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>40933</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>40940</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>40947</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>40954</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>40961</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>40968</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>40975</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>40982</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>40989</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>40996</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>41003</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>41010</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>41017</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>41024</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>41031</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>41038</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>41045</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>41052</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>41059</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>41066</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>41073</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>41080</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>41087</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>41094</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>41101</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>41108</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>41115</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>41122</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>41129</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>41136</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>41143</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>41150</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>41157</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>41164</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>41171</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>41178</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>41185</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>41192</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>41199</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>41206</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>41213</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>41220</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>41227</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>41234</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>41241</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>41248</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>41255</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>41262</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="10">
         <v>41269</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>41276</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="10">
         <v>41283</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>41290</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="10">
         <v>41297</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>41304</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="10">
         <v>41311</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>41318</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="10">
         <v>41325</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>41332</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="10">
         <v>41339</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>41346</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="10">
         <v>41353</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>41360</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="10">
         <v>41367</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>41374</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <v>41381</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>41388</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <v>41395</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>41402</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="10">
         <v>41409</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>41416</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="10">
         <v>41423</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>41430</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="10">
         <v>41437</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>41444</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="10">
         <v>41451</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>41458</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="10">
         <v>41465</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>41472</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="10">
         <v>41479</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>41486</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="10">
         <v>41493</v>
       </c>
@@ -5160,7 +5160,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>41500</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="10">
         <v>41507</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>41514</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="10">
         <v>41521</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>41528</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="10">
         <v>41535</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>41542</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="10">
         <v>41549</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>41556</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="10">
         <v>41563</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>41570</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="10">
         <v>41577</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>41584</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="10">
         <v>41591</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>41598</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="10">
         <v>41605</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>41612</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="10">
         <v>41619</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>41626</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="10">
         <v>41640</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>41647</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>41654</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>41661</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>41668</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>41675</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>41682</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>41689</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>41696</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>41703</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>41710</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>41717</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>41724</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>41731</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>41738</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>41745</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>41752</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>41759</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>41766</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>41773</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="10">
         <v>41780</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>41787</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="10">
         <v>41794</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>41801</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="10">
         <v>41808</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>41815</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="10">
         <v>41822</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>41829</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="10">
         <v>41836</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>41843</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="10">
         <v>41850</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>41857</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="10">
         <v>41864</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>41871</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>41878</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>41885</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>41892</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>41899</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>41906</v>
       </c>
@@ -7538,7 +7538,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>41913</v>
       </c>
@@ -7579,7 +7579,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>41920</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="10">
         <v>41927</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>41934</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="10">
         <v>41941</v>
       </c>
@@ -7743,7 +7743,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>41948</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="10">
         <v>41955</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>41962</v>
       </c>
@@ -7866,7 +7866,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="10">
         <v>41969</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>41976</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="10">
         <v>41983</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>41990</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="10">
         <v>42011</v>
       </c>
@@ -8071,7 +8071,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="10">
         <v>42018</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="10">
         <v>42025</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>42032</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="10">
         <v>42039</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="10">
         <v>42046</v>
       </c>
@@ -8276,7 +8276,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
         <v>42053</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="10">
         <v>42060</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>42067</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="10">
         <v>42074</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>42081</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="10">
         <v>42088</v>
       </c>
@@ -8522,7 +8522,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>42095</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="10">
         <v>42102</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>42109</v>
       </c>
@@ -8645,7 +8645,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="10">
         <v>42116</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>42123</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="10">
         <v>42130</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>42137</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="10">
         <v>42144</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <v>42151</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="10">
         <v>42158</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>42165</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="10">
         <v>42172</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <v>42179</v>
       </c>
@@ -9055,7 +9055,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="10">
         <v>42186</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="10">
         <v>42193</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>42200</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" s="10">
         <v>42207</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>42214</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="10">
         <v>42221</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>42228</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="10">
         <v>42235</v>
       </c>
@@ -9383,7 +9383,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>42242</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="10">
         <v>42249</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="10">
         <v>42256</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" s="10">
         <v>42263</v>
       </c>
@@ -9547,7 +9547,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="10">
         <v>42270</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="10">
         <v>42277</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="10">
         <v>42284</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="10">
         <v>42291</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" s="10">
         <v>42298</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" s="10">
         <v>42305</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" s="10">
         <v>42312</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" s="10">
         <v>42319</v>
       </c>
@@ -9875,7 +9875,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" s="10">
         <v>42326</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" s="10">
         <v>42333</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" s="10">
         <v>42340</v>
       </c>
@@ -9998,7 +9998,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" s="10">
         <v>42347</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233" s="10">
         <v>42354</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234" s="10">
         <v>42361</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235" s="10">
         <v>42368</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236" s="10">
         <v>42375</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237" s="10">
         <v>42382</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238" s="10">
         <v>42389</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" s="10">
         <v>42396</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" s="10">
         <v>42403</v>
       </c>
@@ -10367,7 +10367,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="10">
         <v>42410</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="10">
         <v>42417</v>
       </c>
@@ -10449,7 +10449,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" s="10">
         <v>42424</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244" s="10">
         <v>42431</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="10">
         <v>42438</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" s="10">
         <v>42445</v>
       </c>
@@ -10613,7 +10613,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="10">
         <v>42452</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="10">
         <v>42459</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="10">
         <v>42466</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" s="10">
         <v>42473</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" s="10">
         <v>42480</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="10">
         <v>42487</v>
       </c>
@@ -10859,7 +10859,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="10">
         <v>42494</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="10">
         <v>42501</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" s="10">
         <v>42508</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256" s="10">
         <v>42515</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257" s="10">
         <v>42522</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A258" s="10">
         <v>42529</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259" s="10">
         <v>42536</v>
       </c>
@@ -11146,7 +11146,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260" s="10">
         <v>42543</v>
       </c>
@@ -11187,7 +11187,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261" s="10">
         <v>42550</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262" s="10">
         <v>42557</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A263" s="10">
         <v>42564</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A264" s="10">
         <v>42571</v>
       </c>
@@ -11351,7 +11351,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A265" s="10">
         <v>42578</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A266" s="10">
         <v>42585</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A267" s="10">
         <v>42592</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A268" s="10">
         <v>42599</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A269" s="10">
         <v>42606</v>
       </c>
@@ -11556,7 +11556,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A270" s="10">
         <v>42613</v>
       </c>
@@ -11597,7 +11597,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A271" s="10">
         <v>42620</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A272" s="10">
         <v>42627</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A273" s="10">
         <v>42634</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A274" s="10">
         <v>42641</v>
       </c>
@@ -11761,7 +11761,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A275" s="10">
         <v>42648</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276" s="10">
         <v>42655</v>
       </c>
@@ -11843,7 +11843,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A277" s="10">
         <v>42662</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A278" s="10">
         <v>42669</v>
       </c>
@@ -11925,7 +11925,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A279" s="10">
         <v>42676</v>
       </c>
@@ -11966,7 +11966,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280" s="10">
         <v>42683</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A281" s="10">
         <v>42690</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282" s="10">
         <v>42697</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283" s="10">
         <v>42704</v>
       </c>
@@ -12130,7 +12130,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A284" s="10">
         <v>42711</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A285" s="10">
         <v>42718</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286" s="10">
         <v>42725</v>
       </c>
@@ -12253,7 +12253,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287" s="10">
         <v>42732</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288" s="10">
         <v>42739</v>
       </c>
@@ -12335,7 +12335,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289" s="10">
         <v>42746</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290" s="10">
         <v>42753</v>
       </c>
@@ -12417,7 +12417,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291" s="10">
         <v>42760</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292" s="10">
         <v>42767</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A293" s="10">
         <v>42774</v>
       </c>
@@ -12540,7 +12540,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294" s="10">
         <v>42781</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295" s="10">
         <v>42788</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296" s="10">
         <v>42795</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297" s="10">
         <v>42802</v>
       </c>
@@ -12704,7 +12704,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298" s="10">
         <v>42809</v>
       </c>
@@ -12745,7 +12745,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299" s="10">
         <v>42816</v>
       </c>
@@ -12786,7 +12786,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A300" s="10">
         <v>42823</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301" s="10">
         <v>42830</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302" s="10">
         <v>42837</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303" s="10">
         <v>42844</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304" s="10">
         <v>42851</v>
       </c>
@@ -12991,7 +12991,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A305" s="10">
         <v>42858</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A306" s="10">
         <v>42865</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307" s="10">
         <v>42872</v>
       </c>
@@ -13114,7 +13114,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308" s="10">
         <v>42879</v>
       </c>
@@ -13155,7 +13155,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309" s="10">
         <v>42886</v>
       </c>
@@ -13196,7 +13196,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A310" s="10">
         <v>42893</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A311" s="10">
         <v>42900</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A312" s="10">
         <v>42907</v>
       </c>
@@ -13319,7 +13319,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A313" s="10">
         <v>42914</v>
       </c>
@@ -13360,7 +13360,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A314" s="10">
         <v>42921</v>
       </c>
@@ -13401,7 +13401,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A315" s="10">
         <v>42928</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A316" s="10">
         <v>42935</v>
       </c>
@@ -13483,7 +13483,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A317" s="10">
         <v>42942</v>
       </c>
@@ -13524,7 +13524,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318" s="10">
         <v>42949</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319" s="10">
         <v>42956</v>
       </c>
@@ -13606,7 +13606,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A320" s="10">
         <v>42963</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321" s="10">
         <v>42970</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322" s="10">
         <v>42977</v>
       </c>
@@ -13729,7 +13729,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323" s="10">
         <v>42984</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" s="10">
         <v>42991</v>
       </c>
@@ -13811,7 +13811,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325" s="10">
         <v>42998</v>
       </c>
@@ -13852,7 +13852,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326" s="10">
         <v>43005</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327" s="10">
         <v>43012</v>
       </c>
@@ -13934,7 +13934,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328" s="10">
         <v>43019</v>
       </c>
@@ -13975,7 +13975,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329" s="10">
         <v>43026</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330" s="10">
         <v>43033</v>
       </c>
@@ -14057,7 +14057,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331" s="10">
         <v>43040</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332" s="10">
         <v>43047</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A333" s="10">
         <v>43054</v>
       </c>
@@ -14180,7 +14180,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A334" s="10">
         <v>43061</v>
       </c>
@@ -14221,7 +14221,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A335" s="10">
         <v>43068</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A336" s="10">
         <v>43075</v>
       </c>
@@ -14303,7 +14303,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337" s="10">
         <v>43082</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338" s="10">
         <v>43089</v>
       </c>
@@ -14385,7 +14385,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339" s="10">
         <v>43096</v>
       </c>
@@ -14426,7 +14426,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340" s="10">
         <v>43103</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341" s="10">
         <v>43110</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" s="10">
         <v>43117</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" s="10">
         <v>43124</v>
       </c>
@@ -14590,7 +14590,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" s="10">
         <v>43131</v>
       </c>
@@ -14631,7 +14631,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" s="10">
         <v>43138</v>
       </c>
@@ -14672,7 +14672,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" s="10">
         <v>43145</v>
       </c>
@@ -14713,7 +14713,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" s="10">
         <v>43152</v>
       </c>
@@ -14754,7 +14754,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" s="10">
         <v>43159</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349" s="10">
         <v>43166</v>
       </c>
@@ -14836,7 +14836,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350" s="10">
         <v>43173</v>
       </c>
@@ -14877,7 +14877,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351" s="10">
         <v>43180</v>
       </c>
@@ -14918,7 +14918,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352" s="10">
         <v>43187</v>
       </c>
@@ -14959,7 +14959,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353" s="10">
         <v>43194</v>
       </c>
@@ -15000,7 +15000,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" s="10">
         <v>43201</v>
       </c>
@@ -15041,7 +15041,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" s="10">
         <v>43208</v>
       </c>
@@ -15082,7 +15082,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" s="10">
         <v>43215</v>
       </c>
@@ -15123,7 +15123,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357" s="10">
         <v>43222</v>
       </c>
@@ -15164,7 +15164,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358" s="10">
         <v>43229</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" s="10">
         <v>43236</v>
       </c>
@@ -15246,7 +15246,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" s="10">
         <v>43243</v>
       </c>
@@ -15287,7 +15287,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361" s="10">
         <v>43250</v>
       </c>
@@ -15328,7 +15328,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" s="10">
         <v>43257</v>
       </c>
@@ -15369,7 +15369,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363" s="10">
         <v>43264</v>
       </c>
@@ -15410,7 +15410,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" s="10">
         <v>43271</v>
       </c>
@@ -15451,7 +15451,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365" s="10">
         <v>43278</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366" s="10">
         <v>43285</v>
       </c>
@@ -15533,7 +15533,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367" s="10">
         <v>43292</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368" s="10">
         <v>43299</v>
       </c>
@@ -15615,7 +15615,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A369" s="10">
         <v>43306</v>
       </c>
@@ -15656,7 +15656,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A370" s="10">
         <v>43313</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A371" s="10">
         <v>43320</v>
       </c>
@@ -15738,7 +15738,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A372" s="10">
         <v>43327</v>
       </c>
@@ -15779,7 +15779,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A373" s="10">
         <v>43334</v>
       </c>
@@ -15820,7 +15820,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A374" s="10">
         <v>43341</v>
       </c>
@@ -15861,7 +15861,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A375" s="10">
         <v>43348</v>
       </c>
@@ -15902,7 +15902,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A376" s="10">
         <v>43355</v>
       </c>
@@ -15943,7 +15943,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A377" s="10">
         <v>43362</v>
       </c>
@@ -15984,7 +15984,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A378" s="10">
         <v>43369</v>
       </c>
@@ -16025,7 +16025,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A379" s="10">
         <v>43376</v>
       </c>
@@ -16066,7 +16066,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A380" s="10">
         <v>43383</v>
       </c>
@@ -16107,7 +16107,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A381" s="10">
         <v>43390</v>
       </c>
@@ -16148,7 +16148,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A382" s="10">
         <v>43397</v>
       </c>
@@ -16189,7 +16189,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A383" s="10">
         <v>43404</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A384" s="10">
         <v>43411</v>
       </c>
@@ -16271,7 +16271,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A385" s="10">
         <v>43418</v>
       </c>
@@ -16312,7 +16312,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386" s="10">
         <v>43425</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387" s="10">
         <v>43432</v>
       </c>
@@ -16394,7 +16394,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388" s="10">
         <v>43439</v>
       </c>
@@ -16435,7 +16435,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A389" s="10">
         <v>43446</v>
       </c>
@@ -16476,7 +16476,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A390" s="10">
         <v>43453</v>
       </c>
@@ -16517,7 +16517,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A391" s="10">
         <v>43460</v>
       </c>
@@ -16558,7 +16558,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A392" s="10">
         <v>43467</v>
       </c>
@@ -16599,7 +16599,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A393" s="10">
         <v>43474</v>
       </c>
@@ -16640,7 +16640,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A394" s="10">
         <v>43481</v>
       </c>
@@ -16681,7 +16681,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A395" s="10">
         <v>43488</v>
       </c>
@@ -16722,7 +16722,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A396" s="10">
         <v>43495</v>
       </c>
@@ -16763,7 +16763,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A397" s="10">
         <v>43502</v>
       </c>
@@ -16804,7 +16804,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A398" s="10">
         <v>43509</v>
       </c>
@@ -16845,7 +16845,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A399" s="10">
         <v>43516</v>
       </c>
@@ -16886,7 +16886,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A400" s="10">
         <v>43523</v>
       </c>
@@ -16927,7 +16927,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A401" s="10">
         <v>43530</v>
       </c>
@@ -16968,7 +16968,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A402" s="10">
         <v>43537</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A403" s="10">
         <v>43544</v>
       </c>
@@ -17050,7 +17050,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A404" s="10">
         <v>43551</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A405" s="10">
         <v>43558</v>
       </c>
@@ -17132,7 +17132,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A406" s="10">
         <v>43565</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A407" s="10">
         <v>43572</v>
       </c>
@@ -17214,7 +17214,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A408" s="10">
         <v>43579</v>
       </c>
@@ -17255,7 +17255,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A409" s="10">
         <v>43586</v>
       </c>
@@ -17296,7 +17296,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A410" s="10">
         <v>43593</v>
       </c>
@@ -17337,7 +17337,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A411" s="10">
         <v>43600</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A412" s="10">
         <v>43607</v>
       </c>
@@ -17419,7 +17419,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A413" s="10">
         <v>43614</v>
       </c>
@@ -17460,7 +17460,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A414" s="10">
         <v>43621</v>
       </c>
@@ -17501,7 +17501,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A415" s="10">
         <v>43628</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A416" s="10">
         <v>43635</v>
       </c>
@@ -17583,7 +17583,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A417" s="10">
         <v>43642</v>
       </c>
@@ -17624,7 +17624,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A418" s="10">
         <v>43649</v>
       </c>
@@ -17665,7 +17665,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A419" s="10">
         <v>43656</v>
       </c>
@@ -17706,7 +17706,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A420" s="10">
         <v>43663</v>
       </c>
@@ -17747,7 +17747,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A421" s="10">
         <v>43670</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A422" s="10">
         <v>43677</v>
       </c>
@@ -17829,7 +17829,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A423" s="10">
         <v>43684</v>
       </c>
@@ -17870,7 +17870,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A424" s="10">
         <v>43691</v>
       </c>
@@ -17911,7 +17911,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A425" s="10">
         <v>43698</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A426" s="10">
         <v>43705</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A427" s="10">
         <v>43712</v>
       </c>
@@ -18034,7 +18034,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A428" s="10">
         <v>43719</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A429" s="10">
         <v>43726</v>
       </c>
@@ -18116,7 +18116,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A430" s="10">
         <v>43733</v>
       </c>
@@ -18157,7 +18157,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A431" s="10">
         <v>43740</v>
       </c>
@@ -18198,7 +18198,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A432" s="10">
         <v>43747</v>
       </c>
@@ -18239,7 +18239,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A433" s="10">
         <v>43754</v>
       </c>
@@ -18280,7 +18280,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A434" s="10">
         <v>43761</v>
       </c>
@@ -18321,7 +18321,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A435" s="10">
         <v>43768</v>
       </c>
@@ -18362,7 +18362,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A436" s="10">
         <v>43775</v>
       </c>
@@ -18403,7 +18403,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A437" s="10">
         <v>43782</v>
       </c>
@@ -18444,7 +18444,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A438" s="10">
         <v>43789</v>
       </c>
@@ -18485,7 +18485,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A439" s="10">
         <v>43796</v>
       </c>
@@ -18526,7 +18526,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A440" s="10">
         <v>43803</v>
       </c>
@@ -18567,7 +18567,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A441" s="10">
         <v>43810</v>
       </c>
@@ -18608,7 +18608,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A442" s="10">
         <v>43817</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A443" s="10">
         <v>43831</v>
       </c>
@@ -18690,7 +18690,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A444" s="10">
         <v>43838</v>
       </c>
@@ -18731,7 +18731,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A445" s="10">
         <v>43845</v>
       </c>
@@ -18772,7 +18772,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A446" s="10">
         <v>43852</v>
       </c>
@@ -18813,7 +18813,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A447" s="10">
         <v>43859</v>
       </c>
@@ -18854,7 +18854,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A448" s="10">
         <v>43866</v>
       </c>
@@ -18895,7 +18895,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A449" s="10">
         <v>43873</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A450" s="10">
         <v>43880</v>
       </c>
@@ -18977,7 +18977,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A451" s="10">
         <v>43887</v>
       </c>
@@ -19018,7 +19018,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A452" s="10">
         <v>43894</v>
       </c>
@@ -19059,7 +19059,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A453" s="10">
         <v>43901</v>
       </c>
@@ -19100,7 +19100,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A454" s="10">
         <v>43908</v>
       </c>
@@ -19141,7 +19141,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A455" s="10">
         <v>43915</v>
       </c>
@@ -19182,7 +19182,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A456" s="10">
         <v>43922</v>
       </c>
@@ -19223,7 +19223,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A457" s="10">
         <v>43929</v>
       </c>
@@ -19264,7 +19264,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A458" s="10">
         <v>43936</v>
       </c>
@@ -19305,7 +19305,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A459" s="10">
         <v>43943</v>
       </c>
@@ -19346,7 +19346,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A460" s="10">
         <v>43950</v>
       </c>
@@ -19387,7 +19387,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A461" s="10">
         <v>43957</v>
       </c>
@@ -19428,7 +19428,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A462" s="10">
         <v>43964</v>
       </c>
@@ -19469,7 +19469,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A463" s="10">
         <v>43971</v>
       </c>
@@ -19510,7 +19510,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A464" s="10">
         <v>43978</v>
       </c>
@@ -19551,7 +19551,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A465" s="10">
         <v>43985</v>
       </c>
@@ -19592,7 +19592,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A466" s="10">
         <v>43992</v>
       </c>
@@ -19633,7 +19633,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A467" s="10">
         <v>43999</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A468" s="10">
         <v>44006</v>
       </c>
@@ -19715,7 +19715,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A469" s="10">
         <v>44013</v>
       </c>
@@ -19756,7 +19756,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A470" s="10">
         <v>44020</v>
       </c>
@@ -19797,7 +19797,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A471" s="10">
         <v>44027</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A472" s="10">
         <v>44034</v>
       </c>
@@ -19879,7 +19879,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A473" s="10">
         <v>44041</v>
       </c>
@@ -19920,7 +19920,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A474" s="10">
         <v>44048</v>
       </c>
@@ -19961,7 +19961,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A475" s="10">
         <v>44055</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A476" s="10">
         <v>44062</v>
       </c>
@@ -20043,7 +20043,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A477" s="10">
         <v>44069</v>
       </c>
@@ -20084,7 +20084,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A478" s="10">
         <v>44076</v>
       </c>
@@ -20125,7 +20125,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A479" s="10">
         <v>44083</v>
       </c>
@@ -20166,7 +20166,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A480" s="10">
         <v>44090</v>
       </c>
@@ -20207,7 +20207,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A481" s="10">
         <v>44097</v>
       </c>
@@ -20248,7 +20248,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A482" s="10">
         <v>44104</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A483" s="10">
         <v>44111</v>
       </c>
@@ -20330,7 +20330,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A484" s="10">
         <v>44118</v>
       </c>
@@ -20371,7 +20371,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A485" s="10">
         <v>44125</v>
       </c>
@@ -20412,7 +20412,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A486" s="10">
         <v>44132</v>
       </c>
@@ -20453,7 +20453,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A487" s="10">
         <v>44139</v>
       </c>
@@ -20494,7 +20494,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A488" s="10">
         <v>44146</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A489" s="10">
         <v>44153</v>
       </c>
@@ -20576,7 +20576,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A490" s="10">
         <v>44160</v>
       </c>
@@ -20617,7 +20617,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A491" s="10">
         <v>44167</v>
       </c>
@@ -20658,7 +20658,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A492" s="10">
         <v>44174</v>
       </c>
@@ -20699,7 +20699,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A493" s="10">
         <v>44181</v>
       </c>
@@ -20740,7 +20740,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A494" s="10">
         <v>44188</v>
       </c>
@@ -20781,7 +20781,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A495" s="10">
         <v>44195</v>
       </c>
@@ -20822,7 +20822,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A496" s="10">
         <v>44202</v>
       </c>
@@ -20863,7 +20863,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A497" s="10">
         <v>44209</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A498" s="10">
         <v>44216</v>
       </c>
@@ -20945,7 +20945,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A499" s="10">
         <v>44223</v>
       </c>
@@ -20986,7 +20986,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A500" s="10">
         <v>44230</v>
       </c>
@@ -21027,7 +21027,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A501" s="10">
         <v>44237</v>
       </c>
@@ -21068,7 +21068,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A502" s="10">
         <v>44244</v>
       </c>
@@ -21109,7 +21109,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A503" s="10">
         <v>44251</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A504" s="10">
         <v>44258</v>
       </c>
@@ -21191,7 +21191,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A505" s="10">
         <v>44265</v>
       </c>
@@ -21232,7 +21232,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A506" s="10">
         <v>44272</v>
       </c>
@@ -21273,7 +21273,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A507" s="10">
         <v>44279</v>
       </c>
@@ -21314,7 +21314,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A508" s="10">
         <v>44286</v>
       </c>
@@ -21355,7 +21355,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A509" s="10">
         <v>44293</v>
       </c>
@@ -21396,7 +21396,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A510" s="10">
         <v>44300</v>
       </c>
@@ -21437,7 +21437,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A511" s="10">
         <v>44307</v>
       </c>
@@ -21478,7 +21478,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A512" s="10">
         <v>44314</v>
       </c>
@@ -21519,7 +21519,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A513" s="10">
         <v>44321</v>
       </c>
@@ -21560,7 +21560,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A514" s="10">
         <v>44328</v>
       </c>
@@ -21601,7 +21601,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A515" s="10">
         <v>44335</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A516" s="10">
         <v>44342</v>
       </c>
@@ -21683,7 +21683,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A517" s="10">
         <v>44349</v>
       </c>
@@ -21724,7 +21724,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A518" s="10">
         <v>44356</v>
       </c>
@@ -21765,7 +21765,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A519" s="10">
         <v>44363</v>
       </c>
@@ -21806,7 +21806,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A520" s="10">
         <v>44370</v>
       </c>
@@ -21847,7 +21847,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A521" s="10">
         <v>44377</v>
       </c>
@@ -21888,7 +21888,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A522" s="10">
         <v>44384</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A523" s="10">
         <v>44391</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A524" s="10">
         <v>44398</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A525" s="10">
         <v>44405</v>
       </c>
@@ -22052,7 +22052,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A526" s="10">
         <v>44412</v>
       </c>
@@ -22093,7 +22093,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A527" s="10">
         <v>44419</v>
       </c>
@@ -22134,7 +22134,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A528" s="10">
         <v>44426</v>
       </c>
@@ -22175,7 +22175,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A529" s="10">
         <v>44433</v>
       </c>
@@ -22216,7 +22216,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A530" s="10">
         <v>44440</v>
       </c>
@@ -22257,7 +22257,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A531" s="10">
         <v>44447</v>
       </c>
@@ -22298,7 +22298,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A532" s="10">
         <v>44454</v>
       </c>
@@ -22339,7 +22339,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A533" s="10">
         <v>44461</v>
       </c>
@@ -22380,7 +22380,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A534" s="10">
         <v>44468</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A535" s="10">
         <v>44475</v>
       </c>
@@ -22462,7 +22462,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A536" s="10">
         <v>44482</v>
       </c>
@@ -22503,7 +22503,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A537" s="10">
         <v>44489</v>
       </c>
@@ -22544,7 +22544,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A538" s="10">
         <v>44496</v>
       </c>
@@ -22585,7 +22585,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A539" s="10">
         <v>44503</v>
       </c>
@@ -22626,7 +22626,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A540" s="10">
         <v>44510</v>
       </c>
@@ -22667,7 +22667,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A541" s="10">
         <v>44517</v>
       </c>
@@ -22708,7 +22708,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A542" s="10">
         <v>44524</v>
       </c>
@@ -22749,7 +22749,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A543" s="10">
         <v>44531</v>
       </c>
@@ -22790,7 +22790,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A544" s="10">
         <v>44538</v>
       </c>
@@ -22831,7 +22831,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A545" s="10">
         <v>44545</v>
       </c>
@@ -22872,7 +22872,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A546" s="10">
         <v>44552</v>
       </c>
@@ -22913,7 +22913,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A547" s="10">
         <v>44566</v>
       </c>
@@ -22954,7 +22954,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A548" s="10">
         <v>44573</v>
       </c>
@@ -22995,7 +22995,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A549" s="10">
         <v>44580</v>
       </c>
@@ -23036,7 +23036,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A550" s="10">
         <v>44587</v>
       </c>
@@ -23077,7 +23077,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A551" s="10">
         <v>44594</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A552" s="10">
         <v>44601</v>
       </c>
@@ -23159,7 +23159,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A553" s="10">
         <v>44608</v>
       </c>
@@ -23200,7 +23200,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A554" s="10">
         <v>44615</v>
       </c>
@@ -23241,7 +23241,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A555" s="10">
         <v>44622</v>
       </c>
@@ -23282,7 +23282,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A556" s="10">
         <v>44629</v>
       </c>
@@ -23323,7 +23323,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A557" s="10">
         <v>44636</v>
       </c>
@@ -23364,7 +23364,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A558" s="10">
         <v>44643</v>
       </c>
@@ -23405,7 +23405,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A559" s="10">
         <v>44650</v>
       </c>
@@ -23446,7 +23446,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A560" s="10">
         <v>44657</v>
       </c>
@@ -23487,7 +23487,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A561" s="10">
         <v>44664</v>
       </c>
@@ -23528,7 +23528,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A562" s="10">
         <v>44671</v>
       </c>
@@ -23569,7 +23569,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A563" s="10">
         <v>44678</v>
       </c>
@@ -23610,7 +23610,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A564" s="10">
         <v>44685</v>
       </c>
@@ -23651,7 +23651,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A565" s="10">
         <v>44692</v>
       </c>
@@ -23692,7 +23692,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A566" s="10">
         <v>44699</v>
       </c>
@@ -23733,7 +23733,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A567" s="10">
         <v>44706</v>
       </c>
@@ -23774,7 +23774,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A568" s="10">
         <v>44713</v>
       </c>
@@ -23815,7 +23815,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A569" s="10">
         <v>44720</v>
       </c>
@@ -23856,7 +23856,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A570" s="10">
         <v>44727</v>
       </c>
@@ -23897,7 +23897,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A571" s="10">
         <v>44734</v>
       </c>
@@ -23938,7 +23938,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A572" s="10">
         <v>44741</v>
       </c>
@@ -23979,7 +23979,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A573" s="10">
         <v>44748</v>
       </c>
@@ -24020,7 +24020,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A574" s="10">
         <v>44755</v>
       </c>
@@ -24061,7 +24061,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A575" s="10">
         <v>44762</v>
       </c>
@@ -24102,7 +24102,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A576" s="10">
         <v>44769</v>
       </c>
@@ -24143,7 +24143,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A577" s="10">
         <v>44776</v>
       </c>
@@ -24184,7 +24184,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A578" s="10">
         <v>44783</v>
       </c>
@@ -24225,7 +24225,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A579" s="10">
         <v>44790</v>
       </c>
@@ -24266,7 +24266,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A580" s="10">
         <v>44797</v>
       </c>
@@ -24307,7 +24307,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A581" s="10">
         <v>44804</v>
       </c>
@@ -24348,7 +24348,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A582" s="10">
         <v>44811</v>
       </c>
@@ -24389,7 +24389,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A583" s="10">
         <v>44818</v>
       </c>
@@ -24430,7 +24430,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A584" s="10">
         <v>44825</v>
       </c>
@@ -24471,7 +24471,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A585" s="10">
         <v>44832</v>
       </c>
@@ -24512,7 +24512,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A586" s="10">
         <v>44839</v>
       </c>
@@ -24553,7 +24553,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A587" s="10">
         <v>44846</v>
       </c>
@@ -24594,7 +24594,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A588" s="10">
         <v>44853</v>
       </c>
@@ -24635,7 +24635,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A589" s="10">
         <v>44860</v>
       </c>
@@ -24676,7 +24676,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A590" s="10">
         <v>44867</v>
       </c>
@@ -24717,7 +24717,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A591" s="10">
         <v>44874</v>
       </c>
@@ -24758,7 +24758,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A592" s="10">
         <v>44881</v>
       </c>
@@ -24799,7 +24799,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A593" s="10">
         <v>44888</v>
       </c>
@@ -24840,7 +24840,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A594" s="10">
         <v>44895</v>
       </c>
@@ -24881,7 +24881,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A595" s="10">
         <v>44902</v>
       </c>
@@ -24922,7 +24922,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A596" s="10">
         <v>44909</v>
       </c>
@@ -24963,7 +24963,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A597" s="10">
         <v>44916</v>
       </c>
@@ -25004,7 +25004,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A598" s="10">
         <v>44930</v>
       </c>
@@ -25045,7 +25045,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A599" s="10">
         <v>44937</v>
       </c>
@@ -25086,7 +25086,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A600" s="10">
         <v>44944</v>
       </c>
@@ -25127,7 +25127,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A601" s="10">
         <v>44951</v>
       </c>
@@ -25168,7 +25168,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A602" s="10">
         <v>44958</v>
       </c>
@@ -25209,7 +25209,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A603" s="10">
         <v>44965</v>
       </c>
@@ -25250,7 +25250,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A604" s="10">
         <v>44972</v>
       </c>
@@ -25291,7 +25291,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A605" s="10">
         <v>44979</v>
       </c>
@@ -25332,7 +25332,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A606" s="10">
         <v>44986</v>
       </c>
@@ -25373,7 +25373,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A607" s="10">
         <v>44993</v>
       </c>
@@ -25414,7 +25414,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A608" s="10">
         <v>45000</v>
       </c>
@@ -25455,7 +25455,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A609" s="10">
         <v>45007</v>
       </c>
@@ -25496,7 +25496,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A610" s="10">
         <v>45014</v>
       </c>
@@ -25537,7 +25537,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A611" s="10">
         <v>45021</v>
       </c>
@@ -25578,7 +25578,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A612" s="10">
         <v>45028</v>
       </c>
@@ -25619,7 +25619,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A613" s="10">
         <v>45035</v>
       </c>
@@ -25660,7 +25660,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A614" s="10">
         <v>45042</v>
       </c>
@@ -25701,7 +25701,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A615" s="10">
         <v>45049</v>
       </c>
@@ -25742,7 +25742,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A616" s="10">
         <v>45056</v>
       </c>
@@ -25783,7 +25783,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A617" s="10">
         <v>45063</v>
       </c>
@@ -25824,7 +25824,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A618" s="10">
         <v>45070</v>
       </c>
@@ -25865,7 +25865,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A619" s="10">
         <v>45077</v>
       </c>
@@ -25906,7 +25906,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A620" s="10">
         <v>45084</v>
       </c>
@@ -25947,7 +25947,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A621" s="10">
         <v>45091</v>
       </c>
@@ -25988,7 +25988,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A622" s="10">
         <v>45098</v>
       </c>
@@ -26029,7 +26029,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A623" s="10">
         <v>45105</v>
       </c>
@@ -26070,7 +26070,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A624" s="10">
         <v>45112</v>
       </c>
@@ -26111,7 +26111,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A625" s="10">
         <v>45119</v>
       </c>
@@ -26152,7 +26152,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A626" s="10">
         <v>45126</v>
       </c>
@@ -26193,7 +26193,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A627" s="10">
         <v>45133</v>
       </c>
@@ -26234,7 +26234,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A628" s="10">
         <v>45140</v>
       </c>
@@ -26275,7 +26275,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A629" s="10">
         <v>45147</v>
       </c>
@@ -26316,7 +26316,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A630" s="10">
         <v>45154</v>
       </c>
@@ -26357,7 +26357,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A631" s="10">
         <v>45161</v>
       </c>
@@ -26398,7 +26398,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A632" s="10">
         <v>45168</v>
       </c>
@@ -26439,7 +26439,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A633" s="10">
         <v>45175</v>
       </c>
@@ -26480,7 +26480,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A634" s="10">
         <v>45182</v>
       </c>
@@ -26521,7 +26521,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A635" s="10">
         <v>45189</v>
       </c>
@@ -26562,7 +26562,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A636" s="10">
         <v>45196</v>
       </c>
@@ -26603,7 +26603,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A637" s="10">
         <v>45203</v>
       </c>
@@ -26644,7 +26644,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A638" s="10">
         <v>45210</v>
       </c>
@@ -26685,7 +26685,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A639" s="10">
         <v>45217</v>
       </c>
@@ -26726,7 +26726,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A640" s="10">
         <v>45224</v>
       </c>
@@ -26767,7 +26767,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A641" s="10">
         <v>45231</v>
       </c>
@@ -26808,7 +26808,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A642" s="10">
         <v>45238</v>
       </c>
@@ -26849,7 +26849,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A643" s="10">
         <v>45245</v>
       </c>
@@ -26890,7 +26890,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A644" s="10">
         <v>45252</v>
       </c>
@@ -26931,7 +26931,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A645" s="10">
         <v>45259</v>
       </c>
@@ -26972,7 +26972,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A646" s="10">
         <v>45266</v>
       </c>
@@ -27013,7 +27013,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A647" s="10">
         <v>45273</v>
       </c>
@@ -27054,7 +27054,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A648" s="10">
         <v>45280</v>
       </c>
@@ -27095,7 +27095,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A649" s="10">
         <v>45294</v>
       </c>
@@ -27136,7 +27136,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A650" s="10">
         <v>45301</v>
       </c>
@@ -27177,7 +27177,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A651" s="10">
         <v>45308</v>
       </c>
@@ -27218,7 +27218,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A652" s="10">
         <v>45315</v>
       </c>
@@ -27259,7 +27259,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A653" s="10">
         <v>45322</v>
       </c>
@@ -27300,7 +27300,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A654" s="10">
         <v>45329</v>
       </c>
@@ -27341,7 +27341,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A655" s="10">
         <v>45336</v>
       </c>
@@ -27382,7 +27382,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A656" s="10">
         <v>45343</v>
       </c>
@@ -27423,7 +27423,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A657" s="10">
         <v>45350</v>
       </c>
@@ -27464,7 +27464,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A658" s="10">
         <v>45357</v>
       </c>
@@ -27505,7 +27505,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A659" s="10">
         <v>45364</v>
       </c>
@@ -27546,7 +27546,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A660" s="10">
         <v>45371</v>
       </c>
@@ -27587,7 +27587,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A661" s="10">
         <v>45378</v>
       </c>
@@ -27628,7 +27628,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A662" s="10">
         <v>45385</v>
       </c>
@@ -27669,7 +27669,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A663" s="10">
         <v>45392</v>
       </c>
@@ -27710,7 +27710,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A664" s="10">
         <v>45399</v>
       </c>
@@ -27751,7 +27751,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A665" s="10">
         <v>45406</v>
       </c>
@@ -27792,7 +27792,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A666" s="10">
         <v>45413</v>
       </c>
@@ -27833,7 +27833,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A667" s="10">
         <v>45420</v>
       </c>
@@ -27874,7 +27874,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A668" s="10">
         <v>45427</v>
       </c>
@@ -27915,7 +27915,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A669" s="10">
         <v>45434</v>
       </c>
@@ -27956,7 +27956,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A670" s="10">
         <v>45441</v>
       </c>
@@ -27997,7 +27997,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A671" s="10">
         <v>45448</v>
       </c>
@@ -28038,7 +28038,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A672" s="10">
         <v>45455</v>
       </c>
@@ -28079,7 +28079,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A673" s="10">
         <v>45462</v>
       </c>
@@ -28120,7 +28120,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A674" s="10">
         <v>45469</v>
       </c>
@@ -28161,7 +28161,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A675" s="10">
         <v>45476</v>
       </c>
@@ -28202,7 +28202,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A676" s="10">
         <v>45483</v>
       </c>
@@ -28243,7 +28243,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A677" s="10">
         <v>45490</v>
       </c>
@@ -28284,7 +28284,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A678" s="10">
         <v>45497</v>
       </c>
@@ -28325,7 +28325,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A679" s="10">
         <v>45504</v>
       </c>
@@ -28366,7 +28366,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A680" s="10">
         <v>45511</v>
       </c>
@@ -28407,7 +28407,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A681" s="10">
         <v>45518</v>
       </c>
@@ -28448,7 +28448,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A682" s="10">
         <v>45525</v>
       </c>
@@ -28489,7 +28489,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A683" s="10">
         <v>45532</v>
       </c>
@@ -28530,7 +28530,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A684" s="10">
         <v>45539</v>
       </c>
@@ -28571,7 +28571,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A685" s="10">
         <v>45546</v>
       </c>
@@ -28612,7 +28612,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A686" s="10">
         <v>45553</v>
       </c>
@@ -28653,7 +28653,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A687" s="10">
         <v>45560</v>
       </c>
@@ -28694,7 +28694,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A688" s="10">
         <v>45567</v>
       </c>
@@ -28735,7 +28735,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A689" s="10">
         <v>45574</v>
       </c>
@@ -28776,7 +28776,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A690" s="10">
         <v>45581</v>
       </c>
@@ -28817,7 +28817,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A691" s="10">
         <v>45588</v>
       </c>
@@ -28858,7 +28858,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A692" s="10">
         <v>45595</v>
       </c>
@@ -28899,7 +28899,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A693" s="10">
         <v>45602</v>
       </c>
@@ -28940,7 +28940,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A694" s="10">
         <v>45609</v>
       </c>
@@ -28981,7 +28981,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A695" s="10">
         <v>45616</v>
       </c>
@@ -29022,7 +29022,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A696" s="10">
         <v>45623</v>
       </c>
@@ -29063,7 +29063,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A697" s="10">
         <v>45630</v>
       </c>
@@ -29104,7 +29104,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A698" s="10">
         <v>45637</v>
       </c>
@@ -29145,7 +29145,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A699" s="10">
         <v>45644</v>
       </c>
@@ -29186,7 +29186,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A700" s="10">
         <v>45658</v>
       </c>
@@ -29227,7 +29227,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A701" s="10">
         <v>45665</v>
       </c>
@@ -29268,7 +29268,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A702" s="10">
         <v>45672</v>
       </c>
@@ -29309,7 +29309,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A703" s="10">
         <v>45679</v>
       </c>
@@ -29350,7 +29350,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A704" s="10">
         <v>45686</v>
       </c>
@@ -29391,7 +29391,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A705" s="10">
         <v>45693</v>
       </c>
@@ -29432,7 +29432,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A706" s="10">
         <v>45700</v>
       </c>
@@ -29473,7 +29473,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A707" s="10">
         <v>45707</v>
       </c>
@@ -29514,7 +29514,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A708" s="10">
         <v>45714</v>
       </c>
@@ -29555,7 +29555,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A709" s="10">
         <v>45721</v>
       </c>
@@ -29596,7 +29596,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A710" s="10">
         <v>45728</v>
       </c>
@@ -29637,7 +29637,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A711" s="10">
         <v>45735</v>
       </c>
@@ -29678,7 +29678,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A712" s="10">
         <v>45742</v>
       </c>
@@ -29719,7 +29719,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A713" s="10">
         <v>45749</v>
       </c>
@@ -29760,7 +29760,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A714" s="10">
         <v>45756</v>
       </c>
@@ -29801,7 +29801,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A715" s="10">
         <v>45763</v>
       </c>
@@ -29842,7 +29842,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A716" s="10">
         <v>45770</v>
       </c>
@@ -29883,7 +29883,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A717" s="10">
         <v>45777</v>
       </c>
@@ -29924,7 +29924,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A718" s="10">
         <v>45784</v>
       </c>
@@ -29965,7 +29965,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A719" s="10">
         <v>45791</v>
       </c>
@@ -30006,7 +30006,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A720" s="10">
         <v>45798</v>
       </c>
@@ -30047,7 +30047,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A721" s="10">
         <v>45805</v>
       </c>
@@ -30088,7 +30088,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A722" s="10">
         <v>45812</v>
       </c>
@@ -30129,7 +30129,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A723" s="10">
         <v>45819</v>
       </c>
@@ -30170,7 +30170,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A724" s="10">
         <v>45826</v>
       </c>
@@ -30211,7 +30211,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A725" s="10">
         <v>45833</v>
       </c>
@@ -30252,7 +30252,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A726" s="10">
         <v>45840</v>
       </c>
@@ -30293,7 +30293,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A727" s="10">
         <v>45847</v>
       </c>
@@ -30334,7 +30334,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A728" s="10">
         <v>45854</v>
       </c>
@@ -30375,7 +30375,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A729" s="10">
         <v>45861</v>
       </c>
@@ -30416,7 +30416,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A730" s="10">
         <v>45868</v>
       </c>
@@ -30457,7 +30457,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A731" s="10">
         <v>45875</v>
       </c>
@@ -30498,7 +30498,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A732" s="10">
         <v>45882</v>
       </c>
@@ -30539,7 +30539,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A733" s="10">
         <v>45889</v>
       </c>
@@ -30580,7 +30580,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A734" s="10">
         <v>45896</v>
       </c>
@@ -30621,7 +30621,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A735" s="10">
         <v>45903</v>
       </c>
@@ -30662,7 +30662,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A736" s="10">
         <v>45910</v>
       </c>
@@ -30703,7 +30703,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A737" s="10">
         <v>45917</v>
       </c>
@@ -30744,7 +30744,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A738" s="10">
         <v>45924</v>
       </c>
@@ -30785,7 +30785,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A739" s="10">
         <v>45931</v>
       </c>
@@ -30826,7 +30826,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A740" s="10">
         <v>45938</v>
       </c>
@@ -30867,7 +30867,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A741" s="10">
         <v>45945</v>
       </c>
@@ -30908,7 +30908,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A742" s="10">
         <v>45952</v>
       </c>
@@ -30949,7 +30949,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A743" s="10">
         <v>45959</v>
       </c>
@@ -30990,7 +30990,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A744" s="10">
         <v>45966</v>
       </c>
@@ -31031,7 +31031,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A745" s="10">
         <v>45973</v>
       </c>
@@ -31072,7 +31072,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A746" s="10">
         <v>45980</v>
       </c>
@@ -31113,7 +31113,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A747" s="10">
         <v>45987</v>
       </c>
@@ -31154,7 +31154,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A748" s="10">
         <v>45994</v>
       </c>
@@ -31195,7 +31195,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A749" s="10">
         <v>46001</v>
       </c>
@@ -31236,7 +31236,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A750" s="10">
         <v>46008</v>
       </c>
@@ -31277,7 +31277,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A751" s="10">
         <v>46015</v>
       </c>
@@ -31318,7 +31318,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A752" s="10">
         <v>46022</v>
       </c>
@@ -31357,6 +31357,20 @@
       </c>
       <c r="M752" s="6">
         <v>1652</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A753" s="10">
+        <v>46029</v>
+      </c>
+      <c r="B753" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C753" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D753" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -31369,12 +31383,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
@@ -31393,7 +31407,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
@@ -31418,5 +31432,6 @@
     <hyperlink ref="C2" r:id="rId1" xr:uid="{2661C6AA-C930-4A3C-90DD-F0E5CC18183F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022A661C-4BEA-4CA5-9070-E609FCFC4A61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E174167-E514-47A4-915C-95D9DFE503C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12540" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31359,7 +31359,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A753" s="10">
         <v>46029</v>
       </c>
@@ -31371,6 +31371,33 @@
       </c>
       <c r="D753" s="10" t="s">
         <v>16</v>
+      </c>
+      <c r="E753" s="8">
+        <v>2556.84</v>
+      </c>
+      <c r="F753" s="6">
+        <v>2840</v>
+      </c>
+      <c r="G753" s="6">
+        <v>3885</v>
+      </c>
+      <c r="H753" s="6">
+        <v>3132</v>
+      </c>
+      <c r="I753" s="6">
+        <v>3957</v>
+      </c>
+      <c r="J753" s="6">
+        <v>504</v>
+      </c>
+      <c r="K753" s="6">
+        <v>721</v>
+      </c>
+      <c r="L753" s="6">
+        <v>966</v>
+      </c>
+      <c r="M753" s="6">
+        <v>1685</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308AA1BE-A813-4995-AEA0-947DB41CF37F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF75F284-7502-4C57-AC94-B8747C564402}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17985" yWindow="2235" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31603,7 +31603,7 @@
         <v>16</v>
       </c>
       <c r="E759" s="10">
-        <v>1919</v>
+        <v>1918.72</v>
       </c>
       <c r="F759" s="11">
         <v>2109</v>
@@ -31642,6 +31642,33 @@
       </c>
       <c r="D760" s="8" t="s">
         <v>16</v>
+      </c>
+      <c r="E760" s="10">
+        <v>1898.54</v>
+      </c>
+      <c r="F760" s="11">
+        <v>2094</v>
+      </c>
+      <c r="G760" s="11">
+        <v>2826</v>
+      </c>
+      <c r="H760" s="11">
+        <v>2191</v>
+      </c>
+      <c r="I760" s="11">
+        <v>2771</v>
+      </c>
+      <c r="J760" s="11">
+        <v>543</v>
+      </c>
+      <c r="K760" s="11">
+        <v>726</v>
+      </c>
+      <c r="L760" s="11">
+        <v>958</v>
+      </c>
+      <c r="M760" s="11">
+        <v>1602</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EF60F2-64F1-5949-9554-EBED4603F532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607862E1-A18D-426C-89A4-4CE0DED8BF50}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17940" yWindow="2240" windowWidth="18060" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17940" yWindow="2235" windowWidth="18060" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -97,29 +97,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -128,7 +128,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -136,7 +136,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -175,7 +175,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -186,35 +186,35 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -492,19 +492,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M761"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.6640625" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M763"/>
+  <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="12.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18.125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="10.5" style="11" customWidth="1"/>
-    <col min="14" max="16384" width="7.6640625" style="11"/>
+    <col min="14" max="16384" width="7.625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -545,7 +545,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>40716</v>
       </c>
@@ -586,7 +586,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>40723</v>
       </c>
@@ -627,7 +627,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>40730</v>
       </c>
@@ -668,7 +668,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>40737</v>
       </c>
@@ -709,7 +709,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>40744</v>
       </c>
@@ -750,7 +750,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>40751</v>
       </c>
@@ -791,7 +791,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>40758</v>
       </c>
@@ -832,7 +832,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>40765</v>
       </c>
@@ -873,7 +873,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>40772</v>
       </c>
@@ -914,7 +914,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>40779</v>
       </c>
@@ -955,7 +955,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>40786</v>
       </c>
@@ -996,7 +996,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>40793</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>40800</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>40807</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>40814</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>40821</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>40828</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>40835</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>40842</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>40849</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>40856</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>40863</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>40870</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>40877</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>40884</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>40891</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>40898</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>40905</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>40912</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>40919</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>40926</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>40933</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>40940</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>40947</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>40954</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>40961</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>40968</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>40975</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>40982</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>40989</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>40996</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>41003</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>41010</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>41017</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>41024</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>41031</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>41038</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>41045</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>41052</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>41059</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>41066</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>41073</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>41080</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>41087</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>41094</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>41101</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>41108</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>41115</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>41122</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>41129</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>41136</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>41143</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>41150</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>41157</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>41164</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>41171</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
         <v>41178</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
         <v>41185</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="8">
         <v>41192</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="8">
         <v>41199</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>41206</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
         <v>41213</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
         <v>41220</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>41227</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
         <v>41234</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
         <v>41241</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
         <v>41248</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
         <v>41255</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
         <v>41262</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
         <v>41269</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
         <v>41276</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
         <v>41283</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
         <v>41290</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
         <v>41297</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
         <v>41304</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
         <v>41311</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
         <v>41318</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
         <v>41325</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="8">
         <v>41332</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
         <v>41339</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
         <v>41346</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
         <v>41353</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
         <v>41360</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
         <v>41367</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
         <v>41374</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
         <v>41381</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="8">
         <v>41388</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
         <v>41395</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
         <v>41402</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
         <v>41409</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
         <v>41416</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
         <v>41423</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
         <v>41430</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
         <v>41437</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
         <v>41444</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
         <v>41451</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
         <v>41458</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
         <v>41465</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
         <v>41472</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="8">
         <v>41479</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="8">
         <v>41486</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
         <v>41493</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
         <v>41500</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
         <v>41507</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
         <v>41514</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="8">
         <v>41521</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
         <v>41528</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
         <v>41535</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="8">
         <v>41542</v>
       </c>
@@ -5424,7 +5424,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
         <v>41549</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="8">
         <v>41556</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="8">
         <v>41563</v>
       </c>
@@ -5547,7 +5547,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="8">
         <v>41570</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="8">
         <v>41577</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="8">
         <v>41584</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="8">
         <v>41591</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="8">
         <v>41598</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="8">
         <v>41605</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="8">
         <v>41612</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="8">
         <v>41619</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="8">
         <v>41626</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="8">
         <v>41640</v>
       </c>
@@ -5957,7 +5957,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="8">
         <v>41647</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="8">
         <v>41654</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="8">
         <v>41661</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="8">
         <v>41668</v>
       </c>
@@ -6121,7 +6121,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="8">
         <v>41675</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="8">
         <v>41682</v>
       </c>
@@ -6203,7 +6203,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="8">
         <v>41689</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="8">
         <v>41696</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="8">
         <v>41703</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="8">
         <v>41710</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="8">
         <v>41717</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="8">
         <v>41724</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="8">
         <v>41731</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="8">
         <v>41738</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="8">
         <v>41745</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="8">
         <v>41752</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="8">
         <v>41759</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="8">
         <v>41766</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="8">
         <v>41773</v>
       </c>
@@ -6736,7 +6736,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="8">
         <v>41780</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="8">
         <v>41787</v>
       </c>
@@ -6818,7 +6818,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="8">
         <v>41794</v>
       </c>
@@ -6859,7 +6859,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="8">
         <v>41801</v>
       </c>
@@ -6900,7 +6900,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="8">
         <v>41808</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="8">
         <v>41815</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="8">
         <v>41822</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="8">
         <v>41829</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="8">
         <v>41836</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="8">
         <v>41843</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="8">
         <v>41850</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="8">
         <v>41857</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="8">
         <v>41864</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="8">
         <v>41871</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="8">
         <v>41878</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="8">
         <v>41885</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="8">
         <v>41892</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="8">
         <v>41899</v>
       </c>
@@ -7474,7 +7474,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="8">
         <v>41906</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="8">
         <v>41913</v>
       </c>
@@ -7556,7 +7556,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="8">
         <v>41920</v>
       </c>
@@ -7597,7 +7597,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="8">
         <v>41927</v>
       </c>
@@ -7638,7 +7638,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="8">
         <v>41934</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="8">
         <v>41941</v>
       </c>
@@ -7720,7 +7720,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="8">
         <v>41948</v>
       </c>
@@ -7761,7 +7761,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="8">
         <v>41955</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="8">
         <v>41962</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="8">
         <v>41969</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="8">
         <v>41976</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="8">
         <v>41983</v>
       </c>
@@ -7966,7 +7966,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="8">
         <v>41990</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="8">
         <v>42011</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="8">
         <v>42018</v>
       </c>
@@ -8089,7 +8089,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="8">
         <v>42025</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="8">
         <v>42032</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="8">
         <v>42039</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="8">
         <v>42046</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="8">
         <v>42053</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="8">
         <v>42060</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="8">
         <v>42067</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="8">
         <v>42074</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="8">
         <v>42081</v>
       </c>
@@ -8458,7 +8458,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="8">
         <v>42088</v>
       </c>
@@ -8499,7 +8499,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="8">
         <v>42095</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="8">
         <v>42102</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="8">
         <v>42109</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="8">
         <v>42116</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="8">
         <v>42123</v>
       </c>
@@ -8704,7 +8704,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="8">
         <v>42130</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="8">
         <v>42137</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="8">
         <v>42144</v>
       </c>
@@ -8827,7 +8827,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="8">
         <v>42151</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="8">
         <v>42158</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="8">
         <v>42165</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="8">
         <v>42172</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="8">
         <v>42179</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="8">
         <v>42186</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="8">
         <v>42193</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" s="8">
         <v>42200</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" s="8">
         <v>42207</v>
       </c>
@@ -9196,7 +9196,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="8">
         <v>42214</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="8">
         <v>42221</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="8">
         <v>42228</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="8">
         <v>42235</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="8">
         <v>42242</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="8">
         <v>42249</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="8">
         <v>42256</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" s="8">
         <v>42263</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="8">
         <v>42270</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="8">
         <v>42277</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="8">
         <v>42284</v>
       </c>
@@ -9647,7 +9647,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="8">
         <v>42291</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" s="8">
         <v>42298</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" s="8">
         <v>42305</v>
       </c>
@@ -9770,7 +9770,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" s="8">
         <v>42312</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" s="8">
         <v>42319</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" s="8">
         <v>42326</v>
       </c>
@@ -9893,7 +9893,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" s="8">
         <v>42333</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" s="8">
         <v>42340</v>
       </c>
@@ -9975,7 +9975,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" s="8">
         <v>42347</v>
       </c>
@@ -10016,7 +10016,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233" s="8">
         <v>42354</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234" s="8">
         <v>42361</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
         <v>42368</v>
       </c>
@@ -10139,7 +10139,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236" s="8">
         <v>42375</v>
       </c>
@@ -10180,7 +10180,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237" s="8">
         <v>42382</v>
       </c>
@@ -10221,7 +10221,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238" s="8">
         <v>42389</v>
       </c>
@@ -10262,7 +10262,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" s="8">
         <v>42396</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" s="8">
         <v>42403</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="8">
         <v>42410</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="8">
         <v>42417</v>
       </c>
@@ -10426,7 +10426,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" s="8">
         <v>42424</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244" s="8">
         <v>42431</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="8">
         <v>42438</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
         <v>42445</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="8">
         <v>42452</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="8">
         <v>42459</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="8">
         <v>42466</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" s="8">
         <v>42473</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" s="8">
         <v>42480</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="8">
         <v>42487</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="8">
         <v>42494</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="8">
         <v>42501</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" s="8">
         <v>42508</v>
       </c>
@@ -10959,7 +10959,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256" s="8">
         <v>42515</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257" s="8">
         <v>42522</v>
       </c>
@@ -11041,7 +11041,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A258" s="8">
         <v>42529</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259" s="8">
         <v>42536</v>
       </c>
@@ -11123,7 +11123,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260" s="8">
         <v>42543</v>
       </c>
@@ -11164,7 +11164,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261" s="8">
         <v>42550</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262" s="8">
         <v>42557</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A263" s="8">
         <v>42564</v>
       </c>
@@ -11287,7 +11287,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A264" s="8">
         <v>42571</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A265" s="8">
         <v>42578</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A266" s="8">
         <v>42585</v>
       </c>
@@ -11410,7 +11410,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A267" s="8">
         <v>42592</v>
       </c>
@@ -11451,7 +11451,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A268" s="8">
         <v>42599</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A269" s="8">
         <v>42606</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A270" s="8">
         <v>42613</v>
       </c>
@@ -11574,7 +11574,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A271" s="8">
         <v>42620</v>
       </c>
@@ -11615,7 +11615,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A272" s="8">
         <v>42627</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A273" s="8">
         <v>42634</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A274" s="8">
         <v>42641</v>
       </c>
@@ -11738,7 +11738,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A275" s="8">
         <v>42648</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276" s="8">
         <v>42655</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A277" s="8">
         <v>42662</v>
       </c>
@@ -11861,7 +11861,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A278" s="8">
         <v>42669</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A279" s="8">
         <v>42676</v>
       </c>
@@ -11943,7 +11943,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280" s="8">
         <v>42683</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A281" s="8">
         <v>42690</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282" s="8">
         <v>42697</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283" s="8">
         <v>42704</v>
       </c>
@@ -12107,7 +12107,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A284" s="8">
         <v>42711</v>
       </c>
@@ -12148,7 +12148,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A285" s="8">
         <v>42718</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286" s="8">
         <v>42725</v>
       </c>
@@ -12230,7 +12230,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287" s="8">
         <v>42732</v>
       </c>
@@ -12271,7 +12271,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288" s="8">
         <v>42739</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289" s="8">
         <v>42746</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290" s="8">
         <v>42753</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291" s="8">
         <v>42760</v>
       </c>
@@ -12435,7 +12435,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292" s="8">
         <v>42767</v>
       </c>
@@ -12476,7 +12476,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A293" s="8">
         <v>42774</v>
       </c>
@@ -12517,7 +12517,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294" s="8">
         <v>42781</v>
       </c>
@@ -12558,7 +12558,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295" s="8">
         <v>42788</v>
       </c>
@@ -12599,7 +12599,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296" s="8">
         <v>42795</v>
       </c>
@@ -12640,7 +12640,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297" s="8">
         <v>42802</v>
       </c>
@@ -12681,7 +12681,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298" s="8">
         <v>42809</v>
       </c>
@@ -12722,7 +12722,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299" s="8">
         <v>42816</v>
       </c>
@@ -12763,7 +12763,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A300" s="8">
         <v>42823</v>
       </c>
@@ -12804,7 +12804,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301" s="8">
         <v>42830</v>
       </c>
@@ -12845,7 +12845,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302" s="8">
         <v>42837</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303" s="8">
         <v>42844</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304" s="8">
         <v>42851</v>
       </c>
@@ -12968,7 +12968,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A305" s="8">
         <v>42858</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A306" s="8">
         <v>42865</v>
       </c>
@@ -13050,7 +13050,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307" s="8">
         <v>42872</v>
       </c>
@@ -13091,7 +13091,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308" s="8">
         <v>42879</v>
       </c>
@@ -13132,7 +13132,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309" s="8">
         <v>42886</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A310" s="8">
         <v>42893</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A311" s="8">
         <v>42900</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A312" s="8">
         <v>42907</v>
       </c>
@@ -13296,7 +13296,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A313" s="8">
         <v>42914</v>
       </c>
@@ -13337,7 +13337,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A314" s="8">
         <v>42921</v>
       </c>
@@ -13378,7 +13378,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A315" s="8">
         <v>42928</v>
       </c>
@@ -13419,7 +13419,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A316" s="8">
         <v>42935</v>
       </c>
@@ -13460,7 +13460,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A317" s="8">
         <v>42942</v>
       </c>
@@ -13501,7 +13501,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318" s="8">
         <v>42949</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319" s="8">
         <v>42956</v>
       </c>
@@ -13583,7 +13583,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A320" s="8">
         <v>42963</v>
       </c>
@@ -13624,7 +13624,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321" s="8">
         <v>42970</v>
       </c>
@@ -13665,7 +13665,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322" s="8">
         <v>42977</v>
       </c>
@@ -13706,7 +13706,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323" s="8">
         <v>42984</v>
       </c>
@@ -13747,7 +13747,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" s="8">
         <v>42991</v>
       </c>
@@ -13788,7 +13788,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325" s="8">
         <v>42998</v>
       </c>
@@ -13829,7 +13829,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326" s="8">
         <v>43005</v>
       </c>
@@ -13870,7 +13870,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327" s="8">
         <v>43012</v>
       </c>
@@ -13911,7 +13911,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328" s="8">
         <v>43019</v>
       </c>
@@ -13952,7 +13952,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329" s="8">
         <v>43026</v>
       </c>
@@ -13993,7 +13993,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330" s="8">
         <v>43033</v>
       </c>
@@ -14034,7 +14034,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331" s="8">
         <v>43040</v>
       </c>
@@ -14075,7 +14075,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332" s="8">
         <v>43047</v>
       </c>
@@ -14116,7 +14116,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A333" s="8">
         <v>43054</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A334" s="8">
         <v>43061</v>
       </c>
@@ -14198,7 +14198,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A335" s="8">
         <v>43068</v>
       </c>
@@ -14239,7 +14239,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A336" s="8">
         <v>43075</v>
       </c>
@@ -14280,7 +14280,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337" s="8">
         <v>43082</v>
       </c>
@@ -14321,7 +14321,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338" s="8">
         <v>43089</v>
       </c>
@@ -14362,7 +14362,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339" s="8">
         <v>43096</v>
       </c>
@@ -14403,7 +14403,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340" s="8">
         <v>43103</v>
       </c>
@@ -14444,7 +14444,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341" s="8">
         <v>43110</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" s="8">
         <v>43117</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" s="8">
         <v>43124</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" s="8">
         <v>43131</v>
       </c>
@@ -14608,7 +14608,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" s="8">
         <v>43138</v>
       </c>
@@ -14649,7 +14649,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" s="8">
         <v>43145</v>
       </c>
@@ -14690,7 +14690,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" s="8">
         <v>43152</v>
       </c>
@@ -14731,7 +14731,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" s="8">
         <v>43159</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349" s="8">
         <v>43166</v>
       </c>
@@ -14813,7 +14813,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350" s="8">
         <v>43173</v>
       </c>
@@ -14854,7 +14854,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351" s="8">
         <v>43180</v>
       </c>
@@ -14895,7 +14895,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352" s="8">
         <v>43187</v>
       </c>
@@ -14936,7 +14936,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353" s="8">
         <v>43194</v>
       </c>
@@ -14977,7 +14977,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" s="8">
         <v>43201</v>
       </c>
@@ -15018,7 +15018,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" s="8">
         <v>43208</v>
       </c>
@@ -15059,7 +15059,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" s="8">
         <v>43215</v>
       </c>
@@ -15100,7 +15100,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357" s="8">
         <v>43222</v>
       </c>
@@ -15141,7 +15141,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358" s="8">
         <v>43229</v>
       </c>
@@ -15182,7 +15182,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" s="8">
         <v>43236</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360" s="8">
         <v>43243</v>
       </c>
@@ -15264,7 +15264,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361" s="8">
         <v>43250</v>
       </c>
@@ -15305,7 +15305,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362" s="8">
         <v>43257</v>
       </c>
@@ -15346,7 +15346,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363" s="8">
         <v>43264</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364" s="8">
         <v>43271</v>
       </c>
@@ -15428,7 +15428,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365" s="8">
         <v>43278</v>
       </c>
@@ -15469,7 +15469,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366" s="8">
         <v>43285</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367" s="8">
         <v>43292</v>
       </c>
@@ -15551,7 +15551,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368" s="8">
         <v>43299</v>
       </c>
@@ -15592,7 +15592,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A369" s="8">
         <v>43306</v>
       </c>
@@ -15633,7 +15633,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A370" s="8">
         <v>43313</v>
       </c>
@@ -15674,7 +15674,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A371" s="8">
         <v>43320</v>
       </c>
@@ -15715,7 +15715,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A372" s="8">
         <v>43327</v>
       </c>
@@ -15756,7 +15756,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A373" s="8">
         <v>43334</v>
       </c>
@@ -15797,7 +15797,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A374" s="8">
         <v>43341</v>
       </c>
@@ -15838,7 +15838,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A375" s="8">
         <v>43348</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A376" s="8">
         <v>43355</v>
       </c>
@@ -15920,7 +15920,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A377" s="8">
         <v>43362</v>
       </c>
@@ -15961,7 +15961,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A378" s="8">
         <v>43369</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A379" s="8">
         <v>43376</v>
       </c>
@@ -16043,7 +16043,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A380" s="8">
         <v>43383</v>
       </c>
@@ -16084,7 +16084,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A381" s="8">
         <v>43390</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A382" s="8">
         <v>43397</v>
       </c>
@@ -16166,7 +16166,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A383" s="8">
         <v>43404</v>
       </c>
@@ -16207,7 +16207,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A384" s="8">
         <v>43411</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A385" s="8">
         <v>43418</v>
       </c>
@@ -16289,7 +16289,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386" s="8">
         <v>43425</v>
       </c>
@@ -16330,7 +16330,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387" s="8">
         <v>43432</v>
       </c>
@@ -16371,7 +16371,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388" s="8">
         <v>43439</v>
       </c>
@@ -16412,7 +16412,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A389" s="8">
         <v>43446</v>
       </c>
@@ -16453,7 +16453,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A390" s="8">
         <v>43453</v>
       </c>
@@ -16494,7 +16494,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A391" s="8">
         <v>43460</v>
       </c>
@@ -16535,7 +16535,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A392" s="8">
         <v>43467</v>
       </c>
@@ -16576,7 +16576,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A393" s="8">
         <v>43474</v>
       </c>
@@ -16617,7 +16617,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A394" s="8">
         <v>43481</v>
       </c>
@@ -16658,7 +16658,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A395" s="8">
         <v>43488</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A396" s="8">
         <v>43495</v>
       </c>
@@ -16740,7 +16740,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A397" s="8">
         <v>43502</v>
       </c>
@@ -16781,7 +16781,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A398" s="8">
         <v>43509</v>
       </c>
@@ -16822,7 +16822,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A399" s="8">
         <v>43516</v>
       </c>
@@ -16863,7 +16863,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A400" s="8">
         <v>43523</v>
       </c>
@@ -16904,7 +16904,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A401" s="8">
         <v>43530</v>
       </c>
@@ -16945,7 +16945,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A402" s="8">
         <v>43537</v>
       </c>
@@ -16986,7 +16986,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A403" s="8">
         <v>43544</v>
       </c>
@@ -17027,7 +17027,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A404" s="8">
         <v>43551</v>
       </c>
@@ -17068,7 +17068,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A405" s="8">
         <v>43558</v>
       </c>
@@ -17109,7 +17109,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A406" s="8">
         <v>43565</v>
       </c>
@@ -17150,7 +17150,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A407" s="8">
         <v>43572</v>
       </c>
@@ -17191,7 +17191,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A408" s="8">
         <v>43579</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A409" s="8">
         <v>43586</v>
       </c>
@@ -17273,7 +17273,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A410" s="8">
         <v>43593</v>
       </c>
@@ -17314,7 +17314,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A411" s="8">
         <v>43600</v>
       </c>
@@ -17355,7 +17355,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A412" s="8">
         <v>43607</v>
       </c>
@@ -17396,7 +17396,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A413" s="8">
         <v>43614</v>
       </c>
@@ -17437,7 +17437,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A414" s="8">
         <v>43621</v>
       </c>
@@ -17478,7 +17478,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A415" s="8">
         <v>43628</v>
       </c>
@@ -17519,7 +17519,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A416" s="8">
         <v>43635</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A417" s="8">
         <v>43642</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A418" s="8">
         <v>43649</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A419" s="8">
         <v>43656</v>
       </c>
@@ -17683,7 +17683,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A420" s="8">
         <v>43663</v>
       </c>
@@ -17724,7 +17724,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A421" s="8">
         <v>43670</v>
       </c>
@@ -17765,7 +17765,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A422" s="8">
         <v>43677</v>
       </c>
@@ -17806,7 +17806,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A423" s="8">
         <v>43684</v>
       </c>
@@ -17847,7 +17847,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A424" s="8">
         <v>43691</v>
       </c>
@@ -17888,7 +17888,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A425" s="8">
         <v>43698</v>
       </c>
@@ -17929,7 +17929,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A426" s="8">
         <v>43705</v>
       </c>
@@ -17970,7 +17970,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A427" s="8">
         <v>43712</v>
       </c>
@@ -18011,7 +18011,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A428" s="8">
         <v>43719</v>
       </c>
@@ -18052,7 +18052,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A429" s="8">
         <v>43726</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A430" s="8">
         <v>43733</v>
       </c>
@@ -18134,7 +18134,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A431" s="8">
         <v>43740</v>
       </c>
@@ -18175,7 +18175,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A432" s="8">
         <v>43747</v>
       </c>
@@ -18216,7 +18216,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A433" s="8">
         <v>43754</v>
       </c>
@@ -18257,7 +18257,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A434" s="8">
         <v>43761</v>
       </c>
@@ -18298,7 +18298,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A435" s="8">
         <v>43768</v>
       </c>
@@ -18339,7 +18339,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A436" s="8">
         <v>43775</v>
       </c>
@@ -18380,7 +18380,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A437" s="8">
         <v>43782</v>
       </c>
@@ -18421,7 +18421,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A438" s="8">
         <v>43789</v>
       </c>
@@ -18462,7 +18462,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A439" s="8">
         <v>43796</v>
       </c>
@@ -18503,7 +18503,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A440" s="8">
         <v>43803</v>
       </c>
@@ -18544,7 +18544,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A441" s="8">
         <v>43810</v>
       </c>
@@ -18585,7 +18585,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A442" s="8">
         <v>43817</v>
       </c>
@@ -18626,7 +18626,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A443" s="8">
         <v>43831</v>
       </c>
@@ -18667,7 +18667,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A444" s="8">
         <v>43838</v>
       </c>
@@ -18708,7 +18708,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A445" s="8">
         <v>43845</v>
       </c>
@@ -18749,7 +18749,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A446" s="8">
         <v>43852</v>
       </c>
@@ -18790,7 +18790,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A447" s="8">
         <v>43859</v>
       </c>
@@ -18831,7 +18831,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A448" s="8">
         <v>43866</v>
       </c>
@@ -18872,7 +18872,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A449" s="8">
         <v>43873</v>
       </c>
@@ -18913,7 +18913,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A450" s="8">
         <v>43880</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A451" s="8">
         <v>43887</v>
       </c>
@@ -18995,7 +18995,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A452" s="8">
         <v>43894</v>
       </c>
@@ -19036,7 +19036,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A453" s="8">
         <v>43901</v>
       </c>
@@ -19077,7 +19077,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A454" s="8">
         <v>43908</v>
       </c>
@@ -19118,7 +19118,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A455" s="8">
         <v>43915</v>
       </c>
@@ -19159,7 +19159,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A456" s="8">
         <v>43922</v>
       </c>
@@ -19200,7 +19200,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A457" s="8">
         <v>43929</v>
       </c>
@@ -19241,7 +19241,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A458" s="8">
         <v>43936</v>
       </c>
@@ -19282,7 +19282,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A459" s="8">
         <v>43943</v>
       </c>
@@ -19323,7 +19323,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A460" s="8">
         <v>43950</v>
       </c>
@@ -19364,7 +19364,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A461" s="8">
         <v>43957</v>
       </c>
@@ -19405,7 +19405,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A462" s="8">
         <v>43964</v>
       </c>
@@ -19446,7 +19446,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A463" s="8">
         <v>43971</v>
       </c>
@@ -19487,7 +19487,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A464" s="8">
         <v>43978</v>
       </c>
@@ -19528,7 +19528,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A465" s="8">
         <v>43985</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A466" s="8">
         <v>43992</v>
       </c>
@@ -19610,7 +19610,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A467" s="8">
         <v>43999</v>
       </c>
@@ -19651,7 +19651,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A468" s="8">
         <v>44006</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A469" s="8">
         <v>44013</v>
       </c>
@@ -19733,7 +19733,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A470" s="8">
         <v>44020</v>
       </c>
@@ -19774,7 +19774,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A471" s="8">
         <v>44027</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A472" s="8">
         <v>44034</v>
       </c>
@@ -19856,7 +19856,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A473" s="8">
         <v>44041</v>
       </c>
@@ -19897,7 +19897,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A474" s="8">
         <v>44048</v>
       </c>
@@ -19938,7 +19938,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A475" s="8">
         <v>44055</v>
       </c>
@@ -19979,7 +19979,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A476" s="8">
         <v>44062</v>
       </c>
@@ -20020,7 +20020,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A477" s="8">
         <v>44069</v>
       </c>
@@ -20061,7 +20061,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A478" s="8">
         <v>44076</v>
       </c>
@@ -20102,7 +20102,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A479" s="8">
         <v>44083</v>
       </c>
@@ -20143,7 +20143,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A480" s="8">
         <v>44090</v>
       </c>
@@ -20184,7 +20184,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A481" s="8">
         <v>44097</v>
       </c>
@@ -20225,7 +20225,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A482" s="8">
         <v>44104</v>
       </c>
@@ -20266,7 +20266,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A483" s="8">
         <v>44111</v>
       </c>
@@ -20307,7 +20307,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A484" s="8">
         <v>44118</v>
       </c>
@@ -20348,7 +20348,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A485" s="8">
         <v>44125</v>
       </c>
@@ -20389,7 +20389,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A486" s="8">
         <v>44132</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A487" s="8">
         <v>44139</v>
       </c>
@@ -20471,7 +20471,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A488" s="8">
         <v>44146</v>
       </c>
@@ -20512,7 +20512,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A489" s="8">
         <v>44153</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A490" s="8">
         <v>44160</v>
       </c>
@@ -20594,7 +20594,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A491" s="8">
         <v>44167</v>
       </c>
@@ -20635,7 +20635,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A492" s="8">
         <v>44174</v>
       </c>
@@ -20676,7 +20676,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A493" s="8">
         <v>44181</v>
       </c>
@@ -20717,7 +20717,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A494" s="8">
         <v>44188</v>
       </c>
@@ -20758,7 +20758,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A495" s="8">
         <v>44195</v>
       </c>
@@ -20799,7 +20799,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A496" s="8">
         <v>44202</v>
       </c>
@@ -20840,7 +20840,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A497" s="8">
         <v>44209</v>
       </c>
@@ -20881,7 +20881,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A498" s="8">
         <v>44216</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A499" s="8">
         <v>44223</v>
       </c>
@@ -20963,7 +20963,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A500" s="8">
         <v>44230</v>
       </c>
@@ -21004,7 +21004,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A501" s="8">
         <v>44237</v>
       </c>
@@ -21045,7 +21045,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A502" s="8">
         <v>44244</v>
       </c>
@@ -21086,7 +21086,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A503" s="8">
         <v>44251</v>
       </c>
@@ -21127,7 +21127,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A504" s="8">
         <v>44258</v>
       </c>
@@ -21168,7 +21168,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A505" s="8">
         <v>44265</v>
       </c>
@@ -21209,7 +21209,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A506" s="8">
         <v>44272</v>
       </c>
@@ -21250,7 +21250,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A507" s="8">
         <v>44279</v>
       </c>
@@ -21291,7 +21291,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A508" s="8">
         <v>44286</v>
       </c>
@@ -21332,7 +21332,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A509" s="8">
         <v>44293</v>
       </c>
@@ -21373,7 +21373,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A510" s="8">
         <v>44300</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A511" s="8">
         <v>44307</v>
       </c>
@@ -21455,7 +21455,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A512" s="8">
         <v>44314</v>
       </c>
@@ -21496,7 +21496,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A513" s="8">
         <v>44321</v>
       </c>
@@ -21537,7 +21537,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A514" s="8">
         <v>44328</v>
       </c>
@@ -21578,7 +21578,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A515" s="8">
         <v>44335</v>
       </c>
@@ -21619,7 +21619,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A516" s="8">
         <v>44342</v>
       </c>
@@ -21660,7 +21660,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A517" s="8">
         <v>44349</v>
       </c>
@@ -21701,7 +21701,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A518" s="8">
         <v>44356</v>
       </c>
@@ -21742,7 +21742,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A519" s="8">
         <v>44363</v>
       </c>
@@ -21783,7 +21783,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A520" s="8">
         <v>44370</v>
       </c>
@@ -21824,7 +21824,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A521" s="8">
         <v>44377</v>
       </c>
@@ -21865,7 +21865,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A522" s="8">
         <v>44384</v>
       </c>
@@ -21906,7 +21906,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A523" s="8">
         <v>44391</v>
       </c>
@@ -21947,7 +21947,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A524" s="8">
         <v>44398</v>
       </c>
@@ -21988,7 +21988,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A525" s="8">
         <v>44405</v>
       </c>
@@ -22029,7 +22029,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A526" s="8">
         <v>44412</v>
       </c>
@@ -22070,7 +22070,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A527" s="8">
         <v>44419</v>
       </c>
@@ -22111,7 +22111,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A528" s="8">
         <v>44426</v>
       </c>
@@ -22152,7 +22152,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A529" s="8">
         <v>44433</v>
       </c>
@@ -22193,7 +22193,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A530" s="8">
         <v>44440</v>
       </c>
@@ -22234,7 +22234,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A531" s="8">
         <v>44447</v>
       </c>
@@ -22275,7 +22275,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A532" s="8">
         <v>44454</v>
       </c>
@@ -22316,7 +22316,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A533" s="8">
         <v>44461</v>
       </c>
@@ -22357,7 +22357,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A534" s="8">
         <v>44468</v>
       </c>
@@ -22398,7 +22398,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A535" s="8">
         <v>44475</v>
       </c>
@@ -22439,7 +22439,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A536" s="8">
         <v>44482</v>
       </c>
@@ -22480,7 +22480,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A537" s="8">
         <v>44489</v>
       </c>
@@ -22521,7 +22521,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A538" s="8">
         <v>44496</v>
       </c>
@@ -22562,7 +22562,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A539" s="8">
         <v>44503</v>
       </c>
@@ -22603,7 +22603,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A540" s="8">
         <v>44510</v>
       </c>
@@ -22644,7 +22644,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A541" s="8">
         <v>44517</v>
       </c>
@@ -22685,7 +22685,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A542" s="8">
         <v>44524</v>
       </c>
@@ -22726,7 +22726,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A543" s="8">
         <v>44531</v>
       </c>
@@ -22767,7 +22767,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A544" s="8">
         <v>44538</v>
       </c>
@@ -22808,7 +22808,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A545" s="8">
         <v>44545</v>
       </c>
@@ -22849,7 +22849,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A546" s="8">
         <v>44552</v>
       </c>
@@ -22890,7 +22890,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A547" s="8">
         <v>44566</v>
       </c>
@@ -22931,7 +22931,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A548" s="8">
         <v>44573</v>
       </c>
@@ -22972,7 +22972,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A549" s="8">
         <v>44580</v>
       </c>
@@ -23013,7 +23013,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A550" s="8">
         <v>44587</v>
       </c>
@@ -23054,7 +23054,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A551" s="8">
         <v>44594</v>
       </c>
@@ -23095,7 +23095,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A552" s="8">
         <v>44601</v>
       </c>
@@ -23136,7 +23136,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A553" s="8">
         <v>44608</v>
       </c>
@@ -23177,7 +23177,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A554" s="8">
         <v>44615</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A555" s="8">
         <v>44622</v>
       </c>
@@ -23259,7 +23259,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A556" s="8">
         <v>44629</v>
       </c>
@@ -23300,7 +23300,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A557" s="8">
         <v>44636</v>
       </c>
@@ -23341,7 +23341,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A558" s="8">
         <v>44643</v>
       </c>
@@ -23382,7 +23382,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A559" s="8">
         <v>44650</v>
       </c>
@@ -23423,7 +23423,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A560" s="8">
         <v>44657</v>
       </c>
@@ -23464,7 +23464,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A561" s="8">
         <v>44664</v>
       </c>
@@ -23505,7 +23505,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A562" s="8">
         <v>44671</v>
       </c>
@@ -23546,7 +23546,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A563" s="8">
         <v>44678</v>
       </c>
@@ -23587,7 +23587,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A564" s="8">
         <v>44685</v>
       </c>
@@ -23628,7 +23628,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A565" s="8">
         <v>44692</v>
       </c>
@@ -23669,7 +23669,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A566" s="8">
         <v>44699</v>
       </c>
@@ -23710,7 +23710,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A567" s="8">
         <v>44706</v>
       </c>
@@ -23751,7 +23751,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A568" s="8">
         <v>44713</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A569" s="8">
         <v>44720</v>
       </c>
@@ -23833,7 +23833,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A570" s="8">
         <v>44727</v>
       </c>
@@ -23874,7 +23874,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A571" s="8">
         <v>44734</v>
       </c>
@@ -23915,7 +23915,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A572" s="8">
         <v>44741</v>
       </c>
@@ -23956,7 +23956,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A573" s="8">
         <v>44748</v>
       </c>
@@ -23997,7 +23997,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A574" s="8">
         <v>44755</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A575" s="8">
         <v>44762</v>
       </c>
@@ -24079,7 +24079,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A576" s="8">
         <v>44769</v>
       </c>
@@ -24120,7 +24120,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A577" s="8">
         <v>44776</v>
       </c>
@@ -24161,7 +24161,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A578" s="8">
         <v>44783</v>
       </c>
@@ -24202,7 +24202,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A579" s="8">
         <v>44790</v>
       </c>
@@ -24243,7 +24243,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A580" s="8">
         <v>44797</v>
       </c>
@@ -24284,7 +24284,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A581" s="8">
         <v>44804</v>
       </c>
@@ -24325,7 +24325,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A582" s="8">
         <v>44811</v>
       </c>
@@ -24366,7 +24366,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A583" s="8">
         <v>44818</v>
       </c>
@@ -24407,7 +24407,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A584" s="8">
         <v>44825</v>
       </c>
@@ -24448,7 +24448,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A585" s="8">
         <v>44832</v>
       </c>
@@ -24489,7 +24489,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A586" s="8">
         <v>44839</v>
       </c>
@@ -24530,7 +24530,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A587" s="8">
         <v>44846</v>
       </c>
@@ -24571,7 +24571,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A588" s="8">
         <v>44853</v>
       </c>
@@ -24612,7 +24612,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A589" s="8">
         <v>44860</v>
       </c>
@@ -24653,7 +24653,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A590" s="8">
         <v>44867</v>
       </c>
@@ -24694,7 +24694,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A591" s="8">
         <v>44874</v>
       </c>
@@ -24735,7 +24735,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A592" s="8">
         <v>44881</v>
       </c>
@@ -24776,7 +24776,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A593" s="8">
         <v>44888</v>
       </c>
@@ -24817,7 +24817,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A594" s="8">
         <v>44895</v>
       </c>
@@ -24858,7 +24858,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A595" s="8">
         <v>44902</v>
       </c>
@@ -24899,7 +24899,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A596" s="8">
         <v>44909</v>
       </c>
@@ -24940,7 +24940,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A597" s="8">
         <v>44916</v>
       </c>
@@ -24981,7 +24981,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A598" s="8">
         <v>44930</v>
       </c>
@@ -25022,7 +25022,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A599" s="8">
         <v>44937</v>
       </c>
@@ -25063,7 +25063,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A600" s="8">
         <v>44944</v>
       </c>
@@ -25104,7 +25104,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A601" s="8">
         <v>44951</v>
       </c>
@@ -25145,7 +25145,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A602" s="8">
         <v>44958</v>
       </c>
@@ -25186,7 +25186,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A603" s="8">
         <v>44965</v>
       </c>
@@ -25227,7 +25227,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A604" s="8">
         <v>44972</v>
       </c>
@@ -25268,7 +25268,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A605" s="8">
         <v>44979</v>
       </c>
@@ -25309,7 +25309,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A606" s="8">
         <v>44986</v>
       </c>
@@ -25350,7 +25350,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A607" s="8">
         <v>44993</v>
       </c>
@@ -25391,7 +25391,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A608" s="8">
         <v>45000</v>
       </c>
@@ -25432,7 +25432,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A609" s="8">
         <v>45007</v>
       </c>
@@ -25473,7 +25473,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A610" s="8">
         <v>45014</v>
       </c>
@@ -25514,7 +25514,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A611" s="8">
         <v>45021</v>
       </c>
@@ -25555,7 +25555,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A612" s="8">
         <v>45028</v>
       </c>
@@ -25596,7 +25596,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A613" s="8">
         <v>45035</v>
       </c>
@@ -25637,7 +25637,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A614" s="8">
         <v>45042</v>
       </c>
@@ -25678,7 +25678,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A615" s="8">
         <v>45049</v>
       </c>
@@ -25719,7 +25719,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A616" s="8">
         <v>45056</v>
       </c>
@@ -25760,7 +25760,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A617" s="8">
         <v>45063</v>
       </c>
@@ -25801,7 +25801,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A618" s="8">
         <v>45070</v>
       </c>
@@ -25842,7 +25842,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A619" s="8">
         <v>45077</v>
       </c>
@@ -25883,7 +25883,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A620" s="8">
         <v>45084</v>
       </c>
@@ -25924,7 +25924,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A621" s="8">
         <v>45091</v>
       </c>
@@ -25965,7 +25965,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A622" s="8">
         <v>45098</v>
       </c>
@@ -26006,7 +26006,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A623" s="8">
         <v>45105</v>
       </c>
@@ -26047,7 +26047,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A624" s="8">
         <v>45112</v>
       </c>
@@ -26088,7 +26088,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A625" s="8">
         <v>45119</v>
       </c>
@@ -26129,7 +26129,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A626" s="8">
         <v>45126</v>
       </c>
@@ -26170,7 +26170,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A627" s="8">
         <v>45133</v>
       </c>
@@ -26211,7 +26211,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A628" s="8">
         <v>45140</v>
       </c>
@@ -26252,7 +26252,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A629" s="8">
         <v>45147</v>
       </c>
@@ -26293,7 +26293,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A630" s="8">
         <v>45154</v>
       </c>
@@ -26334,7 +26334,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A631" s="8">
         <v>45161</v>
       </c>
@@ -26375,7 +26375,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A632" s="8">
         <v>45168</v>
       </c>
@@ -26416,7 +26416,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A633" s="8">
         <v>45175</v>
       </c>
@@ -26457,7 +26457,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A634" s="8">
         <v>45182</v>
       </c>
@@ -26498,7 +26498,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A635" s="8">
         <v>45189</v>
       </c>
@@ -26539,7 +26539,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A636" s="8">
         <v>45196</v>
       </c>
@@ -26580,7 +26580,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A637" s="8">
         <v>45203</v>
       </c>
@@ -26621,7 +26621,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A638" s="8">
         <v>45210</v>
       </c>
@@ -26662,7 +26662,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A639" s="8">
         <v>45217</v>
       </c>
@@ -26703,7 +26703,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A640" s="8">
         <v>45224</v>
       </c>
@@ -26744,7 +26744,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A641" s="8">
         <v>45231</v>
       </c>
@@ -26785,7 +26785,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A642" s="8">
         <v>45238</v>
       </c>
@@ -26826,7 +26826,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A643" s="8">
         <v>45245</v>
       </c>
@@ -26867,7 +26867,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A644" s="8">
         <v>45252</v>
       </c>
@@ -26908,7 +26908,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A645" s="8">
         <v>45259</v>
       </c>
@@ -26949,7 +26949,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A646" s="8">
         <v>45266</v>
       </c>
@@ -26990,7 +26990,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A647" s="8">
         <v>45273</v>
       </c>
@@ -27031,7 +27031,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A648" s="8">
         <v>45280</v>
       </c>
@@ -27072,7 +27072,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A649" s="8">
         <v>45294</v>
       </c>
@@ -27113,7 +27113,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A650" s="8">
         <v>45301</v>
       </c>
@@ -27154,7 +27154,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A651" s="8">
         <v>45308</v>
       </c>
@@ -27195,7 +27195,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A652" s="8">
         <v>45315</v>
       </c>
@@ -27236,7 +27236,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A653" s="8">
         <v>45322</v>
       </c>
@@ -27277,7 +27277,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A654" s="8">
         <v>45329</v>
       </c>
@@ -27318,7 +27318,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A655" s="8">
         <v>45336</v>
       </c>
@@ -27359,7 +27359,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A656" s="8">
         <v>45343</v>
       </c>
@@ -27400,7 +27400,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A657" s="8">
         <v>45350</v>
       </c>
@@ -27441,7 +27441,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A658" s="8">
         <v>45357</v>
       </c>
@@ -27482,7 +27482,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A659" s="8">
         <v>45364</v>
       </c>
@@ -27523,7 +27523,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A660" s="8">
         <v>45371</v>
       </c>
@@ -27564,7 +27564,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A661" s="8">
         <v>45378</v>
       </c>
@@ -27605,7 +27605,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A662" s="8">
         <v>45385</v>
       </c>
@@ -27646,7 +27646,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A663" s="8">
         <v>45392</v>
       </c>
@@ -27687,7 +27687,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A664" s="8">
         <v>45399</v>
       </c>
@@ -27728,7 +27728,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A665" s="8">
         <v>45406</v>
       </c>
@@ -27769,7 +27769,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A666" s="8">
         <v>45413</v>
       </c>
@@ -27810,7 +27810,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A667" s="8">
         <v>45420</v>
       </c>
@@ -27851,7 +27851,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A668" s="8">
         <v>45427</v>
       </c>
@@ -27892,7 +27892,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A669" s="8">
         <v>45434</v>
       </c>
@@ -27933,7 +27933,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A670" s="8">
         <v>45441</v>
       </c>
@@ -27974,7 +27974,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A671" s="8">
         <v>45448</v>
       </c>
@@ -28015,7 +28015,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A672" s="8">
         <v>45455</v>
       </c>
@@ -28056,7 +28056,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A673" s="8">
         <v>45462</v>
       </c>
@@ -28097,7 +28097,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A674" s="8">
         <v>45469</v>
       </c>
@@ -28138,7 +28138,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A675" s="8">
         <v>45476</v>
       </c>
@@ -28179,7 +28179,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A676" s="8">
         <v>45483</v>
       </c>
@@ -28220,7 +28220,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A677" s="8">
         <v>45490</v>
       </c>
@@ -28261,7 +28261,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A678" s="8">
         <v>45497</v>
       </c>
@@ -28302,7 +28302,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A679" s="8">
         <v>45504</v>
       </c>
@@ -28343,7 +28343,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A680" s="8">
         <v>45511</v>
       </c>
@@ -28384,7 +28384,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A681" s="8">
         <v>45518</v>
       </c>
@@ -28425,7 +28425,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A682" s="8">
         <v>45525</v>
       </c>
@@ -28466,7 +28466,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A683" s="8">
         <v>45532</v>
       </c>
@@ -28507,7 +28507,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A684" s="8">
         <v>45539</v>
       </c>
@@ -28548,7 +28548,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A685" s="8">
         <v>45546</v>
       </c>
@@ -28589,7 +28589,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A686" s="8">
         <v>45553</v>
       </c>
@@ -28630,7 +28630,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A687" s="8">
         <v>45560</v>
       </c>
@@ -28671,7 +28671,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A688" s="8">
         <v>45567</v>
       </c>
@@ -28712,7 +28712,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A689" s="8">
         <v>45574</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A690" s="8">
         <v>45581</v>
       </c>
@@ -28794,7 +28794,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A691" s="8">
         <v>45588</v>
       </c>
@@ -28835,7 +28835,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A692" s="8">
         <v>45595</v>
       </c>
@@ -28876,7 +28876,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A693" s="8">
         <v>45602</v>
       </c>
@@ -28917,7 +28917,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A694" s="8">
         <v>45609</v>
       </c>
@@ -28958,7 +28958,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A695" s="8">
         <v>45616</v>
       </c>
@@ -28999,7 +28999,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A696" s="8">
         <v>45623</v>
       </c>
@@ -29040,7 +29040,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A697" s="8">
         <v>45630</v>
       </c>
@@ -29081,7 +29081,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A698" s="8">
         <v>45637</v>
       </c>
@@ -29122,7 +29122,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A699" s="8">
         <v>45644</v>
       </c>
@@ -29163,7 +29163,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A700" s="8">
         <v>45658</v>
       </c>
@@ -29204,7 +29204,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A701" s="8">
         <v>45665</v>
       </c>
@@ -29245,7 +29245,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A702" s="8">
         <v>45672</v>
       </c>
@@ -29286,7 +29286,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A703" s="8">
         <v>45679</v>
       </c>
@@ -29327,7 +29327,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A704" s="8">
         <v>45686</v>
       </c>
@@ -29368,7 +29368,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A705" s="8">
         <v>45693</v>
       </c>
@@ -29409,7 +29409,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A706" s="8">
         <v>45700</v>
       </c>
@@ -29450,7 +29450,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A707" s="8">
         <v>45707</v>
       </c>
@@ -29491,7 +29491,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A708" s="8">
         <v>45714</v>
       </c>
@@ -29532,7 +29532,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A709" s="8">
         <v>45721</v>
       </c>
@@ -29573,7 +29573,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A710" s="8">
         <v>45728</v>
       </c>
@@ -29614,7 +29614,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A711" s="8">
         <v>45735</v>
       </c>
@@ -29655,7 +29655,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A712" s="8">
         <v>45742</v>
       </c>
@@ -29696,7 +29696,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A713" s="8">
         <v>45749</v>
       </c>
@@ -29737,7 +29737,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A714" s="8">
         <v>45756</v>
       </c>
@@ -29778,7 +29778,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A715" s="8">
         <v>45763</v>
       </c>
@@ -29819,7 +29819,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A716" s="8">
         <v>45770</v>
       </c>
@@ -29860,7 +29860,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A717" s="8">
         <v>45777</v>
       </c>
@@ -29901,7 +29901,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A718" s="8">
         <v>45784</v>
       </c>
@@ -29942,7 +29942,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A719" s="8">
         <v>45791</v>
       </c>
@@ -29983,7 +29983,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A720" s="8">
         <v>45798</v>
       </c>
@@ -30024,7 +30024,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A721" s="8">
         <v>45805</v>
       </c>
@@ -30065,7 +30065,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A722" s="8">
         <v>45812</v>
       </c>
@@ -30106,7 +30106,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A723" s="8">
         <v>45819</v>
       </c>
@@ -30147,7 +30147,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A724" s="8">
         <v>45826</v>
       </c>
@@ -30188,7 +30188,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A725" s="8">
         <v>45833</v>
       </c>
@@ -30229,7 +30229,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A726" s="8">
         <v>45840</v>
       </c>
@@ -30270,7 +30270,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A727" s="8">
         <v>45847</v>
       </c>
@@ -30311,7 +30311,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A728" s="8">
         <v>45854</v>
       </c>
@@ -30352,7 +30352,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A729" s="8">
         <v>45861</v>
       </c>
@@ -30393,7 +30393,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A730" s="8">
         <v>45868</v>
       </c>
@@ -30434,7 +30434,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A731" s="8">
         <v>45875</v>
       </c>
@@ -30475,7 +30475,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A732" s="8">
         <v>45882</v>
       </c>
@@ -30516,7 +30516,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A733" s="8">
         <v>45889</v>
       </c>
@@ -30557,7 +30557,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A734" s="8">
         <v>45896</v>
       </c>
@@ -30598,7 +30598,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A735" s="8">
         <v>45903</v>
       </c>
@@ -30639,7 +30639,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A736" s="8">
         <v>45910</v>
       </c>
@@ -30680,7 +30680,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A737" s="8">
         <v>45917</v>
       </c>
@@ -30721,7 +30721,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A738" s="8">
         <v>45924</v>
       </c>
@@ -30762,7 +30762,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A739" s="8">
         <v>45931</v>
       </c>
@@ -30803,7 +30803,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A740" s="8">
         <v>45938</v>
       </c>
@@ -30844,7 +30844,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A741" s="8">
         <v>45945</v>
       </c>
@@ -30885,7 +30885,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A742" s="8">
         <v>45952</v>
       </c>
@@ -30926,7 +30926,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A743" s="8">
         <v>45959</v>
       </c>
@@ -30967,7 +30967,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A744" s="8">
         <v>45966</v>
       </c>
@@ -31008,7 +31008,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A745" s="8">
         <v>45973</v>
       </c>
@@ -31049,7 +31049,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A746" s="8">
         <v>45980</v>
       </c>
@@ -31090,7 +31090,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A747" s="8">
         <v>45987</v>
       </c>
@@ -31131,7 +31131,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A748" s="8">
         <v>45994</v>
       </c>
@@ -31172,7 +31172,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A749" s="8">
         <v>46001</v>
       </c>
@@ -31213,7 +31213,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A750" s="8">
         <v>46008</v>
       </c>
@@ -31254,7 +31254,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A751" s="8">
         <v>46015</v>
       </c>
@@ -31295,7 +31295,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A752" s="8">
         <v>46022</v>
       </c>
@@ -31336,7 +31336,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A753" s="8">
         <v>46029</v>
       </c>
@@ -31377,7 +31377,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A754" s="8">
         <v>46036</v>
       </c>
@@ -31418,7 +31418,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A755" s="8">
         <v>46043</v>
       </c>
@@ -31459,7 +31459,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A756" s="8">
         <v>46050</v>
       </c>
@@ -31500,7 +31500,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A757" s="8">
         <v>46057</v>
       </c>
@@ -31541,7 +31541,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A758" s="8">
         <v>46064</v>
       </c>
@@ -31582,7 +31582,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A759" s="8">
         <v>46071</v>
       </c>
@@ -31623,7 +31623,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A760" s="8">
         <v>46078</v>
       </c>
@@ -31664,7 +31664,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A761" s="8">
         <v>46085</v>
       </c>
@@ -31703,6 +31703,61 @@
       </c>
       <c r="M761" s="11">
         <v>1570</v>
+      </c>
+    </row>
+    <row r="762" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A762" s="8">
+        <v>46092</v>
+      </c>
+      <c r="B762" s="8">
+        <v>46093</v>
+      </c>
+      <c r="C762" s="9">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D762" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E762" s="10">
+        <v>2122.5700000000002</v>
+      </c>
+      <c r="F762" s="11">
+        <v>2443</v>
+      </c>
+      <c r="G762" s="11">
+        <v>3120</v>
+      </c>
+      <c r="H762" s="11">
+        <v>2503</v>
+      </c>
+      <c r="I762" s="11">
+        <v>3080</v>
+      </c>
+      <c r="J762" s="11">
+        <v>528</v>
+      </c>
+      <c r="K762" s="11">
+        <v>723</v>
+      </c>
+      <c r="L762" s="11">
+        <v>942</v>
+      </c>
+      <c r="M762" s="11">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="763" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A763" s="8">
+        <v>46099</v>
+      </c>
+      <c r="B763" s="8">
+        <v>46100</v>
+      </c>
+      <c r="C763" s="9">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D763" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -31715,12 +31770,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -31739,7 +31794,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD10CEE-B763-4799-B075-5C5F2093731C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA698C4-29F5-41C4-8922-96F90B6C5D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17940" yWindow="2235" windowWidth="18060" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -98,29 +98,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -129,7 +129,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -137,7 +137,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -176,7 +176,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -187,35 +187,35 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -233,7 +233,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2568,6 +2568,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4862,6 +4868,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>2172.33</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>2279.21</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7192,6 +7201,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9486,6 +9501,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>2478</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>2552</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11816,6 +11834,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14110,6 +14134,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>3108</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>3474</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16440,6 +16467,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18734,6 +18767,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>2591</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>2686</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21064,6 +21100,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23358,6 +23400,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>3310</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>3393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25688,6 +25733,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -27982,6 +28033,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>539</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>595</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30314,6 +30368,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -32608,6 +32668,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>727</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -34940,6 +35003,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37234,6 +37303,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>961</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>970</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -39566,6 +39638,12 @@
                 <c:pt idx="761">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="762">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -41860,6 +41938,9 @@
                 </c:pt>
                 <c:pt idx="761">
                   <c:v>1504</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>1542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -42035,6 +42116,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -42042,7 +42124,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -42937,19 +43018,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M763"/>
-  <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="12.75" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M765"/>
+  <sheetFormatPr defaultColWidth="7.6328125" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="18.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.5" style="11" customWidth="1"/>
-    <col min="14" max="16384" width="7.625" style="11"/>
+    <col min="3" max="3" width="11.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.453125" style="11" customWidth="1"/>
+    <col min="14" max="16384" width="7.6328125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="7" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -42990,7 +43071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="A2" s="8">
         <v>40716</v>
       </c>
@@ -43031,7 +43112,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13">
       <c r="A3" s="8">
         <v>40723</v>
       </c>
@@ -43072,7 +43153,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13">
       <c r="A4" s="8">
         <v>40730</v>
       </c>
@@ -43113,7 +43194,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13">
       <c r="A5" s="8">
         <v>40737</v>
       </c>
@@ -43154,7 +43235,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="A6" s="8">
         <v>40744</v>
       </c>
@@ -43195,7 +43276,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13">
       <c r="A7" s="8">
         <v>40751</v>
       </c>
@@ -43236,7 +43317,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="A8" s="8">
         <v>40758</v>
       </c>
@@ -43277,7 +43358,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13">
       <c r="A9" s="8">
         <v>40765</v>
       </c>
@@ -43318,7 +43399,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13">
       <c r="A10" s="8">
         <v>40772</v>
       </c>
@@ -43359,7 +43440,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13">
       <c r="A11" s="8">
         <v>40779</v>
       </c>
@@ -43400,7 +43481,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13">
       <c r="A12" s="8">
         <v>40786</v>
       </c>
@@ -43441,7 +43522,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13">
       <c r="A13" s="8">
         <v>40793</v>
       </c>
@@ -43482,7 +43563,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13">
       <c r="A14" s="8">
         <v>40800</v>
       </c>
@@ -43523,7 +43604,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13">
       <c r="A15" s="8">
         <v>40807</v>
       </c>
@@ -43564,7 +43645,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13">
       <c r="A16" s="8">
         <v>40814</v>
       </c>
@@ -43605,7 +43686,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="8">
         <v>40821</v>
       </c>
@@ -43646,7 +43727,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="8">
         <v>40828</v>
       </c>
@@ -43687,7 +43768,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="8">
         <v>40835</v>
       </c>
@@ -43728,7 +43809,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="8">
         <v>40842</v>
       </c>
@@ -43769,7 +43850,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="8">
         <v>40849</v>
       </c>
@@ -43810,7 +43891,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="8">
         <v>40856</v>
       </c>
@@ -43851,7 +43932,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="8">
         <v>40863</v>
       </c>
@@ -43892,7 +43973,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="8">
         <v>40870</v>
       </c>
@@ -43933,7 +44014,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="8">
         <v>40877</v>
       </c>
@@ -43974,7 +44055,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="8">
         <v>40884</v>
       </c>
@@ -44015,7 +44096,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="8">
         <v>40891</v>
       </c>
@@ -44056,7 +44137,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="8">
         <v>40898</v>
       </c>
@@ -44097,7 +44178,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="8">
         <v>40905</v>
       </c>
@@ -44138,7 +44219,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="8">
         <v>40912</v>
       </c>
@@ -44179,7 +44260,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="8">
         <v>40919</v>
       </c>
@@ -44220,7 +44301,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13">
       <c r="A32" s="8">
         <v>40926</v>
       </c>
@@ -44261,7 +44342,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13">
       <c r="A33" s="8">
         <v>40933</v>
       </c>
@@ -44302,7 +44383,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13">
       <c r="A34" s="8">
         <v>40940</v>
       </c>
@@ -44343,7 +44424,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13">
       <c r="A35" s="8">
         <v>40947</v>
       </c>
@@ -44384,7 +44465,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13">
       <c r="A36" s="8">
         <v>40954</v>
       </c>
@@ -44425,7 +44506,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13">
       <c r="A37" s="8">
         <v>40961</v>
       </c>
@@ -44466,7 +44547,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13">
       <c r="A38" s="8">
         <v>40968</v>
       </c>
@@ -44507,7 +44588,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13">
       <c r="A39" s="8">
         <v>40975</v>
       </c>
@@ -44548,7 +44629,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13">
       <c r="A40" s="8">
         <v>40982</v>
       </c>
@@ -44589,7 +44670,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13">
       <c r="A41" s="8">
         <v>40989</v>
       </c>
@@ -44630,7 +44711,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13">
       <c r="A42" s="8">
         <v>40996</v>
       </c>
@@ -44671,7 +44752,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13">
       <c r="A43" s="8">
         <v>41003</v>
       </c>
@@ -44712,7 +44793,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13">
       <c r="A44" s="8">
         <v>41010</v>
       </c>
@@ -44753,7 +44834,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13">
       <c r="A45" s="8">
         <v>41017</v>
       </c>
@@ -44794,7 +44875,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13">
       <c r="A46" s="8">
         <v>41024</v>
       </c>
@@ -44835,7 +44916,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13">
       <c r="A47" s="8">
         <v>41031</v>
       </c>
@@ -44876,7 +44957,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13">
       <c r="A48" s="8">
         <v>41038</v>
       </c>
@@ -44917,7 +44998,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13">
       <c r="A49" s="8">
         <v>41045</v>
       </c>
@@ -44958,7 +45039,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13">
       <c r="A50" s="8">
         <v>41052</v>
       </c>
@@ -44999,7 +45080,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13">
       <c r="A51" s="8">
         <v>41059</v>
       </c>
@@ -45040,7 +45121,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13">
       <c r="A52" s="8">
         <v>41066</v>
       </c>
@@ -45081,7 +45162,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13">
       <c r="A53" s="8">
         <v>41073</v>
       </c>
@@ -45122,7 +45203,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13">
       <c r="A54" s="8">
         <v>41080</v>
       </c>
@@ -45163,7 +45244,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13">
       <c r="A55" s="8">
         <v>41087</v>
       </c>
@@ -45204,7 +45285,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13">
       <c r="A56" s="8">
         <v>41094</v>
       </c>
@@ -45245,7 +45326,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13">
       <c r="A57" s="8">
         <v>41101</v>
       </c>
@@ -45286,7 +45367,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13">
       <c r="A58" s="8">
         <v>41108</v>
       </c>
@@ -45327,7 +45408,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13">
       <c r="A59" s="8">
         <v>41115</v>
       </c>
@@ -45368,7 +45449,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13">
       <c r="A60" s="8">
         <v>41122</v>
       </c>
@@ -45409,7 +45490,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13">
       <c r="A61" s="8">
         <v>41129</v>
       </c>
@@ -45450,7 +45531,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13">
       <c r="A62" s="8">
         <v>41136</v>
       </c>
@@ -45491,7 +45572,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13">
       <c r="A63" s="8">
         <v>41143</v>
       </c>
@@ -45532,7 +45613,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13">
       <c r="A64" s="8">
         <v>41150</v>
       </c>
@@ -45573,7 +45654,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13">
       <c r="A65" s="8">
         <v>41157</v>
       </c>
@@ -45614,7 +45695,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13">
       <c r="A66" s="8">
         <v>41164</v>
       </c>
@@ -45655,7 +45736,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13">
       <c r="A67" s="8">
         <v>41171</v>
       </c>
@@ -45696,7 +45777,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13">
       <c r="A68" s="8">
         <v>41178</v>
       </c>
@@ -45737,7 +45818,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13">
       <c r="A69" s="8">
         <v>41185</v>
       </c>
@@ -45778,7 +45859,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13">
       <c r="A70" s="8">
         <v>41192</v>
       </c>
@@ -45819,7 +45900,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13">
       <c r="A71" s="8">
         <v>41199</v>
       </c>
@@ -45860,7 +45941,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13">
       <c r="A72" s="8">
         <v>41206</v>
       </c>
@@ -45901,7 +45982,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13">
       <c r="A73" s="8">
         <v>41213</v>
       </c>
@@ -45942,7 +46023,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13">
       <c r="A74" s="8">
         <v>41220</v>
       </c>
@@ -45983,7 +46064,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13">
       <c r="A75" s="8">
         <v>41227</v>
       </c>
@@ -46024,7 +46105,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13">
       <c r="A76" s="8">
         <v>41234</v>
       </c>
@@ -46065,7 +46146,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13">
       <c r="A77" s="8">
         <v>41241</v>
       </c>
@@ -46106,7 +46187,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13">
       <c r="A78" s="8">
         <v>41248</v>
       </c>
@@ -46147,7 +46228,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13">
       <c r="A79" s="8">
         <v>41255</v>
       </c>
@@ -46188,7 +46269,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13">
       <c r="A80" s="8">
         <v>41262</v>
       </c>
@@ -46229,7 +46310,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13">
       <c r="A81" s="8">
         <v>41269</v>
       </c>
@@ -46270,7 +46351,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13">
       <c r="A82" s="8">
         <v>41276</v>
       </c>
@@ -46311,7 +46392,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13">
       <c r="A83" s="8">
         <v>41283</v>
       </c>
@@ -46352,7 +46433,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13">
       <c r="A84" s="8">
         <v>41290</v>
       </c>
@@ -46393,7 +46474,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13">
       <c r="A85" s="8">
         <v>41297</v>
       </c>
@@ -46434,7 +46515,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13">
       <c r="A86" s="8">
         <v>41304</v>
       </c>
@@ -46475,7 +46556,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13">
       <c r="A87" s="8">
         <v>41311</v>
       </c>
@@ -46516,7 +46597,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13">
       <c r="A88" s="8">
         <v>41318</v>
       </c>
@@ -46557,7 +46638,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13">
       <c r="A89" s="8">
         <v>41325</v>
       </c>
@@ -46598,7 +46679,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13">
       <c r="A90" s="8">
         <v>41332</v>
       </c>
@@ -46639,7 +46720,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13">
       <c r="A91" s="8">
         <v>41339</v>
       </c>
@@ -46680,7 +46761,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13">
       <c r="A92" s="8">
         <v>41346</v>
       </c>
@@ -46721,7 +46802,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13">
       <c r="A93" s="8">
         <v>41353</v>
       </c>
@@ -46762,7 +46843,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13">
       <c r="A94" s="8">
         <v>41360</v>
       </c>
@@ -46803,7 +46884,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13">
       <c r="A95" s="8">
         <v>41367</v>
       </c>
@@ -46844,7 +46925,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13">
       <c r="A96" s="8">
         <v>41374</v>
       </c>
@@ -46885,7 +46966,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13">
       <c r="A97" s="8">
         <v>41381</v>
       </c>
@@ -46926,7 +47007,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13">
       <c r="A98" s="8">
         <v>41388</v>
       </c>
@@ -46967,7 +47048,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13">
       <c r="A99" s="8">
         <v>41395</v>
       </c>
@@ -47008,7 +47089,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13">
       <c r="A100" s="8">
         <v>41402</v>
       </c>
@@ -47049,7 +47130,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13">
       <c r="A101" s="8">
         <v>41409</v>
       </c>
@@ -47090,7 +47171,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13">
       <c r="A102" s="8">
         <v>41416</v>
       </c>
@@ -47131,7 +47212,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13">
       <c r="A103" s="8">
         <v>41423</v>
       </c>
@@ -47172,7 +47253,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13">
       <c r="A104" s="8">
         <v>41430</v>
       </c>
@@ -47213,7 +47294,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13">
       <c r="A105" s="8">
         <v>41437</v>
       </c>
@@ -47254,7 +47335,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13">
       <c r="A106" s="8">
         <v>41444</v>
       </c>
@@ -47295,7 +47376,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13">
       <c r="A107" s="8">
         <v>41451</v>
       </c>
@@ -47336,7 +47417,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13">
       <c r="A108" s="8">
         <v>41458</v>
       </c>
@@ -47377,7 +47458,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13">
       <c r="A109" s="8">
         <v>41465</v>
       </c>
@@ -47418,7 +47499,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13">
       <c r="A110" s="8">
         <v>41472</v>
       </c>
@@ -47459,7 +47540,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13">
       <c r="A111" s="8">
         <v>41479</v>
       </c>
@@ -47500,7 +47581,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13">
       <c r="A112" s="8">
         <v>41486</v>
       </c>
@@ -47541,7 +47622,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13">
       <c r="A113" s="8">
         <v>41493</v>
       </c>
@@ -47582,7 +47663,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13">
       <c r="A114" s="8">
         <v>41500</v>
       </c>
@@ -47623,7 +47704,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13">
       <c r="A115" s="8">
         <v>41507</v>
       </c>
@@ -47664,7 +47745,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13">
       <c r="A116" s="8">
         <v>41514</v>
       </c>
@@ -47705,7 +47786,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13">
       <c r="A117" s="8">
         <v>41521</v>
       </c>
@@ -47746,7 +47827,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13">
       <c r="A118" s="8">
         <v>41528</v>
       </c>
@@ -47787,7 +47868,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13">
       <c r="A119" s="8">
         <v>41535</v>
       </c>
@@ -47828,7 +47909,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13">
       <c r="A120" s="8">
         <v>41542</v>
       </c>
@@ -47869,7 +47950,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13">
       <c r="A121" s="8">
         <v>41549</v>
       </c>
@@ -47910,7 +47991,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13">
       <c r="A122" s="8">
         <v>41556</v>
       </c>
@@ -47951,7 +48032,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13">
       <c r="A123" s="8">
         <v>41563</v>
       </c>
@@ -47992,7 +48073,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13">
       <c r="A124" s="8">
         <v>41570</v>
       </c>
@@ -48033,7 +48114,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13">
       <c r="A125" s="8">
         <v>41577</v>
       </c>
@@ -48074,7 +48155,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13">
       <c r="A126" s="8">
         <v>41584</v>
       </c>
@@ -48115,7 +48196,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13">
       <c r="A127" s="8">
         <v>41591</v>
       </c>
@@ -48156,7 +48237,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13">
       <c r="A128" s="8">
         <v>41598</v>
       </c>
@@ -48197,7 +48278,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13">
       <c r="A129" s="8">
         <v>41605</v>
       </c>
@@ -48238,7 +48319,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13">
       <c r="A130" s="8">
         <v>41612</v>
       </c>
@@ -48279,7 +48360,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13">
       <c r="A131" s="8">
         <v>41619</v>
       </c>
@@ -48320,7 +48401,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13">
       <c r="A132" s="8">
         <v>41626</v>
       </c>
@@ -48361,7 +48442,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13">
       <c r="A133" s="8">
         <v>41640</v>
       </c>
@@ -48402,7 +48483,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13">
       <c r="A134" s="8">
         <v>41647</v>
       </c>
@@ -48443,7 +48524,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13">
       <c r="A135" s="8">
         <v>41654</v>
       </c>
@@ -48484,7 +48565,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13">
       <c r="A136" s="8">
         <v>41661</v>
       </c>
@@ -48525,7 +48606,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13">
       <c r="A137" s="8">
         <v>41668</v>
       </c>
@@ -48566,7 +48647,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13">
       <c r="A138" s="8">
         <v>41675</v>
       </c>
@@ -48607,7 +48688,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13">
       <c r="A139" s="8">
         <v>41682</v>
       </c>
@@ -48648,7 +48729,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13">
       <c r="A140" s="8">
         <v>41689</v>
       </c>
@@ -48689,7 +48770,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13">
       <c r="A141" s="8">
         <v>41696</v>
       </c>
@@ -48730,7 +48811,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13">
       <c r="A142" s="8">
         <v>41703</v>
       </c>
@@ -48771,7 +48852,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13">
       <c r="A143" s="8">
         <v>41710</v>
       </c>
@@ -48812,7 +48893,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13">
       <c r="A144" s="8">
         <v>41717</v>
       </c>
@@ -48853,7 +48934,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13">
       <c r="A145" s="8">
         <v>41724</v>
       </c>
@@ -48894,7 +48975,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13">
       <c r="A146" s="8">
         <v>41731</v>
       </c>
@@ -48935,7 +49016,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13">
       <c r="A147" s="8">
         <v>41738</v>
       </c>
@@ -48976,7 +49057,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13">
       <c r="A148" s="8">
         <v>41745</v>
       </c>
@@ -49017,7 +49098,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13">
       <c r="A149" s="8">
         <v>41752</v>
       </c>
@@ -49058,7 +49139,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13">
       <c r="A150" s="8">
         <v>41759</v>
       </c>
@@ -49099,7 +49180,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13">
       <c r="A151" s="8">
         <v>41766</v>
       </c>
@@ -49140,7 +49221,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13">
       <c r="A152" s="8">
         <v>41773</v>
       </c>
@@ -49181,7 +49262,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13">
       <c r="A153" s="8">
         <v>41780</v>
       </c>
@@ -49222,7 +49303,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13">
       <c r="A154" s="8">
         <v>41787</v>
       </c>
@@ -49263,7 +49344,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13">
       <c r="A155" s="8">
         <v>41794</v>
       </c>
@@ -49304,7 +49385,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13">
       <c r="A156" s="8">
         <v>41801</v>
       </c>
@@ -49345,7 +49426,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13">
       <c r="A157" s="8">
         <v>41808</v>
       </c>
@@ -49386,7 +49467,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13">
       <c r="A158" s="8">
         <v>41815</v>
       </c>
@@ -49427,7 +49508,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13">
       <c r="A159" s="8">
         <v>41822</v>
       </c>
@@ -49468,7 +49549,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13">
       <c r="A160" s="8">
         <v>41829</v>
       </c>
@@ -49509,7 +49590,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13">
       <c r="A161" s="8">
         <v>41836</v>
       </c>
@@ -49550,7 +49631,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13">
       <c r="A162" s="8">
         <v>41843</v>
       </c>
@@ -49591,7 +49672,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13">
       <c r="A163" s="8">
         <v>41850</v>
       </c>
@@ -49632,7 +49713,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13">
       <c r="A164" s="8">
         <v>41857</v>
       </c>
@@ -49673,7 +49754,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13">
       <c r="A165" s="8">
         <v>41864</v>
       </c>
@@ -49714,7 +49795,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13">
       <c r="A166" s="8">
         <v>41871</v>
       </c>
@@ -49755,7 +49836,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13">
       <c r="A167" s="8">
         <v>41878</v>
       </c>
@@ -49796,7 +49877,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13">
       <c r="A168" s="8">
         <v>41885</v>
       </c>
@@ -49837,7 +49918,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13">
       <c r="A169" s="8">
         <v>41892</v>
       </c>
@@ -49878,7 +49959,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13">
       <c r="A170" s="8">
         <v>41899</v>
       </c>
@@ -49919,7 +50000,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13">
       <c r="A171" s="8">
         <v>41906</v>
       </c>
@@ -49960,7 +50041,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13">
       <c r="A172" s="8">
         <v>41913</v>
       </c>
@@ -50001,7 +50082,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13">
       <c r="A173" s="8">
         <v>41920</v>
       </c>
@@ -50042,7 +50123,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13">
       <c r="A174" s="8">
         <v>41927</v>
       </c>
@@ -50083,7 +50164,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13">
       <c r="A175" s="8">
         <v>41934</v>
       </c>
@@ -50124,7 +50205,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13">
       <c r="A176" s="8">
         <v>41941</v>
       </c>
@@ -50165,7 +50246,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13">
       <c r="A177" s="8">
         <v>41948</v>
       </c>
@@ -50206,7 +50287,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13">
       <c r="A178" s="8">
         <v>41955</v>
       </c>
@@ -50247,7 +50328,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13">
       <c r="A179" s="8">
         <v>41962</v>
       </c>
@@ -50288,7 +50369,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13">
       <c r="A180" s="8">
         <v>41969</v>
       </c>
@@ -50329,7 +50410,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13">
       <c r="A181" s="8">
         <v>41976</v>
       </c>
@@ -50370,7 +50451,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13">
       <c r="A182" s="8">
         <v>41983</v>
       </c>
@@ -50411,7 +50492,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13">
       <c r="A183" s="8">
         <v>41990</v>
       </c>
@@ -50452,7 +50533,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13">
       <c r="A184" s="8">
         <v>42011</v>
       </c>
@@ -50493,7 +50574,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13">
       <c r="A185" s="8">
         <v>42018</v>
       </c>
@@ -50534,7 +50615,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13">
       <c r="A186" s="8">
         <v>42025</v>
       </c>
@@ -50575,7 +50656,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13">
       <c r="A187" s="8">
         <v>42032</v>
       </c>
@@ -50616,7 +50697,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13">
       <c r="A188" s="8">
         <v>42039</v>
       </c>
@@ -50657,7 +50738,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13">
       <c r="A189" s="8">
         <v>42046</v>
       </c>
@@ -50698,7 +50779,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13">
       <c r="A190" s="8">
         <v>42053</v>
       </c>
@@ -50739,7 +50820,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13">
       <c r="A191" s="8">
         <v>42060</v>
       </c>
@@ -50780,7 +50861,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13">
       <c r="A192" s="8">
         <v>42067</v>
       </c>
@@ -50821,7 +50902,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13">
       <c r="A193" s="8">
         <v>42074</v>
       </c>
@@ -50862,7 +50943,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13">
       <c r="A194" s="8">
         <v>42081</v>
       </c>
@@ -50903,7 +50984,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13">
       <c r="A195" s="8">
         <v>42088</v>
       </c>
@@ -50944,7 +51025,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13">
       <c r="A196" s="8">
         <v>42095</v>
       </c>
@@ -50985,7 +51066,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13">
       <c r="A197" s="8">
         <v>42102</v>
       </c>
@@ -51026,7 +51107,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13">
       <c r="A198" s="8">
         <v>42109</v>
       </c>
@@ -51067,7 +51148,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13">
       <c r="A199" s="8">
         <v>42116</v>
       </c>
@@ -51108,7 +51189,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13">
       <c r="A200" s="8">
         <v>42123</v>
       </c>
@@ -51149,7 +51230,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13">
       <c r="A201" s="8">
         <v>42130</v>
       </c>
@@ -51190,7 +51271,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13">
       <c r="A202" s="8">
         <v>42137</v>
       </c>
@@ -51231,7 +51312,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13">
       <c r="A203" s="8">
         <v>42144</v>
       </c>
@@ -51272,7 +51353,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13">
       <c r="A204" s="8">
         <v>42151</v>
       </c>
@@ -51313,7 +51394,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13">
       <c r="A205" s="8">
         <v>42158</v>
       </c>
@@ -51354,7 +51435,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13">
       <c r="A206" s="8">
         <v>42165</v>
       </c>
@@ -51395,7 +51476,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13">
       <c r="A207" s="8">
         <v>42172</v>
       </c>
@@ -51436,7 +51517,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13">
       <c r="A208" s="8">
         <v>42179</v>
       </c>
@@ -51477,7 +51558,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13">
       <c r="A209" s="8">
         <v>42186</v>
       </c>
@@ -51518,7 +51599,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13">
       <c r="A210" s="8">
         <v>42193</v>
       </c>
@@ -51559,7 +51640,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13">
       <c r="A211" s="8">
         <v>42200</v>
       </c>
@@ -51600,7 +51681,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13">
       <c r="A212" s="8">
         <v>42207</v>
       </c>
@@ -51641,7 +51722,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13">
       <c r="A213" s="8">
         <v>42214</v>
       </c>
@@ -51682,7 +51763,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13">
       <c r="A214" s="8">
         <v>42221</v>
       </c>
@@ -51723,7 +51804,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13">
       <c r="A215" s="8">
         <v>42228</v>
       </c>
@@ -51764,7 +51845,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13">
       <c r="A216" s="8">
         <v>42235</v>
       </c>
@@ -51805,7 +51886,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13">
       <c r="A217" s="8">
         <v>42242</v>
       </c>
@@ -51846,7 +51927,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13">
       <c r="A218" s="8">
         <v>42249</v>
       </c>
@@ -51887,7 +51968,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13">
       <c r="A219" s="8">
         <v>42256</v>
       </c>
@@ -51928,7 +52009,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13">
       <c r="A220" s="8">
         <v>42263</v>
       </c>
@@ -51969,7 +52050,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13">
       <c r="A221" s="8">
         <v>42270</v>
       </c>
@@ -52010,7 +52091,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13">
       <c r="A222" s="8">
         <v>42277</v>
       </c>
@@ -52051,7 +52132,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13">
       <c r="A223" s="8">
         <v>42284</v>
       </c>
@@ -52092,7 +52173,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13">
       <c r="A224" s="8">
         <v>42291</v>
       </c>
@@ -52133,7 +52214,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:13">
       <c r="A225" s="8">
         <v>42298</v>
       </c>
@@ -52174,7 +52255,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:13">
       <c r="A226" s="8">
         <v>42305</v>
       </c>
@@ -52215,7 +52296,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:13">
       <c r="A227" s="8">
         <v>42312</v>
       </c>
@@ -52256,7 +52337,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:13">
       <c r="A228" s="8">
         <v>42319</v>
       </c>
@@ -52297,7 +52378,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:13">
       <c r="A229" s="8">
         <v>42326</v>
       </c>
@@ -52338,7 +52419,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:13">
       <c r="A230" s="8">
         <v>42333</v>
       </c>
@@ -52379,7 +52460,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:13">
       <c r="A231" s="8">
         <v>42340</v>
       </c>
@@ -52420,7 +52501,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:13">
       <c r="A232" s="8">
         <v>42347</v>
       </c>
@@ -52461,7 +52542,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:13">
       <c r="A233" s="8">
         <v>42354</v>
       </c>
@@ -52502,7 +52583,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:13">
       <c r="A234" s="8">
         <v>42361</v>
       </c>
@@ -52543,7 +52624,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:13">
       <c r="A235" s="8">
         <v>42368</v>
       </c>
@@ -52584,7 +52665,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:13">
       <c r="A236" s="8">
         <v>42375</v>
       </c>
@@ -52625,7 +52706,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:13">
       <c r="A237" s="8">
         <v>42382</v>
       </c>
@@ -52666,7 +52747,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:13">
       <c r="A238" s="8">
         <v>42389</v>
       </c>
@@ -52707,7 +52788,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:13">
       <c r="A239" s="8">
         <v>42396</v>
       </c>
@@ -52748,7 +52829,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:13">
       <c r="A240" s="8">
         <v>42403</v>
       </c>
@@ -52789,7 +52870,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:13">
       <c r="A241" s="8">
         <v>42410</v>
       </c>
@@ -52830,7 +52911,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:13">
       <c r="A242" s="8">
         <v>42417</v>
       </c>
@@ -52871,7 +52952,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:13">
       <c r="A243" s="8">
         <v>42424</v>
       </c>
@@ -52912,7 +52993,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:13">
       <c r="A244" s="8">
         <v>42431</v>
       </c>
@@ -52953,7 +53034,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:13">
       <c r="A245" s="8">
         <v>42438</v>
       </c>
@@ -52994,7 +53075,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:13">
       <c r="A246" s="8">
         <v>42445</v>
       </c>
@@ -53035,7 +53116,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:13">
       <c r="A247" s="8">
         <v>42452</v>
       </c>
@@ -53076,7 +53157,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:13">
       <c r="A248" s="8">
         <v>42459</v>
       </c>
@@ -53117,7 +53198,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:13">
       <c r="A249" s="8">
         <v>42466</v>
       </c>
@@ -53158,7 +53239,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:13">
       <c r="A250" s="8">
         <v>42473</v>
       </c>
@@ -53199,7 +53280,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:13">
       <c r="A251" s="8">
         <v>42480</v>
       </c>
@@ -53240,7 +53321,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:13">
       <c r="A252" s="8">
         <v>42487</v>
       </c>
@@ -53281,7 +53362,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:13">
       <c r="A253" s="8">
         <v>42494</v>
       </c>
@@ -53322,7 +53403,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:13">
       <c r="A254" s="8">
         <v>42501</v>
       </c>
@@ -53363,7 +53444,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:13">
       <c r="A255" s="8">
         <v>42508</v>
       </c>
@@ -53404,7 +53485,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:13">
       <c r="A256" s="8">
         <v>42515</v>
       </c>
@@ -53445,7 +53526,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:13">
       <c r="A257" s="8">
         <v>42522</v>
       </c>
@@ -53486,7 +53567,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:13">
       <c r="A258" s="8">
         <v>42529</v>
       </c>
@@ -53527,7 +53608,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:13">
       <c r="A259" s="8">
         <v>42536</v>
       </c>
@@ -53568,7 +53649,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13">
       <c r="A260" s="8">
         <v>42543</v>
       </c>
@@ -53609,7 +53690,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:13">
       <c r="A261" s="8">
         <v>42550</v>
       </c>
@@ -53650,7 +53731,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13">
       <c r="A262" s="8">
         <v>42557</v>
       </c>
@@ -53691,7 +53772,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:13">
       <c r="A263" s="8">
         <v>42564</v>
       </c>
@@ -53732,7 +53813,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13">
       <c r="A264" s="8">
         <v>42571</v>
       </c>
@@ -53773,7 +53854,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13">
       <c r="A265" s="8">
         <v>42578</v>
       </c>
@@ -53814,7 +53895,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13">
       <c r="A266" s="8">
         <v>42585</v>
       </c>
@@ -53855,7 +53936,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:13">
       <c r="A267" s="8">
         <v>42592</v>
       </c>
@@ -53896,7 +53977,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:13">
       <c r="A268" s="8">
         <v>42599</v>
       </c>
@@ -53937,7 +54018,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:13">
       <c r="A269" s="8">
         <v>42606</v>
       </c>
@@ -53978,7 +54059,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:13">
       <c r="A270" s="8">
         <v>42613</v>
       </c>
@@ -54019,7 +54100,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:13">
       <c r="A271" s="8">
         <v>42620</v>
       </c>
@@ -54060,7 +54141,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:13">
       <c r="A272" s="8">
         <v>42627</v>
       </c>
@@ -54101,7 +54182,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:13">
       <c r="A273" s="8">
         <v>42634</v>
       </c>
@@ -54142,7 +54223,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:13">
       <c r="A274" s="8">
         <v>42641</v>
       </c>
@@ -54183,7 +54264,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:13">
       <c r="A275" s="8">
         <v>42648</v>
       </c>
@@ -54224,7 +54305,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13">
       <c r="A276" s="8">
         <v>42655</v>
       </c>
@@ -54265,7 +54346,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:13">
       <c r="A277" s="8">
         <v>42662</v>
       </c>
@@ -54306,7 +54387,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:13">
       <c r="A278" s="8">
         <v>42669</v>
       </c>
@@ -54347,7 +54428,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:13">
       <c r="A279" s="8">
         <v>42676</v>
       </c>
@@ -54388,7 +54469,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:13">
       <c r="A280" s="8">
         <v>42683</v>
       </c>
@@ -54429,7 +54510,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:13">
       <c r="A281" s="8">
         <v>42690</v>
       </c>
@@ -54470,7 +54551,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:13">
       <c r="A282" s="8">
         <v>42697</v>
       </c>
@@ -54511,7 +54592,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:13">
       <c r="A283" s="8">
         <v>42704</v>
       </c>
@@ -54552,7 +54633,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:13">
       <c r="A284" s="8">
         <v>42711</v>
       </c>
@@ -54593,7 +54674,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:13">
       <c r="A285" s="8">
         <v>42718</v>
       </c>
@@ -54634,7 +54715,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:13">
       <c r="A286" s="8">
         <v>42725</v>
       </c>
@@ -54675,7 +54756,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:13">
       <c r="A287" s="8">
         <v>42732</v>
       </c>
@@ -54716,7 +54797,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:13">
       <c r="A288" s="8">
         <v>42739</v>
       </c>
@@ -54757,7 +54838,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:13">
       <c r="A289" s="8">
         <v>42746</v>
       </c>
@@ -54798,7 +54879,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:13">
       <c r="A290" s="8">
         <v>42753</v>
       </c>
@@ -54839,7 +54920,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:13">
       <c r="A291" s="8">
         <v>42760</v>
       </c>
@@ -54880,7 +54961,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:13">
       <c r="A292" s="8">
         <v>42767</v>
       </c>
@@ -54921,7 +55002,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:13">
       <c r="A293" s="8">
         <v>42774</v>
       </c>
@@ -54962,7 +55043,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:13">
       <c r="A294" s="8">
         <v>42781</v>
       </c>
@@ -55003,7 +55084,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:13">
       <c r="A295" s="8">
         <v>42788</v>
       </c>
@@ -55044,7 +55125,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:13">
       <c r="A296" s="8">
         <v>42795</v>
       </c>
@@ -55085,7 +55166,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:13">
       <c r="A297" s="8">
         <v>42802</v>
       </c>
@@ -55126,7 +55207,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:13">
       <c r="A298" s="8">
         <v>42809</v>
       </c>
@@ -55167,7 +55248,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:13">
       <c r="A299" s="8">
         <v>42816</v>
       </c>
@@ -55208,7 +55289,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:13">
       <c r="A300" s="8">
         <v>42823</v>
       </c>
@@ -55249,7 +55330,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:13">
       <c r="A301" s="8">
         <v>42830</v>
       </c>
@@ -55290,7 +55371,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:13">
       <c r="A302" s="8">
         <v>42837</v>
       </c>
@@ -55331,7 +55412,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:13">
       <c r="A303" s="8">
         <v>42844</v>
       </c>
@@ -55372,7 +55453,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:13">
       <c r="A304" s="8">
         <v>42851</v>
       </c>
@@ -55413,7 +55494,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:13">
       <c r="A305" s="8">
         <v>42858</v>
       </c>
@@ -55454,7 +55535,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:13">
       <c r="A306" s="8">
         <v>42865</v>
       </c>
@@ -55495,7 +55576,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:13">
       <c r="A307" s="8">
         <v>42872</v>
       </c>
@@ -55536,7 +55617,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:13">
       <c r="A308" s="8">
         <v>42879</v>
       </c>
@@ -55577,7 +55658,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:13">
       <c r="A309" s="8">
         <v>42886</v>
       </c>
@@ -55618,7 +55699,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:13">
       <c r="A310" s="8">
         <v>42893</v>
       </c>
@@ -55659,7 +55740,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:13">
       <c r="A311" s="8">
         <v>42900</v>
       </c>
@@ -55700,7 +55781,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:13">
       <c r="A312" s="8">
         <v>42907</v>
       </c>
@@ -55741,7 +55822,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:13">
       <c r="A313" s="8">
         <v>42914</v>
       </c>
@@ -55782,7 +55863,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:13">
       <c r="A314" s="8">
         <v>42921</v>
       </c>
@@ -55823,7 +55904,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:13">
       <c r="A315" s="8">
         <v>42928</v>
       </c>
@@ -55864,7 +55945,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:13">
       <c r="A316" s="8">
         <v>42935</v>
       </c>
@@ -55905,7 +55986,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:13">
       <c r="A317" s="8">
         <v>42942</v>
       </c>
@@ -55946,7 +56027,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:13">
       <c r="A318" s="8">
         <v>42949</v>
       </c>
@@ -55987,7 +56068,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:13">
       <c r="A319" s="8">
         <v>42956</v>
       </c>
@@ -56028,7 +56109,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:13">
       <c r="A320" s="8">
         <v>42963</v>
       </c>
@@ -56069,7 +56150,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:13">
       <c r="A321" s="8">
         <v>42970</v>
       </c>
@@ -56110,7 +56191,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:13">
       <c r="A322" s="8">
         <v>42977</v>
       </c>
@@ -56151,7 +56232,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:13">
       <c r="A323" s="8">
         <v>42984</v>
       </c>
@@ -56192,7 +56273,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13">
       <c r="A324" s="8">
         <v>42991</v>
       </c>
@@ -56233,7 +56314,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:13">
       <c r="A325" s="8">
         <v>42998</v>
       </c>
@@ -56274,7 +56355,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:13">
       <c r="A326" s="8">
         <v>43005</v>
       </c>
@@ -56315,7 +56396,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:13">
       <c r="A327" s="8">
         <v>43012</v>
       </c>
@@ -56356,7 +56437,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:13">
       <c r="A328" s="8">
         <v>43019</v>
       </c>
@@ -56397,7 +56478,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:13">
       <c r="A329" s="8">
         <v>43026</v>
       </c>
@@ -56438,7 +56519,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:13">
       <c r="A330" s="8">
         <v>43033</v>
       </c>
@@ -56479,7 +56560,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:13">
       <c r="A331" s="8">
         <v>43040</v>
       </c>
@@ -56520,7 +56601,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:13">
       <c r="A332" s="8">
         <v>43047</v>
       </c>
@@ -56561,7 +56642,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:13">
       <c r="A333" s="8">
         <v>43054</v>
       </c>
@@ -56602,7 +56683,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:13">
       <c r="A334" s="8">
         <v>43061</v>
       </c>
@@ -56643,7 +56724,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:13">
       <c r="A335" s="8">
         <v>43068</v>
       </c>
@@ -56684,7 +56765,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:13">
       <c r="A336" s="8">
         <v>43075</v>
       </c>
@@ -56725,7 +56806,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13">
       <c r="A337" s="8">
         <v>43082</v>
       </c>
@@ -56766,7 +56847,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:13">
       <c r="A338" s="8">
         <v>43089</v>
       </c>
@@ -56807,7 +56888,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13">
       <c r="A339" s="8">
         <v>43096</v>
       </c>
@@ -56848,7 +56929,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:13">
       <c r="A340" s="8">
         <v>43103</v>
       </c>
@@ -56889,7 +56970,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:13">
       <c r="A341" s="8">
         <v>43110</v>
       </c>
@@ -56930,7 +57011,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:13">
       <c r="A342" s="8">
         <v>43117</v>
       </c>
@@ -56971,7 +57052,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:13">
       <c r="A343" s="8">
         <v>43124</v>
       </c>
@@ -57012,7 +57093,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:13">
       <c r="A344" s="8">
         <v>43131</v>
       </c>
@@ -57053,7 +57134,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:13">
       <c r="A345" s="8">
         <v>43138</v>
       </c>
@@ -57094,7 +57175,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:13">
       <c r="A346" s="8">
         <v>43145</v>
       </c>
@@ -57135,7 +57216,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:13">
       <c r="A347" s="8">
         <v>43152</v>
       </c>
@@ -57176,7 +57257,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:13">
       <c r="A348" s="8">
         <v>43159</v>
       </c>
@@ -57217,7 +57298,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:13">
       <c r="A349" s="8">
         <v>43166</v>
       </c>
@@ -57258,7 +57339,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:13">
       <c r="A350" s="8">
         <v>43173</v>
       </c>
@@ -57299,7 +57380,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:13">
       <c r="A351" s="8">
         <v>43180</v>
       </c>
@@ -57340,7 +57421,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:13">
       <c r="A352" s="8">
         <v>43187</v>
       </c>
@@ -57381,7 +57462,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:13">
       <c r="A353" s="8">
         <v>43194</v>
       </c>
@@ -57422,7 +57503,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:13">
       <c r="A354" s="8">
         <v>43201</v>
       </c>
@@ -57463,7 +57544,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:13">
       <c r="A355" s="8">
         <v>43208</v>
       </c>
@@ -57504,7 +57585,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:13">
       <c r="A356" s="8">
         <v>43215</v>
       </c>
@@ -57545,7 +57626,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:13">
       <c r="A357" s="8">
         <v>43222</v>
       </c>
@@ -57586,7 +57667,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:13">
       <c r="A358" s="8">
         <v>43229</v>
       </c>
@@ -57627,7 +57708,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:13">
       <c r="A359" s="8">
         <v>43236</v>
       </c>
@@ -57668,7 +57749,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:13">
       <c r="A360" s="8">
         <v>43243</v>
       </c>
@@ -57709,7 +57790,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:13">
       <c r="A361" s="8">
         <v>43250</v>
       </c>
@@ -57750,7 +57831,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:13">
       <c r="A362" s="8">
         <v>43257</v>
       </c>
@@ -57791,7 +57872,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:13">
       <c r="A363" s="8">
         <v>43264</v>
       </c>
@@ -57832,7 +57913,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:13">
       <c r="A364" s="8">
         <v>43271</v>
       </c>
@@ -57873,7 +57954,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:13">
       <c r="A365" s="8">
         <v>43278</v>
       </c>
@@ -57914,7 +57995,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:13">
       <c r="A366" s="8">
         <v>43285</v>
       </c>
@@ -57955,7 +58036,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:13">
       <c r="A367" s="8">
         <v>43292</v>
       </c>
@@ -57996,7 +58077,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:13">
       <c r="A368" s="8">
         <v>43299</v>
       </c>
@@ -58037,7 +58118,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:13">
       <c r="A369" s="8">
         <v>43306</v>
       </c>
@@ -58078,7 +58159,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:13">
       <c r="A370" s="8">
         <v>43313</v>
       </c>
@@ -58119,7 +58200,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:13">
       <c r="A371" s="8">
         <v>43320</v>
       </c>
@@ -58160,7 +58241,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:13">
       <c r="A372" s="8">
         <v>43327</v>
       </c>
@@ -58201,7 +58282,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:13">
       <c r="A373" s="8">
         <v>43334</v>
       </c>
@@ -58242,7 +58323,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:13">
       <c r="A374" s="8">
         <v>43341</v>
       </c>
@@ -58283,7 +58364,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:13">
       <c r="A375" s="8">
         <v>43348</v>
       </c>
@@ -58324,7 +58405,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:13">
       <c r="A376" s="8">
         <v>43355</v>
       </c>
@@ -58365,7 +58446,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:13">
       <c r="A377" s="8">
         <v>43362</v>
       </c>
@@ -58406,7 +58487,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:13">
       <c r="A378" s="8">
         <v>43369</v>
       </c>
@@ -58447,7 +58528,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:13">
       <c r="A379" s="8">
         <v>43376</v>
       </c>
@@ -58488,7 +58569,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:13">
       <c r="A380" s="8">
         <v>43383</v>
       </c>
@@ -58529,7 +58610,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:13">
       <c r="A381" s="8">
         <v>43390</v>
       </c>
@@ -58570,7 +58651,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:13">
       <c r="A382" s="8">
         <v>43397</v>
       </c>
@@ -58611,7 +58692,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:13">
       <c r="A383" s="8">
         <v>43404</v>
       </c>
@@ -58652,7 +58733,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:13">
       <c r="A384" s="8">
         <v>43411</v>
       </c>
@@ -58693,7 +58774,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:13">
       <c r="A385" s="8">
         <v>43418</v>
       </c>
@@ -58734,7 +58815,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:13">
       <c r="A386" s="8">
         <v>43425</v>
       </c>
@@ -58775,7 +58856,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:13">
       <c r="A387" s="8">
         <v>43432</v>
       </c>
@@ -58816,7 +58897,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:13">
       <c r="A388" s="8">
         <v>43439</v>
       </c>
@@ -58857,7 +58938,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:13">
       <c r="A389" s="8">
         <v>43446</v>
       </c>
@@ -58898,7 +58979,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:13">
       <c r="A390" s="8">
         <v>43453</v>
       </c>
@@ -58939,7 +59020,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:13">
       <c r="A391" s="8">
         <v>43460</v>
       </c>
@@ -58980,7 +59061,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:13">
       <c r="A392" s="8">
         <v>43467</v>
       </c>
@@ -59021,7 +59102,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:13">
       <c r="A393" s="8">
         <v>43474</v>
       </c>
@@ -59062,7 +59143,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:13">
       <c r="A394" s="8">
         <v>43481</v>
       </c>
@@ -59103,7 +59184,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:13">
       <c r="A395" s="8">
         <v>43488</v>
       </c>
@@ -59144,7 +59225,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:13">
       <c r="A396" s="8">
         <v>43495</v>
       </c>
@@ -59185,7 +59266,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:13">
       <c r="A397" s="8">
         <v>43502</v>
       </c>
@@ -59226,7 +59307,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:13">
       <c r="A398" s="8">
         <v>43509</v>
       </c>
@@ -59267,7 +59348,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:13">
       <c r="A399" s="8">
         <v>43516</v>
       </c>
@@ -59308,7 +59389,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:13">
       <c r="A400" s="8">
         <v>43523</v>
       </c>
@@ -59349,7 +59430,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:13">
       <c r="A401" s="8">
         <v>43530</v>
       </c>
@@ -59390,7 +59471,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:13">
       <c r="A402" s="8">
         <v>43537</v>
       </c>
@@ -59431,7 +59512,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:13">
       <c r="A403" s="8">
         <v>43544</v>
       </c>
@@ -59472,7 +59553,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:13">
       <c r="A404" s="8">
         <v>43551</v>
       </c>
@@ -59513,7 +59594,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:13">
       <c r="A405" s="8">
         <v>43558</v>
       </c>
@@ -59554,7 +59635,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:13">
       <c r="A406" s="8">
         <v>43565</v>
       </c>
@@ -59595,7 +59676,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:13">
       <c r="A407" s="8">
         <v>43572</v>
       </c>
@@ -59636,7 +59717,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:13">
       <c r="A408" s="8">
         <v>43579</v>
       </c>
@@ -59677,7 +59758,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:13">
       <c r="A409" s="8">
         <v>43586</v>
       </c>
@@ -59718,7 +59799,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:13">
       <c r="A410" s="8">
         <v>43593</v>
       </c>
@@ -59759,7 +59840,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:13">
       <c r="A411" s="8">
         <v>43600</v>
       </c>
@@ -59800,7 +59881,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:13">
       <c r="A412" s="8">
         <v>43607</v>
       </c>
@@ -59841,7 +59922,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:13">
       <c r="A413" s="8">
         <v>43614</v>
       </c>
@@ -59882,7 +59963,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:13">
       <c r="A414" s="8">
         <v>43621</v>
       </c>
@@ -59923,7 +60004,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:13">
       <c r="A415" s="8">
         <v>43628</v>
       </c>
@@ -59964,7 +60045,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:13">
       <c r="A416" s="8">
         <v>43635</v>
       </c>
@@ -60005,7 +60086,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:13">
       <c r="A417" s="8">
         <v>43642</v>
       </c>
@@ -60046,7 +60127,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:13">
       <c r="A418" s="8">
         <v>43649</v>
       </c>
@@ -60087,7 +60168,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:13">
       <c r="A419" s="8">
         <v>43656</v>
       </c>
@@ -60128,7 +60209,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:13">
       <c r="A420" s="8">
         <v>43663</v>
       </c>
@@ -60169,7 +60250,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:13">
       <c r="A421" s="8">
         <v>43670</v>
       </c>
@@ -60210,7 +60291,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:13">
       <c r="A422" s="8">
         <v>43677</v>
       </c>
@@ -60251,7 +60332,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:13">
       <c r="A423" s="8">
         <v>43684</v>
       </c>
@@ -60292,7 +60373,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:13">
       <c r="A424" s="8">
         <v>43691</v>
       </c>
@@ -60333,7 +60414,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:13">
       <c r="A425" s="8">
         <v>43698</v>
       </c>
@@ -60374,7 +60455,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:13">
       <c r="A426" s="8">
         <v>43705</v>
       </c>
@@ -60415,7 +60496,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:13">
       <c r="A427" s="8">
         <v>43712</v>
       </c>
@@ -60456,7 +60537,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:13">
       <c r="A428" s="8">
         <v>43719</v>
       </c>
@@ -60497,7 +60578,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:13">
       <c r="A429" s="8">
         <v>43726</v>
       </c>
@@ -60538,7 +60619,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:13">
       <c r="A430" s="8">
         <v>43733</v>
       </c>
@@ -60579,7 +60660,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:13">
       <c r="A431" s="8">
         <v>43740</v>
       </c>
@@ -60620,7 +60701,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:13">
       <c r="A432" s="8">
         <v>43747</v>
       </c>
@@ -60661,7 +60742,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:13">
       <c r="A433" s="8">
         <v>43754</v>
       </c>
@@ -60702,7 +60783,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:13">
       <c r="A434" s="8">
         <v>43761</v>
       </c>
@@ -60743,7 +60824,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:13">
       <c r="A435" s="8">
         <v>43768</v>
       </c>
@@ -60784,7 +60865,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:13">
       <c r="A436" s="8">
         <v>43775</v>
       </c>
@@ -60825,7 +60906,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:13">
       <c r="A437" s="8">
         <v>43782</v>
       </c>
@@ -60866,7 +60947,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:13">
       <c r="A438" s="8">
         <v>43789</v>
       </c>
@@ -60907,7 +60988,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:13">
       <c r="A439" s="8">
         <v>43796</v>
       </c>
@@ -60948,7 +61029,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:13">
       <c r="A440" s="8">
         <v>43803</v>
       </c>
@@ -60989,7 +61070,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:13">
       <c r="A441" s="8">
         <v>43810</v>
       </c>
@@ -61030,7 +61111,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:13">
       <c r="A442" s="8">
         <v>43817</v>
       </c>
@@ -61071,7 +61152,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:13">
       <c r="A443" s="8">
         <v>43831</v>
       </c>
@@ -61112,7 +61193,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:13">
       <c r="A444" s="8">
         <v>43838</v>
       </c>
@@ -61153,7 +61234,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:13">
       <c r="A445" s="8">
         <v>43845</v>
       </c>
@@ -61194,7 +61275,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:13">
       <c r="A446" s="8">
         <v>43852</v>
       </c>
@@ -61235,7 +61316,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:13">
       <c r="A447" s="8">
         <v>43859</v>
       </c>
@@ -61276,7 +61357,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:13">
       <c r="A448" s="8">
         <v>43866</v>
       </c>
@@ -61317,7 +61398,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:13">
       <c r="A449" s="8">
         <v>43873</v>
       </c>
@@ -61358,7 +61439,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:13">
       <c r="A450" s="8">
         <v>43880</v>
       </c>
@@ -61399,7 +61480,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:13">
       <c r="A451" s="8">
         <v>43887</v>
       </c>
@@ -61440,7 +61521,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:13">
       <c r="A452" s="8">
         <v>43894</v>
       </c>
@@ -61481,7 +61562,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:13">
       <c r="A453" s="8">
         <v>43901</v>
       </c>
@@ -61522,7 +61603,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:13">
       <c r="A454" s="8">
         <v>43908</v>
       </c>
@@ -61563,7 +61644,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:13">
       <c r="A455" s="8">
         <v>43915</v>
       </c>
@@ -61604,7 +61685,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:13">
       <c r="A456" s="8">
         <v>43922</v>
       </c>
@@ -61645,7 +61726,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:13">
       <c r="A457" s="8">
         <v>43929</v>
       </c>
@@ -61686,7 +61767,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:13">
       <c r="A458" s="8">
         <v>43936</v>
       </c>
@@ -61727,7 +61808,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:13">
       <c r="A459" s="8">
         <v>43943</v>
       </c>
@@ -61768,7 +61849,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:13">
       <c r="A460" s="8">
         <v>43950</v>
       </c>
@@ -61809,7 +61890,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:13">
       <c r="A461" s="8">
         <v>43957</v>
       </c>
@@ -61850,7 +61931,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:13">
       <c r="A462" s="8">
         <v>43964</v>
       </c>
@@ -61891,7 +61972,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:13">
       <c r="A463" s="8">
         <v>43971</v>
       </c>
@@ -61932,7 +62013,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:13">
       <c r="A464" s="8">
         <v>43978</v>
       </c>
@@ -61973,7 +62054,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:13">
       <c r="A465" s="8">
         <v>43985</v>
       </c>
@@ -62014,7 +62095,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:13">
       <c r="A466" s="8">
         <v>43992</v>
       </c>
@@ -62055,7 +62136,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:13">
       <c r="A467" s="8">
         <v>43999</v>
       </c>
@@ -62096,7 +62177,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:13">
       <c r="A468" s="8">
         <v>44006</v>
       </c>
@@ -62137,7 +62218,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:13">
       <c r="A469" s="8">
         <v>44013</v>
       </c>
@@ -62178,7 +62259,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:13">
       <c r="A470" s="8">
         <v>44020</v>
       </c>
@@ -62219,7 +62300,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:13">
       <c r="A471" s="8">
         <v>44027</v>
       </c>
@@ -62260,7 +62341,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:13">
       <c r="A472" s="8">
         <v>44034</v>
       </c>
@@ -62301,7 +62382,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:13">
       <c r="A473" s="8">
         <v>44041</v>
       </c>
@@ -62342,7 +62423,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:13">
       <c r="A474" s="8">
         <v>44048</v>
       </c>
@@ -62383,7 +62464,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:13">
       <c r="A475" s="8">
         <v>44055</v>
       </c>
@@ -62424,7 +62505,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:13">
       <c r="A476" s="8">
         <v>44062</v>
       </c>
@@ -62465,7 +62546,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:13">
       <c r="A477" s="8">
         <v>44069</v>
       </c>
@@ -62506,7 +62587,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:13">
       <c r="A478" s="8">
         <v>44076</v>
       </c>
@@ -62547,7 +62628,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:13">
       <c r="A479" s="8">
         <v>44083</v>
       </c>
@@ -62588,7 +62669,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:13">
       <c r="A480" s="8">
         <v>44090</v>
       </c>
@@ -62629,7 +62710,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:13">
       <c r="A481" s="8">
         <v>44097</v>
       </c>
@@ -62670,7 +62751,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:13">
       <c r="A482" s="8">
         <v>44104</v>
       </c>
@@ -62711,7 +62792,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:13">
       <c r="A483" s="8">
         <v>44111</v>
       </c>
@@ -62752,7 +62833,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:13">
       <c r="A484" s="8">
         <v>44118</v>
       </c>
@@ -62793,7 +62874,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:13">
       <c r="A485" s="8">
         <v>44125</v>
       </c>
@@ -62834,7 +62915,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:13">
       <c r="A486" s="8">
         <v>44132</v>
       </c>
@@ -62875,7 +62956,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:13">
       <c r="A487" s="8">
         <v>44139</v>
       </c>
@@ -62916,7 +62997,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:13">
       <c r="A488" s="8">
         <v>44146</v>
       </c>
@@ -62957,7 +63038,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:13">
       <c r="A489" s="8">
         <v>44153</v>
       </c>
@@ -62998,7 +63079,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:13">
       <c r="A490" s="8">
         <v>44160</v>
       </c>
@@ -63039,7 +63120,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:13">
       <c r="A491" s="8">
         <v>44167</v>
       </c>
@@ -63080,7 +63161,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:13">
       <c r="A492" s="8">
         <v>44174</v>
       </c>
@@ -63121,7 +63202,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:13">
       <c r="A493" s="8">
         <v>44181</v>
       </c>
@@ -63162,7 +63243,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:13">
       <c r="A494" s="8">
         <v>44188</v>
       </c>
@@ -63203,7 +63284,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:13">
       <c r="A495" s="8">
         <v>44195</v>
       </c>
@@ -63244,7 +63325,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:13">
       <c r="A496" s="8">
         <v>44202</v>
       </c>
@@ -63285,7 +63366,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:13">
       <c r="A497" s="8">
         <v>44209</v>
       </c>
@@ -63326,7 +63407,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:13">
       <c r="A498" s="8">
         <v>44216</v>
       </c>
@@ -63367,7 +63448,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:13">
       <c r="A499" s="8">
         <v>44223</v>
       </c>
@@ -63408,7 +63489,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:13">
       <c r="A500" s="8">
         <v>44230</v>
       </c>
@@ -63449,7 +63530,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:13">
       <c r="A501" s="8">
         <v>44237</v>
       </c>
@@ -63490,7 +63571,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:13">
       <c r="A502" s="8">
         <v>44244</v>
       </c>
@@ -63531,7 +63612,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:13">
       <c r="A503" s="8">
         <v>44251</v>
       </c>
@@ -63572,7 +63653,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:13">
       <c r="A504" s="8">
         <v>44258</v>
       </c>
@@ -63613,7 +63694,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:13">
       <c r="A505" s="8">
         <v>44265</v>
       </c>
@@ -63654,7 +63735,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:13">
       <c r="A506" s="8">
         <v>44272</v>
       </c>
@@ -63695,7 +63776,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:13">
       <c r="A507" s="8">
         <v>44279</v>
       </c>
@@ -63736,7 +63817,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:13">
       <c r="A508" s="8">
         <v>44286</v>
       </c>
@@ -63777,7 +63858,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:13">
       <c r="A509" s="8">
         <v>44293</v>
       </c>
@@ -63818,7 +63899,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:13">
       <c r="A510" s="8">
         <v>44300</v>
       </c>
@@ -63859,7 +63940,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:13">
       <c r="A511" s="8">
         <v>44307</v>
       </c>
@@ -63900,7 +63981,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:13">
       <c r="A512" s="8">
         <v>44314</v>
       </c>
@@ -63941,7 +64022,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:13">
       <c r="A513" s="8">
         <v>44321</v>
       </c>
@@ -63982,7 +64063,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:13">
       <c r="A514" s="8">
         <v>44328</v>
       </c>
@@ -64023,7 +64104,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:13">
       <c r="A515" s="8">
         <v>44335</v>
       </c>
@@ -64064,7 +64145,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:13">
       <c r="A516" s="8">
         <v>44342</v>
       </c>
@@ -64105,7 +64186,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:13">
       <c r="A517" s="8">
         <v>44349</v>
       </c>
@@ -64146,7 +64227,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:13">
       <c r="A518" s="8">
         <v>44356</v>
       </c>
@@ -64187,7 +64268,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:13">
       <c r="A519" s="8">
         <v>44363</v>
       </c>
@@ -64228,7 +64309,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:13">
       <c r="A520" s="8">
         <v>44370</v>
       </c>
@@ -64269,7 +64350,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:13">
       <c r="A521" s="8">
         <v>44377</v>
       </c>
@@ -64310,7 +64391,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:13">
       <c r="A522" s="8">
         <v>44384</v>
       </c>
@@ -64351,7 +64432,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:13">
       <c r="A523" s="8">
         <v>44391</v>
       </c>
@@ -64392,7 +64473,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:13">
       <c r="A524" s="8">
         <v>44398</v>
       </c>
@@ -64433,7 +64514,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:13">
       <c r="A525" s="8">
         <v>44405</v>
       </c>
@@ -64474,7 +64555,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:13">
       <c r="A526" s="8">
         <v>44412</v>
       </c>
@@ -64515,7 +64596,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:13">
       <c r="A527" s="8">
         <v>44419</v>
       </c>
@@ -64556,7 +64637,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:13">
       <c r="A528" s="8">
         <v>44426</v>
       </c>
@@ -64597,7 +64678,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:13">
       <c r="A529" s="8">
         <v>44433</v>
       </c>
@@ -64638,7 +64719,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:13">
       <c r="A530" s="8">
         <v>44440</v>
       </c>
@@ -64679,7 +64760,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:13">
       <c r="A531" s="8">
         <v>44447</v>
       </c>
@@ -64720,7 +64801,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:13">
       <c r="A532" s="8">
         <v>44454</v>
       </c>
@@ -64761,7 +64842,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:13">
       <c r="A533" s="8">
         <v>44461</v>
       </c>
@@ -64802,7 +64883,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:13">
       <c r="A534" s="8">
         <v>44468</v>
       </c>
@@ -64843,7 +64924,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:13">
       <c r="A535" s="8">
         <v>44475</v>
       </c>
@@ -64884,7 +64965,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:13">
       <c r="A536" s="8">
         <v>44482</v>
       </c>
@@ -64925,7 +65006,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:13">
       <c r="A537" s="8">
         <v>44489</v>
       </c>
@@ -64966,7 +65047,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:13">
       <c r="A538" s="8">
         <v>44496</v>
       </c>
@@ -65007,7 +65088,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:13">
       <c r="A539" s="8">
         <v>44503</v>
       </c>
@@ -65048,7 +65129,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:13">
       <c r="A540" s="8">
         <v>44510</v>
       </c>
@@ -65089,7 +65170,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:13">
       <c r="A541" s="8">
         <v>44517</v>
       </c>
@@ -65130,7 +65211,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:13">
       <c r="A542" s="8">
         <v>44524</v>
       </c>
@@ -65171,7 +65252,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:13">
       <c r="A543" s="8">
         <v>44531</v>
       </c>
@@ -65212,7 +65293,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:13">
       <c r="A544" s="8">
         <v>44538</v>
       </c>
@@ -65253,7 +65334,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:13">
       <c r="A545" s="8">
         <v>44545</v>
       </c>
@@ -65294,7 +65375,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:13">
       <c r="A546" s="8">
         <v>44552</v>
       </c>
@@ -65335,7 +65416,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:13">
       <c r="A547" s="8">
         <v>44566</v>
       </c>
@@ -65376,7 +65457,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:13">
       <c r="A548" s="8">
         <v>44573</v>
       </c>
@@ -65417,7 +65498,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:13">
       <c r="A549" s="8">
         <v>44580</v>
       </c>
@@ -65458,7 +65539,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:13">
       <c r="A550" s="8">
         <v>44587</v>
       </c>
@@ -65499,7 +65580,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:13">
       <c r="A551" s="8">
         <v>44594</v>
       </c>
@@ -65540,7 +65621,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:13">
       <c r="A552" s="8">
         <v>44601</v>
       </c>
@@ -65581,7 +65662,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:13">
       <c r="A553" s="8">
         <v>44608</v>
       </c>
@@ -65622,7 +65703,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:13">
       <c r="A554" s="8">
         <v>44615</v>
       </c>
@@ -65663,7 +65744,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:13">
       <c r="A555" s="8">
         <v>44622</v>
       </c>
@@ -65704,7 +65785,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:13">
       <c r="A556" s="8">
         <v>44629</v>
       </c>
@@ -65745,7 +65826,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:13">
       <c r="A557" s="8">
         <v>44636</v>
       </c>
@@ -65786,7 +65867,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:13">
       <c r="A558" s="8">
         <v>44643</v>
       </c>
@@ -65827,7 +65908,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:13">
       <c r="A559" s="8">
         <v>44650</v>
       </c>
@@ -65868,7 +65949,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:13">
       <c r="A560" s="8">
         <v>44657</v>
       </c>
@@ -65909,7 +65990,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:13">
       <c r="A561" s="8">
         <v>44664</v>
       </c>
@@ -65950,7 +66031,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:13">
       <c r="A562" s="8">
         <v>44671</v>
       </c>
@@ -65991,7 +66072,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:13">
       <c r="A563" s="8">
         <v>44678</v>
       </c>
@@ -66032,7 +66113,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:13">
       <c r="A564" s="8">
         <v>44685</v>
       </c>
@@ -66073,7 +66154,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:13">
       <c r="A565" s="8">
         <v>44692</v>
       </c>
@@ -66114,7 +66195,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:13">
       <c r="A566" s="8">
         <v>44699</v>
       </c>
@@ -66155,7 +66236,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:13">
       <c r="A567" s="8">
         <v>44706</v>
       </c>
@@ -66196,7 +66277,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:13">
       <c r="A568" s="8">
         <v>44713</v>
       </c>
@@ -66237,7 +66318,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:13">
       <c r="A569" s="8">
         <v>44720</v>
       </c>
@@ -66278,7 +66359,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:13">
       <c r="A570" s="8">
         <v>44727</v>
       </c>
@@ -66319,7 +66400,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:13">
       <c r="A571" s="8">
         <v>44734</v>
       </c>
@@ -66360,7 +66441,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:13">
       <c r="A572" s="8">
         <v>44741</v>
       </c>
@@ -66401,7 +66482,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:13">
       <c r="A573" s="8">
         <v>44748</v>
       </c>
@@ -66442,7 +66523,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:13">
       <c r="A574" s="8">
         <v>44755</v>
       </c>
@@ -66483,7 +66564,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:13">
       <c r="A575" s="8">
         <v>44762</v>
       </c>
@@ -66524,7 +66605,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:13">
       <c r="A576" s="8">
         <v>44769</v>
       </c>
@@ -66565,7 +66646,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:13">
       <c r="A577" s="8">
         <v>44776</v>
       </c>
@@ -66606,7 +66687,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:13">
       <c r="A578" s="8">
         <v>44783</v>
       </c>
@@ -66647,7 +66728,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:13">
       <c r="A579" s="8">
         <v>44790</v>
       </c>
@@ -66688,7 +66769,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:13">
       <c r="A580" s="8">
         <v>44797</v>
       </c>
@@ -66729,7 +66810,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:13">
       <c r="A581" s="8">
         <v>44804</v>
       </c>
@@ -66770,7 +66851,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:13">
       <c r="A582" s="8">
         <v>44811</v>
       </c>
@@ -66811,7 +66892,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:13">
       <c r="A583" s="8">
         <v>44818</v>
       </c>
@@ -66852,7 +66933,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:13">
       <c r="A584" s="8">
         <v>44825</v>
       </c>
@@ -66893,7 +66974,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:13">
       <c r="A585" s="8">
         <v>44832</v>
       </c>
@@ -66934,7 +67015,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:13">
       <c r="A586" s="8">
         <v>44839</v>
       </c>
@@ -66975,7 +67056,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:13">
       <c r="A587" s="8">
         <v>44846</v>
       </c>
@@ -67016,7 +67097,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:13">
       <c r="A588" s="8">
         <v>44853</v>
       </c>
@@ -67057,7 +67138,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:13">
       <c r="A589" s="8">
         <v>44860</v>
       </c>
@@ -67098,7 +67179,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:13">
       <c r="A590" s="8">
         <v>44867</v>
       </c>
@@ -67139,7 +67220,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:13">
       <c r="A591" s="8">
         <v>44874</v>
       </c>
@@ -67180,7 +67261,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:13">
       <c r="A592" s="8">
         <v>44881</v>
       </c>
@@ -67221,7 +67302,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:13">
       <c r="A593" s="8">
         <v>44888</v>
       </c>
@@ -67262,7 +67343,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:13">
       <c r="A594" s="8">
         <v>44895</v>
       </c>
@@ -67303,7 +67384,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:13">
       <c r="A595" s="8">
         <v>44902</v>
       </c>
@@ -67344,7 +67425,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:13">
       <c r="A596" s="8">
         <v>44909</v>
       </c>
@@ -67385,7 +67466,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:13">
       <c r="A597" s="8">
         <v>44916</v>
       </c>
@@ -67426,7 +67507,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:13">
       <c r="A598" s="8">
         <v>44930</v>
       </c>
@@ -67467,7 +67548,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:13">
       <c r="A599" s="8">
         <v>44937</v>
       </c>
@@ -67508,7 +67589,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:13">
       <c r="A600" s="8">
         <v>44944</v>
       </c>
@@ -67549,7 +67630,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:13">
       <c r="A601" s="8">
         <v>44951</v>
       </c>
@@ -67590,7 +67671,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:13">
       <c r="A602" s="8">
         <v>44958</v>
       </c>
@@ -67631,7 +67712,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:13">
       <c r="A603" s="8">
         <v>44965</v>
       </c>
@@ -67672,7 +67753,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:13">
       <c r="A604" s="8">
         <v>44972</v>
       </c>
@@ -67713,7 +67794,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:13">
       <c r="A605" s="8">
         <v>44979</v>
       </c>
@@ -67754,7 +67835,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:13">
       <c r="A606" s="8">
         <v>44986</v>
       </c>
@@ -67795,7 +67876,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:13">
       <c r="A607" s="8">
         <v>44993</v>
       </c>
@@ -67836,7 +67917,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:13">
       <c r="A608" s="8">
         <v>45000</v>
       </c>
@@ -67877,7 +67958,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:13">
       <c r="A609" s="8">
         <v>45007</v>
       </c>
@@ -67918,7 +67999,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:13">
       <c r="A610" s="8">
         <v>45014</v>
       </c>
@@ -67959,7 +68040,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:13">
       <c r="A611" s="8">
         <v>45021</v>
       </c>
@@ -68000,7 +68081,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:13">
       <c r="A612" s="8">
         <v>45028</v>
       </c>
@@ -68041,7 +68122,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:13">
       <c r="A613" s="8">
         <v>45035</v>
       </c>
@@ -68082,7 +68163,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:13">
       <c r="A614" s="8">
         <v>45042</v>
       </c>
@@ -68123,7 +68204,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:13">
       <c r="A615" s="8">
         <v>45049</v>
       </c>
@@ -68164,7 +68245,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:13">
       <c r="A616" s="8">
         <v>45056</v>
       </c>
@@ -68205,7 +68286,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:13">
       <c r="A617" s="8">
         <v>45063</v>
       </c>
@@ -68246,7 +68327,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:13">
       <c r="A618" s="8">
         <v>45070</v>
       </c>
@@ -68287,7 +68368,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:13">
       <c r="A619" s="8">
         <v>45077</v>
       </c>
@@ -68328,7 +68409,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:13">
       <c r="A620" s="8">
         <v>45084</v>
       </c>
@@ -68369,7 +68450,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:13">
       <c r="A621" s="8">
         <v>45091</v>
       </c>
@@ -68410,7 +68491,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:13">
       <c r="A622" s="8">
         <v>45098</v>
       </c>
@@ -68451,7 +68532,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:13">
       <c r="A623" s="8">
         <v>45105</v>
       </c>
@@ -68492,7 +68573,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:13">
       <c r="A624" s="8">
         <v>45112</v>
       </c>
@@ -68533,7 +68614,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:13">
       <c r="A625" s="8">
         <v>45119</v>
       </c>
@@ -68574,7 +68655,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:13">
       <c r="A626" s="8">
         <v>45126</v>
       </c>
@@ -68615,7 +68696,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:13">
       <c r="A627" s="8">
         <v>45133</v>
       </c>
@@ -68656,7 +68737,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:13">
       <c r="A628" s="8">
         <v>45140</v>
       </c>
@@ -68697,7 +68778,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:13">
       <c r="A629" s="8">
         <v>45147</v>
       </c>
@@ -68738,7 +68819,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:13">
       <c r="A630" s="8">
         <v>45154</v>
       </c>
@@ -68779,7 +68860,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:13">
       <c r="A631" s="8">
         <v>45161</v>
       </c>
@@ -68820,7 +68901,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:13">
       <c r="A632" s="8">
         <v>45168</v>
       </c>
@@ -68861,7 +68942,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:13">
       <c r="A633" s="8">
         <v>45175</v>
       </c>
@@ -68902,7 +68983,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:13">
       <c r="A634" s="8">
         <v>45182</v>
       </c>
@@ -68943,7 +69024,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:13">
       <c r="A635" s="8">
         <v>45189</v>
       </c>
@@ -68984,7 +69065,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:13">
       <c r="A636" s="8">
         <v>45196</v>
       </c>
@@ -69025,7 +69106,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:13">
       <c r="A637" s="8">
         <v>45203</v>
       </c>
@@ -69066,7 +69147,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:13">
       <c r="A638" s="8">
         <v>45210</v>
       </c>
@@ -69107,7 +69188,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:13">
       <c r="A639" s="8">
         <v>45217</v>
       </c>
@@ -69148,7 +69229,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:13">
       <c r="A640" s="8">
         <v>45224</v>
       </c>
@@ -69189,7 +69270,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:13">
       <c r="A641" s="8">
         <v>45231</v>
       </c>
@@ -69230,7 +69311,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:13">
       <c r="A642" s="8">
         <v>45238</v>
       </c>
@@ -69271,7 +69352,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:13">
       <c r="A643" s="8">
         <v>45245</v>
       </c>
@@ -69312,7 +69393,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:13">
       <c r="A644" s="8">
         <v>45252</v>
       </c>
@@ -69353,7 +69434,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:13">
       <c r="A645" s="8">
         <v>45259</v>
       </c>
@@ -69394,7 +69475,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:13">
       <c r="A646" s="8">
         <v>45266</v>
       </c>
@@ -69435,7 +69516,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:13">
       <c r="A647" s="8">
         <v>45273</v>
       </c>
@@ -69476,7 +69557,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:13">
       <c r="A648" s="8">
         <v>45280</v>
       </c>
@@ -69517,7 +69598,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:13">
       <c r="A649" s="8">
         <v>45294</v>
       </c>
@@ -69558,7 +69639,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:13">
       <c r="A650" s="8">
         <v>45301</v>
       </c>
@@ -69599,7 +69680,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:13">
       <c r="A651" s="8">
         <v>45308</v>
       </c>
@@ -69640,7 +69721,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:13">
       <c r="A652" s="8">
         <v>45315</v>
       </c>
@@ -69681,7 +69762,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:13">
       <c r="A653" s="8">
         <v>45322</v>
       </c>
@@ -69722,7 +69803,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:13">
       <c r="A654" s="8">
         <v>45329</v>
       </c>
@@ -69763,7 +69844,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:13">
       <c r="A655" s="8">
         <v>45336</v>
       </c>
@@ -69804,7 +69885,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:13">
       <c r="A656" s="8">
         <v>45343</v>
       </c>
@@ -69845,7 +69926,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:13">
       <c r="A657" s="8">
         <v>45350</v>
       </c>
@@ -69886,7 +69967,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:13">
       <c r="A658" s="8">
         <v>45357</v>
       </c>
@@ -69927,7 +70008,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:13">
       <c r="A659" s="8">
         <v>45364</v>
       </c>
@@ -69968,7 +70049,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:13">
       <c r="A660" s="8">
         <v>45371</v>
       </c>
@@ -70009,7 +70090,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:13">
       <c r="A661" s="8">
         <v>45378</v>
       </c>
@@ -70050,7 +70131,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:13">
       <c r="A662" s="8">
         <v>45385</v>
       </c>
@@ -70091,7 +70172,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:13">
       <c r="A663" s="8">
         <v>45392</v>
       </c>
@@ -70132,7 +70213,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:13">
       <c r="A664" s="8">
         <v>45399</v>
       </c>
@@ -70173,7 +70254,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:13">
       <c r="A665" s="8">
         <v>45406</v>
       </c>
@@ -70214,7 +70295,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:13">
       <c r="A666" s="8">
         <v>45413</v>
       </c>
@@ -70255,7 +70336,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:13">
       <c r="A667" s="8">
         <v>45420</v>
       </c>
@@ -70296,7 +70377,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:13">
       <c r="A668" s="8">
         <v>45427</v>
       </c>
@@ -70337,7 +70418,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:13">
       <c r="A669" s="8">
         <v>45434</v>
       </c>
@@ -70378,7 +70459,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:13">
       <c r="A670" s="8">
         <v>45441</v>
       </c>
@@ -70419,7 +70500,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:13">
       <c r="A671" s="8">
         <v>45448</v>
       </c>
@@ -70460,7 +70541,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:13">
       <c r="A672" s="8">
         <v>45455</v>
       </c>
@@ -70501,7 +70582,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:13">
       <c r="A673" s="8">
         <v>45462</v>
       </c>
@@ -70542,7 +70623,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:13">
       <c r="A674" s="8">
         <v>45469</v>
       </c>
@@ -70583,7 +70664,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:13">
       <c r="A675" s="8">
         <v>45476</v>
       </c>
@@ -70624,7 +70705,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:13">
       <c r="A676" s="8">
         <v>45483</v>
       </c>
@@ -70665,7 +70746,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:13">
       <c r="A677" s="8">
         <v>45490</v>
       </c>
@@ -70706,7 +70787,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:13">
       <c r="A678" s="8">
         <v>45497</v>
       </c>
@@ -70747,7 +70828,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:13">
       <c r="A679" s="8">
         <v>45504</v>
       </c>
@@ -70788,7 +70869,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:13">
       <c r="A680" s="8">
         <v>45511</v>
       </c>
@@ -70829,7 +70910,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:13">
       <c r="A681" s="8">
         <v>45518</v>
       </c>
@@ -70870,7 +70951,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:13">
       <c r="A682" s="8">
         <v>45525</v>
       </c>
@@ -70911,7 +70992,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:13">
       <c r="A683" s="8">
         <v>45532</v>
       </c>
@@ -70952,7 +71033,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:13">
       <c r="A684" s="8">
         <v>45539</v>
       </c>
@@ -70993,7 +71074,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:13">
       <c r="A685" s="8">
         <v>45546</v>
       </c>
@@ -71034,7 +71115,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:13">
       <c r="A686" s="8">
         <v>45553</v>
       </c>
@@ -71075,7 +71156,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:13">
       <c r="A687" s="8">
         <v>45560</v>
       </c>
@@ -71116,7 +71197,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:13">
       <c r="A688" s="8">
         <v>45567</v>
       </c>
@@ -71157,7 +71238,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:13">
       <c r="A689" s="8">
         <v>45574</v>
       </c>
@@ -71198,7 +71279,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:13">
       <c r="A690" s="8">
         <v>45581</v>
       </c>
@@ -71239,7 +71320,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:13">
       <c r="A691" s="8">
         <v>45588</v>
       </c>
@@ -71280,7 +71361,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:13">
       <c r="A692" s="8">
         <v>45595</v>
       </c>
@@ -71321,7 +71402,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:13">
       <c r="A693" s="8">
         <v>45602</v>
       </c>
@@ -71362,7 +71443,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:13">
       <c r="A694" s="8">
         <v>45609</v>
       </c>
@@ -71403,7 +71484,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:13">
       <c r="A695" s="8">
         <v>45616</v>
       </c>
@@ -71444,7 +71525,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:13">
       <c r="A696" s="8">
         <v>45623</v>
       </c>
@@ -71485,7 +71566,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:13">
       <c r="A697" s="8">
         <v>45630</v>
       </c>
@@ -71526,7 +71607,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:13">
       <c r="A698" s="8">
         <v>45637</v>
       </c>
@@ -71567,7 +71648,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:13">
       <c r="A699" s="8">
         <v>45644</v>
       </c>
@@ -71608,7 +71689,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:13">
       <c r="A700" s="8">
         <v>45658</v>
       </c>
@@ -71649,7 +71730,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:13">
       <c r="A701" s="8">
         <v>45665</v>
       </c>
@@ -71690,7 +71771,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:13">
       <c r="A702" s="8">
         <v>45672</v>
       </c>
@@ -71731,7 +71812,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:13">
       <c r="A703" s="8">
         <v>45679</v>
       </c>
@@ -71772,7 +71853,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:13">
       <c r="A704" s="8">
         <v>45686</v>
       </c>
@@ -71813,7 +71894,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:13">
       <c r="A705" s="8">
         <v>45693</v>
       </c>
@@ -71854,7 +71935,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:13">
       <c r="A706" s="8">
         <v>45700</v>
       </c>
@@ -71895,7 +71976,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:13">
       <c r="A707" s="8">
         <v>45707</v>
       </c>
@@ -71936,7 +72017,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:13">
       <c r="A708" s="8">
         <v>45714</v>
       </c>
@@ -71977,7 +72058,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:13">
       <c r="A709" s="8">
         <v>45721</v>
       </c>
@@ -72018,7 +72099,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:13">
       <c r="A710" s="8">
         <v>45728</v>
       </c>
@@ -72059,7 +72140,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:13">
       <c r="A711" s="8">
         <v>45735</v>
       </c>
@@ -72100,7 +72181,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:13">
       <c r="A712" s="8">
         <v>45742</v>
       </c>
@@ -72141,7 +72222,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:13">
       <c r="A713" s="8">
         <v>45749</v>
       </c>
@@ -72182,7 +72263,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:13">
       <c r="A714" s="8">
         <v>45756</v>
       </c>
@@ -72223,7 +72304,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:13">
       <c r="A715" s="8">
         <v>45763</v>
       </c>
@@ -72264,7 +72345,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:13">
       <c r="A716" s="8">
         <v>45770</v>
       </c>
@@ -72305,7 +72386,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:13">
       <c r="A717" s="8">
         <v>45777</v>
       </c>
@@ -72346,7 +72427,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:13">
       <c r="A718" s="8">
         <v>45784</v>
       </c>
@@ -72387,7 +72468,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:13">
       <c r="A719" s="8">
         <v>45791</v>
       </c>
@@ -72428,7 +72509,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:13">
       <c r="A720" s="8">
         <v>45798</v>
       </c>
@@ -72469,7 +72550,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:13">
       <c r="A721" s="8">
         <v>45805</v>
       </c>
@@ -72510,7 +72591,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:13">
       <c r="A722" s="8">
         <v>45812</v>
       </c>
@@ -72551,7 +72632,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:13">
       <c r="A723" s="8">
         <v>45819</v>
       </c>
@@ -72592,7 +72673,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:13">
       <c r="A724" s="8">
         <v>45826</v>
       </c>
@@ -72633,7 +72714,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:13">
       <c r="A725" s="8">
         <v>45833</v>
       </c>
@@ -72674,7 +72755,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:13">
       <c r="A726" s="8">
         <v>45840</v>
       </c>
@@ -72715,7 +72796,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:13">
       <c r="A727" s="8">
         <v>45847</v>
       </c>
@@ -72756,7 +72837,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:13">
       <c r="A728" s="8">
         <v>45854</v>
       </c>
@@ -72797,7 +72878,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:13">
       <c r="A729" s="8">
         <v>45861</v>
       </c>
@@ -72838,7 +72919,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:13">
       <c r="A730" s="8">
         <v>45868</v>
       </c>
@@ -72879,7 +72960,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:13">
       <c r="A731" s="8">
         <v>45875</v>
       </c>
@@ -72920,7 +73001,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:13">
       <c r="A732" s="8">
         <v>45882</v>
       </c>
@@ -72961,7 +73042,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:13">
       <c r="A733" s="8">
         <v>45889</v>
       </c>
@@ -73002,7 +73083,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:13">
       <c r="A734" s="8">
         <v>45896</v>
       </c>
@@ -73043,7 +73124,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:13">
       <c r="A735" s="8">
         <v>45903</v>
       </c>
@@ -73084,7 +73165,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:13">
       <c r="A736" s="8">
         <v>45910</v>
       </c>
@@ -73125,7 +73206,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:13">
       <c r="A737" s="8">
         <v>45917</v>
       </c>
@@ -73166,7 +73247,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:13">
       <c r="A738" s="8">
         <v>45924</v>
       </c>
@@ -73207,7 +73288,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:13">
       <c r="A739" s="8">
         <v>45931</v>
       </c>
@@ -73248,7 +73329,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:13">
       <c r="A740" s="8">
         <v>45938</v>
       </c>
@@ -73289,7 +73370,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:13">
       <c r="A741" s="8">
         <v>45945</v>
       </c>
@@ -73330,7 +73411,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:13">
       <c r="A742" s="8">
         <v>45952</v>
       </c>
@@ -73371,7 +73452,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:13">
       <c r="A743" s="8">
         <v>45959</v>
       </c>
@@ -73412,7 +73493,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:13">
       <c r="A744" s="8">
         <v>45966</v>
       </c>
@@ -73453,7 +73534,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:13">
       <c r="A745" s="8">
         <v>45973</v>
       </c>
@@ -73494,7 +73575,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:13">
       <c r="A746" s="8">
         <v>45980</v>
       </c>
@@ -73535,7 +73616,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:13">
       <c r="A747" s="8">
         <v>45987</v>
       </c>
@@ -73576,7 +73657,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:13">
       <c r="A748" s="8">
         <v>45994</v>
       </c>
@@ -73617,7 +73698,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:13">
       <c r="A749" s="8">
         <v>46001</v>
       </c>
@@ -73658,7 +73739,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:13">
       <c r="A750" s="8">
         <v>46008</v>
       </c>
@@ -73699,7 +73780,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:13">
       <c r="A751" s="8">
         <v>46015</v>
       </c>
@@ -73740,7 +73821,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:13">
       <c r="A752" s="8">
         <v>46022</v>
       </c>
@@ -73781,7 +73862,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:13">
       <c r="A753" s="8">
         <v>46029</v>
       </c>
@@ -73822,7 +73903,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:13">
       <c r="A754" s="8">
         <v>46036</v>
       </c>
@@ -73863,7 +73944,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:13">
       <c r="A755" s="8">
         <v>46043</v>
       </c>
@@ -73904,7 +73985,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:13">
       <c r="A756" s="8">
         <v>46050</v>
       </c>
@@ -73945,7 +74026,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:13">
       <c r="A757" s="8">
         <v>46057</v>
       </c>
@@ -73986,7 +74067,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:13">
       <c r="A758" s="8">
         <v>46064</v>
       </c>
@@ -74027,7 +74108,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:13">
       <c r="A759" s="8">
         <v>46071</v>
       </c>
@@ -74068,7 +74149,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:13">
       <c r="A760" s="8">
         <v>46078</v>
       </c>
@@ -74109,7 +74190,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:13">
       <c r="A761" s="8">
         <v>46085</v>
       </c>
@@ -74150,7 +74231,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:13">
       <c r="A762" s="8">
         <v>46092</v>
       </c>
@@ -74191,7 +74272,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:13">
       <c r="A763" s="8">
         <v>46099</v>
       </c>
@@ -74230,6 +74311,61 @@
       </c>
       <c r="M763" s="11">
         <v>1504</v>
+      </c>
+    </row>
+    <row r="764" spans="1:13">
+      <c r="A764" s="8">
+        <v>46106</v>
+      </c>
+      <c r="B764" s="8">
+        <v>46107</v>
+      </c>
+      <c r="C764" s="9">
+        <v>0.58333333333334103</v>
+      </c>
+      <c r="D764" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E764" s="10">
+        <v>2279.21</v>
+      </c>
+      <c r="F764" s="11">
+        <v>2552</v>
+      </c>
+      <c r="G764" s="11">
+        <v>3474</v>
+      </c>
+      <c r="H764" s="11">
+        <v>2686</v>
+      </c>
+      <c r="I764" s="11">
+        <v>3393</v>
+      </c>
+      <c r="J764" s="11">
+        <v>595</v>
+      </c>
+      <c r="K764" s="11">
+        <v>729</v>
+      </c>
+      <c r="L764" s="11">
+        <v>970</v>
+      </c>
+      <c r="M764" s="11">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="765" spans="1:13">
+      <c r="A765" s="8">
+        <v>46113</v>
+      </c>
+      <c r="B765" s="8">
+        <v>46114</v>
+      </c>
+      <c r="C765" s="9">
+        <v>0.58333333333334503</v>
+      </c>
+      <c r="D765" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -74242,7 +74378,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -74253,12 +74389,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -74277,7 +74413,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA698C4-29F5-41C4-8922-96F90B6C5D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F39A97-D10B-4CAD-8E2D-2C279FBD4703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4872,6 +4872,9 @@
                 <c:pt idx="762">
                   <c:v>2279.21</c:v>
                 </c:pt>
+                <c:pt idx="763">
+                  <c:v>2287.31</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9505,6 +9508,9 @@
                 <c:pt idx="762">
                   <c:v>2552</c:v>
                 </c:pt>
+                <c:pt idx="763">
+                  <c:v>2543</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -14138,6 +14144,9 @@
                 <c:pt idx="762">
                   <c:v>3474</c:v>
                 </c:pt>
+                <c:pt idx="763">
+                  <c:v>3529</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -18771,6 +18780,9 @@
                 <c:pt idx="762">
                   <c:v>2686</c:v>
                 </c:pt>
+                <c:pt idx="763">
+                  <c:v>2663</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -23404,6 +23416,9 @@
                 <c:pt idx="762">
                   <c:v>3393</c:v>
                 </c:pt>
+                <c:pt idx="763">
+                  <c:v>3434</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -28036,6 +28051,9 @@
                 </c:pt>
                 <c:pt idx="762">
                   <c:v>595</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>605</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -32672,6 +32690,9 @@
                 <c:pt idx="762">
                   <c:v>729</c:v>
                 </c:pt>
+                <c:pt idx="763">
+                  <c:v>742</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -37307,6 +37328,9 @@
                 <c:pt idx="762">
                   <c:v>970</c:v>
                 </c:pt>
+                <c:pt idx="763">
+                  <c:v>1001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -41941,6 +41965,9 @@
                 </c:pt>
                 <c:pt idx="762">
                   <c:v>1542</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>1579</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -74367,6 +74394,33 @@
       <c r="D765" s="8" t="s">
         <v>15</v>
       </c>
+      <c r="E765" s="10">
+        <v>2287.31</v>
+      </c>
+      <c r="F765" s="11">
+        <v>2543</v>
+      </c>
+      <c r="G765" s="11">
+        <v>3529</v>
+      </c>
+      <c r="H765" s="11">
+        <v>2663</v>
+      </c>
+      <c r="I765" s="11">
+        <v>3434</v>
+      </c>
+      <c r="J765" s="11">
+        <v>605</v>
+      </c>
+      <c r="K765" s="11">
+        <v>742</v>
+      </c>
+      <c r="L765" s="11">
+        <v>1001</v>
+      </c>
+      <c r="M765" s="11">
+        <v>1579</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2F9DC0-27FF-45EC-ADDB-967FD398CACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D06477D-2119-4890-AB10-87136DDC208A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -98,29 +98,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -129,7 +129,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -137,7 +137,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -176,7 +176,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -187,35 +187,35 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -233,7 +233,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2577,6 +2577,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4880,6 +4883,9 @@
                 </c:pt>
                 <c:pt idx="764">
                   <c:v>2308.7800000000002</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>2245.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7219,6 +7225,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9522,6 +9531,9 @@
                 </c:pt>
                 <c:pt idx="764">
                   <c:v>2308</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>2229</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11861,6 +11873,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14164,6 +14179,9 @@
                 </c:pt>
                 <c:pt idx="764">
                   <c:v>3420</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>3343</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16503,6 +16521,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18806,6 +18827,9 @@
                 </c:pt>
                 <c:pt idx="764">
                   <c:v>2910</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>2810</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21145,6 +21169,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23448,6 +23475,9 @@
                 </c:pt>
                 <c:pt idx="764">
                   <c:v>3671</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>3552</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25787,6 +25817,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28090,6 +28123,9 @@
                 </c:pt>
                 <c:pt idx="764">
                   <c:v>592</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>599</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30431,6 +30467,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -32733,6 +32772,9 @@
                   <c:v>742</c:v>
                 </c:pt>
                 <c:pt idx="764">
+                  <c:v>762</c:v>
+                </c:pt>
+                <c:pt idx="765">
                   <c:v>762</c:v>
                 </c:pt>
               </c:numCache>
@@ -35075,6 +35117,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37378,6 +37423,9 @@
                 </c:pt>
                 <c:pt idx="764">
                   <c:v>1063</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>1022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -39719,6 +39767,9 @@
                 <c:pt idx="764">
                   <c:v>46121</c:v>
                 </c:pt>
+                <c:pt idx="765">
+                  <c:v>46128</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42022,6 +42073,9 @@
                 </c:pt>
                 <c:pt idx="764">
                   <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>2030</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43099,19 +43153,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M766"/>
-  <sheetFormatPr defaultColWidth="7.59765625" defaultRowHeight="12.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M767"/>
+  <sheetFormatPr defaultColWidth="7.6328125" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8984375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="18.09765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.5" style="9" customWidth="1"/>
-    <col min="14" max="16384" width="7.59765625" style="9"/>
+    <col min="3" max="3" width="11.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.453125" style="9" customWidth="1"/>
+    <col min="14" max="16384" width="7.6328125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="6" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -43152,7 +43206,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13">
       <c r="A2" s="7">
         <v>40716</v>
       </c>
@@ -43193,7 +43247,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13">
       <c r="A3" s="7">
         <v>40723</v>
       </c>
@@ -43234,7 +43288,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13">
       <c r="A4" s="7">
         <v>40730</v>
       </c>
@@ -43275,7 +43329,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13">
       <c r="A5" s="7">
         <v>40737</v>
       </c>
@@ -43316,7 +43370,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13">
       <c r="A6" s="7">
         <v>40744</v>
       </c>
@@ -43357,7 +43411,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13">
       <c r="A7" s="7">
         <v>40751</v>
       </c>
@@ -43398,7 +43452,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13">
       <c r="A8" s="7">
         <v>40758</v>
       </c>
@@ -43439,7 +43493,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13">
       <c r="A9" s="7">
         <v>40765</v>
       </c>
@@ -43480,7 +43534,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13">
       <c r="A10" s="7">
         <v>40772</v>
       </c>
@@ -43521,7 +43575,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13">
       <c r="A11" s="7">
         <v>40779</v>
       </c>
@@ -43562,7 +43616,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13">
       <c r="A12" s="7">
         <v>40786</v>
       </c>
@@ -43603,7 +43657,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13">
       <c r="A13" s="7">
         <v>40793</v>
       </c>
@@ -43644,7 +43698,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13">
       <c r="A14" s="7">
         <v>40800</v>
       </c>
@@ -43685,7 +43739,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13">
       <c r="A15" s="7">
         <v>40807</v>
       </c>
@@ -43726,7 +43780,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13">
       <c r="A16" s="7">
         <v>40814</v>
       </c>
@@ -43767,7 +43821,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13">
       <c r="A17" s="7">
         <v>40821</v>
       </c>
@@ -43808,7 +43862,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13">
       <c r="A18" s="7">
         <v>40828</v>
       </c>
@@ -43849,7 +43903,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13">
       <c r="A19" s="7">
         <v>40835</v>
       </c>
@@ -43890,7 +43944,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13">
       <c r="A20" s="7">
         <v>40842</v>
       </c>
@@ -43931,7 +43985,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13">
       <c r="A21" s="7">
         <v>40849</v>
       </c>
@@ -43972,7 +44026,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13">
       <c r="A22" s="7">
         <v>40856</v>
       </c>
@@ -44013,7 +44067,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13">
       <c r="A23" s="7">
         <v>40863</v>
       </c>
@@ -44054,7 +44108,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13">
       <c r="A24" s="7">
         <v>40870</v>
       </c>
@@ -44095,7 +44149,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13">
       <c r="A25" s="7">
         <v>40877</v>
       </c>
@@ -44136,7 +44190,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13">
       <c r="A26" s="7">
         <v>40884</v>
       </c>
@@ -44177,7 +44231,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13">
       <c r="A27" s="7">
         <v>40891</v>
       </c>
@@ -44218,7 +44272,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13">
       <c r="A28" s="7">
         <v>40898</v>
       </c>
@@ -44259,7 +44313,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13">
       <c r="A29" s="7">
         <v>40905</v>
       </c>
@@ -44300,7 +44354,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13">
       <c r="A30" s="7">
         <v>40912</v>
       </c>
@@ -44341,7 +44395,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13">
       <c r="A31" s="7">
         <v>40919</v>
       </c>
@@ -44382,7 +44436,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13">
       <c r="A32" s="7">
         <v>40926</v>
       </c>
@@ -44423,7 +44477,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13">
       <c r="A33" s="7">
         <v>40933</v>
       </c>
@@ -44464,7 +44518,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13">
       <c r="A34" s="7">
         <v>40940</v>
       </c>
@@ -44505,7 +44559,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13">
       <c r="A35" s="7">
         <v>40947</v>
       </c>
@@ -44546,7 +44600,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13">
       <c r="A36" s="7">
         <v>40954</v>
       </c>
@@ -44587,7 +44641,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13">
       <c r="A37" s="7">
         <v>40961</v>
       </c>
@@ -44628,7 +44682,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13">
       <c r="A38" s="7">
         <v>40968</v>
       </c>
@@ -44669,7 +44723,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13">
       <c r="A39" s="7">
         <v>40975</v>
       </c>
@@ -44710,7 +44764,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13">
       <c r="A40" s="7">
         <v>40982</v>
       </c>
@@ -44751,7 +44805,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13">
       <c r="A41" s="7">
         <v>40989</v>
       </c>
@@ -44792,7 +44846,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13">
       <c r="A42" s="7">
         <v>40996</v>
       </c>
@@ -44833,7 +44887,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13">
       <c r="A43" s="7">
         <v>41003</v>
       </c>
@@ -44874,7 +44928,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13">
       <c r="A44" s="7">
         <v>41010</v>
       </c>
@@ -44915,7 +44969,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13">
       <c r="A45" s="7">
         <v>41017</v>
       </c>
@@ -44956,7 +45010,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13">
       <c r="A46" s="7">
         <v>41024</v>
       </c>
@@ -44997,7 +45051,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13">
       <c r="A47" s="7">
         <v>41031</v>
       </c>
@@ -45038,7 +45092,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13">
       <c r="A48" s="7">
         <v>41038</v>
       </c>
@@ -45079,7 +45133,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13">
       <c r="A49" s="7">
         <v>41045</v>
       </c>
@@ -45120,7 +45174,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13">
       <c r="A50" s="7">
         <v>41052</v>
       </c>
@@ -45161,7 +45215,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13">
       <c r="A51" s="7">
         <v>41059</v>
       </c>
@@ -45202,7 +45256,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13">
       <c r="A52" s="7">
         <v>41066</v>
       </c>
@@ -45243,7 +45297,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13">
       <c r="A53" s="7">
         <v>41073</v>
       </c>
@@ -45284,7 +45338,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13">
       <c r="A54" s="7">
         <v>41080</v>
       </c>
@@ -45325,7 +45379,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13">
       <c r="A55" s="7">
         <v>41087</v>
       </c>
@@ -45366,7 +45420,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13">
       <c r="A56" s="7">
         <v>41094</v>
       </c>
@@ -45407,7 +45461,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13">
       <c r="A57" s="7">
         <v>41101</v>
       </c>
@@ -45448,7 +45502,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13">
       <c r="A58" s="7">
         <v>41108</v>
       </c>
@@ -45489,7 +45543,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13">
       <c r="A59" s="7">
         <v>41115</v>
       </c>
@@ -45530,7 +45584,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13">
       <c r="A60" s="7">
         <v>41122</v>
       </c>
@@ -45571,7 +45625,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13">
       <c r="A61" s="7">
         <v>41129</v>
       </c>
@@ -45612,7 +45666,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13">
       <c r="A62" s="7">
         <v>41136</v>
       </c>
@@ -45653,7 +45707,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13">
       <c r="A63" s="7">
         <v>41143</v>
       </c>
@@ -45694,7 +45748,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13">
       <c r="A64" s="7">
         <v>41150</v>
       </c>
@@ -45735,7 +45789,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:13">
       <c r="A65" s="7">
         <v>41157</v>
       </c>
@@ -45776,7 +45830,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13">
       <c r="A66" s="7">
         <v>41164</v>
       </c>
@@ -45817,7 +45871,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13">
       <c r="A67" s="7">
         <v>41171</v>
       </c>
@@ -45858,7 +45912,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:13">
       <c r="A68" s="7">
         <v>41178</v>
       </c>
@@ -45899,7 +45953,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13">
       <c r="A69" s="7">
         <v>41185</v>
       </c>
@@ -45940,7 +45994,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:13">
       <c r="A70" s="7">
         <v>41192</v>
       </c>
@@ -45981,7 +46035,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:13">
       <c r="A71" s="7">
         <v>41199</v>
       </c>
@@ -46022,7 +46076,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13">
       <c r="A72" s="7">
         <v>41206</v>
       </c>
@@ -46063,7 +46117,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:13">
       <c r="A73" s="7">
         <v>41213</v>
       </c>
@@ -46104,7 +46158,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:13">
       <c r="A74" s="7">
         <v>41220</v>
       </c>
@@ -46145,7 +46199,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:13">
       <c r="A75" s="7">
         <v>41227</v>
       </c>
@@ -46186,7 +46240,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:13">
       <c r="A76" s="7">
         <v>41234</v>
       </c>
@@ -46227,7 +46281,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:13">
       <c r="A77" s="7">
         <v>41241</v>
       </c>
@@ -46268,7 +46322,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:13">
       <c r="A78" s="7">
         <v>41248</v>
       </c>
@@ -46309,7 +46363,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:13">
       <c r="A79" s="7">
         <v>41255</v>
       </c>
@@ -46350,7 +46404,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:13">
       <c r="A80" s="7">
         <v>41262</v>
       </c>
@@ -46391,7 +46445,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:13">
       <c r="A81" s="7">
         <v>41269</v>
       </c>
@@ -46432,7 +46486,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:13">
       <c r="A82" s="7">
         <v>41276</v>
       </c>
@@ -46473,7 +46527,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:13">
       <c r="A83" s="7">
         <v>41283</v>
       </c>
@@ -46514,7 +46568,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:13">
       <c r="A84" s="7">
         <v>41290</v>
       </c>
@@ -46555,7 +46609,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:13">
       <c r="A85" s="7">
         <v>41297</v>
       </c>
@@ -46596,7 +46650,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:13">
       <c r="A86" s="7">
         <v>41304</v>
       </c>
@@ -46637,7 +46691,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:13">
       <c r="A87" s="7">
         <v>41311</v>
       </c>
@@ -46678,7 +46732,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:13">
       <c r="A88" s="7">
         <v>41318</v>
       </c>
@@ -46719,7 +46773,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:13">
       <c r="A89" s="7">
         <v>41325</v>
       </c>
@@ -46760,7 +46814,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:13">
       <c r="A90" s="7">
         <v>41332</v>
       </c>
@@ -46801,7 +46855,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:13">
       <c r="A91" s="7">
         <v>41339</v>
       </c>
@@ -46842,7 +46896,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:13">
       <c r="A92" s="7">
         <v>41346</v>
       </c>
@@ -46883,7 +46937,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:13">
       <c r="A93" s="7">
         <v>41353</v>
       </c>
@@ -46924,7 +46978,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:13">
       <c r="A94" s="7">
         <v>41360</v>
       </c>
@@ -46965,7 +47019,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:13">
       <c r="A95" s="7">
         <v>41367</v>
       </c>
@@ -47006,7 +47060,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:13">
       <c r="A96" s="7">
         <v>41374</v>
       </c>
@@ -47047,7 +47101,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:13">
       <c r="A97" s="7">
         <v>41381</v>
       </c>
@@ -47088,7 +47142,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:13">
       <c r="A98" s="7">
         <v>41388</v>
       </c>
@@ -47129,7 +47183,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:13">
       <c r="A99" s="7">
         <v>41395</v>
       </c>
@@ -47170,7 +47224,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:13">
       <c r="A100" s="7">
         <v>41402</v>
       </c>
@@ -47211,7 +47265,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:13">
       <c r="A101" s="7">
         <v>41409</v>
       </c>
@@ -47252,7 +47306,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:13">
       <c r="A102" s="7">
         <v>41416</v>
       </c>
@@ -47293,7 +47347,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:13">
       <c r="A103" s="7">
         <v>41423</v>
       </c>
@@ -47334,7 +47388,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:13">
       <c r="A104" s="7">
         <v>41430</v>
       </c>
@@ -47375,7 +47429,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:13">
       <c r="A105" s="7">
         <v>41437</v>
       </c>
@@ -47416,7 +47470,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:13">
       <c r="A106" s="7">
         <v>41444</v>
       </c>
@@ -47457,7 +47511,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:13">
       <c r="A107" s="7">
         <v>41451</v>
       </c>
@@ -47498,7 +47552,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:13">
       <c r="A108" s="7">
         <v>41458</v>
       </c>
@@ -47539,7 +47593,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:13">
       <c r="A109" s="7">
         <v>41465</v>
       </c>
@@ -47580,7 +47634,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:13">
       <c r="A110" s="7">
         <v>41472</v>
       </c>
@@ -47621,7 +47675,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:13">
       <c r="A111" s="7">
         <v>41479</v>
       </c>
@@ -47662,7 +47716,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:13">
       <c r="A112" s="7">
         <v>41486</v>
       </c>
@@ -47703,7 +47757,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:13">
       <c r="A113" s="7">
         <v>41493</v>
       </c>
@@ -47744,7 +47798,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:13">
       <c r="A114" s="7">
         <v>41500</v>
       </c>
@@ -47785,7 +47839,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:13">
       <c r="A115" s="7">
         <v>41507</v>
       </c>
@@ -47826,7 +47880,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:13">
       <c r="A116" s="7">
         <v>41514</v>
       </c>
@@ -47867,7 +47921,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:13">
       <c r="A117" s="7">
         <v>41521</v>
       </c>
@@ -47908,7 +47962,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:13">
       <c r="A118" s="7">
         <v>41528</v>
       </c>
@@ -47949,7 +48003,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:13">
       <c r="A119" s="7">
         <v>41535</v>
       </c>
@@ -47990,7 +48044,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:13">
       <c r="A120" s="7">
         <v>41542</v>
       </c>
@@ -48031,7 +48085,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:13">
       <c r="A121" s="7">
         <v>41549</v>
       </c>
@@ -48072,7 +48126,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:13">
       <c r="A122" s="7">
         <v>41556</v>
       </c>
@@ -48113,7 +48167,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:13">
       <c r="A123" s="7">
         <v>41563</v>
       </c>
@@ -48154,7 +48208,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:13">
       <c r="A124" s="7">
         <v>41570</v>
       </c>
@@ -48195,7 +48249,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:13">
       <c r="A125" s="7">
         <v>41577</v>
       </c>
@@ -48236,7 +48290,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:13">
       <c r="A126" s="7">
         <v>41584</v>
       </c>
@@ -48277,7 +48331,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:13">
       <c r="A127" s="7">
         <v>41591</v>
       </c>
@@ -48318,7 +48372,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:13">
       <c r="A128" s="7">
         <v>41598</v>
       </c>
@@ -48359,7 +48413,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:13">
       <c r="A129" s="7">
         <v>41605</v>
       </c>
@@ -48400,7 +48454,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:13">
       <c r="A130" s="7">
         <v>41612</v>
       </c>
@@ -48441,7 +48495,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:13">
       <c r="A131" s="7">
         <v>41619</v>
       </c>
@@ -48482,7 +48536,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:13">
       <c r="A132" s="7">
         <v>41626</v>
       </c>
@@ -48523,7 +48577,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:13">
       <c r="A133" s="7">
         <v>41640</v>
       </c>
@@ -48564,7 +48618,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:13">
       <c r="A134" s="7">
         <v>41647</v>
       </c>
@@ -48605,7 +48659,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:13">
       <c r="A135" s="7">
         <v>41654</v>
       </c>
@@ -48646,7 +48700,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:13">
       <c r="A136" s="7">
         <v>41661</v>
       </c>
@@ -48687,7 +48741,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:13">
       <c r="A137" s="7">
         <v>41668</v>
       </c>
@@ -48728,7 +48782,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:13">
       <c r="A138" s="7">
         <v>41675</v>
       </c>
@@ -48769,7 +48823,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:13">
       <c r="A139" s="7">
         <v>41682</v>
       </c>
@@ -48810,7 +48864,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:13">
       <c r="A140" s="7">
         <v>41689</v>
       </c>
@@ -48851,7 +48905,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:13">
       <c r="A141" s="7">
         <v>41696</v>
       </c>
@@ -48892,7 +48946,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:13">
       <c r="A142" s="7">
         <v>41703</v>
       </c>
@@ -48933,7 +48987,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:13">
       <c r="A143" s="7">
         <v>41710</v>
       </c>
@@ -48974,7 +49028,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:13">
       <c r="A144" s="7">
         <v>41717</v>
       </c>
@@ -49015,7 +49069,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:13">
       <c r="A145" s="7">
         <v>41724</v>
       </c>
@@ -49056,7 +49110,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:13">
       <c r="A146" s="7">
         <v>41731</v>
       </c>
@@ -49097,7 +49151,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:13">
       <c r="A147" s="7">
         <v>41738</v>
       </c>
@@ -49138,7 +49192,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:13">
       <c r="A148" s="7">
         <v>41745</v>
       </c>
@@ -49179,7 +49233,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:13">
       <c r="A149" s="7">
         <v>41752</v>
       </c>
@@ -49220,7 +49274,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:13">
       <c r="A150" s="7">
         <v>41759</v>
       </c>
@@ -49261,7 +49315,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:13">
       <c r="A151" s="7">
         <v>41766</v>
       </c>
@@ -49302,7 +49356,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:13">
       <c r="A152" s="7">
         <v>41773</v>
       </c>
@@ -49343,7 +49397,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:13">
       <c r="A153" s="7">
         <v>41780</v>
       </c>
@@ -49384,7 +49438,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:13">
       <c r="A154" s="7">
         <v>41787</v>
       </c>
@@ -49425,7 +49479,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:13">
       <c r="A155" s="7">
         <v>41794</v>
       </c>
@@ -49466,7 +49520,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:13">
       <c r="A156" s="7">
         <v>41801</v>
       </c>
@@ -49507,7 +49561,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:13">
       <c r="A157" s="7">
         <v>41808</v>
       </c>
@@ -49548,7 +49602,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:13">
       <c r="A158" s="7">
         <v>41815</v>
       </c>
@@ -49589,7 +49643,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:13">
       <c r="A159" s="7">
         <v>41822</v>
       </c>
@@ -49630,7 +49684,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:13">
       <c r="A160" s="7">
         <v>41829</v>
       </c>
@@ -49671,7 +49725,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:13">
       <c r="A161" s="7">
         <v>41836</v>
       </c>
@@ -49712,7 +49766,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:13">
       <c r="A162" s="7">
         <v>41843</v>
       </c>
@@ -49753,7 +49807,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:13">
       <c r="A163" s="7">
         <v>41850</v>
       </c>
@@ -49794,7 +49848,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:13">
       <c r="A164" s="7">
         <v>41857</v>
       </c>
@@ -49835,7 +49889,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:13">
       <c r="A165" s="7">
         <v>41864</v>
       </c>
@@ -49876,7 +49930,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:13">
       <c r="A166" s="7">
         <v>41871</v>
       </c>
@@ -49917,7 +49971,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:13">
       <c r="A167" s="7">
         <v>41878</v>
       </c>
@@ -49958,7 +50012,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:13">
       <c r="A168" s="7">
         <v>41885</v>
       </c>
@@ -49999,7 +50053,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:13">
       <c r="A169" s="7">
         <v>41892</v>
       </c>
@@ -50040,7 +50094,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:13">
       <c r="A170" s="7">
         <v>41899</v>
       </c>
@@ -50081,7 +50135,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:13">
       <c r="A171" s="7">
         <v>41906</v>
       </c>
@@ -50122,7 +50176,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:13">
       <c r="A172" s="7">
         <v>41913</v>
       </c>
@@ -50163,7 +50217,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:13">
       <c r="A173" s="7">
         <v>41920</v>
       </c>
@@ -50204,7 +50258,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:13">
       <c r="A174" s="7">
         <v>41927</v>
       </c>
@@ -50245,7 +50299,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:13">
       <c r="A175" s="7">
         <v>41934</v>
       </c>
@@ -50286,7 +50340,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:13">
       <c r="A176" s="7">
         <v>41941</v>
       </c>
@@ -50327,7 +50381,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:13">
       <c r="A177" s="7">
         <v>41948</v>
       </c>
@@ -50368,7 +50422,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:13">
       <c r="A178" s="7">
         <v>41955</v>
       </c>
@@ -50409,7 +50463,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:13">
       <c r="A179" s="7">
         <v>41962</v>
       </c>
@@ -50450,7 +50504,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:13">
       <c r="A180" s="7">
         <v>41969</v>
       </c>
@@ -50491,7 +50545,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:13">
       <c r="A181" s="7">
         <v>41976</v>
       </c>
@@ -50532,7 +50586,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:13">
       <c r="A182" s="7">
         <v>41983</v>
       </c>
@@ -50573,7 +50627,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:13">
       <c r="A183" s="7">
         <v>41990</v>
       </c>
@@ -50614,7 +50668,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:13">
       <c r="A184" s="7">
         <v>42011</v>
       </c>
@@ -50655,7 +50709,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:13">
       <c r="A185" s="7">
         <v>42018</v>
       </c>
@@ -50696,7 +50750,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:13">
       <c r="A186" s="7">
         <v>42025</v>
       </c>
@@ -50737,7 +50791,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:13">
       <c r="A187" s="7">
         <v>42032</v>
       </c>
@@ -50778,7 +50832,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:13">
       <c r="A188" s="7">
         <v>42039</v>
       </c>
@@ -50819,7 +50873,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:13">
       <c r="A189" s="7">
         <v>42046</v>
       </c>
@@ -50860,7 +50914,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:13">
       <c r="A190" s="7">
         <v>42053</v>
       </c>
@@ -50901,7 +50955,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:13">
       <c r="A191" s="7">
         <v>42060</v>
       </c>
@@ -50942,7 +50996,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:13">
       <c r="A192" s="7">
         <v>42067</v>
       </c>
@@ -50983,7 +51037,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:13">
       <c r="A193" s="7">
         <v>42074</v>
       </c>
@@ -51024,7 +51078,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:13">
       <c r="A194" s="7">
         <v>42081</v>
       </c>
@@ -51065,7 +51119,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:13">
       <c r="A195" s="7">
         <v>42088</v>
       </c>
@@ -51106,7 +51160,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:13">
       <c r="A196" s="7">
         <v>42095</v>
       </c>
@@ -51147,7 +51201,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:13">
       <c r="A197" s="7">
         <v>42102</v>
       </c>
@@ -51188,7 +51242,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:13">
       <c r="A198" s="7">
         <v>42109</v>
       </c>
@@ -51229,7 +51283,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:13">
       <c r="A199" s="7">
         <v>42116</v>
       </c>
@@ -51270,7 +51324,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:13">
       <c r="A200" s="7">
         <v>42123</v>
       </c>
@@ -51311,7 +51365,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:13">
       <c r="A201" s="7">
         <v>42130</v>
       </c>
@@ -51352,7 +51406,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:13">
       <c r="A202" s="7">
         <v>42137</v>
       </c>
@@ -51393,7 +51447,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:13">
       <c r="A203" s="7">
         <v>42144</v>
       </c>
@@ -51434,7 +51488,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:13">
       <c r="A204" s="7">
         <v>42151</v>
       </c>
@@ -51475,7 +51529,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:13">
       <c r="A205" s="7">
         <v>42158</v>
       </c>
@@ -51516,7 +51570,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:13">
       <c r="A206" s="7">
         <v>42165</v>
       </c>
@@ -51557,7 +51611,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:13">
       <c r="A207" s="7">
         <v>42172</v>
       </c>
@@ -51598,7 +51652,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:13">
       <c r="A208" s="7">
         <v>42179</v>
       </c>
@@ -51639,7 +51693,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:13">
       <c r="A209" s="7">
         <v>42186</v>
       </c>
@@ -51680,7 +51734,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:13">
       <c r="A210" s="7">
         <v>42193</v>
       </c>
@@ -51721,7 +51775,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:13">
       <c r="A211" s="7">
         <v>42200</v>
       </c>
@@ -51762,7 +51816,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:13">
       <c r="A212" s="7">
         <v>42207</v>
       </c>
@@ -51803,7 +51857,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:13">
       <c r="A213" s="7">
         <v>42214</v>
       </c>
@@ -51844,7 +51898,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:13">
       <c r="A214" s="7">
         <v>42221</v>
       </c>
@@ -51885,7 +51939,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:13">
       <c r="A215" s="7">
         <v>42228</v>
       </c>
@@ -51926,7 +51980,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:13">
       <c r="A216" s="7">
         <v>42235</v>
       </c>
@@ -51967,7 +52021,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:13">
       <c r="A217" s="7">
         <v>42242</v>
       </c>
@@ -52008,7 +52062,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:13">
       <c r="A218" s="7">
         <v>42249</v>
       </c>
@@ -52049,7 +52103,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:13">
       <c r="A219" s="7">
         <v>42256</v>
       </c>
@@ -52090,7 +52144,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:13">
       <c r="A220" s="7">
         <v>42263</v>
       </c>
@@ -52131,7 +52185,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:13">
       <c r="A221" s="7">
         <v>42270</v>
       </c>
@@ -52172,7 +52226,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:13">
       <c r="A222" s="7">
         <v>42277</v>
       </c>
@@ -52213,7 +52267,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:13">
       <c r="A223" s="7">
         <v>42284</v>
       </c>
@@ -52254,7 +52308,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:13">
       <c r="A224" s="7">
         <v>42291</v>
       </c>
@@ -52295,7 +52349,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:13">
       <c r="A225" s="7">
         <v>42298</v>
       </c>
@@ -52336,7 +52390,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:13">
       <c r="A226" s="7">
         <v>42305</v>
       </c>
@@ -52377,7 +52431,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:13">
       <c r="A227" s="7">
         <v>42312</v>
       </c>
@@ -52418,7 +52472,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:13">
       <c r="A228" s="7">
         <v>42319</v>
       </c>
@@ -52459,7 +52513,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:13">
       <c r="A229" s="7">
         <v>42326</v>
       </c>
@@ -52500,7 +52554,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:13">
       <c r="A230" s="7">
         <v>42333</v>
       </c>
@@ -52541,7 +52595,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:13">
       <c r="A231" s="7">
         <v>42340</v>
       </c>
@@ -52582,7 +52636,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:13">
       <c r="A232" s="7">
         <v>42347</v>
       </c>
@@ -52623,7 +52677,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:13">
       <c r="A233" s="7">
         <v>42354</v>
       </c>
@@ -52664,7 +52718,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:13">
       <c r="A234" s="7">
         <v>42361</v>
       </c>
@@ -52705,7 +52759,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:13">
       <c r="A235" s="7">
         <v>42368</v>
       </c>
@@ -52746,7 +52800,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:13">
       <c r="A236" s="7">
         <v>42375</v>
       </c>
@@ -52787,7 +52841,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:13">
       <c r="A237" s="7">
         <v>42382</v>
       </c>
@@ -52828,7 +52882,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:13">
       <c r="A238" s="7">
         <v>42389</v>
       </c>
@@ -52869,7 +52923,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:13">
       <c r="A239" s="7">
         <v>42396</v>
       </c>
@@ -52910,7 +52964,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:13">
       <c r="A240" s="7">
         <v>42403</v>
       </c>
@@ -52951,7 +53005,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:13">
       <c r="A241" s="7">
         <v>42410</v>
       </c>
@@ -52992,7 +53046,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:13">
       <c r="A242" s="7">
         <v>42417</v>
       </c>
@@ -53033,7 +53087,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:13">
       <c r="A243" s="7">
         <v>42424</v>
       </c>
@@ -53074,7 +53128,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:13">
       <c r="A244" s="7">
         <v>42431</v>
       </c>
@@ -53115,7 +53169,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:13">
       <c r="A245" s="7">
         <v>42438</v>
       </c>
@@ -53156,7 +53210,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:13">
       <c r="A246" s="7">
         <v>42445</v>
       </c>
@@ -53197,7 +53251,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:13">
       <c r="A247" s="7">
         <v>42452</v>
       </c>
@@ -53238,7 +53292,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:13">
       <c r="A248" s="7">
         <v>42459</v>
       </c>
@@ -53279,7 +53333,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:13">
       <c r="A249" s="7">
         <v>42466</v>
       </c>
@@ -53320,7 +53374,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:13">
       <c r="A250" s="7">
         <v>42473</v>
       </c>
@@ -53361,7 +53415,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:13">
       <c r="A251" s="7">
         <v>42480</v>
       </c>
@@ -53402,7 +53456,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:13">
       <c r="A252" s="7">
         <v>42487</v>
       </c>
@@ -53443,7 +53497,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:13">
       <c r="A253" s="7">
         <v>42494</v>
       </c>
@@ -53484,7 +53538,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:13">
       <c r="A254" s="7">
         <v>42501</v>
       </c>
@@ -53525,7 +53579,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:13">
       <c r="A255" s="7">
         <v>42508</v>
       </c>
@@ -53566,7 +53620,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:13">
       <c r="A256" s="7">
         <v>42515</v>
       </c>
@@ -53607,7 +53661,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:13">
       <c r="A257" s="7">
         <v>42522</v>
       </c>
@@ -53648,7 +53702,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:13">
       <c r="A258" s="7">
         <v>42529</v>
       </c>
@@ -53689,7 +53743,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:13">
       <c r="A259" s="7">
         <v>42536</v>
       </c>
@@ -53730,7 +53784,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:13">
       <c r="A260" s="7">
         <v>42543</v>
       </c>
@@ -53771,7 +53825,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:13">
       <c r="A261" s="7">
         <v>42550</v>
       </c>
@@ -53812,7 +53866,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:13">
       <c r="A262" s="7">
         <v>42557</v>
       </c>
@@ -53853,7 +53907,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:13">
       <c r="A263" s="7">
         <v>42564</v>
       </c>
@@ -53894,7 +53948,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:13">
       <c r="A264" s="7">
         <v>42571</v>
       </c>
@@ -53935,7 +53989,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:13">
       <c r="A265" s="7">
         <v>42578</v>
       </c>
@@ -53976,7 +54030,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:13">
       <c r="A266" s="7">
         <v>42585</v>
       </c>
@@ -54017,7 +54071,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:13">
       <c r="A267" s="7">
         <v>42592</v>
       </c>
@@ -54058,7 +54112,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:13">
       <c r="A268" s="7">
         <v>42599</v>
       </c>
@@ -54099,7 +54153,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:13">
       <c r="A269" s="7">
         <v>42606</v>
       </c>
@@ -54140,7 +54194,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:13">
       <c r="A270" s="7">
         <v>42613</v>
       </c>
@@ -54181,7 +54235,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:13">
       <c r="A271" s="7">
         <v>42620</v>
       </c>
@@ -54222,7 +54276,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:13">
       <c r="A272" s="7">
         <v>42627</v>
       </c>
@@ -54263,7 +54317,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:13">
       <c r="A273" s="7">
         <v>42634</v>
       </c>
@@ -54304,7 +54358,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:13">
       <c r="A274" s="7">
         <v>42641</v>
       </c>
@@ -54345,7 +54399,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:13">
       <c r="A275" s="7">
         <v>42648</v>
       </c>
@@ -54386,7 +54440,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:13">
       <c r="A276" s="7">
         <v>42655</v>
       </c>
@@ -54427,7 +54481,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:13">
       <c r="A277" s="7">
         <v>42662</v>
       </c>
@@ -54468,7 +54522,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:13">
       <c r="A278" s="7">
         <v>42669</v>
       </c>
@@ -54509,7 +54563,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:13">
       <c r="A279" s="7">
         <v>42676</v>
       </c>
@@ -54550,7 +54604,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:13">
       <c r="A280" s="7">
         <v>42683</v>
       </c>
@@ -54591,7 +54645,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:13">
       <c r="A281" s="7">
         <v>42690</v>
       </c>
@@ -54632,7 +54686,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:13">
       <c r="A282" s="7">
         <v>42697</v>
       </c>
@@ -54673,7 +54727,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:13">
       <c r="A283" s="7">
         <v>42704</v>
       </c>
@@ -54714,7 +54768,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:13">
       <c r="A284" s="7">
         <v>42711</v>
       </c>
@@ -54755,7 +54809,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:13">
       <c r="A285" s="7">
         <v>42718</v>
       </c>
@@ -54796,7 +54850,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:13">
       <c r="A286" s="7">
         <v>42725</v>
       </c>
@@ -54837,7 +54891,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:13">
       <c r="A287" s="7">
         <v>42732</v>
       </c>
@@ -54878,7 +54932,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:13">
       <c r="A288" s="7">
         <v>42739</v>
       </c>
@@ -54919,7 +54973,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:13">
       <c r="A289" s="7">
         <v>42746</v>
       </c>
@@ -54960,7 +55014,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:13">
       <c r="A290" s="7">
         <v>42753</v>
       </c>
@@ -55001,7 +55055,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:13">
       <c r="A291" s="7">
         <v>42760</v>
       </c>
@@ -55042,7 +55096,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:13">
       <c r="A292" s="7">
         <v>42767</v>
       </c>
@@ -55083,7 +55137,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:13">
       <c r="A293" s="7">
         <v>42774</v>
       </c>
@@ -55124,7 +55178,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:13">
       <c r="A294" s="7">
         <v>42781</v>
       </c>
@@ -55165,7 +55219,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:13">
       <c r="A295" s="7">
         <v>42788</v>
       </c>
@@ -55206,7 +55260,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:13">
       <c r="A296" s="7">
         <v>42795</v>
       </c>
@@ -55247,7 +55301,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:13">
       <c r="A297" s="7">
         <v>42802</v>
       </c>
@@ -55288,7 +55342,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:13">
       <c r="A298" s="7">
         <v>42809</v>
       </c>
@@ -55329,7 +55383,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:13">
       <c r="A299" s="7">
         <v>42816</v>
       </c>
@@ -55370,7 +55424,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:13">
       <c r="A300" s="7">
         <v>42823</v>
       </c>
@@ -55411,7 +55465,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:13">
       <c r="A301" s="7">
         <v>42830</v>
       </c>
@@ -55452,7 +55506,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:13">
       <c r="A302" s="7">
         <v>42837</v>
       </c>
@@ -55493,7 +55547,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:13">
       <c r="A303" s="7">
         <v>42844</v>
       </c>
@@ -55534,7 +55588,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:13">
       <c r="A304" s="7">
         <v>42851</v>
       </c>
@@ -55575,7 +55629,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:13">
       <c r="A305" s="7">
         <v>42858</v>
       </c>
@@ -55616,7 +55670,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:13">
       <c r="A306" s="7">
         <v>42865</v>
       </c>
@@ -55657,7 +55711,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:13">
       <c r="A307" s="7">
         <v>42872</v>
       </c>
@@ -55698,7 +55752,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:13">
       <c r="A308" s="7">
         <v>42879</v>
       </c>
@@ -55739,7 +55793,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:13">
       <c r="A309" s="7">
         <v>42886</v>
       </c>
@@ -55780,7 +55834,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:13">
       <c r="A310" s="7">
         <v>42893</v>
       </c>
@@ -55821,7 +55875,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:13">
       <c r="A311" s="7">
         <v>42900</v>
       </c>
@@ -55862,7 +55916,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:13">
       <c r="A312" s="7">
         <v>42907</v>
       </c>
@@ -55903,7 +55957,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:13">
       <c r="A313" s="7">
         <v>42914</v>
       </c>
@@ -55944,7 +55998,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:13">
       <c r="A314" s="7">
         <v>42921</v>
       </c>
@@ -55985,7 +56039,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:13">
       <c r="A315" s="7">
         <v>42928</v>
       </c>
@@ -56026,7 +56080,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:13">
       <c r="A316" s="7">
         <v>42935</v>
       </c>
@@ -56067,7 +56121,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:13">
       <c r="A317" s="7">
         <v>42942</v>
       </c>
@@ -56108,7 +56162,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:13">
       <c r="A318" s="7">
         <v>42949</v>
       </c>
@@ -56149,7 +56203,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:13">
       <c r="A319" s="7">
         <v>42956</v>
       </c>
@@ -56190,7 +56244,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:13">
       <c r="A320" s="7">
         <v>42963</v>
       </c>
@@ -56231,7 +56285,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:13">
       <c r="A321" s="7">
         <v>42970</v>
       </c>
@@ -56272,7 +56326,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:13">
       <c r="A322" s="7">
         <v>42977</v>
       </c>
@@ -56313,7 +56367,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:13">
       <c r="A323" s="7">
         <v>42984</v>
       </c>
@@ -56354,7 +56408,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:13">
       <c r="A324" s="7">
         <v>42991</v>
       </c>
@@ -56395,7 +56449,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:13">
       <c r="A325" s="7">
         <v>42998</v>
       </c>
@@ -56436,7 +56490,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:13">
       <c r="A326" s="7">
         <v>43005</v>
       </c>
@@ -56477,7 +56531,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:13">
       <c r="A327" s="7">
         <v>43012</v>
       </c>
@@ -56518,7 +56572,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:13">
       <c r="A328" s="7">
         <v>43019</v>
       </c>
@@ -56559,7 +56613,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:13">
       <c r="A329" s="7">
         <v>43026</v>
       </c>
@@ -56600,7 +56654,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:13">
       <c r="A330" s="7">
         <v>43033</v>
       </c>
@@ -56641,7 +56695,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:13">
       <c r="A331" s="7">
         <v>43040</v>
       </c>
@@ -56682,7 +56736,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:13">
       <c r="A332" s="7">
         <v>43047</v>
       </c>
@@ -56723,7 +56777,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:13">
       <c r="A333" s="7">
         <v>43054</v>
       </c>
@@ -56764,7 +56818,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:13">
       <c r="A334" s="7">
         <v>43061</v>
       </c>
@@ -56805,7 +56859,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:13">
       <c r="A335" s="7">
         <v>43068</v>
       </c>
@@ -56846,7 +56900,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:13">
       <c r="A336" s="7">
         <v>43075</v>
       </c>
@@ -56887,7 +56941,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:13">
       <c r="A337" s="7">
         <v>43082</v>
       </c>
@@ -56928,7 +56982,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:13">
       <c r="A338" s="7">
         <v>43089</v>
       </c>
@@ -56969,7 +57023,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:13">
       <c r="A339" s="7">
         <v>43096</v>
       </c>
@@ -57010,7 +57064,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:13">
       <c r="A340" s="7">
         <v>43103</v>
       </c>
@@ -57051,7 +57105,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:13">
       <c r="A341" s="7">
         <v>43110</v>
       </c>
@@ -57092,7 +57146,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:13">
       <c r="A342" s="7">
         <v>43117</v>
       </c>
@@ -57133,7 +57187,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:13">
       <c r="A343" s="7">
         <v>43124</v>
       </c>
@@ -57174,7 +57228,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:13">
       <c r="A344" s="7">
         <v>43131</v>
       </c>
@@ -57215,7 +57269,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:13">
       <c r="A345" s="7">
         <v>43138</v>
       </c>
@@ -57256,7 +57310,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:13">
       <c r="A346" s="7">
         <v>43145</v>
       </c>
@@ -57297,7 +57351,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:13">
       <c r="A347" s="7">
         <v>43152</v>
       </c>
@@ -57338,7 +57392,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:13">
       <c r="A348" s="7">
         <v>43159</v>
       </c>
@@ -57379,7 +57433,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:13">
       <c r="A349" s="7">
         <v>43166</v>
       </c>
@@ -57420,7 +57474,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:13">
       <c r="A350" s="7">
         <v>43173</v>
       </c>
@@ -57461,7 +57515,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:13">
       <c r="A351" s="7">
         <v>43180</v>
       </c>
@@ -57502,7 +57556,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:13">
       <c r="A352" s="7">
         <v>43187</v>
       </c>
@@ -57543,7 +57597,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:13">
       <c r="A353" s="7">
         <v>43194</v>
       </c>
@@ -57584,7 +57638,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:13">
       <c r="A354" s="7">
         <v>43201</v>
       </c>
@@ -57625,7 +57679,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:13">
       <c r="A355" s="7">
         <v>43208</v>
       </c>
@@ -57666,7 +57720,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:13">
       <c r="A356" s="7">
         <v>43215</v>
       </c>
@@ -57707,7 +57761,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:13">
       <c r="A357" s="7">
         <v>43222</v>
       </c>
@@ -57748,7 +57802,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:13">
       <c r="A358" s="7">
         <v>43229</v>
       </c>
@@ -57789,7 +57843,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:13">
       <c r="A359" s="7">
         <v>43236</v>
       </c>
@@ -57830,7 +57884,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:13">
       <c r="A360" s="7">
         <v>43243</v>
       </c>
@@ -57871,7 +57925,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:13">
       <c r="A361" s="7">
         <v>43250</v>
       </c>
@@ -57912,7 +57966,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:13">
       <c r="A362" s="7">
         <v>43257</v>
       </c>
@@ -57953,7 +58007,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:13">
       <c r="A363" s="7">
         <v>43264</v>
       </c>
@@ -57994,7 +58048,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:13">
       <c r="A364" s="7">
         <v>43271</v>
       </c>
@@ -58035,7 +58089,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:13">
       <c r="A365" s="7">
         <v>43278</v>
       </c>
@@ -58076,7 +58130,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:13">
       <c r="A366" s="7">
         <v>43285</v>
       </c>
@@ -58117,7 +58171,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:13">
       <c r="A367" s="7">
         <v>43292</v>
       </c>
@@ -58158,7 +58212,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:13">
       <c r="A368" s="7">
         <v>43299</v>
       </c>
@@ -58199,7 +58253,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:13">
       <c r="A369" s="7">
         <v>43306</v>
       </c>
@@ -58240,7 +58294,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:13">
       <c r="A370" s="7">
         <v>43313</v>
       </c>
@@ -58281,7 +58335,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:13">
       <c r="A371" s="7">
         <v>43320</v>
       </c>
@@ -58322,7 +58376,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:13">
       <c r="A372" s="7">
         <v>43327</v>
       </c>
@@ -58363,7 +58417,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:13">
       <c r="A373" s="7">
         <v>43334</v>
       </c>
@@ -58404,7 +58458,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:13">
       <c r="A374" s="7">
         <v>43341</v>
       </c>
@@ -58445,7 +58499,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:13">
       <c r="A375" s="7">
         <v>43348</v>
       </c>
@@ -58486,7 +58540,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:13">
       <c r="A376" s="7">
         <v>43355</v>
       </c>
@@ -58527,7 +58581,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:13">
       <c r="A377" s="7">
         <v>43362</v>
       </c>
@@ -58568,7 +58622,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:13">
       <c r="A378" s="7">
         <v>43369</v>
       </c>
@@ -58609,7 +58663,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:13">
       <c r="A379" s="7">
         <v>43376</v>
       </c>
@@ -58650,7 +58704,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:13">
       <c r="A380" s="7">
         <v>43383</v>
       </c>
@@ -58691,7 +58745,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:13">
       <c r="A381" s="7">
         <v>43390</v>
       </c>
@@ -58732,7 +58786,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:13">
       <c r="A382" s="7">
         <v>43397</v>
       </c>
@@ -58773,7 +58827,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:13">
       <c r="A383" s="7">
         <v>43404</v>
       </c>
@@ -58814,7 +58868,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:13">
       <c r="A384" s="7">
         <v>43411</v>
       </c>
@@ -58855,7 +58909,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:13">
       <c r="A385" s="7">
         <v>43418</v>
       </c>
@@ -58896,7 +58950,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:13">
       <c r="A386" s="7">
         <v>43425</v>
       </c>
@@ -58937,7 +58991,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:13">
       <c r="A387" s="7">
         <v>43432</v>
       </c>
@@ -58978,7 +59032,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:13">
       <c r="A388" s="7">
         <v>43439</v>
       </c>
@@ -59019,7 +59073,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:13">
       <c r="A389" s="7">
         <v>43446</v>
       </c>
@@ -59060,7 +59114,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:13">
       <c r="A390" s="7">
         <v>43453</v>
       </c>
@@ -59101,7 +59155,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:13">
       <c r="A391" s="7">
         <v>43460</v>
       </c>
@@ -59142,7 +59196,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:13">
       <c r="A392" s="7">
         <v>43467</v>
       </c>
@@ -59183,7 +59237,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:13">
       <c r="A393" s="7">
         <v>43474</v>
       </c>
@@ -59224,7 +59278,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:13">
       <c r="A394" s="7">
         <v>43481</v>
       </c>
@@ -59265,7 +59319,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:13">
       <c r="A395" s="7">
         <v>43488</v>
       </c>
@@ -59306,7 +59360,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:13">
       <c r="A396" s="7">
         <v>43495</v>
       </c>
@@ -59347,7 +59401,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:13">
       <c r="A397" s="7">
         <v>43502</v>
       </c>
@@ -59388,7 +59442,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:13">
       <c r="A398" s="7">
         <v>43509</v>
       </c>
@@ -59429,7 +59483,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:13">
       <c r="A399" s="7">
         <v>43516</v>
       </c>
@@ -59470,7 +59524,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:13">
       <c r="A400" s="7">
         <v>43523</v>
       </c>
@@ -59511,7 +59565,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:13">
       <c r="A401" s="7">
         <v>43530</v>
       </c>
@@ -59552,7 +59606,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:13">
       <c r="A402" s="7">
         <v>43537</v>
       </c>
@@ -59593,7 +59647,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:13">
       <c r="A403" s="7">
         <v>43544</v>
       </c>
@@ -59634,7 +59688,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:13">
       <c r="A404" s="7">
         <v>43551</v>
       </c>
@@ -59675,7 +59729,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:13">
       <c r="A405" s="7">
         <v>43558</v>
       </c>
@@ -59716,7 +59770,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:13">
       <c r="A406" s="7">
         <v>43565</v>
       </c>
@@ -59757,7 +59811,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:13">
       <c r="A407" s="7">
         <v>43572</v>
       </c>
@@ -59798,7 +59852,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:13">
       <c r="A408" s="7">
         <v>43579</v>
       </c>
@@ -59839,7 +59893,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:13">
       <c r="A409" s="7">
         <v>43586</v>
       </c>
@@ -59880,7 +59934,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:13">
       <c r="A410" s="7">
         <v>43593</v>
       </c>
@@ -59921,7 +59975,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:13">
       <c r="A411" s="7">
         <v>43600</v>
       </c>
@@ -59962,7 +60016,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:13">
       <c r="A412" s="7">
         <v>43607</v>
       </c>
@@ -60003,7 +60057,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:13">
       <c r="A413" s="7">
         <v>43614</v>
       </c>
@@ -60044,7 +60098,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:13">
       <c r="A414" s="7">
         <v>43621</v>
       </c>
@@ -60085,7 +60139,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:13">
       <c r="A415" s="7">
         <v>43628</v>
       </c>
@@ -60126,7 +60180,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:13">
       <c r="A416" s="7">
         <v>43635</v>
       </c>
@@ -60167,7 +60221,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:13">
       <c r="A417" s="7">
         <v>43642</v>
       </c>
@@ -60208,7 +60262,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:13">
       <c r="A418" s="7">
         <v>43649</v>
       </c>
@@ -60249,7 +60303,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:13">
       <c r="A419" s="7">
         <v>43656</v>
       </c>
@@ -60290,7 +60344,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:13">
       <c r="A420" s="7">
         <v>43663</v>
       </c>
@@ -60331,7 +60385,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:13">
       <c r="A421" s="7">
         <v>43670</v>
       </c>
@@ -60372,7 +60426,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:13">
       <c r="A422" s="7">
         <v>43677</v>
       </c>
@@ -60413,7 +60467,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:13">
       <c r="A423" s="7">
         <v>43684</v>
       </c>
@@ -60454,7 +60508,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:13">
       <c r="A424" s="7">
         <v>43691</v>
       </c>
@@ -60495,7 +60549,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:13">
       <c r="A425" s="7">
         <v>43698</v>
       </c>
@@ -60536,7 +60590,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:13">
       <c r="A426" s="7">
         <v>43705</v>
       </c>
@@ -60577,7 +60631,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:13">
       <c r="A427" s="7">
         <v>43712</v>
       </c>
@@ -60618,7 +60672,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:13">
       <c r="A428" s="7">
         <v>43719</v>
       </c>
@@ -60659,7 +60713,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:13">
       <c r="A429" s="7">
         <v>43726</v>
       </c>
@@ -60700,7 +60754,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:13">
       <c r="A430" s="7">
         <v>43733</v>
       </c>
@@ -60741,7 +60795,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:13">
       <c r="A431" s="7">
         <v>43740</v>
       </c>
@@ -60782,7 +60836,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:13">
       <c r="A432" s="7">
         <v>43747</v>
       </c>
@@ -60823,7 +60877,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:13">
       <c r="A433" s="7">
         <v>43754</v>
       </c>
@@ -60864,7 +60918,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:13">
       <c r="A434" s="7">
         <v>43761</v>
       </c>
@@ -60905,7 +60959,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:13">
       <c r="A435" s="7">
         <v>43768</v>
       </c>
@@ -60946,7 +61000,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:13">
       <c r="A436" s="7">
         <v>43775</v>
       </c>
@@ -60987,7 +61041,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:13">
       <c r="A437" s="7">
         <v>43782</v>
       </c>
@@ -61028,7 +61082,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:13">
       <c r="A438" s="7">
         <v>43789</v>
       </c>
@@ -61069,7 +61123,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:13">
       <c r="A439" s="7">
         <v>43796</v>
       </c>
@@ -61110,7 +61164,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:13">
       <c r="A440" s="7">
         <v>43803</v>
       </c>
@@ -61151,7 +61205,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:13">
       <c r="A441" s="7">
         <v>43810</v>
       </c>
@@ -61192,7 +61246,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:13">
       <c r="A442" s="7">
         <v>43817</v>
       </c>
@@ -61233,7 +61287,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:13">
       <c r="A443" s="7">
         <v>43831</v>
       </c>
@@ -61274,7 +61328,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:13">
       <c r="A444" s="7">
         <v>43838</v>
       </c>
@@ -61315,7 +61369,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:13">
       <c r="A445" s="7">
         <v>43845</v>
       </c>
@@ -61356,7 +61410,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:13">
       <c r="A446" s="7">
         <v>43852</v>
       </c>
@@ -61397,7 +61451,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:13">
       <c r="A447" s="7">
         <v>43859</v>
       </c>
@@ -61438,7 +61492,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:13">
       <c r="A448" s="7">
         <v>43866</v>
       </c>
@@ -61479,7 +61533,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:13">
       <c r="A449" s="7">
         <v>43873</v>
       </c>
@@ -61520,7 +61574,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:13">
       <c r="A450" s="7">
         <v>43880</v>
       </c>
@@ -61561,7 +61615,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:13">
       <c r="A451" s="7">
         <v>43887</v>
       </c>
@@ -61602,7 +61656,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:13">
       <c r="A452" s="7">
         <v>43894</v>
       </c>
@@ -61643,7 +61697,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:13">
       <c r="A453" s="7">
         <v>43901</v>
       </c>
@@ -61684,7 +61738,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:13">
       <c r="A454" s="7">
         <v>43908</v>
       </c>
@@ -61725,7 +61779,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:13">
       <c r="A455" s="7">
         <v>43915</v>
       </c>
@@ -61766,7 +61820,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:13">
       <c r="A456" s="7">
         <v>43922</v>
       </c>
@@ -61807,7 +61861,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:13">
       <c r="A457" s="7">
         <v>43929</v>
       </c>
@@ -61848,7 +61902,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:13">
       <c r="A458" s="7">
         <v>43936</v>
       </c>
@@ -61889,7 +61943,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:13">
       <c r="A459" s="7">
         <v>43943</v>
       </c>
@@ -61930,7 +61984,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:13">
       <c r="A460" s="7">
         <v>43950</v>
       </c>
@@ -61971,7 +62025,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:13">
       <c r="A461" s="7">
         <v>43957</v>
       </c>
@@ -62012,7 +62066,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:13">
       <c r="A462" s="7">
         <v>43964</v>
       </c>
@@ -62053,7 +62107,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:13">
       <c r="A463" s="7">
         <v>43971</v>
       </c>
@@ -62094,7 +62148,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:13">
       <c r="A464" s="7">
         <v>43978</v>
       </c>
@@ -62135,7 +62189,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:13">
       <c r="A465" s="7">
         <v>43985</v>
       </c>
@@ -62176,7 +62230,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:13">
       <c r="A466" s="7">
         <v>43992</v>
       </c>
@@ -62217,7 +62271,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:13">
       <c r="A467" s="7">
         <v>43999</v>
       </c>
@@ -62258,7 +62312,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:13">
       <c r="A468" s="7">
         <v>44006</v>
       </c>
@@ -62299,7 +62353,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:13">
       <c r="A469" s="7">
         <v>44013</v>
       </c>
@@ -62340,7 +62394,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:13">
       <c r="A470" s="7">
         <v>44020</v>
       </c>
@@ -62381,7 +62435,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:13">
       <c r="A471" s="7">
         <v>44027</v>
       </c>
@@ -62422,7 +62476,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:13">
       <c r="A472" s="7">
         <v>44034</v>
       </c>
@@ -62463,7 +62517,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:13">
       <c r="A473" s="7">
         <v>44041</v>
       </c>
@@ -62504,7 +62558,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:13">
       <c r="A474" s="7">
         <v>44048</v>
       </c>
@@ -62545,7 +62599,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:13">
       <c r="A475" s="7">
         <v>44055</v>
       </c>
@@ -62586,7 +62640,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:13">
       <c r="A476" s="7">
         <v>44062</v>
       </c>
@@ -62627,7 +62681,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:13">
       <c r="A477" s="7">
         <v>44069</v>
       </c>
@@ -62668,7 +62722,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:13">
       <c r="A478" s="7">
         <v>44076</v>
       </c>
@@ -62709,7 +62763,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:13">
       <c r="A479" s="7">
         <v>44083</v>
       </c>
@@ -62750,7 +62804,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:13">
       <c r="A480" s="7">
         <v>44090</v>
       </c>
@@ -62791,7 +62845,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:13">
       <c r="A481" s="7">
         <v>44097</v>
       </c>
@@ -62832,7 +62886,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:13">
       <c r="A482" s="7">
         <v>44104</v>
       </c>
@@ -62873,7 +62927,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:13">
       <c r="A483" s="7">
         <v>44111</v>
       </c>
@@ -62914,7 +62968,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:13">
       <c r="A484" s="7">
         <v>44118</v>
       </c>
@@ -62955,7 +63009,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:13">
       <c r="A485" s="7">
         <v>44125</v>
       </c>
@@ -62996,7 +63050,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:13">
       <c r="A486" s="7">
         <v>44132</v>
       </c>
@@ -63037,7 +63091,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:13">
       <c r="A487" s="7">
         <v>44139</v>
       </c>
@@ -63078,7 +63132,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:13">
       <c r="A488" s="7">
         <v>44146</v>
       </c>
@@ -63119,7 +63173,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:13">
       <c r="A489" s="7">
         <v>44153</v>
       </c>
@@ -63160,7 +63214,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:13">
       <c r="A490" s="7">
         <v>44160</v>
       </c>
@@ -63201,7 +63255,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:13">
       <c r="A491" s="7">
         <v>44167</v>
       </c>
@@ -63242,7 +63296,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:13">
       <c r="A492" s="7">
         <v>44174</v>
       </c>
@@ -63283,7 +63337,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:13">
       <c r="A493" s="7">
         <v>44181</v>
       </c>
@@ -63324,7 +63378,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:13">
       <c r="A494" s="7">
         <v>44188</v>
       </c>
@@ -63365,7 +63419,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:13">
       <c r="A495" s="7">
         <v>44195</v>
       </c>
@@ -63406,7 +63460,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:13">
       <c r="A496" s="7">
         <v>44202</v>
       </c>
@@ -63447,7 +63501,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:13">
       <c r="A497" s="7">
         <v>44209</v>
       </c>
@@ -63488,7 +63542,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:13">
       <c r="A498" s="7">
         <v>44216</v>
       </c>
@@ -63529,7 +63583,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:13">
       <c r="A499" s="7">
         <v>44223</v>
       </c>
@@ -63570,7 +63624,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:13">
       <c r="A500" s="7">
         <v>44230</v>
       </c>
@@ -63611,7 +63665,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:13">
       <c r="A501" s="7">
         <v>44237</v>
       </c>
@@ -63652,7 +63706,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:13">
       <c r="A502" s="7">
         <v>44244</v>
       </c>
@@ -63693,7 +63747,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:13">
       <c r="A503" s="7">
         <v>44251</v>
       </c>
@@ -63734,7 +63788,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:13">
       <c r="A504" s="7">
         <v>44258</v>
       </c>
@@ -63775,7 +63829,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:13">
       <c r="A505" s="7">
         <v>44265</v>
       </c>
@@ -63816,7 +63870,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:13">
       <c r="A506" s="7">
         <v>44272</v>
       </c>
@@ -63857,7 +63911,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:13">
       <c r="A507" s="7">
         <v>44279</v>
       </c>
@@ -63898,7 +63952,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:13">
       <c r="A508" s="7">
         <v>44286</v>
       </c>
@@ -63939,7 +63993,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:13">
       <c r="A509" s="7">
         <v>44293</v>
       </c>
@@ -63980,7 +64034,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:13">
       <c r="A510" s="7">
         <v>44300</v>
       </c>
@@ -64021,7 +64075,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:13">
       <c r="A511" s="7">
         <v>44307</v>
       </c>
@@ -64062,7 +64116,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:13">
       <c r="A512" s="7">
         <v>44314</v>
       </c>
@@ -64103,7 +64157,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:13">
       <c r="A513" s="7">
         <v>44321</v>
       </c>
@@ -64144,7 +64198,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:13">
       <c r="A514" s="7">
         <v>44328</v>
       </c>
@@ -64185,7 +64239,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:13">
       <c r="A515" s="7">
         <v>44335</v>
       </c>
@@ -64226,7 +64280,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:13">
       <c r="A516" s="7">
         <v>44342</v>
       </c>
@@ -64267,7 +64321,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:13">
       <c r="A517" s="7">
         <v>44349</v>
       </c>
@@ -64308,7 +64362,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:13">
       <c r="A518" s="7">
         <v>44356</v>
       </c>
@@ -64349,7 +64403,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:13">
       <c r="A519" s="7">
         <v>44363</v>
       </c>
@@ -64390,7 +64444,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:13">
       <c r="A520" s="7">
         <v>44370</v>
       </c>
@@ -64431,7 +64485,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:13">
       <c r="A521" s="7">
         <v>44377</v>
       </c>
@@ -64472,7 +64526,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:13">
       <c r="A522" s="7">
         <v>44384</v>
       </c>
@@ -64513,7 +64567,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:13">
       <c r="A523" s="7">
         <v>44391</v>
       </c>
@@ -64554,7 +64608,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:13">
       <c r="A524" s="7">
         <v>44398</v>
       </c>
@@ -64595,7 +64649,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:13">
       <c r="A525" s="7">
         <v>44405</v>
       </c>
@@ -64636,7 +64690,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:13">
       <c r="A526" s="7">
         <v>44412</v>
       </c>
@@ -64677,7 +64731,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:13">
       <c r="A527" s="7">
         <v>44419</v>
       </c>
@@ -64718,7 +64772,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:13">
       <c r="A528" s="7">
         <v>44426</v>
       </c>
@@ -64759,7 +64813,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:13">
       <c r="A529" s="7">
         <v>44433</v>
       </c>
@@ -64800,7 +64854,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:13">
       <c r="A530" s="7">
         <v>44440</v>
       </c>
@@ -64841,7 +64895,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:13">
       <c r="A531" s="7">
         <v>44447</v>
       </c>
@@ -64882,7 +64936,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:13">
       <c r="A532" s="7">
         <v>44454</v>
       </c>
@@ -64923,7 +64977,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:13">
       <c r="A533" s="7">
         <v>44461</v>
       </c>
@@ -64964,7 +65018,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:13">
       <c r="A534" s="7">
         <v>44468</v>
       </c>
@@ -65005,7 +65059,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:13">
       <c r="A535" s="7">
         <v>44475</v>
       </c>
@@ -65046,7 +65100,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:13">
       <c r="A536" s="7">
         <v>44482</v>
       </c>
@@ -65087,7 +65141,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:13">
       <c r="A537" s="7">
         <v>44489</v>
       </c>
@@ -65128,7 +65182,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:13">
       <c r="A538" s="7">
         <v>44496</v>
       </c>
@@ -65169,7 +65223,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:13">
       <c r="A539" s="7">
         <v>44503</v>
       </c>
@@ -65210,7 +65264,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:13">
       <c r="A540" s="7">
         <v>44510</v>
       </c>
@@ -65251,7 +65305,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:13">
       <c r="A541" s="7">
         <v>44517</v>
       </c>
@@ -65292,7 +65346,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:13">
       <c r="A542" s="7">
         <v>44524</v>
       </c>
@@ -65333,7 +65387,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:13">
       <c r="A543" s="7">
         <v>44531</v>
       </c>
@@ -65374,7 +65428,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:13">
       <c r="A544" s="7">
         <v>44538</v>
       </c>
@@ -65415,7 +65469,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:13">
       <c r="A545" s="7">
         <v>44545</v>
       </c>
@@ -65456,7 +65510,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:13">
       <c r="A546" s="7">
         <v>44552</v>
       </c>
@@ -65497,7 +65551,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:13">
       <c r="A547" s="7">
         <v>44566</v>
       </c>
@@ -65538,7 +65592,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:13">
       <c r="A548" s="7">
         <v>44573</v>
       </c>
@@ -65579,7 +65633,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:13">
       <c r="A549" s="7">
         <v>44580</v>
       </c>
@@ -65620,7 +65674,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:13">
       <c r="A550" s="7">
         <v>44587</v>
       </c>
@@ -65661,7 +65715,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:13">
       <c r="A551" s="7">
         <v>44594</v>
       </c>
@@ -65702,7 +65756,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:13">
       <c r="A552" s="7">
         <v>44601</v>
       </c>
@@ -65743,7 +65797,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:13">
       <c r="A553" s="7">
         <v>44608</v>
       </c>
@@ -65784,7 +65838,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:13">
       <c r="A554" s="7">
         <v>44615</v>
       </c>
@@ -65825,7 +65879,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:13">
       <c r="A555" s="7">
         <v>44622</v>
       </c>
@@ -65866,7 +65920,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:13">
       <c r="A556" s="7">
         <v>44629</v>
       </c>
@@ -65907,7 +65961,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:13">
       <c r="A557" s="7">
         <v>44636</v>
       </c>
@@ -65948,7 +66002,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:13">
       <c r="A558" s="7">
         <v>44643</v>
       </c>
@@ -65989,7 +66043,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:13">
       <c r="A559" s="7">
         <v>44650</v>
       </c>
@@ -66030,7 +66084,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:13">
       <c r="A560" s="7">
         <v>44657</v>
       </c>
@@ -66071,7 +66125,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:13">
       <c r="A561" s="7">
         <v>44664</v>
       </c>
@@ -66112,7 +66166,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:13">
       <c r="A562" s="7">
         <v>44671</v>
       </c>
@@ -66153,7 +66207,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:13">
       <c r="A563" s="7">
         <v>44678</v>
       </c>
@@ -66194,7 +66248,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:13">
       <c r="A564" s="7">
         <v>44685</v>
       </c>
@@ -66235,7 +66289,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:13">
       <c r="A565" s="7">
         <v>44692</v>
       </c>
@@ -66276,7 +66330,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:13">
       <c r="A566" s="7">
         <v>44699</v>
       </c>
@@ -66317,7 +66371,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:13">
       <c r="A567" s="7">
         <v>44706</v>
       </c>
@@ -66358,7 +66412,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:13">
       <c r="A568" s="7">
         <v>44713</v>
       </c>
@@ -66399,7 +66453,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:13">
       <c r="A569" s="7">
         <v>44720</v>
       </c>
@@ -66440,7 +66494,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:13">
       <c r="A570" s="7">
         <v>44727</v>
       </c>
@@ -66481,7 +66535,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:13">
       <c r="A571" s="7">
         <v>44734</v>
       </c>
@@ -66522,7 +66576,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:13">
       <c r="A572" s="7">
         <v>44741</v>
       </c>
@@ -66563,7 +66617,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:13">
       <c r="A573" s="7">
         <v>44748</v>
       </c>
@@ -66604,7 +66658,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:13">
       <c r="A574" s="7">
         <v>44755</v>
       </c>
@@ -66645,7 +66699,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:13">
       <c r="A575" s="7">
         <v>44762</v>
       </c>
@@ -66686,7 +66740,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:13">
       <c r="A576" s="7">
         <v>44769</v>
       </c>
@@ -66727,7 +66781,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:13">
       <c r="A577" s="7">
         <v>44776</v>
       </c>
@@ -66768,7 +66822,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:13">
       <c r="A578" s="7">
         <v>44783</v>
       </c>
@@ -66809,7 +66863,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:13">
       <c r="A579" s="7">
         <v>44790</v>
       </c>
@@ -66850,7 +66904,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:13">
       <c r="A580" s="7">
         <v>44797</v>
       </c>
@@ -66891,7 +66945,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:13">
       <c r="A581" s="7">
         <v>44804</v>
       </c>
@@ -66932,7 +66986,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:13">
       <c r="A582" s="7">
         <v>44811</v>
       </c>
@@ -66973,7 +67027,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:13">
       <c r="A583" s="7">
         <v>44818</v>
       </c>
@@ -67014,7 +67068,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:13">
       <c r="A584" s="7">
         <v>44825</v>
       </c>
@@ -67055,7 +67109,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:13">
       <c r="A585" s="7">
         <v>44832</v>
       </c>
@@ -67096,7 +67150,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:13">
       <c r="A586" s="7">
         <v>44839</v>
       </c>
@@ -67137,7 +67191,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:13">
       <c r="A587" s="7">
         <v>44846</v>
       </c>
@@ -67178,7 +67232,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:13">
       <c r="A588" s="7">
         <v>44853</v>
       </c>
@@ -67219,7 +67273,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:13">
       <c r="A589" s="7">
         <v>44860</v>
       </c>
@@ -67260,7 +67314,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:13">
       <c r="A590" s="7">
         <v>44867</v>
       </c>
@@ -67301,7 +67355,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:13">
       <c r="A591" s="7">
         <v>44874</v>
       </c>
@@ -67342,7 +67396,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:13">
       <c r="A592" s="7">
         <v>44881</v>
       </c>
@@ -67383,7 +67437,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:13">
       <c r="A593" s="7">
         <v>44888</v>
       </c>
@@ -67424,7 +67478,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:13">
       <c r="A594" s="7">
         <v>44895</v>
       </c>
@@ -67465,7 +67519,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:13">
       <c r="A595" s="7">
         <v>44902</v>
       </c>
@@ -67506,7 +67560,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:13">
       <c r="A596" s="7">
         <v>44909</v>
       </c>
@@ -67547,7 +67601,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:13">
       <c r="A597" s="7">
         <v>44916</v>
       </c>
@@ -67588,7 +67642,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:13">
       <c r="A598" s="7">
         <v>44930</v>
       </c>
@@ -67629,7 +67683,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:13">
       <c r="A599" s="7">
         <v>44937</v>
       </c>
@@ -67670,7 +67724,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:13">
       <c r="A600" s="7">
         <v>44944</v>
       </c>
@@ -67711,7 +67765,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:13">
       <c r="A601" s="7">
         <v>44951</v>
       </c>
@@ -67752,7 +67806,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:13">
       <c r="A602" s="7">
         <v>44958</v>
       </c>
@@ -67793,7 +67847,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:13">
       <c r="A603" s="7">
         <v>44965</v>
       </c>
@@ -67834,7 +67888,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:13">
       <c r="A604" s="7">
         <v>44972</v>
       </c>
@@ -67875,7 +67929,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:13">
       <c r="A605" s="7">
         <v>44979</v>
       </c>
@@ -67916,7 +67970,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:13">
       <c r="A606" s="7">
         <v>44986</v>
       </c>
@@ -67957,7 +68011,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:13">
       <c r="A607" s="7">
         <v>44993</v>
       </c>
@@ -67998,7 +68052,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:13">
       <c r="A608" s="7">
         <v>45000</v>
       </c>
@@ -68039,7 +68093,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:13">
       <c r="A609" s="7">
         <v>45007</v>
       </c>
@@ -68080,7 +68134,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:13">
       <c r="A610" s="7">
         <v>45014</v>
       </c>
@@ -68121,7 +68175,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:13">
       <c r="A611" s="7">
         <v>45021</v>
       </c>
@@ -68162,7 +68216,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:13">
       <c r="A612" s="7">
         <v>45028</v>
       </c>
@@ -68203,7 +68257,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:13">
       <c r="A613" s="7">
         <v>45035</v>
       </c>
@@ -68244,7 +68298,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:13">
       <c r="A614" s="7">
         <v>45042</v>
       </c>
@@ -68285,7 +68339,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:13">
       <c r="A615" s="7">
         <v>45049</v>
       </c>
@@ -68326,7 +68380,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:13">
       <c r="A616" s="7">
         <v>45056</v>
       </c>
@@ -68367,7 +68421,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:13">
       <c r="A617" s="7">
         <v>45063</v>
       </c>
@@ -68408,7 +68462,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:13">
       <c r="A618" s="7">
         <v>45070</v>
       </c>
@@ -68449,7 +68503,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:13">
       <c r="A619" s="7">
         <v>45077</v>
       </c>
@@ -68490,7 +68544,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:13">
       <c r="A620" s="7">
         <v>45084</v>
       </c>
@@ -68531,7 +68585,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:13">
       <c r="A621" s="7">
         <v>45091</v>
       </c>
@@ -68572,7 +68626,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:13">
       <c r="A622" s="7">
         <v>45098</v>
       </c>
@@ -68613,7 +68667,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:13">
       <c r="A623" s="7">
         <v>45105</v>
       </c>
@@ -68654,7 +68708,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:13">
       <c r="A624" s="7">
         <v>45112</v>
       </c>
@@ -68695,7 +68749,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:13">
       <c r="A625" s="7">
         <v>45119</v>
       </c>
@@ -68736,7 +68790,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:13">
       <c r="A626" s="7">
         <v>45126</v>
       </c>
@@ -68777,7 +68831,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:13">
       <c r="A627" s="7">
         <v>45133</v>
       </c>
@@ -68818,7 +68872,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:13">
       <c r="A628" s="7">
         <v>45140</v>
       </c>
@@ -68859,7 +68913,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:13">
       <c r="A629" s="7">
         <v>45147</v>
       </c>
@@ -68900,7 +68954,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:13">
       <c r="A630" s="7">
         <v>45154</v>
       </c>
@@ -68941,7 +68995,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:13">
       <c r="A631" s="7">
         <v>45161</v>
       </c>
@@ -68982,7 +69036,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:13">
       <c r="A632" s="7">
         <v>45168</v>
       </c>
@@ -69023,7 +69077,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:13">
       <c r="A633" s="7">
         <v>45175</v>
       </c>
@@ -69064,7 +69118,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:13">
       <c r="A634" s="7">
         <v>45182</v>
       </c>
@@ -69105,7 +69159,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:13">
       <c r="A635" s="7">
         <v>45189</v>
       </c>
@@ -69146,7 +69200,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:13">
       <c r="A636" s="7">
         <v>45196</v>
       </c>
@@ -69187,7 +69241,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:13">
       <c r="A637" s="7">
         <v>45203</v>
       </c>
@@ -69228,7 +69282,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:13">
       <c r="A638" s="7">
         <v>45210</v>
       </c>
@@ -69269,7 +69323,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:13">
       <c r="A639" s="7">
         <v>45217</v>
       </c>
@@ -69310,7 +69364,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:13">
       <c r="A640" s="7">
         <v>45224</v>
       </c>
@@ -69351,7 +69405,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:13">
       <c r="A641" s="7">
         <v>45231</v>
       </c>
@@ -69392,7 +69446,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:13">
       <c r="A642" s="7">
         <v>45238</v>
       </c>
@@ -69433,7 +69487,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:13">
       <c r="A643" s="7">
         <v>45245</v>
       </c>
@@ -69474,7 +69528,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:13">
       <c r="A644" s="7">
         <v>45252</v>
       </c>
@@ -69515,7 +69569,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:13">
       <c r="A645" s="7">
         <v>45259</v>
       </c>
@@ -69556,7 +69610,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:13">
       <c r="A646" s="7">
         <v>45266</v>
       </c>
@@ -69597,7 +69651,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:13">
       <c r="A647" s="7">
         <v>45273</v>
       </c>
@@ -69638,7 +69692,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:13">
       <c r="A648" s="7">
         <v>45280</v>
       </c>
@@ -69679,7 +69733,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:13">
       <c r="A649" s="7">
         <v>45294</v>
       </c>
@@ -69720,7 +69774,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:13">
       <c r="A650" s="7">
         <v>45301</v>
       </c>
@@ -69761,7 +69815,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:13">
       <c r="A651" s="7">
         <v>45308</v>
       </c>
@@ -69802,7 +69856,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:13">
       <c r="A652" s="7">
         <v>45315</v>
       </c>
@@ -69843,7 +69897,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:13">
       <c r="A653" s="7">
         <v>45322</v>
       </c>
@@ -69884,7 +69938,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:13">
       <c r="A654" s="7">
         <v>45329</v>
       </c>
@@ -69925,7 +69979,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:13">
       <c r="A655" s="7">
         <v>45336</v>
       </c>
@@ -69966,7 +70020,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:13">
       <c r="A656" s="7">
         <v>45343</v>
       </c>
@@ -70007,7 +70061,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:13">
       <c r="A657" s="7">
         <v>45350</v>
       </c>
@@ -70048,7 +70102,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:13">
       <c r="A658" s="7">
         <v>45357</v>
       </c>
@@ -70089,7 +70143,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:13">
       <c r="A659" s="7">
         <v>45364</v>
       </c>
@@ -70130,7 +70184,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:13">
       <c r="A660" s="7">
         <v>45371</v>
       </c>
@@ -70171,7 +70225,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:13">
       <c r="A661" s="7">
         <v>45378</v>
       </c>
@@ -70212,7 +70266,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:13">
       <c r="A662" s="7">
         <v>45385</v>
       </c>
@@ -70253,7 +70307,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:13">
       <c r="A663" s="7">
         <v>45392</v>
       </c>
@@ -70294,7 +70348,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:13">
       <c r="A664" s="7">
         <v>45399</v>
       </c>
@@ -70335,7 +70389,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:13">
       <c r="A665" s="7">
         <v>45406</v>
       </c>
@@ -70376,7 +70430,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:13">
       <c r="A666" s="7">
         <v>45413</v>
       </c>
@@ -70417,7 +70471,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:13">
       <c r="A667" s="7">
         <v>45420</v>
       </c>
@@ -70458,7 +70512,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:13">
       <c r="A668" s="7">
         <v>45427</v>
       </c>
@@ -70499,7 +70553,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:13">
       <c r="A669" s="7">
         <v>45434</v>
       </c>
@@ -70540,7 +70594,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:13">
       <c r="A670" s="7">
         <v>45441</v>
       </c>
@@ -70581,7 +70635,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:13">
       <c r="A671" s="7">
         <v>45448</v>
       </c>
@@ -70622,7 +70676,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:13">
       <c r="A672" s="7">
         <v>45455</v>
       </c>
@@ -70663,7 +70717,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:13">
       <c r="A673" s="7">
         <v>45462</v>
       </c>
@@ -70704,7 +70758,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:13">
       <c r="A674" s="7">
         <v>45469</v>
       </c>
@@ -70745,7 +70799,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:13">
       <c r="A675" s="7">
         <v>45476</v>
       </c>
@@ -70786,7 +70840,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:13">
       <c r="A676" s="7">
         <v>45483</v>
       </c>
@@ -70827,7 +70881,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:13">
       <c r="A677" s="7">
         <v>45490</v>
       </c>
@@ -70868,7 +70922,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:13">
       <c r="A678" s="7">
         <v>45497</v>
       </c>
@@ -70909,7 +70963,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:13">
       <c r="A679" s="7">
         <v>45504</v>
       </c>
@@ -70950,7 +71004,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:13">
       <c r="A680" s="7">
         <v>45511</v>
       </c>
@@ -70991,7 +71045,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:13">
       <c r="A681" s="7">
         <v>45518</v>
       </c>
@@ -71032,7 +71086,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:13">
       <c r="A682" s="7">
         <v>45525</v>
       </c>
@@ -71073,7 +71127,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:13">
       <c r="A683" s="7">
         <v>45532</v>
       </c>
@@ -71114,7 +71168,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:13">
       <c r="A684" s="7">
         <v>45539</v>
       </c>
@@ -71155,7 +71209,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:13">
       <c r="A685" s="7">
         <v>45546</v>
       </c>
@@ -71196,7 +71250,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:13">
       <c r="A686" s="7">
         <v>45553</v>
       </c>
@@ -71237,7 +71291,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:13">
       <c r="A687" s="7">
         <v>45560</v>
       </c>
@@ -71278,7 +71332,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:13">
       <c r="A688" s="7">
         <v>45567</v>
       </c>
@@ -71319,7 +71373,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:13">
       <c r="A689" s="7">
         <v>45574</v>
       </c>
@@ -71360,7 +71414,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:13">
       <c r="A690" s="7">
         <v>45581</v>
       </c>
@@ -71401,7 +71455,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:13">
       <c r="A691" s="7">
         <v>45588</v>
       </c>
@@ -71442,7 +71496,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:13">
       <c r="A692" s="7">
         <v>45595</v>
       </c>
@@ -71483,7 +71537,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:13">
       <c r="A693" s="7">
         <v>45602</v>
       </c>
@@ -71524,7 +71578,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:13">
       <c r="A694" s="7">
         <v>45609</v>
       </c>
@@ -71565,7 +71619,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:13">
       <c r="A695" s="7">
         <v>45616</v>
       </c>
@@ -71606,7 +71660,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:13">
       <c r="A696" s="7">
         <v>45623</v>
       </c>
@@ -71647,7 +71701,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:13">
       <c r="A697" s="7">
         <v>45630</v>
       </c>
@@ -71688,7 +71742,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:13">
       <c r="A698" s="7">
         <v>45637</v>
       </c>
@@ -71729,7 +71783,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:13">
       <c r="A699" s="7">
         <v>45644</v>
       </c>
@@ -71770,7 +71824,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:13">
       <c r="A700" s="7">
         <v>45658</v>
       </c>
@@ -71811,7 +71865,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:13">
       <c r="A701" s="7">
         <v>45665</v>
       </c>
@@ -71852,7 +71906,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:13">
       <c r="A702" s="7">
         <v>45672</v>
       </c>
@@ -71893,7 +71947,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:13">
       <c r="A703" s="7">
         <v>45679</v>
       </c>
@@ -71934,7 +71988,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:13">
       <c r="A704" s="7">
         <v>45686</v>
       </c>
@@ -71975,7 +72029,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:13">
       <c r="A705" s="7">
         <v>45693</v>
       </c>
@@ -72016,7 +72070,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:13">
       <c r="A706" s="7">
         <v>45700</v>
       </c>
@@ -72057,7 +72111,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:13">
       <c r="A707" s="7">
         <v>45707</v>
       </c>
@@ -72098,7 +72152,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:13">
       <c r="A708" s="7">
         <v>45714</v>
       </c>
@@ -72139,7 +72193,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:13">
       <c r="A709" s="7">
         <v>45721</v>
       </c>
@@ -72180,7 +72234,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:13">
       <c r="A710" s="7">
         <v>45728</v>
       </c>
@@ -72221,7 +72275,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:13">
       <c r="A711" s="7">
         <v>45735</v>
       </c>
@@ -72262,7 +72316,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:13">
       <c r="A712" s="7">
         <v>45742</v>
       </c>
@@ -72303,7 +72357,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:13">
       <c r="A713" s="7">
         <v>45749</v>
       </c>
@@ -72344,7 +72398,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:13">
       <c r="A714" s="7">
         <v>45756</v>
       </c>
@@ -72385,7 +72439,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:13">
       <c r="A715" s="7">
         <v>45763</v>
       </c>
@@ -72426,7 +72480,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:13">
       <c r="A716" s="7">
         <v>45770</v>
       </c>
@@ -72467,7 +72521,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:13">
       <c r="A717" s="7">
         <v>45777</v>
       </c>
@@ -72508,7 +72562,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:13">
       <c r="A718" s="7">
         <v>45784</v>
       </c>
@@ -72549,7 +72603,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:13">
       <c r="A719" s="7">
         <v>45791</v>
       </c>
@@ -72590,7 +72644,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:13">
       <c r="A720" s="7">
         <v>45798</v>
       </c>
@@ -72631,7 +72685,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:13">
       <c r="A721" s="7">
         <v>45805</v>
       </c>
@@ -72672,7 +72726,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:13">
       <c r="A722" s="7">
         <v>45812</v>
       </c>
@@ -72713,7 +72767,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:13">
       <c r="A723" s="7">
         <v>45819</v>
       </c>
@@ -72754,7 +72808,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:13">
       <c r="A724" s="7">
         <v>45826</v>
       </c>
@@ -72795,7 +72849,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:13">
       <c r="A725" s="7">
         <v>45833</v>
       </c>
@@ -72836,7 +72890,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:13">
       <c r="A726" s="7">
         <v>45840</v>
       </c>
@@ -72877,7 +72931,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:13">
       <c r="A727" s="7">
         <v>45847</v>
       </c>
@@ -72918,7 +72972,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:13">
       <c r="A728" s="7">
         <v>45854</v>
       </c>
@@ -72959,7 +73013,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:13">
       <c r="A729" s="7">
         <v>45861</v>
       </c>
@@ -73000,7 +73054,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:13">
       <c r="A730" s="7">
         <v>45868</v>
       </c>
@@ -73041,7 +73095,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:13">
       <c r="A731" s="7">
         <v>45875</v>
       </c>
@@ -73082,7 +73136,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:13">
       <c r="A732" s="7">
         <v>45882</v>
       </c>
@@ -73123,7 +73177,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:13">
       <c r="A733" s="7">
         <v>45889</v>
       </c>
@@ -73164,7 +73218,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:13">
       <c r="A734" s="7">
         <v>45896</v>
       </c>
@@ -73205,7 +73259,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:13">
       <c r="A735" s="7">
         <v>45903</v>
       </c>
@@ -73246,7 +73300,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:13">
       <c r="A736" s="7">
         <v>45910</v>
       </c>
@@ -73287,7 +73341,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:13">
       <c r="A737" s="7">
         <v>45917</v>
       </c>
@@ -73328,7 +73382,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:13">
       <c r="A738" s="7">
         <v>45924</v>
       </c>
@@ -73369,7 +73423,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:13">
       <c r="A739" s="7">
         <v>45931</v>
       </c>
@@ -73410,7 +73464,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:13">
       <c r="A740" s="7">
         <v>45938</v>
       </c>
@@ -73451,7 +73505,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:13">
       <c r="A741" s="7">
         <v>45945</v>
       </c>
@@ -73492,7 +73546,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:13">
       <c r="A742" s="7">
         <v>45952</v>
       </c>
@@ -73533,7 +73587,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:13">
       <c r="A743" s="7">
         <v>45959</v>
       </c>
@@ -73574,7 +73628,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:13">
       <c r="A744" s="7">
         <v>45966</v>
       </c>
@@ -73615,7 +73669,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:13">
       <c r="A745" s="7">
         <v>45973</v>
       </c>
@@ -73656,7 +73710,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:13">
       <c r="A746" s="7">
         <v>45980</v>
       </c>
@@ -73697,7 +73751,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:13">
       <c r="A747" s="7">
         <v>45987</v>
       </c>
@@ -73738,7 +73792,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:13">
       <c r="A748" s="7">
         <v>45994</v>
       </c>
@@ -73779,7 +73833,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:13">
       <c r="A749" s="7">
         <v>46001</v>
       </c>
@@ -73820,7 +73874,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:13">
       <c r="A750" s="7">
         <v>46008</v>
       </c>
@@ -73861,7 +73915,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:13">
       <c r="A751" s="7">
         <v>46015</v>
       </c>
@@ -73902,7 +73956,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:13">
       <c r="A752" s="7">
         <v>46022</v>
       </c>
@@ -73943,7 +73997,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:13">
       <c r="A753" s="7">
         <v>46029</v>
       </c>
@@ -73984,7 +74038,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:13">
       <c r="A754" s="7">
         <v>46036</v>
       </c>
@@ -74025,7 +74079,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:13">
       <c r="A755" s="7">
         <v>46043</v>
       </c>
@@ -74066,7 +74120,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:13">
       <c r="A756" s="7">
         <v>46050</v>
       </c>
@@ -74107,7 +74161,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:13">
       <c r="A757" s="7">
         <v>46057</v>
       </c>
@@ -74148,7 +74202,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:13">
       <c r="A758" s="7">
         <v>46064</v>
       </c>
@@ -74189,7 +74243,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:13">
       <c r="A759" s="7">
         <v>46071</v>
       </c>
@@ -74230,7 +74284,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:13">
       <c r="A760" s="7">
         <v>46078</v>
       </c>
@@ -74271,7 +74325,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:13">
       <c r="A761" s="7">
         <v>46085</v>
       </c>
@@ -74312,7 +74366,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:13">
       <c r="A762" s="7">
         <v>46092</v>
       </c>
@@ -74353,7 +74407,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:13">
       <c r="A763" s="7">
         <v>46099</v>
       </c>
@@ -74394,7 +74448,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:13">
       <c r="A764" s="7">
         <v>46106</v>
       </c>
@@ -74435,7 +74489,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:13">
       <c r="A765" s="7">
         <v>46113</v>
       </c>
@@ -74476,7 +74530,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:13">
       <c r="A766" s="7">
         <v>46120</v>
       </c>
@@ -74515,6 +74569,47 @@
       </c>
       <c r="M766" s="9">
         <v>1968</v>
+      </c>
+    </row>
+    <row r="767" spans="1:13">
+      <c r="A767" s="7">
+        <v>46127</v>
+      </c>
+      <c r="B767" s="7">
+        <v>46128</v>
+      </c>
+      <c r="C767" s="11">
+        <v>0.58333333333335302</v>
+      </c>
+      <c r="D767" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E767" s="8">
+        <v>2245.9</v>
+      </c>
+      <c r="F767" s="9">
+        <v>2229</v>
+      </c>
+      <c r="G767" s="9">
+        <v>3343</v>
+      </c>
+      <c r="H767" s="9">
+        <v>2810</v>
+      </c>
+      <c r="I767" s="9">
+        <v>3552</v>
+      </c>
+      <c r="J767" s="9">
+        <v>599</v>
+      </c>
+      <c r="K767" s="9">
+        <v>762</v>
+      </c>
+      <c r="L767" s="9">
+        <v>1022</v>
+      </c>
+      <c r="M767" s="9">
+        <v>2030</v>
       </c>
     </row>
   </sheetData>
@@ -74527,7 +74622,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -74538,12 +74633,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:14">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -74562,7 +74657,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:14">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D519113-1594-4712-9B77-CEE7332857B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F446B6FE-0646-4870-A576-CF2920833922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,6 +21,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F446B6FE-0646-4870-A576-CF2920833922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A07486-4593-4A04-8E84-C58396AB6566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -2592,6 +2592,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4901,6 +4907,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>2231.71</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>2216.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7246,6 +7255,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9555,6 +9570,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>2147</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>2127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11900,6 +11918,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14209,6 +14233,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>3071</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>3039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16554,6 +16581,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18863,6 +18896,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>2934</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>2930</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21208,6 +21244,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23517,6 +23559,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>3562</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>3483</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25862,6 +25907,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28171,6 +28222,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>607</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30518,6 +30572,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -32827,6 +32887,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>784</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>796</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35174,6 +35237,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37483,6 +37552,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>1031</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>1014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -39830,6 +39902,12 @@
                 <c:pt idx="766">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="767">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42139,6 +42217,9 @@
                 </c:pt>
                 <c:pt idx="766">
                   <c:v>2326</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>2327</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43216,7 +43297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M768"/>
+  <dimension ref="A1:M770"/>
   <sheetFormatPr defaultColWidth="7.59765625" defaultRowHeight="12.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
@@ -74714,6 +74795,61 @@
       </c>
       <c r="M768" s="9">
         <v>2326</v>
+      </c>
+    </row>
+    <row r="769" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A769" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B769" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C769" s="11">
+        <v>0.58333333333334503</v>
+      </c>
+      <c r="D769" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E769" s="8">
+        <v>2216.42</v>
+      </c>
+      <c r="F769" s="9">
+        <v>2127</v>
+      </c>
+      <c r="G769" s="9">
+        <v>3039</v>
+      </c>
+      <c r="H769" s="9">
+        <v>2930</v>
+      </c>
+      <c r="I769" s="9">
+        <v>3483</v>
+      </c>
+      <c r="J769" s="9">
+        <v>616</v>
+      </c>
+      <c r="K769" s="9">
+        <v>796</v>
+      </c>
+      <c r="L769" s="9">
+        <v>1014</v>
+      </c>
+      <c r="M769" s="9">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="770" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A770" s="7">
+        <v>46148</v>
+      </c>
+      <c r="B770" s="7">
+        <v>46149</v>
+      </c>
+      <c r="C770" s="11">
+        <v>0.58333333333334103</v>
+      </c>
+      <c r="D770" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F6437E-1C20-484F-9351-70CD2690DD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C42283-9A8E-4901-BF58-E26718B14FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -2598,6 +2598,9 @@
                 <c:pt idx="768">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7264,6 +7267,9 @@
                 <c:pt idx="768">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11930,6 +11936,9 @@
                 <c:pt idx="768">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16596,6 +16605,9 @@
                 <c:pt idx="768">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -21262,6 +21274,9 @@
                 <c:pt idx="768">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -25927,6 +25942,9 @@
                 </c:pt>
                 <c:pt idx="768">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30596,6 +30614,9 @@
                 <c:pt idx="768">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -35264,6 +35285,9 @@
                 <c:pt idx="768">
                   <c:v>46149</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -39931,6 +39955,9 @@
                 </c:pt>
                 <c:pt idx="768">
                   <c:v>46149</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>46156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43324,7 +43351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M770"/>
+  <dimension ref="A1:M771"/>
   <sheetFormatPr defaultColWidth="7.59765625" defaultRowHeight="12.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
@@ -74904,6 +74931,20 @@
       </c>
       <c r="M770" s="9">
         <v>2314</v>
+      </c>
+    </row>
+    <row r="771" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A771" s="7">
+        <v>46155</v>
+      </c>
+      <c r="B771" s="7">
+        <v>46156</v>
+      </c>
+      <c r="C771" s="11">
+        <v>0.58333333333327297</v>
+      </c>
+      <c r="D771" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C42283-9A8E-4901-BF58-E26718B14FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE66BFFA-A24C-40E8-AB19-D66F537140F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,29 +107,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -138,7 +138,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -146,7 +146,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -196,28 +196,28 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4917,6 +4917,9 @@
                 <c:pt idx="768">
                   <c:v>2285.6</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>2553.39</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9586,6 +9589,9 @@
                 <c:pt idx="768">
                   <c:v>2170</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>2413</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -14255,6 +14261,9 @@
                 <c:pt idx="768">
                   <c:v>3075</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>3701</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -18924,6 +18933,9 @@
                 <c:pt idx="768">
                   <c:v>3062</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>3357</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -23593,6 +23605,9 @@
                 <c:pt idx="768">
                   <c:v>3721</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>4252</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -28261,6 +28276,9 @@
                 </c:pt>
                 <c:pt idx="768">
                   <c:v>631</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>644</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -32933,6 +32951,9 @@
                 <c:pt idx="768">
                   <c:v>792</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>791</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -37604,6 +37625,9 @@
                 <c:pt idx="768">
                   <c:v>1023</c:v>
                 </c:pt>
+                <c:pt idx="769">
+                  <c:v>1030</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -42274,6 +42298,9 @@
                 </c:pt>
                 <c:pt idx="768">
                   <c:v>2314</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>2388</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43352,18 +43379,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M771"/>
-  <sheetFormatPr defaultColWidth="7.59765625" defaultRowHeight="12.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="7.5546875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8984375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="18.09765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.5" style="9" customWidth="1"/>
-    <col min="14" max="16384" width="7.59765625" style="9"/>
+    <col min="3" max="3" width="11.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.44140625" style="9" customWidth="1"/>
+    <col min="14" max="16384" width="7.5546875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="6" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -43404,7 +43431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13">
       <c r="A2" s="7">
         <v>40716</v>
       </c>
@@ -43445,7 +43472,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13">
       <c r="A3" s="7">
         <v>40723</v>
       </c>
@@ -43486,7 +43513,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13">
       <c r="A4" s="7">
         <v>40730</v>
       </c>
@@ -43527,7 +43554,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13">
       <c r="A5" s="7">
         <v>40737</v>
       </c>
@@ -43568,7 +43595,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13">
       <c r="A6" s="7">
         <v>40744</v>
       </c>
@@ -43609,7 +43636,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13">
       <c r="A7" s="7">
         <v>40751</v>
       </c>
@@ -43650,7 +43677,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13">
       <c r="A8" s="7">
         <v>40758</v>
       </c>
@@ -43691,7 +43718,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13">
       <c r="A9" s="7">
         <v>40765</v>
       </c>
@@ -43732,7 +43759,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13">
       <c r="A10" s="7">
         <v>40772</v>
       </c>
@@ -43773,7 +43800,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13">
       <c r="A11" s="7">
         <v>40779</v>
       </c>
@@ -43814,7 +43841,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13">
       <c r="A12" s="7">
         <v>40786</v>
       </c>
@@ -43855,7 +43882,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13">
       <c r="A13" s="7">
         <v>40793</v>
       </c>
@@ -43896,7 +43923,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13">
       <c r="A14" s="7">
         <v>40800</v>
       </c>
@@ -43937,7 +43964,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13">
       <c r="A15" s="7">
         <v>40807</v>
       </c>
@@ -43978,7 +44005,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13">
       <c r="A16" s="7">
         <v>40814</v>
       </c>
@@ -44019,7 +44046,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13">
       <c r="A17" s="7">
         <v>40821</v>
       </c>
@@ -44060,7 +44087,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13">
       <c r="A18" s="7">
         <v>40828</v>
       </c>
@@ -44101,7 +44128,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13">
       <c r="A19" s="7">
         <v>40835</v>
       </c>
@@ -44142,7 +44169,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13">
       <c r="A20" s="7">
         <v>40842</v>
       </c>
@@ -44183,7 +44210,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13">
       <c r="A21" s="7">
         <v>40849</v>
       </c>
@@ -44224,7 +44251,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13">
       <c r="A22" s="7">
         <v>40856</v>
       </c>
@@ -44265,7 +44292,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13">
       <c r="A23" s="7">
         <v>40863</v>
       </c>
@@ -44306,7 +44333,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13">
       <c r="A24" s="7">
         <v>40870</v>
       </c>
@@ -44347,7 +44374,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13">
       <c r="A25" s="7">
         <v>40877</v>
       </c>
@@ -44388,7 +44415,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13">
       <c r="A26" s="7">
         <v>40884</v>
       </c>
@@ -44429,7 +44456,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13">
       <c r="A27" s="7">
         <v>40891</v>
       </c>
@@ -44470,7 +44497,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13">
       <c r="A28" s="7">
         <v>40898</v>
       </c>
@@ -44511,7 +44538,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13">
       <c r="A29" s="7">
         <v>40905</v>
       </c>
@@ -44552,7 +44579,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13">
       <c r="A30" s="7">
         <v>40912</v>
       </c>
@@ -44593,7 +44620,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13">
       <c r="A31" s="7">
         <v>40919</v>
       </c>
@@ -44634,7 +44661,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13">
       <c r="A32" s="7">
         <v>40926</v>
       </c>
@@ -44675,7 +44702,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13">
       <c r="A33" s="7">
         <v>40933</v>
       </c>
@@ -44716,7 +44743,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13">
       <c r="A34" s="7">
         <v>40940</v>
       </c>
@@ -44757,7 +44784,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13">
       <c r="A35" s="7">
         <v>40947</v>
       </c>
@@ -44798,7 +44825,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13">
       <c r="A36" s="7">
         <v>40954</v>
       </c>
@@ -44839,7 +44866,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13">
       <c r="A37" s="7">
         <v>40961</v>
       </c>
@@ -44880,7 +44907,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13">
       <c r="A38" s="7">
         <v>40968</v>
       </c>
@@ -44921,7 +44948,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13">
       <c r="A39" s="7">
         <v>40975</v>
       </c>
@@ -44962,7 +44989,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13">
       <c r="A40" s="7">
         <v>40982</v>
       </c>
@@ -45003,7 +45030,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13">
       <c r="A41" s="7">
         <v>40989</v>
       </c>
@@ -45044,7 +45071,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13">
       <c r="A42" s="7">
         <v>40996</v>
       </c>
@@ -45085,7 +45112,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13">
       <c r="A43" s="7">
         <v>41003</v>
       </c>
@@ -45126,7 +45153,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13">
       <c r="A44" s="7">
         <v>41010</v>
       </c>
@@ -45167,7 +45194,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13">
       <c r="A45" s="7">
         <v>41017</v>
       </c>
@@ -45208,7 +45235,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13">
       <c r="A46" s="7">
         <v>41024</v>
       </c>
@@ -45249,7 +45276,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13">
       <c r="A47" s="7">
         <v>41031</v>
       </c>
@@ -45290,7 +45317,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13">
       <c r="A48" s="7">
         <v>41038</v>
       </c>
@@ -45331,7 +45358,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13">
       <c r="A49" s="7">
         <v>41045</v>
       </c>
@@ -45372,7 +45399,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13">
       <c r="A50" s="7">
         <v>41052</v>
       </c>
@@ -45413,7 +45440,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13">
       <c r="A51" s="7">
         <v>41059</v>
       </c>
@@ -45454,7 +45481,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13">
       <c r="A52" s="7">
         <v>41066</v>
       </c>
@@ -45495,7 +45522,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13">
       <c r="A53" s="7">
         <v>41073</v>
       </c>
@@ -45536,7 +45563,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13">
       <c r="A54" s="7">
         <v>41080</v>
       </c>
@@ -45577,7 +45604,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13">
       <c r="A55" s="7">
         <v>41087</v>
       </c>
@@ -45618,7 +45645,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13">
       <c r="A56" s="7">
         <v>41094</v>
       </c>
@@ -45659,7 +45686,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13">
       <c r="A57" s="7">
         <v>41101</v>
       </c>
@@ -45700,7 +45727,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13">
       <c r="A58" s="7">
         <v>41108</v>
       </c>
@@ -45741,7 +45768,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13">
       <c r="A59" s="7">
         <v>41115</v>
       </c>
@@ -45782,7 +45809,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13">
       <c r="A60" s="7">
         <v>41122</v>
       </c>
@@ -45823,7 +45850,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13">
       <c r="A61" s="7">
         <v>41129</v>
       </c>
@@ -45864,7 +45891,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13">
       <c r="A62" s="7">
         <v>41136</v>
       </c>
@@ -45905,7 +45932,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13">
       <c r="A63" s="7">
         <v>41143</v>
       </c>
@@ -45946,7 +45973,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13">
       <c r="A64" s="7">
         <v>41150</v>
       </c>
@@ -45987,7 +46014,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:13">
       <c r="A65" s="7">
         <v>41157</v>
       </c>
@@ -46028,7 +46055,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13">
       <c r="A66" s="7">
         <v>41164</v>
       </c>
@@ -46069,7 +46096,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13">
       <c r="A67" s="7">
         <v>41171</v>
       </c>
@@ -46110,7 +46137,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:13">
       <c r="A68" s="7">
         <v>41178</v>
       </c>
@@ -46151,7 +46178,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13">
       <c r="A69" s="7">
         <v>41185</v>
       </c>
@@ -46192,7 +46219,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:13">
       <c r="A70" s="7">
         <v>41192</v>
       </c>
@@ -46233,7 +46260,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:13">
       <c r="A71" s="7">
         <v>41199</v>
       </c>
@@ -46274,7 +46301,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13">
       <c r="A72" s="7">
         <v>41206</v>
       </c>
@@ -46315,7 +46342,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:13">
       <c r="A73" s="7">
         <v>41213</v>
       </c>
@@ -46356,7 +46383,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:13">
       <c r="A74" s="7">
         <v>41220</v>
       </c>
@@ -46397,7 +46424,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:13">
       <c r="A75" s="7">
         <v>41227</v>
       </c>
@@ -46438,7 +46465,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:13">
       <c r="A76" s="7">
         <v>41234</v>
       </c>
@@ -46479,7 +46506,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:13">
       <c r="A77" s="7">
         <v>41241</v>
       </c>
@@ -46520,7 +46547,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:13">
       <c r="A78" s="7">
         <v>41248</v>
       </c>
@@ -46561,7 +46588,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:13">
       <c r="A79" s="7">
         <v>41255</v>
       </c>
@@ -46602,7 +46629,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:13">
       <c r="A80" s="7">
         <v>41262</v>
       </c>
@@ -46643,7 +46670,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:13">
       <c r="A81" s="7">
         <v>41269</v>
       </c>
@@ -46684,7 +46711,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:13">
       <c r="A82" s="7">
         <v>41276</v>
       </c>
@@ -46725,7 +46752,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:13">
       <c r="A83" s="7">
         <v>41283</v>
       </c>
@@ -46766,7 +46793,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:13">
       <c r="A84" s="7">
         <v>41290</v>
       </c>
@@ -46807,7 +46834,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:13">
       <c r="A85" s="7">
         <v>41297</v>
       </c>
@@ -46848,7 +46875,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:13">
       <c r="A86" s="7">
         <v>41304</v>
       </c>
@@ -46889,7 +46916,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:13">
       <c r="A87" s="7">
         <v>41311</v>
       </c>
@@ -46930,7 +46957,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:13">
       <c r="A88" s="7">
         <v>41318</v>
       </c>
@@ -46971,7 +46998,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:13">
       <c r="A89" s="7">
         <v>41325</v>
       </c>
@@ -47012,7 +47039,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:13">
       <c r="A90" s="7">
         <v>41332</v>
       </c>
@@ -47053,7 +47080,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:13">
       <c r="A91" s="7">
         <v>41339</v>
       </c>
@@ -47094,7 +47121,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:13">
       <c r="A92" s="7">
         <v>41346</v>
       </c>
@@ -47135,7 +47162,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:13">
       <c r="A93" s="7">
         <v>41353</v>
       </c>
@@ -47176,7 +47203,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:13">
       <c r="A94" s="7">
         <v>41360</v>
       </c>
@@ -47217,7 +47244,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:13">
       <c r="A95" s="7">
         <v>41367</v>
       </c>
@@ -47258,7 +47285,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:13">
       <c r="A96" s="7">
         <v>41374</v>
       </c>
@@ -47299,7 +47326,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:13">
       <c r="A97" s="7">
         <v>41381</v>
       </c>
@@ -47340,7 +47367,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:13">
       <c r="A98" s="7">
         <v>41388</v>
       </c>
@@ -47381,7 +47408,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:13">
       <c r="A99" s="7">
         <v>41395</v>
       </c>
@@ -47422,7 +47449,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:13">
       <c r="A100" s="7">
         <v>41402</v>
       </c>
@@ -47463,7 +47490,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:13">
       <c r="A101" s="7">
         <v>41409</v>
       </c>
@@ -47504,7 +47531,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:13">
       <c r="A102" s="7">
         <v>41416</v>
       </c>
@@ -47545,7 +47572,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:13">
       <c r="A103" s="7">
         <v>41423</v>
       </c>
@@ -47586,7 +47613,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:13">
       <c r="A104" s="7">
         <v>41430</v>
       </c>
@@ -47627,7 +47654,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:13">
       <c r="A105" s="7">
         <v>41437</v>
       </c>
@@ -47668,7 +47695,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:13">
       <c r="A106" s="7">
         <v>41444</v>
       </c>
@@ -47709,7 +47736,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:13">
       <c r="A107" s="7">
         <v>41451</v>
       </c>
@@ -47750,7 +47777,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:13">
       <c r="A108" s="7">
         <v>41458</v>
       </c>
@@ -47791,7 +47818,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:13">
       <c r="A109" s="7">
         <v>41465</v>
       </c>
@@ -47832,7 +47859,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:13">
       <c r="A110" s="7">
         <v>41472</v>
       </c>
@@ -47873,7 +47900,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:13">
       <c r="A111" s="7">
         <v>41479</v>
       </c>
@@ -47914,7 +47941,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:13">
       <c r="A112" s="7">
         <v>41486</v>
       </c>
@@ -47955,7 +47982,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:13">
       <c r="A113" s="7">
         <v>41493</v>
       </c>
@@ -47996,7 +48023,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:13">
       <c r="A114" s="7">
         <v>41500</v>
       </c>
@@ -48037,7 +48064,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:13">
       <c r="A115" s="7">
         <v>41507</v>
       </c>
@@ -48078,7 +48105,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:13">
       <c r="A116" s="7">
         <v>41514</v>
       </c>
@@ -48119,7 +48146,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:13">
       <c r="A117" s="7">
         <v>41521</v>
       </c>
@@ -48160,7 +48187,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:13">
       <c r="A118" s="7">
         <v>41528</v>
       </c>
@@ -48201,7 +48228,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:13">
       <c r="A119" s="7">
         <v>41535</v>
       </c>
@@ -48242,7 +48269,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:13">
       <c r="A120" s="7">
         <v>41542</v>
       </c>
@@ -48283,7 +48310,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:13">
       <c r="A121" s="7">
         <v>41549</v>
       </c>
@@ -48324,7 +48351,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:13">
       <c r="A122" s="7">
         <v>41556</v>
       </c>
@@ -48365,7 +48392,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:13">
       <c r="A123" s="7">
         <v>41563</v>
       </c>
@@ -48406,7 +48433,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:13">
       <c r="A124" s="7">
         <v>41570</v>
       </c>
@@ -48447,7 +48474,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:13">
       <c r="A125" s="7">
         <v>41577</v>
       </c>
@@ -48488,7 +48515,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:13">
       <c r="A126" s="7">
         <v>41584</v>
       </c>
@@ -48529,7 +48556,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:13">
       <c r="A127" s="7">
         <v>41591</v>
       </c>
@@ -48570,7 +48597,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:13">
       <c r="A128" s="7">
         <v>41598</v>
       </c>
@@ -48611,7 +48638,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:13">
       <c r="A129" s="7">
         <v>41605</v>
       </c>
@@ -48652,7 +48679,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:13">
       <c r="A130" s="7">
         <v>41612</v>
       </c>
@@ -48693,7 +48720,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:13">
       <c r="A131" s="7">
         <v>41619</v>
       </c>
@@ -48734,7 +48761,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:13">
       <c r="A132" s="7">
         <v>41626</v>
       </c>
@@ -48775,7 +48802,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:13">
       <c r="A133" s="7">
         <v>41640</v>
       </c>
@@ -48816,7 +48843,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:13">
       <c r="A134" s="7">
         <v>41647</v>
       </c>
@@ -48857,7 +48884,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:13">
       <c r="A135" s="7">
         <v>41654</v>
       </c>
@@ -48898,7 +48925,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:13">
       <c r="A136" s="7">
         <v>41661</v>
       </c>
@@ -48939,7 +48966,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:13">
       <c r="A137" s="7">
         <v>41668</v>
       </c>
@@ -48980,7 +49007,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:13">
       <c r="A138" s="7">
         <v>41675</v>
       </c>
@@ -49021,7 +49048,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:13">
       <c r="A139" s="7">
         <v>41682</v>
       </c>
@@ -49062,7 +49089,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:13">
       <c r="A140" s="7">
         <v>41689</v>
       </c>
@@ -49103,7 +49130,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:13">
       <c r="A141" s="7">
         <v>41696</v>
       </c>
@@ -49144,7 +49171,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:13">
       <c r="A142" s="7">
         <v>41703</v>
       </c>
@@ -49185,7 +49212,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:13">
       <c r="A143" s="7">
         <v>41710</v>
       </c>
@@ -49226,7 +49253,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:13">
       <c r="A144" s="7">
         <v>41717</v>
       </c>
@@ -49267,7 +49294,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:13">
       <c r="A145" s="7">
         <v>41724</v>
       </c>
@@ -49308,7 +49335,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:13">
       <c r="A146" s="7">
         <v>41731</v>
       </c>
@@ -49349,7 +49376,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:13">
       <c r="A147" s="7">
         <v>41738</v>
       </c>
@@ -49390,7 +49417,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:13">
       <c r="A148" s="7">
         <v>41745</v>
       </c>
@@ -49431,7 +49458,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:13">
       <c r="A149" s="7">
         <v>41752</v>
       </c>
@@ -49472,7 +49499,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:13">
       <c r="A150" s="7">
         <v>41759</v>
       </c>
@@ -49513,7 +49540,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:13">
       <c r="A151" s="7">
         <v>41766</v>
       </c>
@@ -49554,7 +49581,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:13">
       <c r="A152" s="7">
         <v>41773</v>
       </c>
@@ -49595,7 +49622,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:13">
       <c r="A153" s="7">
         <v>41780</v>
       </c>
@@ -49636,7 +49663,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:13">
       <c r="A154" s="7">
         <v>41787</v>
       </c>
@@ -49677,7 +49704,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:13">
       <c r="A155" s="7">
         <v>41794</v>
       </c>
@@ -49718,7 +49745,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:13">
       <c r="A156" s="7">
         <v>41801</v>
       </c>
@@ -49759,7 +49786,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:13">
       <c r="A157" s="7">
         <v>41808</v>
       </c>
@@ -49800,7 +49827,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:13">
       <c r="A158" s="7">
         <v>41815</v>
       </c>
@@ -49841,7 +49868,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:13">
       <c r="A159" s="7">
         <v>41822</v>
       </c>
@@ -49882,7 +49909,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:13">
       <c r="A160" s="7">
         <v>41829</v>
       </c>
@@ -49923,7 +49950,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:13">
       <c r="A161" s="7">
         <v>41836</v>
       </c>
@@ -49964,7 +49991,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:13">
       <c r="A162" s="7">
         <v>41843</v>
       </c>
@@ -50005,7 +50032,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:13">
       <c r="A163" s="7">
         <v>41850</v>
       </c>
@@ -50046,7 +50073,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:13">
       <c r="A164" s="7">
         <v>41857</v>
       </c>
@@ -50087,7 +50114,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:13">
       <c r="A165" s="7">
         <v>41864</v>
       </c>
@@ -50128,7 +50155,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:13">
       <c r="A166" s="7">
         <v>41871</v>
       </c>
@@ -50169,7 +50196,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:13">
       <c r="A167" s="7">
         <v>41878</v>
       </c>
@@ -50210,7 +50237,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:13">
       <c r="A168" s="7">
         <v>41885</v>
       </c>
@@ -50251,7 +50278,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:13">
       <c r="A169" s="7">
         <v>41892</v>
       </c>
@@ -50292,7 +50319,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:13">
       <c r="A170" s="7">
         <v>41899</v>
       </c>
@@ -50333,7 +50360,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:13">
       <c r="A171" s="7">
         <v>41906</v>
       </c>
@@ -50374,7 +50401,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:13">
       <c r="A172" s="7">
         <v>41913</v>
       </c>
@@ -50415,7 +50442,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:13">
       <c r="A173" s="7">
         <v>41920</v>
       </c>
@@ -50456,7 +50483,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:13">
       <c r="A174" s="7">
         <v>41927</v>
       </c>
@@ -50497,7 +50524,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:13">
       <c r="A175" s="7">
         <v>41934</v>
       </c>
@@ -50538,7 +50565,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:13">
       <c r="A176" s="7">
         <v>41941</v>
       </c>
@@ -50579,7 +50606,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:13">
       <c r="A177" s="7">
         <v>41948</v>
       </c>
@@ -50620,7 +50647,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:13">
       <c r="A178" s="7">
         <v>41955</v>
       </c>
@@ -50661,7 +50688,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:13">
       <c r="A179" s="7">
         <v>41962</v>
       </c>
@@ -50702,7 +50729,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:13">
       <c r="A180" s="7">
         <v>41969</v>
       </c>
@@ -50743,7 +50770,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:13">
       <c r="A181" s="7">
         <v>41976</v>
       </c>
@@ -50784,7 +50811,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:13">
       <c r="A182" s="7">
         <v>41983</v>
       </c>
@@ -50825,7 +50852,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:13">
       <c r="A183" s="7">
         <v>41990</v>
       </c>
@@ -50866,7 +50893,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:13">
       <c r="A184" s="7">
         <v>42011</v>
       </c>
@@ -50907,7 +50934,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:13">
       <c r="A185" s="7">
         <v>42018</v>
       </c>
@@ -50948,7 +50975,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:13">
       <c r="A186" s="7">
         <v>42025</v>
       </c>
@@ -50989,7 +51016,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:13">
       <c r="A187" s="7">
         <v>42032</v>
       </c>
@@ -51030,7 +51057,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:13">
       <c r="A188" s="7">
         <v>42039</v>
       </c>
@@ -51071,7 +51098,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:13">
       <c r="A189" s="7">
         <v>42046</v>
       </c>
@@ -51112,7 +51139,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:13">
       <c r="A190" s="7">
         <v>42053</v>
       </c>
@@ -51153,7 +51180,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:13">
       <c r="A191" s="7">
         <v>42060</v>
       </c>
@@ -51194,7 +51221,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:13">
       <c r="A192" s="7">
         <v>42067</v>
       </c>
@@ -51235,7 +51262,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:13">
       <c r="A193" s="7">
         <v>42074</v>
       </c>
@@ -51276,7 +51303,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:13">
       <c r="A194" s="7">
         <v>42081</v>
       </c>
@@ -51317,7 +51344,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:13">
       <c r="A195" s="7">
         <v>42088</v>
       </c>
@@ -51358,7 +51385,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:13">
       <c r="A196" s="7">
         <v>42095</v>
       </c>
@@ -51399,7 +51426,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:13">
       <c r="A197" s="7">
         <v>42102</v>
       </c>
@@ -51440,7 +51467,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:13">
       <c r="A198" s="7">
         <v>42109</v>
       </c>
@@ -51481,7 +51508,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:13">
       <c r="A199" s="7">
         <v>42116</v>
       </c>
@@ -51522,7 +51549,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:13">
       <c r="A200" s="7">
         <v>42123</v>
       </c>
@@ -51563,7 +51590,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:13">
       <c r="A201" s="7">
         <v>42130</v>
       </c>
@@ -51604,7 +51631,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:13">
       <c r="A202" s="7">
         <v>42137</v>
       </c>
@@ -51645,7 +51672,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:13">
       <c r="A203" s="7">
         <v>42144</v>
       </c>
@@ -51686,7 +51713,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:13">
       <c r="A204" s="7">
         <v>42151</v>
       </c>
@@ -51727,7 +51754,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:13">
       <c r="A205" s="7">
         <v>42158</v>
       </c>
@@ -51768,7 +51795,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:13">
       <c r="A206" s="7">
         <v>42165</v>
       </c>
@@ -51809,7 +51836,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:13">
       <c r="A207" s="7">
         <v>42172</v>
       </c>
@@ -51850,7 +51877,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:13">
       <c r="A208" s="7">
         <v>42179</v>
       </c>
@@ -51891,7 +51918,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:13">
       <c r="A209" s="7">
         <v>42186</v>
       </c>
@@ -51932,7 +51959,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:13">
       <c r="A210" s="7">
         <v>42193</v>
       </c>
@@ -51973,7 +52000,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:13">
       <c r="A211" s="7">
         <v>42200</v>
       </c>
@@ -52014,7 +52041,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:13">
       <c r="A212" s="7">
         <v>42207</v>
       </c>
@@ -52055,7 +52082,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:13">
       <c r="A213" s="7">
         <v>42214</v>
       </c>
@@ -52096,7 +52123,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:13">
       <c r="A214" s="7">
         <v>42221</v>
       </c>
@@ -52137,7 +52164,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:13">
       <c r="A215" s="7">
         <v>42228</v>
       </c>
@@ -52178,7 +52205,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:13">
       <c r="A216" s="7">
         <v>42235</v>
       </c>
@@ -52219,7 +52246,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:13">
       <c r="A217" s="7">
         <v>42242</v>
       </c>
@@ -52260,7 +52287,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:13">
       <c r="A218" s="7">
         <v>42249</v>
       </c>
@@ -52301,7 +52328,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:13">
       <c r="A219" s="7">
         <v>42256</v>
       </c>
@@ -52342,7 +52369,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:13">
       <c r="A220" s="7">
         <v>42263</v>
       </c>
@@ -52383,7 +52410,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:13">
       <c r="A221" s="7">
         <v>42270</v>
       </c>
@@ -52424,7 +52451,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:13">
       <c r="A222" s="7">
         <v>42277</v>
       </c>
@@ -52465,7 +52492,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:13">
       <c r="A223" s="7">
         <v>42284</v>
       </c>
@@ -52506,7 +52533,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:13">
       <c r="A224" s="7">
         <v>42291</v>
       </c>
@@ -52547,7 +52574,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:13">
       <c r="A225" s="7">
         <v>42298</v>
       </c>
@@ -52588,7 +52615,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:13">
       <c r="A226" s="7">
         <v>42305</v>
       </c>
@@ -52629,7 +52656,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:13">
       <c r="A227" s="7">
         <v>42312</v>
       </c>
@@ -52670,7 +52697,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:13">
       <c r="A228" s="7">
         <v>42319</v>
       </c>
@@ -52711,7 +52738,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:13">
       <c r="A229" s="7">
         <v>42326</v>
       </c>
@@ -52752,7 +52779,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:13">
       <c r="A230" s="7">
         <v>42333</v>
       </c>
@@ -52793,7 +52820,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:13">
       <c r="A231" s="7">
         <v>42340</v>
       </c>
@@ -52834,7 +52861,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:13">
       <c r="A232" s="7">
         <v>42347</v>
       </c>
@@ -52875,7 +52902,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:13">
       <c r="A233" s="7">
         <v>42354</v>
       </c>
@@ -52916,7 +52943,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:13">
       <c r="A234" s="7">
         <v>42361</v>
       </c>
@@ -52957,7 +52984,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:13">
       <c r="A235" s="7">
         <v>42368</v>
       </c>
@@ -52998,7 +53025,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:13">
       <c r="A236" s="7">
         <v>42375</v>
       </c>
@@ -53039,7 +53066,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:13">
       <c r="A237" s="7">
         <v>42382</v>
       </c>
@@ -53080,7 +53107,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:13">
       <c r="A238" s="7">
         <v>42389</v>
       </c>
@@ -53121,7 +53148,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:13">
       <c r="A239" s="7">
         <v>42396</v>
       </c>
@@ -53162,7 +53189,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:13">
       <c r="A240" s="7">
         <v>42403</v>
       </c>
@@ -53203,7 +53230,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:13">
       <c r="A241" s="7">
         <v>42410</v>
       </c>
@@ -53244,7 +53271,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:13">
       <c r="A242" s="7">
         <v>42417</v>
       </c>
@@ -53285,7 +53312,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:13">
       <c r="A243" s="7">
         <v>42424</v>
       </c>
@@ -53326,7 +53353,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:13">
       <c r="A244" s="7">
         <v>42431</v>
       </c>
@@ -53367,7 +53394,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:13">
       <c r="A245" s="7">
         <v>42438</v>
       </c>
@@ -53408,7 +53435,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:13">
       <c r="A246" s="7">
         <v>42445</v>
       </c>
@@ -53449,7 +53476,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:13">
       <c r="A247" s="7">
         <v>42452</v>
       </c>
@@ -53490,7 +53517,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:13">
       <c r="A248" s="7">
         <v>42459</v>
       </c>
@@ -53531,7 +53558,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:13">
       <c r="A249" s="7">
         <v>42466</v>
       </c>
@@ -53572,7 +53599,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:13">
       <c r="A250" s="7">
         <v>42473</v>
       </c>
@@ -53613,7 +53640,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:13">
       <c r="A251" s="7">
         <v>42480</v>
       </c>
@@ -53654,7 +53681,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:13">
       <c r="A252" s="7">
         <v>42487</v>
       </c>
@@ -53695,7 +53722,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:13">
       <c r="A253" s="7">
         <v>42494</v>
       </c>
@@ -53736,7 +53763,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:13">
       <c r="A254" s="7">
         <v>42501</v>
       </c>
@@ -53777,7 +53804,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:13">
       <c r="A255" s="7">
         <v>42508</v>
       </c>
@@ -53818,7 +53845,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:13">
       <c r="A256" s="7">
         <v>42515</v>
       </c>
@@ -53859,7 +53886,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:13">
       <c r="A257" s="7">
         <v>42522</v>
       </c>
@@ -53900,7 +53927,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:13">
       <c r="A258" s="7">
         <v>42529</v>
       </c>
@@ -53941,7 +53968,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:13">
       <c r="A259" s="7">
         <v>42536</v>
       </c>
@@ -53982,7 +54009,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:13">
       <c r="A260" s="7">
         <v>42543</v>
       </c>
@@ -54023,7 +54050,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:13">
       <c r="A261" s="7">
         <v>42550</v>
       </c>
@@ -54064,7 +54091,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:13">
       <c r="A262" s="7">
         <v>42557</v>
       </c>
@@ -54105,7 +54132,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:13">
       <c r="A263" s="7">
         <v>42564</v>
       </c>
@@ -54146,7 +54173,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:13">
       <c r="A264" s="7">
         <v>42571</v>
       </c>
@@ -54187,7 +54214,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:13">
       <c r="A265" s="7">
         <v>42578</v>
       </c>
@@ -54228,7 +54255,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:13">
       <c r="A266" s="7">
         <v>42585</v>
       </c>
@@ -54269,7 +54296,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:13">
       <c r="A267" s="7">
         <v>42592</v>
       </c>
@@ -54310,7 +54337,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:13">
       <c r="A268" s="7">
         <v>42599</v>
       </c>
@@ -54351,7 +54378,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:13">
       <c r="A269" s="7">
         <v>42606</v>
       </c>
@@ -54392,7 +54419,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:13">
       <c r="A270" s="7">
         <v>42613</v>
       </c>
@@ -54433,7 +54460,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:13">
       <c r="A271" s="7">
         <v>42620</v>
       </c>
@@ -54474,7 +54501,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:13">
       <c r="A272" s="7">
         <v>42627</v>
       </c>
@@ -54515,7 +54542,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:13">
       <c r="A273" s="7">
         <v>42634</v>
       </c>
@@ -54556,7 +54583,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:13">
       <c r="A274" s="7">
         <v>42641</v>
       </c>
@@ -54597,7 +54624,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:13">
       <c r="A275" s="7">
         <v>42648</v>
       </c>
@@ -54638,7 +54665,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:13">
       <c r="A276" s="7">
         <v>42655</v>
       </c>
@@ -54679,7 +54706,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:13">
       <c r="A277" s="7">
         <v>42662</v>
       </c>
@@ -54720,7 +54747,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:13">
       <c r="A278" s="7">
         <v>42669</v>
       </c>
@@ -54761,7 +54788,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:13">
       <c r="A279" s="7">
         <v>42676</v>
       </c>
@@ -54802,7 +54829,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:13">
       <c r="A280" s="7">
         <v>42683</v>
       </c>
@@ -54843,7 +54870,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:13">
       <c r="A281" s="7">
         <v>42690</v>
       </c>
@@ -54884,7 +54911,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:13">
       <c r="A282" s="7">
         <v>42697</v>
       </c>
@@ -54925,7 +54952,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:13">
       <c r="A283" s="7">
         <v>42704</v>
       </c>
@@ -54966,7 +54993,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:13">
       <c r="A284" s="7">
         <v>42711</v>
       </c>
@@ -55007,7 +55034,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:13">
       <c r="A285" s="7">
         <v>42718</v>
       </c>
@@ -55048,7 +55075,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:13">
       <c r="A286" s="7">
         <v>42725</v>
       </c>
@@ -55089,7 +55116,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:13">
       <c r="A287" s="7">
         <v>42732</v>
       </c>
@@ -55130,7 +55157,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:13">
       <c r="A288" s="7">
         <v>42739</v>
       </c>
@@ -55171,7 +55198,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:13">
       <c r="A289" s="7">
         <v>42746</v>
       </c>
@@ -55212,7 +55239,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:13">
       <c r="A290" s="7">
         <v>42753</v>
       </c>
@@ -55253,7 +55280,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:13">
       <c r="A291" s="7">
         <v>42760</v>
       </c>
@@ -55294,7 +55321,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:13">
       <c r="A292" s="7">
         <v>42767</v>
       </c>
@@ -55335,7 +55362,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:13">
       <c r="A293" s="7">
         <v>42774</v>
       </c>
@@ -55376,7 +55403,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:13">
       <c r="A294" s="7">
         <v>42781</v>
       </c>
@@ -55417,7 +55444,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:13">
       <c r="A295" s="7">
         <v>42788</v>
       </c>
@@ -55458,7 +55485,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:13">
       <c r="A296" s="7">
         <v>42795</v>
       </c>
@@ -55499,7 +55526,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:13">
       <c r="A297" s="7">
         <v>42802</v>
       </c>
@@ -55540,7 +55567,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:13">
       <c r="A298" s="7">
         <v>42809</v>
       </c>
@@ -55581,7 +55608,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:13">
       <c r="A299" s="7">
         <v>42816</v>
       </c>
@@ -55622,7 +55649,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:13">
       <c r="A300" s="7">
         <v>42823</v>
       </c>
@@ -55663,7 +55690,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:13">
       <c r="A301" s="7">
         <v>42830</v>
       </c>
@@ -55704,7 +55731,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:13">
       <c r="A302" s="7">
         <v>42837</v>
       </c>
@@ -55745,7 +55772,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:13">
       <c r="A303" s="7">
         <v>42844</v>
       </c>
@@ -55786,7 +55813,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:13">
       <c r="A304" s="7">
         <v>42851</v>
       </c>
@@ -55827,7 +55854,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:13">
       <c r="A305" s="7">
         <v>42858</v>
       </c>
@@ -55868,7 +55895,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:13">
       <c r="A306" s="7">
         <v>42865</v>
       </c>
@@ -55909,7 +55936,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:13">
       <c r="A307" s="7">
         <v>42872</v>
       </c>
@@ -55950,7 +55977,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:13">
       <c r="A308" s="7">
         <v>42879</v>
       </c>
@@ -55991,7 +56018,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:13">
       <c r="A309" s="7">
         <v>42886</v>
       </c>
@@ -56032,7 +56059,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:13">
       <c r="A310" s="7">
         <v>42893</v>
       </c>
@@ -56073,7 +56100,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:13">
       <c r="A311" s="7">
         <v>42900</v>
       </c>
@@ -56114,7 +56141,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:13">
       <c r="A312" s="7">
         <v>42907</v>
       </c>
@@ -56155,7 +56182,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:13">
       <c r="A313" s="7">
         <v>42914</v>
       </c>
@@ -56196,7 +56223,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:13">
       <c r="A314" s="7">
         <v>42921</v>
       </c>
@@ -56237,7 +56264,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:13">
       <c r="A315" s="7">
         <v>42928</v>
       </c>
@@ -56278,7 +56305,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:13">
       <c r="A316" s="7">
         <v>42935</v>
       </c>
@@ -56319,7 +56346,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:13">
       <c r="A317" s="7">
         <v>42942</v>
       </c>
@@ -56360,7 +56387,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:13">
       <c r="A318" s="7">
         <v>42949</v>
       </c>
@@ -56401,7 +56428,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:13">
       <c r="A319" s="7">
         <v>42956</v>
       </c>
@@ -56442,7 +56469,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:13">
       <c r="A320" s="7">
         <v>42963</v>
       </c>
@@ -56483,7 +56510,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:13">
       <c r="A321" s="7">
         <v>42970</v>
       </c>
@@ -56524,7 +56551,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:13">
       <c r="A322" s="7">
         <v>42977</v>
       </c>
@@ -56565,7 +56592,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:13">
       <c r="A323" s="7">
         <v>42984</v>
       </c>
@@ -56606,7 +56633,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:13">
       <c r="A324" s="7">
         <v>42991</v>
       </c>
@@ -56647,7 +56674,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:13">
       <c r="A325" s="7">
         <v>42998</v>
       </c>
@@ -56688,7 +56715,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:13">
       <c r="A326" s="7">
         <v>43005</v>
       </c>
@@ -56729,7 +56756,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:13">
       <c r="A327" s="7">
         <v>43012</v>
       </c>
@@ -56770,7 +56797,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:13">
       <c r="A328" s="7">
         <v>43019</v>
       </c>
@@ -56811,7 +56838,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:13">
       <c r="A329" s="7">
         <v>43026</v>
       </c>
@@ -56852,7 +56879,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:13">
       <c r="A330" s="7">
         <v>43033</v>
       </c>
@@ -56893,7 +56920,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:13">
       <c r="A331" s="7">
         <v>43040</v>
       </c>
@@ -56934,7 +56961,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:13">
       <c r="A332" s="7">
         <v>43047</v>
       </c>
@@ -56975,7 +57002,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:13">
       <c r="A333" s="7">
         <v>43054</v>
       </c>
@@ -57016,7 +57043,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:13">
       <c r="A334" s="7">
         <v>43061</v>
       </c>
@@ -57057,7 +57084,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:13">
       <c r="A335" s="7">
         <v>43068</v>
       </c>
@@ -57098,7 +57125,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:13">
       <c r="A336" s="7">
         <v>43075</v>
       </c>
@@ -57139,7 +57166,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:13">
       <c r="A337" s="7">
         <v>43082</v>
       </c>
@@ -57180,7 +57207,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:13">
       <c r="A338" s="7">
         <v>43089</v>
       </c>
@@ -57221,7 +57248,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:13">
       <c r="A339" s="7">
         <v>43096</v>
       </c>
@@ -57262,7 +57289,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:13">
       <c r="A340" s="7">
         <v>43103</v>
       </c>
@@ -57303,7 +57330,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:13">
       <c r="A341" s="7">
         <v>43110</v>
       </c>
@@ -57344,7 +57371,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:13">
       <c r="A342" s="7">
         <v>43117</v>
       </c>
@@ -57385,7 +57412,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:13">
       <c r="A343" s="7">
         <v>43124</v>
       </c>
@@ -57426,7 +57453,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:13">
       <c r="A344" s="7">
         <v>43131</v>
       </c>
@@ -57467,7 +57494,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:13">
       <c r="A345" s="7">
         <v>43138</v>
       </c>
@@ -57508,7 +57535,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:13">
       <c r="A346" s="7">
         <v>43145</v>
       </c>
@@ -57549,7 +57576,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:13">
       <c r="A347" s="7">
         <v>43152</v>
       </c>
@@ -57590,7 +57617,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:13">
       <c r="A348" s="7">
         <v>43159</v>
       </c>
@@ -57631,7 +57658,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:13">
       <c r="A349" s="7">
         <v>43166</v>
       </c>
@@ -57672,7 +57699,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:13">
       <c r="A350" s="7">
         <v>43173</v>
       </c>
@@ -57713,7 +57740,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:13">
       <c r="A351" s="7">
         <v>43180</v>
       </c>
@@ -57754,7 +57781,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:13">
       <c r="A352" s="7">
         <v>43187</v>
       </c>
@@ -57795,7 +57822,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:13">
       <c r="A353" s="7">
         <v>43194</v>
       </c>
@@ -57836,7 +57863,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:13">
       <c r="A354" s="7">
         <v>43201</v>
       </c>
@@ -57877,7 +57904,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:13">
       <c r="A355" s="7">
         <v>43208</v>
       </c>
@@ -57918,7 +57945,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:13">
       <c r="A356" s="7">
         <v>43215</v>
       </c>
@@ -57959,7 +57986,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:13">
       <c r="A357" s="7">
         <v>43222</v>
       </c>
@@ -58000,7 +58027,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:13">
       <c r="A358" s="7">
         <v>43229</v>
       </c>
@@ -58041,7 +58068,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:13">
       <c r="A359" s="7">
         <v>43236</v>
       </c>
@@ -58082,7 +58109,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:13">
       <c r="A360" s="7">
         <v>43243</v>
       </c>
@@ -58123,7 +58150,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:13">
       <c r="A361" s="7">
         <v>43250</v>
       </c>
@@ -58164,7 +58191,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:13">
       <c r="A362" s="7">
         <v>43257</v>
       </c>
@@ -58205,7 +58232,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:13">
       <c r="A363" s="7">
         <v>43264</v>
       </c>
@@ -58246,7 +58273,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:13">
       <c r="A364" s="7">
         <v>43271</v>
       </c>
@@ -58287,7 +58314,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:13">
       <c r="A365" s="7">
         <v>43278</v>
       </c>
@@ -58328,7 +58355,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:13">
       <c r="A366" s="7">
         <v>43285</v>
       </c>
@@ -58369,7 +58396,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:13">
       <c r="A367" s="7">
         <v>43292</v>
       </c>
@@ -58410,7 +58437,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:13">
       <c r="A368" s="7">
         <v>43299</v>
       </c>
@@ -58451,7 +58478,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:13">
       <c r="A369" s="7">
         <v>43306</v>
       </c>
@@ -58492,7 +58519,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:13">
       <c r="A370" s="7">
         <v>43313</v>
       </c>
@@ -58533,7 +58560,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:13">
       <c r="A371" s="7">
         <v>43320</v>
       </c>
@@ -58574,7 +58601,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:13">
       <c r="A372" s="7">
         <v>43327</v>
       </c>
@@ -58615,7 +58642,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:13">
       <c r="A373" s="7">
         <v>43334</v>
       </c>
@@ -58656,7 +58683,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:13">
       <c r="A374" s="7">
         <v>43341</v>
       </c>
@@ -58697,7 +58724,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:13">
       <c r="A375" s="7">
         <v>43348</v>
       </c>
@@ -58738,7 +58765,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:13">
       <c r="A376" s="7">
         <v>43355</v>
       </c>
@@ -58779,7 +58806,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:13">
       <c r="A377" s="7">
         <v>43362</v>
       </c>
@@ -58820,7 +58847,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:13">
       <c r="A378" s="7">
         <v>43369</v>
       </c>
@@ -58861,7 +58888,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:13">
       <c r="A379" s="7">
         <v>43376</v>
       </c>
@@ -58902,7 +58929,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:13">
       <c r="A380" s="7">
         <v>43383</v>
       </c>
@@ -58943,7 +58970,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:13">
       <c r="A381" s="7">
         <v>43390</v>
       </c>
@@ -58984,7 +59011,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:13">
       <c r="A382" s="7">
         <v>43397</v>
       </c>
@@ -59025,7 +59052,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:13">
       <c r="A383" s="7">
         <v>43404</v>
       </c>
@@ -59066,7 +59093,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:13">
       <c r="A384" s="7">
         <v>43411</v>
       </c>
@@ -59107,7 +59134,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:13">
       <c r="A385" s="7">
         <v>43418</v>
       </c>
@@ -59148,7 +59175,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:13">
       <c r="A386" s="7">
         <v>43425</v>
       </c>
@@ -59189,7 +59216,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:13">
       <c r="A387" s="7">
         <v>43432</v>
       </c>
@@ -59230,7 +59257,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:13">
       <c r="A388" s="7">
         <v>43439</v>
       </c>
@@ -59271,7 +59298,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:13">
       <c r="A389" s="7">
         <v>43446</v>
       </c>
@@ -59312,7 +59339,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:13">
       <c r="A390" s="7">
         <v>43453</v>
       </c>
@@ -59353,7 +59380,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:13">
       <c r="A391" s="7">
         <v>43460</v>
       </c>
@@ -59394,7 +59421,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:13">
       <c r="A392" s="7">
         <v>43467</v>
       </c>
@@ -59435,7 +59462,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:13">
       <c r="A393" s="7">
         <v>43474</v>
       </c>
@@ -59476,7 +59503,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:13">
       <c r="A394" s="7">
         <v>43481</v>
       </c>
@@ -59517,7 +59544,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:13">
       <c r="A395" s="7">
         <v>43488</v>
       </c>
@@ -59558,7 +59585,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:13">
       <c r="A396" s="7">
         <v>43495</v>
       </c>
@@ -59599,7 +59626,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:13">
       <c r="A397" s="7">
         <v>43502</v>
       </c>
@@ -59640,7 +59667,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:13">
       <c r="A398" s="7">
         <v>43509</v>
       </c>
@@ -59681,7 +59708,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:13">
       <c r="A399" s="7">
         <v>43516</v>
       </c>
@@ -59722,7 +59749,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:13">
       <c r="A400" s="7">
         <v>43523</v>
       </c>
@@ -59763,7 +59790,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:13">
       <c r="A401" s="7">
         <v>43530</v>
       </c>
@@ -59804,7 +59831,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:13">
       <c r="A402" s="7">
         <v>43537</v>
       </c>
@@ -59845,7 +59872,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:13">
       <c r="A403" s="7">
         <v>43544</v>
       </c>
@@ -59886,7 +59913,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:13">
       <c r="A404" s="7">
         <v>43551</v>
       </c>
@@ -59927,7 +59954,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:13">
       <c r="A405" s="7">
         <v>43558</v>
       </c>
@@ -59968,7 +59995,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:13">
       <c r="A406" s="7">
         <v>43565</v>
       </c>
@@ -60009,7 +60036,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:13">
       <c r="A407" s="7">
         <v>43572</v>
       </c>
@@ -60050,7 +60077,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:13">
       <c r="A408" s="7">
         <v>43579</v>
       </c>
@@ -60091,7 +60118,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:13">
       <c r="A409" s="7">
         <v>43586</v>
       </c>
@@ -60132,7 +60159,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:13">
       <c r="A410" s="7">
         <v>43593</v>
       </c>
@@ -60173,7 +60200,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:13">
       <c r="A411" s="7">
         <v>43600</v>
       </c>
@@ -60214,7 +60241,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:13">
       <c r="A412" s="7">
         <v>43607</v>
       </c>
@@ -60255,7 +60282,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:13">
       <c r="A413" s="7">
         <v>43614</v>
       </c>
@@ -60296,7 +60323,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:13">
       <c r="A414" s="7">
         <v>43621</v>
       </c>
@@ -60337,7 +60364,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:13">
       <c r="A415" s="7">
         <v>43628</v>
       </c>
@@ -60378,7 +60405,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:13">
       <c r="A416" s="7">
         <v>43635</v>
       </c>
@@ -60419,7 +60446,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:13">
       <c r="A417" s="7">
         <v>43642</v>
       </c>
@@ -60460,7 +60487,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:13">
       <c r="A418" s="7">
         <v>43649</v>
       </c>
@@ -60501,7 +60528,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:13">
       <c r="A419" s="7">
         <v>43656</v>
       </c>
@@ -60542,7 +60569,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:13">
       <c r="A420" s="7">
         <v>43663</v>
       </c>
@@ -60583,7 +60610,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:13">
       <c r="A421" s="7">
         <v>43670</v>
       </c>
@@ -60624,7 +60651,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:13">
       <c r="A422" s="7">
         <v>43677</v>
       </c>
@@ -60665,7 +60692,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:13">
       <c r="A423" s="7">
         <v>43684</v>
       </c>
@@ -60706,7 +60733,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:13">
       <c r="A424" s="7">
         <v>43691</v>
       </c>
@@ -60747,7 +60774,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:13">
       <c r="A425" s="7">
         <v>43698</v>
       </c>
@@ -60788,7 +60815,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:13">
       <c r="A426" s="7">
         <v>43705</v>
       </c>
@@ -60829,7 +60856,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:13">
       <c r="A427" s="7">
         <v>43712</v>
       </c>
@@ -60870,7 +60897,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:13">
       <c r="A428" s="7">
         <v>43719</v>
       </c>
@@ -60911,7 +60938,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:13">
       <c r="A429" s="7">
         <v>43726</v>
       </c>
@@ -60952,7 +60979,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:13">
       <c r="A430" s="7">
         <v>43733</v>
       </c>
@@ -60993,7 +61020,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:13">
       <c r="A431" s="7">
         <v>43740</v>
       </c>
@@ -61034,7 +61061,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:13">
       <c r="A432" s="7">
         <v>43747</v>
       </c>
@@ -61075,7 +61102,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:13">
       <c r="A433" s="7">
         <v>43754</v>
       </c>
@@ -61116,7 +61143,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:13">
       <c r="A434" s="7">
         <v>43761</v>
       </c>
@@ -61157,7 +61184,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:13">
       <c r="A435" s="7">
         <v>43768</v>
       </c>
@@ -61198,7 +61225,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:13">
       <c r="A436" s="7">
         <v>43775</v>
       </c>
@@ -61239,7 +61266,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:13">
       <c r="A437" s="7">
         <v>43782</v>
       </c>
@@ -61280,7 +61307,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:13">
       <c r="A438" s="7">
         <v>43789</v>
       </c>
@@ -61321,7 +61348,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:13">
       <c r="A439" s="7">
         <v>43796</v>
       </c>
@@ -61362,7 +61389,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:13">
       <c r="A440" s="7">
         <v>43803</v>
       </c>
@@ -61403,7 +61430,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:13">
       <c r="A441" s="7">
         <v>43810</v>
       </c>
@@ -61444,7 +61471,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:13">
       <c r="A442" s="7">
         <v>43817</v>
       </c>
@@ -61485,7 +61512,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:13">
       <c r="A443" s="7">
         <v>43831</v>
       </c>
@@ -61526,7 +61553,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:13">
       <c r="A444" s="7">
         <v>43838</v>
       </c>
@@ -61567,7 +61594,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:13">
       <c r="A445" s="7">
         <v>43845</v>
       </c>
@@ -61608,7 +61635,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:13">
       <c r="A446" s="7">
         <v>43852</v>
       </c>
@@ -61649,7 +61676,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:13">
       <c r="A447" s="7">
         <v>43859</v>
       </c>
@@ -61690,7 +61717,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:13">
       <c r="A448" s="7">
         <v>43866</v>
       </c>
@@ -61731,7 +61758,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:13">
       <c r="A449" s="7">
         <v>43873</v>
       </c>
@@ -61772,7 +61799,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:13">
       <c r="A450" s="7">
         <v>43880</v>
       </c>
@@ -61813,7 +61840,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:13">
       <c r="A451" s="7">
         <v>43887</v>
       </c>
@@ -61854,7 +61881,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:13">
       <c r="A452" s="7">
         <v>43894</v>
       </c>
@@ -61895,7 +61922,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:13">
       <c r="A453" s="7">
         <v>43901</v>
       </c>
@@ -61936,7 +61963,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:13">
       <c r="A454" s="7">
         <v>43908</v>
       </c>
@@ -61977,7 +62004,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:13">
       <c r="A455" s="7">
         <v>43915</v>
       </c>
@@ -62018,7 +62045,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:13">
       <c r="A456" s="7">
         <v>43922</v>
       </c>
@@ -62059,7 +62086,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:13">
       <c r="A457" s="7">
         <v>43929</v>
       </c>
@@ -62100,7 +62127,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:13">
       <c r="A458" s="7">
         <v>43936</v>
       </c>
@@ -62141,7 +62168,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:13">
       <c r="A459" s="7">
         <v>43943</v>
       </c>
@@ -62182,7 +62209,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:13">
       <c r="A460" s="7">
         <v>43950</v>
       </c>
@@ -62223,7 +62250,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:13">
       <c r="A461" s="7">
         <v>43957</v>
       </c>
@@ -62264,7 +62291,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:13">
       <c r="A462" s="7">
         <v>43964</v>
       </c>
@@ -62305,7 +62332,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:13">
       <c r="A463" s="7">
         <v>43971</v>
       </c>
@@ -62346,7 +62373,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:13">
       <c r="A464" s="7">
         <v>43978</v>
       </c>
@@ -62387,7 +62414,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:13">
       <c r="A465" s="7">
         <v>43985</v>
       </c>
@@ -62428,7 +62455,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:13">
       <c r="A466" s="7">
         <v>43992</v>
       </c>
@@ -62469,7 +62496,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:13">
       <c r="A467" s="7">
         <v>43999</v>
       </c>
@@ -62510,7 +62537,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:13">
       <c r="A468" s="7">
         <v>44006</v>
       </c>
@@ -62551,7 +62578,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:13">
       <c r="A469" s="7">
         <v>44013</v>
       </c>
@@ -62592,7 +62619,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:13">
       <c r="A470" s="7">
         <v>44020</v>
       </c>
@@ -62633,7 +62660,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:13">
       <c r="A471" s="7">
         <v>44027</v>
       </c>
@@ -62674,7 +62701,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:13">
       <c r="A472" s="7">
         <v>44034</v>
       </c>
@@ -62715,7 +62742,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:13">
       <c r="A473" s="7">
         <v>44041</v>
       </c>
@@ -62756,7 +62783,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:13">
       <c r="A474" s="7">
         <v>44048</v>
       </c>
@@ -62797,7 +62824,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:13">
       <c r="A475" s="7">
         <v>44055</v>
       </c>
@@ -62838,7 +62865,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:13">
       <c r="A476" s="7">
         <v>44062</v>
       </c>
@@ -62879,7 +62906,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:13">
       <c r="A477" s="7">
         <v>44069</v>
       </c>
@@ -62920,7 +62947,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:13">
       <c r="A478" s="7">
         <v>44076</v>
       </c>
@@ -62961,7 +62988,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:13">
       <c r="A479" s="7">
         <v>44083</v>
       </c>
@@ -63002,7 +63029,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:13">
       <c r="A480" s="7">
         <v>44090</v>
       </c>
@@ -63043,7 +63070,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:13">
       <c r="A481" s="7">
         <v>44097</v>
       </c>
@@ -63084,7 +63111,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:13">
       <c r="A482" s="7">
         <v>44104</v>
       </c>
@@ -63125,7 +63152,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:13">
       <c r="A483" s="7">
         <v>44111</v>
       </c>
@@ -63166,7 +63193,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:13">
       <c r="A484" s="7">
         <v>44118</v>
       </c>
@@ -63207,7 +63234,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:13">
       <c r="A485" s="7">
         <v>44125</v>
       </c>
@@ -63248,7 +63275,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:13">
       <c r="A486" s="7">
         <v>44132</v>
       </c>
@@ -63289,7 +63316,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:13">
       <c r="A487" s="7">
         <v>44139</v>
       </c>
@@ -63330,7 +63357,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:13">
       <c r="A488" s="7">
         <v>44146</v>
       </c>
@@ -63371,7 +63398,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:13">
       <c r="A489" s="7">
         <v>44153</v>
       </c>
@@ -63412,7 +63439,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:13">
       <c r="A490" s="7">
         <v>44160</v>
       </c>
@@ -63453,7 +63480,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:13">
       <c r="A491" s="7">
         <v>44167</v>
       </c>
@@ -63494,7 +63521,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:13">
       <c r="A492" s="7">
         <v>44174</v>
       </c>
@@ -63535,7 +63562,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:13">
       <c r="A493" s="7">
         <v>44181</v>
       </c>
@@ -63576,7 +63603,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:13">
       <c r="A494" s="7">
         <v>44188</v>
       </c>
@@ -63617,7 +63644,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:13">
       <c r="A495" s="7">
         <v>44195</v>
       </c>
@@ -63658,7 +63685,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:13">
       <c r="A496" s="7">
         <v>44202</v>
       </c>
@@ -63699,7 +63726,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:13">
       <c r="A497" s="7">
         <v>44209</v>
       </c>
@@ -63740,7 +63767,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:13">
       <c r="A498" s="7">
         <v>44216</v>
       </c>
@@ -63781,7 +63808,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:13">
       <c r="A499" s="7">
         <v>44223</v>
       </c>
@@ -63822,7 +63849,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:13">
       <c r="A500" s="7">
         <v>44230</v>
       </c>
@@ -63863,7 +63890,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:13">
       <c r="A501" s="7">
         <v>44237</v>
       </c>
@@ -63904,7 +63931,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:13">
       <c r="A502" s="7">
         <v>44244</v>
       </c>
@@ -63945,7 +63972,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:13">
       <c r="A503" s="7">
         <v>44251</v>
       </c>
@@ -63986,7 +64013,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:13">
       <c r="A504" s="7">
         <v>44258</v>
       </c>
@@ -64027,7 +64054,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:13">
       <c r="A505" s="7">
         <v>44265</v>
       </c>
@@ -64068,7 +64095,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:13">
       <c r="A506" s="7">
         <v>44272</v>
       </c>
@@ -64109,7 +64136,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:13">
       <c r="A507" s="7">
         <v>44279</v>
       </c>
@@ -64150,7 +64177,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:13">
       <c r="A508" s="7">
         <v>44286</v>
       </c>
@@ -64191,7 +64218,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:13">
       <c r="A509" s="7">
         <v>44293</v>
       </c>
@@ -64232,7 +64259,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:13">
       <c r="A510" s="7">
         <v>44300</v>
       </c>
@@ -64273,7 +64300,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:13">
       <c r="A511" s="7">
         <v>44307</v>
       </c>
@@ -64314,7 +64341,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:13">
       <c r="A512" s="7">
         <v>44314</v>
       </c>
@@ -64355,7 +64382,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:13">
       <c r="A513" s="7">
         <v>44321</v>
       </c>
@@ -64396,7 +64423,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:13">
       <c r="A514" s="7">
         <v>44328</v>
       </c>
@@ -64437,7 +64464,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:13">
       <c r="A515" s="7">
         <v>44335</v>
       </c>
@@ -64478,7 +64505,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:13">
       <c r="A516" s="7">
         <v>44342</v>
       </c>
@@ -64519,7 +64546,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:13">
       <c r="A517" s="7">
         <v>44349</v>
       </c>
@@ -64560,7 +64587,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:13">
       <c r="A518" s="7">
         <v>44356</v>
       </c>
@@ -64601,7 +64628,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:13">
       <c r="A519" s="7">
         <v>44363</v>
       </c>
@@ -64642,7 +64669,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:13">
       <c r="A520" s="7">
         <v>44370</v>
       </c>
@@ -64683,7 +64710,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:13">
       <c r="A521" s="7">
         <v>44377</v>
       </c>
@@ -64724,7 +64751,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:13">
       <c r="A522" s="7">
         <v>44384</v>
       </c>
@@ -64765,7 +64792,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:13">
       <c r="A523" s="7">
         <v>44391</v>
       </c>
@@ -64806,7 +64833,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:13">
       <c r="A524" s="7">
         <v>44398</v>
       </c>
@@ -64847,7 +64874,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:13">
       <c r="A525" s="7">
         <v>44405</v>
       </c>
@@ -64888,7 +64915,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:13">
       <c r="A526" s="7">
         <v>44412</v>
       </c>
@@ -64929,7 +64956,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:13">
       <c r="A527" s="7">
         <v>44419</v>
       </c>
@@ -64970,7 +64997,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:13">
       <c r="A528" s="7">
         <v>44426</v>
       </c>
@@ -65011,7 +65038,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:13">
       <c r="A529" s="7">
         <v>44433</v>
       </c>
@@ -65052,7 +65079,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:13">
       <c r="A530" s="7">
         <v>44440</v>
       </c>
@@ -65093,7 +65120,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:13">
       <c r="A531" s="7">
         <v>44447</v>
       </c>
@@ -65134,7 +65161,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:13">
       <c r="A532" s="7">
         <v>44454</v>
       </c>
@@ -65175,7 +65202,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:13">
       <c r="A533" s="7">
         <v>44461</v>
       </c>
@@ -65216,7 +65243,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:13">
       <c r="A534" s="7">
         <v>44468</v>
       </c>
@@ -65257,7 +65284,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:13">
       <c r="A535" s="7">
         <v>44475</v>
       </c>
@@ -65298,7 +65325,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:13">
       <c r="A536" s="7">
         <v>44482</v>
       </c>
@@ -65339,7 +65366,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:13">
       <c r="A537" s="7">
         <v>44489</v>
       </c>
@@ -65380,7 +65407,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:13">
       <c r="A538" s="7">
         <v>44496</v>
       </c>
@@ -65421,7 +65448,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:13">
       <c r="A539" s="7">
         <v>44503</v>
       </c>
@@ -65462,7 +65489,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:13">
       <c r="A540" s="7">
         <v>44510</v>
       </c>
@@ -65503,7 +65530,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:13">
       <c r="A541" s="7">
         <v>44517</v>
       </c>
@@ -65544,7 +65571,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:13">
       <c r="A542" s="7">
         <v>44524</v>
       </c>
@@ -65585,7 +65612,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:13">
       <c r="A543" s="7">
         <v>44531</v>
       </c>
@@ -65626,7 +65653,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:13">
       <c r="A544" s="7">
         <v>44538</v>
       </c>
@@ -65667,7 +65694,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:13">
       <c r="A545" s="7">
         <v>44545</v>
       </c>
@@ -65708,7 +65735,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:13">
       <c r="A546" s="7">
         <v>44552</v>
       </c>
@@ -65749,7 +65776,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:13">
       <c r="A547" s="7">
         <v>44566</v>
       </c>
@@ -65790,7 +65817,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:13">
       <c r="A548" s="7">
         <v>44573</v>
       </c>
@@ -65831,7 +65858,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:13">
       <c r="A549" s="7">
         <v>44580</v>
       </c>
@@ -65872,7 +65899,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:13">
       <c r="A550" s="7">
         <v>44587</v>
       </c>
@@ -65913,7 +65940,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:13">
       <c r="A551" s="7">
         <v>44594</v>
       </c>
@@ -65954,7 +65981,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:13">
       <c r="A552" s="7">
         <v>44601</v>
       </c>
@@ -65995,7 +66022,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:13">
       <c r="A553" s="7">
         <v>44608</v>
       </c>
@@ -66036,7 +66063,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:13">
       <c r="A554" s="7">
         <v>44615</v>
       </c>
@@ -66077,7 +66104,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:13">
       <c r="A555" s="7">
         <v>44622</v>
       </c>
@@ -66118,7 +66145,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:13">
       <c r="A556" s="7">
         <v>44629</v>
       </c>
@@ -66159,7 +66186,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:13">
       <c r="A557" s="7">
         <v>44636</v>
       </c>
@@ -66200,7 +66227,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:13">
       <c r="A558" s="7">
         <v>44643</v>
       </c>
@@ -66241,7 +66268,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:13">
       <c r="A559" s="7">
         <v>44650</v>
       </c>
@@ -66282,7 +66309,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:13">
       <c r="A560" s="7">
         <v>44657</v>
       </c>
@@ -66323,7 +66350,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:13">
       <c r="A561" s="7">
         <v>44664</v>
       </c>
@@ -66364,7 +66391,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:13">
       <c r="A562" s="7">
         <v>44671</v>
       </c>
@@ -66405,7 +66432,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:13">
       <c r="A563" s="7">
         <v>44678</v>
       </c>
@@ -66446,7 +66473,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:13">
       <c r="A564" s="7">
         <v>44685</v>
       </c>
@@ -66487,7 +66514,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:13">
       <c r="A565" s="7">
         <v>44692</v>
       </c>
@@ -66528,7 +66555,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:13">
       <c r="A566" s="7">
         <v>44699</v>
       </c>
@@ -66569,7 +66596,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:13">
       <c r="A567" s="7">
         <v>44706</v>
       </c>
@@ -66610,7 +66637,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:13">
       <c r="A568" s="7">
         <v>44713</v>
       </c>
@@ -66651,7 +66678,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:13">
       <c r="A569" s="7">
         <v>44720</v>
       </c>
@@ -66692,7 +66719,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:13">
       <c r="A570" s="7">
         <v>44727</v>
       </c>
@@ -66733,7 +66760,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:13">
       <c r="A571" s="7">
         <v>44734</v>
       </c>
@@ -66774,7 +66801,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:13">
       <c r="A572" s="7">
         <v>44741</v>
       </c>
@@ -66815,7 +66842,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:13">
       <c r="A573" s="7">
         <v>44748</v>
       </c>
@@ -66856,7 +66883,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:13">
       <c r="A574" s="7">
         <v>44755</v>
       </c>
@@ -66897,7 +66924,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:13">
       <c r="A575" s="7">
         <v>44762</v>
       </c>
@@ -66938,7 +66965,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:13">
       <c r="A576" s="7">
         <v>44769</v>
       </c>
@@ -66979,7 +67006,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:13">
       <c r="A577" s="7">
         <v>44776</v>
       </c>
@@ -67020,7 +67047,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:13">
       <c r="A578" s="7">
         <v>44783</v>
       </c>
@@ -67061,7 +67088,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:13">
       <c r="A579" s="7">
         <v>44790</v>
       </c>
@@ -67102,7 +67129,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:13">
       <c r="A580" s="7">
         <v>44797</v>
       </c>
@@ -67143,7 +67170,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:13">
       <c r="A581" s="7">
         <v>44804</v>
       </c>
@@ -67184,7 +67211,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:13">
       <c r="A582" s="7">
         <v>44811</v>
       </c>
@@ -67225,7 +67252,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:13">
       <c r="A583" s="7">
         <v>44818</v>
       </c>
@@ -67266,7 +67293,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:13">
       <c r="A584" s="7">
         <v>44825</v>
       </c>
@@ -67307,7 +67334,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:13">
       <c r="A585" s="7">
         <v>44832</v>
       </c>
@@ -67348,7 +67375,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:13">
       <c r="A586" s="7">
         <v>44839</v>
       </c>
@@ -67389,7 +67416,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:13">
       <c r="A587" s="7">
         <v>44846</v>
       </c>
@@ -67430,7 +67457,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:13">
       <c r="A588" s="7">
         <v>44853</v>
       </c>
@@ -67471,7 +67498,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:13">
       <c r="A589" s="7">
         <v>44860</v>
       </c>
@@ -67512,7 +67539,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:13">
       <c r="A590" s="7">
         <v>44867</v>
       </c>
@@ -67553,7 +67580,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:13">
       <c r="A591" s="7">
         <v>44874</v>
       </c>
@@ -67594,7 +67621,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:13">
       <c r="A592" s="7">
         <v>44881</v>
       </c>
@@ -67635,7 +67662,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:13">
       <c r="A593" s="7">
         <v>44888</v>
       </c>
@@ -67676,7 +67703,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:13">
       <c r="A594" s="7">
         <v>44895</v>
       </c>
@@ -67717,7 +67744,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:13">
       <c r="A595" s="7">
         <v>44902</v>
       </c>
@@ -67758,7 +67785,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:13">
       <c r="A596" s="7">
         <v>44909</v>
       </c>
@@ -67799,7 +67826,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:13">
       <c r="A597" s="7">
         <v>44916</v>
       </c>
@@ -67840,7 +67867,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:13">
       <c r="A598" s="7">
         <v>44930</v>
       </c>
@@ -67881,7 +67908,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:13">
       <c r="A599" s="7">
         <v>44937</v>
       </c>
@@ -67922,7 +67949,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:13">
       <c r="A600" s="7">
         <v>44944</v>
       </c>
@@ -67963,7 +67990,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:13">
       <c r="A601" s="7">
         <v>44951</v>
       </c>
@@ -68004,7 +68031,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:13">
       <c r="A602" s="7">
         <v>44958</v>
       </c>
@@ -68045,7 +68072,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:13">
       <c r="A603" s="7">
         <v>44965</v>
       </c>
@@ -68086,7 +68113,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:13">
       <c r="A604" s="7">
         <v>44972</v>
       </c>
@@ -68127,7 +68154,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:13">
       <c r="A605" s="7">
         <v>44979</v>
       </c>
@@ -68168,7 +68195,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:13">
       <c r="A606" s="7">
         <v>44986</v>
       </c>
@@ -68209,7 +68236,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:13">
       <c r="A607" s="7">
         <v>44993</v>
       </c>
@@ -68250,7 +68277,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:13">
       <c r="A608" s="7">
         <v>45000</v>
       </c>
@@ -68291,7 +68318,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:13">
       <c r="A609" s="7">
         <v>45007</v>
       </c>
@@ -68332,7 +68359,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:13">
       <c r="A610" s="7">
         <v>45014</v>
       </c>
@@ -68373,7 +68400,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:13">
       <c r="A611" s="7">
         <v>45021</v>
       </c>
@@ -68414,7 +68441,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:13">
       <c r="A612" s="7">
         <v>45028</v>
       </c>
@@ -68455,7 +68482,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:13">
       <c r="A613" s="7">
         <v>45035</v>
       </c>
@@ -68496,7 +68523,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:13">
       <c r="A614" s="7">
         <v>45042</v>
       </c>
@@ -68537,7 +68564,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:13">
       <c r="A615" s="7">
         <v>45049</v>
       </c>
@@ -68578,7 +68605,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:13">
       <c r="A616" s="7">
         <v>45056</v>
       </c>
@@ -68619,7 +68646,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:13">
       <c r="A617" s="7">
         <v>45063</v>
       </c>
@@ -68660,7 +68687,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:13">
       <c r="A618" s="7">
         <v>45070</v>
       </c>
@@ -68701,7 +68728,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:13">
       <c r="A619" s="7">
         <v>45077</v>
       </c>
@@ -68742,7 +68769,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:13">
       <c r="A620" s="7">
         <v>45084</v>
       </c>
@@ -68783,7 +68810,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:13">
       <c r="A621" s="7">
         <v>45091</v>
       </c>
@@ -68824,7 +68851,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:13">
       <c r="A622" s="7">
         <v>45098</v>
       </c>
@@ -68865,7 +68892,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:13">
       <c r="A623" s="7">
         <v>45105</v>
       </c>
@@ -68906,7 +68933,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:13">
       <c r="A624" s="7">
         <v>45112</v>
       </c>
@@ -68947,7 +68974,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:13">
       <c r="A625" s="7">
         <v>45119</v>
       </c>
@@ -68988,7 +69015,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:13">
       <c r="A626" s="7">
         <v>45126</v>
       </c>
@@ -69029,7 +69056,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:13">
       <c r="A627" s="7">
         <v>45133</v>
       </c>
@@ -69070,7 +69097,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:13">
       <c r="A628" s="7">
         <v>45140</v>
       </c>
@@ -69111,7 +69138,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:13">
       <c r="A629" s="7">
         <v>45147</v>
       </c>
@@ -69152,7 +69179,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:13">
       <c r="A630" s="7">
         <v>45154</v>
       </c>
@@ -69193,7 +69220,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:13">
       <c r="A631" s="7">
         <v>45161</v>
       </c>
@@ -69234,7 +69261,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:13">
       <c r="A632" s="7">
         <v>45168</v>
       </c>
@@ -69275,7 +69302,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:13">
       <c r="A633" s="7">
         <v>45175</v>
       </c>
@@ -69316,7 +69343,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:13">
       <c r="A634" s="7">
         <v>45182</v>
       </c>
@@ -69357,7 +69384,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:13">
       <c r="A635" s="7">
         <v>45189</v>
       </c>
@@ -69398,7 +69425,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:13">
       <c r="A636" s="7">
         <v>45196</v>
       </c>
@@ -69439,7 +69466,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:13">
       <c r="A637" s="7">
         <v>45203</v>
       </c>
@@ -69480,7 +69507,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:13">
       <c r="A638" s="7">
         <v>45210</v>
       </c>
@@ -69521,7 +69548,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:13">
       <c r="A639" s="7">
         <v>45217</v>
       </c>
@@ -69562,7 +69589,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:13">
       <c r="A640" s="7">
         <v>45224</v>
       </c>
@@ -69603,7 +69630,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:13">
       <c r="A641" s="7">
         <v>45231</v>
       </c>
@@ -69644,7 +69671,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:13">
       <c r="A642" s="7">
         <v>45238</v>
       </c>
@@ -69685,7 +69712,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:13">
       <c r="A643" s="7">
         <v>45245</v>
       </c>
@@ -69726,7 +69753,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:13">
       <c r="A644" s="7">
         <v>45252</v>
       </c>
@@ -69767,7 +69794,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:13">
       <c r="A645" s="7">
         <v>45259</v>
       </c>
@@ -69808,7 +69835,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:13">
       <c r="A646" s="7">
         <v>45266</v>
       </c>
@@ -69849,7 +69876,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:13">
       <c r="A647" s="7">
         <v>45273</v>
       </c>
@@ -69890,7 +69917,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:13">
       <c r="A648" s="7">
         <v>45280</v>
       </c>
@@ -69931,7 +69958,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:13">
       <c r="A649" s="7">
         <v>45294</v>
       </c>
@@ -69972,7 +69999,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:13">
       <c r="A650" s="7">
         <v>45301</v>
       </c>
@@ -70013,7 +70040,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:13">
       <c r="A651" s="7">
         <v>45308</v>
       </c>
@@ -70054,7 +70081,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:13">
       <c r="A652" s="7">
         <v>45315</v>
       </c>
@@ -70095,7 +70122,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:13">
       <c r="A653" s="7">
         <v>45322</v>
       </c>
@@ -70136,7 +70163,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:13">
       <c r="A654" s="7">
         <v>45329</v>
       </c>
@@ -70177,7 +70204,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:13">
       <c r="A655" s="7">
         <v>45336</v>
       </c>
@@ -70218,7 +70245,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:13">
       <c r="A656" s="7">
         <v>45343</v>
       </c>
@@ -70259,7 +70286,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:13">
       <c r="A657" s="7">
         <v>45350</v>
       </c>
@@ -70300,7 +70327,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:13">
       <c r="A658" s="7">
         <v>45357</v>
       </c>
@@ -70341,7 +70368,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:13">
       <c r="A659" s="7">
         <v>45364</v>
       </c>
@@ -70382,7 +70409,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:13">
       <c r="A660" s="7">
         <v>45371</v>
       </c>
@@ -70423,7 +70450,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:13">
       <c r="A661" s="7">
         <v>45378</v>
       </c>
@@ -70464,7 +70491,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:13">
       <c r="A662" s="7">
         <v>45385</v>
       </c>
@@ -70505,7 +70532,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:13">
       <c r="A663" s="7">
         <v>45392</v>
       </c>
@@ -70546,7 +70573,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:13">
       <c r="A664" s="7">
         <v>45399</v>
       </c>
@@ -70587,7 +70614,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:13">
       <c r="A665" s="7">
         <v>45406</v>
       </c>
@@ -70628,7 +70655,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:13">
       <c r="A666" s="7">
         <v>45413</v>
       </c>
@@ -70669,7 +70696,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:13">
       <c r="A667" s="7">
         <v>45420</v>
       </c>
@@ -70710,7 +70737,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:13">
       <c r="A668" s="7">
         <v>45427</v>
       </c>
@@ -70751,7 +70778,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:13">
       <c r="A669" s="7">
         <v>45434</v>
       </c>
@@ -70792,7 +70819,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:13">
       <c r="A670" s="7">
         <v>45441</v>
       </c>
@@ -70833,7 +70860,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:13">
       <c r="A671" s="7">
         <v>45448</v>
       </c>
@@ -70874,7 +70901,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:13">
       <c r="A672" s="7">
         <v>45455</v>
       </c>
@@ -70915,7 +70942,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:13">
       <c r="A673" s="7">
         <v>45462</v>
       </c>
@@ -70956,7 +70983,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:13">
       <c r="A674" s="7">
         <v>45469</v>
       </c>
@@ -70997,7 +71024,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:13">
       <c r="A675" s="7">
         <v>45476</v>
       </c>
@@ -71038,7 +71065,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:13">
       <c r="A676" s="7">
         <v>45483</v>
       </c>
@@ -71079,7 +71106,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:13">
       <c r="A677" s="7">
         <v>45490</v>
       </c>
@@ -71120,7 +71147,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:13">
       <c r="A678" s="7">
         <v>45497</v>
       </c>
@@ -71161,7 +71188,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:13">
       <c r="A679" s="7">
         <v>45504</v>
       </c>
@@ -71202,7 +71229,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:13">
       <c r="A680" s="7">
         <v>45511</v>
       </c>
@@ -71243,7 +71270,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:13">
       <c r="A681" s="7">
         <v>45518</v>
       </c>
@@ -71284,7 +71311,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:13">
       <c r="A682" s="7">
         <v>45525</v>
       </c>
@@ -71325,7 +71352,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:13">
       <c r="A683" s="7">
         <v>45532</v>
       </c>
@@ -71366,7 +71393,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:13">
       <c r="A684" s="7">
         <v>45539</v>
       </c>
@@ -71407,7 +71434,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:13">
       <c r="A685" s="7">
         <v>45546</v>
       </c>
@@ -71448,7 +71475,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:13">
       <c r="A686" s="7">
         <v>45553</v>
       </c>
@@ -71489,7 +71516,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:13">
       <c r="A687" s="7">
         <v>45560</v>
       </c>
@@ -71530,7 +71557,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:13">
       <c r="A688" s="7">
         <v>45567</v>
       </c>
@@ -71571,7 +71598,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:13">
       <c r="A689" s="7">
         <v>45574</v>
       </c>
@@ -71612,7 +71639,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:13">
       <c r="A690" s="7">
         <v>45581</v>
       </c>
@@ -71653,7 +71680,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:13">
       <c r="A691" s="7">
         <v>45588</v>
       </c>
@@ -71694,7 +71721,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:13">
       <c r="A692" s="7">
         <v>45595</v>
       </c>
@@ -71735,7 +71762,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:13">
       <c r="A693" s="7">
         <v>45602</v>
       </c>
@@ -71776,7 +71803,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:13">
       <c r="A694" s="7">
         <v>45609</v>
       </c>
@@ -71817,7 +71844,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:13">
       <c r="A695" s="7">
         <v>45616</v>
       </c>
@@ -71858,7 +71885,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:13">
       <c r="A696" s="7">
         <v>45623</v>
       </c>
@@ -71899,7 +71926,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:13">
       <c r="A697" s="7">
         <v>45630</v>
       </c>
@@ -71940,7 +71967,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:13">
       <c r="A698" s="7">
         <v>45637</v>
       </c>
@@ -71981,7 +72008,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:13">
       <c r="A699" s="7">
         <v>45644</v>
       </c>
@@ -72022,7 +72049,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:13">
       <c r="A700" s="7">
         <v>45658</v>
       </c>
@@ -72063,7 +72090,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:13">
       <c r="A701" s="7">
         <v>45665</v>
       </c>
@@ -72104,7 +72131,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:13">
       <c r="A702" s="7">
         <v>45672</v>
       </c>
@@ -72145,7 +72172,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:13">
       <c r="A703" s="7">
         <v>45679</v>
       </c>
@@ -72186,7 +72213,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:13">
       <c r="A704" s="7">
         <v>45686</v>
       </c>
@@ -72227,7 +72254,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:13">
       <c r="A705" s="7">
         <v>45693</v>
       </c>
@@ -72268,7 +72295,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:13">
       <c r="A706" s="7">
         <v>45700</v>
       </c>
@@ -72309,7 +72336,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:13">
       <c r="A707" s="7">
         <v>45707</v>
       </c>
@@ -72350,7 +72377,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:13">
       <c r="A708" s="7">
         <v>45714</v>
       </c>
@@ -72391,7 +72418,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:13">
       <c r="A709" s="7">
         <v>45721</v>
       </c>
@@ -72432,7 +72459,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:13">
       <c r="A710" s="7">
         <v>45728</v>
       </c>
@@ -72473,7 +72500,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:13">
       <c r="A711" s="7">
         <v>45735</v>
       </c>
@@ -72514,7 +72541,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:13">
       <c r="A712" s="7">
         <v>45742</v>
       </c>
@@ -72555,7 +72582,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:13">
       <c r="A713" s="7">
         <v>45749</v>
       </c>
@@ -72596,7 +72623,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:13">
       <c r="A714" s="7">
         <v>45756</v>
       </c>
@@ -72637,7 +72664,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:13">
       <c r="A715" s="7">
         <v>45763</v>
       </c>
@@ -72678,7 +72705,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:13">
       <c r="A716" s="7">
         <v>45770</v>
       </c>
@@ -72719,7 +72746,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:13">
       <c r="A717" s="7">
         <v>45777</v>
       </c>
@@ -72760,7 +72787,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:13">
       <c r="A718" s="7">
         <v>45784</v>
       </c>
@@ -72801,7 +72828,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:13">
       <c r="A719" s="7">
         <v>45791</v>
       </c>
@@ -72842,7 +72869,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:13">
       <c r="A720" s="7">
         <v>45798</v>
       </c>
@@ -72883,7 +72910,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:13">
       <c r="A721" s="7">
         <v>45805</v>
       </c>
@@ -72924,7 +72951,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:13">
       <c r="A722" s="7">
         <v>45812</v>
       </c>
@@ -72965,7 +72992,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:13">
       <c r="A723" s="7">
         <v>45819</v>
       </c>
@@ -73006,7 +73033,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:13">
       <c r="A724" s="7">
         <v>45826</v>
       </c>
@@ -73047,7 +73074,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:13">
       <c r="A725" s="7">
         <v>45833</v>
       </c>
@@ -73088,7 +73115,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:13">
       <c r="A726" s="7">
         <v>45840</v>
       </c>
@@ -73129,7 +73156,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:13">
       <c r="A727" s="7">
         <v>45847</v>
       </c>
@@ -73170,7 +73197,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:13">
       <c r="A728" s="7">
         <v>45854</v>
       </c>
@@ -73211,7 +73238,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:13">
       <c r="A729" s="7">
         <v>45861</v>
       </c>
@@ -73252,7 +73279,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:13">
       <c r="A730" s="7">
         <v>45868</v>
       </c>
@@ -73293,7 +73320,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:13">
       <c r="A731" s="7">
         <v>45875</v>
       </c>
@@ -73334,7 +73361,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:13">
       <c r="A732" s="7">
         <v>45882</v>
       </c>
@@ -73375,7 +73402,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:13">
       <c r="A733" s="7">
         <v>45889</v>
       </c>
@@ -73416,7 +73443,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:13">
       <c r="A734" s="7">
         <v>45896</v>
       </c>
@@ -73457,7 +73484,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:13">
       <c r="A735" s="7">
         <v>45903</v>
       </c>
@@ -73498,7 +73525,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:13">
       <c r="A736" s="7">
         <v>45910</v>
       </c>
@@ -73539,7 +73566,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:13">
       <c r="A737" s="7">
         <v>45917</v>
       </c>
@@ -73580,7 +73607,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:13">
       <c r="A738" s="7">
         <v>45924</v>
       </c>
@@ -73621,7 +73648,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:13">
       <c r="A739" s="7">
         <v>45931</v>
       </c>
@@ -73662,7 +73689,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:13">
       <c r="A740" s="7">
         <v>45938</v>
       </c>
@@ -73703,7 +73730,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:13">
       <c r="A741" s="7">
         <v>45945</v>
       </c>
@@ -73744,7 +73771,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:13">
       <c r="A742" s="7">
         <v>45952</v>
       </c>
@@ -73785,7 +73812,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:13">
       <c r="A743" s="7">
         <v>45959</v>
       </c>
@@ -73826,7 +73853,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:13">
       <c r="A744" s="7">
         <v>45966</v>
       </c>
@@ -73867,7 +73894,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:13">
       <c r="A745" s="7">
         <v>45973</v>
       </c>
@@ -73908,7 +73935,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:13">
       <c r="A746" s="7">
         <v>45980</v>
       </c>
@@ -73949,7 +73976,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:13">
       <c r="A747" s="7">
         <v>45987</v>
       </c>
@@ -73990,7 +74017,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:13">
       <c r="A748" s="7">
         <v>45994</v>
       </c>
@@ -74031,7 +74058,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:13">
       <c r="A749" s="7">
         <v>46001</v>
       </c>
@@ -74072,7 +74099,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:13">
       <c r="A750" s="7">
         <v>46008</v>
       </c>
@@ -74113,7 +74140,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:13">
       <c r="A751" s="7">
         <v>46015</v>
       </c>
@@ -74154,7 +74181,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:13">
       <c r="A752" s="7">
         <v>46022</v>
       </c>
@@ -74195,7 +74222,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:13">
       <c r="A753" s="7">
         <v>46029</v>
       </c>
@@ -74236,7 +74263,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:13">
       <c r="A754" s="7">
         <v>46036</v>
       </c>
@@ -74277,7 +74304,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:13">
       <c r="A755" s="7">
         <v>46043</v>
       </c>
@@ -74318,7 +74345,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:13">
       <c r="A756" s="7">
         <v>46050</v>
       </c>
@@ -74359,7 +74386,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:13">
       <c r="A757" s="7">
         <v>46057</v>
       </c>
@@ -74400,7 +74427,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:13">
       <c r="A758" s="7">
         <v>46064</v>
       </c>
@@ -74441,7 +74468,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:13">
       <c r="A759" s="7">
         <v>46071</v>
       </c>
@@ -74482,7 +74509,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:13">
       <c r="A760" s="7">
         <v>46078</v>
       </c>
@@ -74523,7 +74550,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:13">
       <c r="A761" s="7">
         <v>46085</v>
       </c>
@@ -74564,7 +74591,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:13">
       <c r="A762" s="7">
         <v>46092</v>
       </c>
@@ -74605,7 +74632,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:13">
       <c r="A763" s="7">
         <v>46099</v>
       </c>
@@ -74646,7 +74673,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:13">
       <c r="A764" s="7">
         <v>46106</v>
       </c>
@@ -74687,7 +74714,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:13">
       <c r="A765" s="7">
         <v>46113</v>
       </c>
@@ -74728,7 +74755,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:13">
       <c r="A766" s="7">
         <v>46120</v>
       </c>
@@ -74769,7 +74796,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:13">
       <c r="A767" s="7">
         <v>46127</v>
       </c>
@@ -74810,7 +74837,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:13">
       <c r="A768" s="7">
         <v>46134</v>
       </c>
@@ -74851,7 +74878,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:13">
       <c r="A769" s="7">
         <v>46141</v>
       </c>
@@ -74892,7 +74919,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:13">
       <c r="A770" s="7">
         <v>46148</v>
       </c>
@@ -74933,7 +74960,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:13">
       <c r="A771" s="7">
         <v>46155</v>
       </c>
@@ -74945,6 +74972,33 @@
       </c>
       <c r="D771" s="7" t="s">
         <v>15</v>
+      </c>
+      <c r="E771" s="8">
+        <v>2553.39</v>
+      </c>
+      <c r="F771" s="9">
+        <v>2413</v>
+      </c>
+      <c r="G771" s="9">
+        <v>3701</v>
+      </c>
+      <c r="H771" s="9">
+        <v>3357</v>
+      </c>
+      <c r="I771" s="9">
+        <v>4252</v>
+      </c>
+      <c r="J771" s="9">
+        <v>644</v>
+      </c>
+      <c r="K771" s="9">
+        <v>791</v>
+      </c>
+      <c r="L771" s="9">
+        <v>1030</v>
+      </c>
+      <c r="M771" s="9">
+        <v>2388</v>
       </c>
     </row>
   </sheetData>
@@ -74957,7 +75011,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -74968,12 +75022,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:14">
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
@@ -74992,7 +75046,7 @@
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:14">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE66BFFA-A24C-40E8-AB19-D66F537140F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CD327E-A2B2-4169-B871-6172276710C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="10872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -43381,10 +43381,10 @@
   <dimension ref="A1:M771"/>
   <sheetFormatPr defaultColWidth="7.5546875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.109375" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="10.44140625" style="9" customWidth="1"/>
     <col min="14" max="16384" width="7.5546875" style="9"/>

--- a/data/freight/world container index.xlsx
+++ b/data/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CD327E-A2B2-4169-B871-6172276710C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DE0117-81E9-4D69-B662-9583E3E4A91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="10872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -222,9 +222,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -242,7 +242,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2601,6 +2601,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4919,6 +4922,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>2553.39</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>2711.77</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7273,6 +7279,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9591,6 +9600,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>2413</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>2773</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11945,6 +11957,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14263,6 +14278,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>3701</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>4082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16617,6 +16635,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18935,6 +18956,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>3357</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>3385</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21289,6 +21313,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23607,6 +23634,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>4252</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>4317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -25961,6 +25991,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28279,6 +28312,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>644</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>650</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30635,6 +30671,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -32953,6 +32992,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>791</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35309,6 +35351,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37627,6 +37672,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>1030</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>1002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -39983,6 +40031,9 @@
                 <c:pt idx="769">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="770">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42301,6 +42352,9 @@
                 </c:pt>
                 <c:pt idx="769">
                   <c:v>2388</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>2453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43378,16 +43432,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M771"/>
-  <sheetFormatPr defaultColWidth="7.5546875" defaultRowHeight="12.6"/>
+  <dimension ref="A1:M772"/>
+  <sheetFormatPr defaultColWidth="7.54296875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.44140625" style="9" customWidth="1"/>
-    <col min="14" max="16384" width="7.5546875" style="9"/>
+    <col min="3" max="3" width="12.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.453125" style="9" customWidth="1"/>
+    <col min="14" max="16384" width="7.54296875" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="6" customFormat="1">
@@ -74999,6 +75053,47 @@
       </c>
       <c r="M771" s="9">
         <v>2388</v>
+      </c>
+    </row>
+    <row r="772" spans="1:13">
+      <c r="A772" s="7">
+        <v>46162</v>
+      </c>
+      <c r="B772" s="7">
+        <v>46163</v>
+      </c>
+      <c r="C772" s="11">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D772" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E772" s="8">
+        <v>2711.77</v>
+      </c>
+      <c r="F772" s="9">
+        <v>2773</v>
+      </c>
+      <c r="G772" s="9">
+        <v>4082</v>
+      </c>
+      <c r="H772" s="9">
+        <v>3385</v>
+      </c>
+      <c r="I772" s="9">
+        <v>4317</v>
+      </c>
+      <c r="J772" s="9">
+        <v>650</v>
+      </c>
+      <c r="K772" s="9">
+        <v>809</v>
+      </c>
+      <c r="L772" s="9">
+        <v>1002</v>
+      </c>
+      <c r="M772" s="9">
+        <v>2453</v>
       </c>
     </row>
   </sheetData>
@@ -75011,7 +75106,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75022,9 +75117,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14">
